--- a/test_results/test_lagrangian_always_done_5b_8envs.xlsx
+++ b/test_results/test_lagrangian_always_done_5b_8envs.xlsx
@@ -505,29 +505,29 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>(Vec (+ (+ in_1_1 in_1_0) (+ in_0_1 in_0_0)) (+ (+ (+ in_1_2 in_1_1) (+ in_1_0 in_0_2)) (+ in_0_1 in_0_0)) (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ in_1_2 in_1_1) (+ in_0_2 in_0_1)) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) (+ (+ (+ in_2_1 in_2_0) (+ in_1_1 in_1_0)) (+ in_0_1 in_0_0)) (+ (+ (+ in_2_2 (+ in_2_1 in_2_0)) (+ in_1_2 in_1_1)) (+ (+ in_1_0 in_0_2) (+ in_0_1 in_0_0))) (+ (+ (+ in_2_2 in_2_1) (+ in_1_2 in_1_1)) (+ in_0_2 in_0_1)) (+ (+ in_2_1 in_2_0) (+ in_1_1 in_1_0)) (+ (+ (+ in_2_2 in_2_1) (+ in_2_0 in_1_2)) (+ in_1_1 in_1_0)) (+ (+ in_2_2 in_2_1) (+ in_1_2 in_1_1)))</t>
+          <t>(Vec (+ (+ in_1_1 in_1_0) (+ in_0_1 in_0_0)) (+ (+ (+ in_1_2 in_1_1) (+ in_1_0 in_0_2)) (+ in_0_1 in_0_0)) (+ (+ in_1_2 in_1_1) (- (- (+ in_0_2 in_0_1) 0) 0)) (+ (+ (+ in_2_1 in_2_0) (+ in_1_1 in_1_0)) (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (* 1 (+ in_0_1 in_0_0)))))))))))))))))))))))))))))))))))))))))))))))))))))))))))))))))))))))))) (+ (+ (+ in_2_2 (+ in_2_1 in_2_0)) (+ in_1_2 in_1_1)) (+ (+ in_1_0 in_0_2) (+ in_0_1 in_0_0))) (+ (+ (+ in_2_2 in_2_1) (+ in_1_2 in_1_1)) (+ in_0_2 in_0_1)) (+ (+ in_2_1 in_2_0) (+ in_1_1 in_1_0)) (+ (+ (+ in_2_2 in_2_1) (+ in_2_0 in_1_2)) (+ in_1_1 in_1_0)) (+ (+ in_2_2 in_2_1) (+ in_1_2 in_1_1)))</t>
         </is>
       </c>
       <c r="E2" t="n">
         <v>10006</v>
       </c>
       <c r="F2" t="n">
-        <v>28578</v>
+        <v>28577</v>
       </c>
       <c r="G2" t="n">
-        <v>-185.61</v>
+        <v>-185.6</v>
       </c>
       <c r="H2" t="n">
         <v>7.19</v>
       </c>
       <c r="I2" t="n">
-        <v>93.44</v>
+        <v>124.43</v>
       </c>
       <c r="J2" t="b">
         <v>0</v>
       </c>
       <c r="K2" t="n">
-        <v>206.56</v>
+        <v>175.57</v>
       </c>
       <c r="L2" t="n">
         <v>75</v>
@@ -547,29 +547,29 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>(Vec (+ (+ in_1_1 in_1_0) (+ in_0_1 in_0_0)) (+ (+ (+ in_1_2 in_1_1) (+ in_1_0 in_0_2)) (+ in_0_1 in_0_0)) (+ (+ (+ in_1_3 in_1_2) (+ in_1_1 in_0_3)) (+ in_0_2 in_0_1)) (+ (+ (+ in_1_4 in_1_3) (+ in_1_2 in_0_4)) (+ in_0_3 in_0_2)) (+ (+ in_1_4 in_1_3) (+ in_0_4 in_0_3)) (+ (+ (+ in_2_1 in_2_0) (+ in_1_1 in_1_0)) (+ in_0_1 in_0_0)) (+ (+ (+ in_2_2 (+ in_2_1 in_2_0)) (+ in_1_2 in_1_1)) (+ (+ in_1_0 in_0_2) (+ in_0_1 in_0_0))) (+ (+ (+ in_2_3 (+ in_2_2 in_2_1)) (+ in_1_3 in_1_2)) (+ (+ in_1_1 in_0_3) (+ in_0_2 in_0_1))) (+ (+ (+ in_2_4 (+ in_2_3 in_2_2)) (+ in_1_4 in_1_3)) (+ (+ in_1_2 in_0_4) (+ in_0_3 in_0_2))) (+ (+ (+ in_2_4 in_2_3) (+ in_1_4 in_1_3)) (+ in_0_4 in_0_3)) (+ (+ (+ in_3_1 in_3_0) (+ in_2_1 in_2_0)) (+ in_1_1 in_1_0)) (+ (+ (+ in_3_2 (+ in_3_1 in_3_0)) (+ in_2_2 in_2_1)) (+ (+ in_2_0 in_1_2) (+ in_1_1 in_1_0))) (+ (+ (+ in_3_3 (+ in_3_2 in_3_1)) (+ in_2_3 in_2_2)) (+ (+ in_2_1 in_1_3) (+ in_1_2 in_1_1))) (+ (+ (+ in_3_4 (+ in_3_3 in_3_2)) (+ in_2_4 in_2_3)) (+ (+ in_2_2 in_1_4) (+ in_1_3 in_1_2))) (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (+ (+ (+ in_3_4 in_3_3) (+ in_2_4 in_2_3)) (+ in_1_4 in_1_3)) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) (+ (+ (+ in_4_1 in_4_0) (+ in_3_1 in_3_0)) (+ in_2_1 in_2_0)) (+ (+ (+ in_4_2 (+ in_4_1 in_4_0)) (+ in_3_2 in_3_1)) (+ (+ in_3_0 in_2_2) (+ in_2_1 in_2_0))) (+ (+ (+ in_4_3 (+ in_4_2 in_4_1)) (+ in_3_3 in_3_2)) (+ (+ in_3_1 in_2_3) (+ in_2_2 in_2_1))) (+ (+ (+ in_4_4 (+ in_4_3 in_4_2)) (+ in_3_4 in_3_3)) (+ (+ in_3_2 in_2_4) (+ in_2_3 in_2_2))) (+ (+ (+ in_4_4 in_4_3) (+ in_3_4 in_3_3)) (+ in_2_4 in_2_3)) (+ (+ in_4_1 in_4_0) (+ in_3_1 in_3_0)) (+ (+ (+ in_4_2 in_4_1) (+ in_4_0 in_3_2)) (+ in_3_1 in_3_0)) (+ (+ (+ in_4_3 in_4_2) (+ in_4_1 in_3_3)) (+ in_3_2 in_3_1)) (+ (+ (+ in_4_4 in_4_3) (+ in_4_2 in_3_4)) (+ in_3_3 in_3_2)) (+ (+ in_4_4 in_4_3) (+ in_3_4 in_3_3)))</t>
+          <t>(Vec (+ (+ in_1_1 in_1_0) (+ in_0_1 in_0_0)) (+ (+ (+ in_1_2 in_1_1) (+ in_1_0 in_0_2)) (+ in_0_1 in_0_0)) (+ (+ (+ in_1_3 in_1_2) (+ in_1_1 in_0_3)) (+ in_0_2 in_0_1)) (+ (+ (+ in_1_4 in_1_3) (+ in_1_2 in_0_4)) (+ in_0_3 in_0_2)) (+ (+ in_1_4 in_1_3) (+ in_0_4 in_0_3)) (+ (+ (+ in_2_1 in_2_0) (+ in_1_1 in_1_0)) (+ in_0_1 in_0_0)) (+ (+ (+ in_2_2 (+ in_2_1 in_2_0)) (+ in_1_2 in_1_1)) (+ (+ in_1_0 in_0_2) (+ in_0_1 in_0_0))) (+ (+ (+ in_2_3 (+ in_2_2 in_2_1)) (+ in_1_3 in_1_2)) (+ (+ in_1_1 in_0_3) (+ in_0_2 in_0_1))) (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (+ (+ (+ in_2_4 (+ in_2_3 in_2_2)) (+ in_1_4 in_1_3)) (+ (+ in_1_2 in_0_4) (+ in_0_3 in_0_2))) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) (+ (+ (+ in_2_4 in_2_3) (+ in_1_4 in_1_3)) (+ in_0_4 in_0_3)) (+ (+ (+ in_3_1 in_3_0) (+ in_2_1 in_2_0)) (+ in_1_1 in_1_0)) (+ (+ (+ in_3_2 (+ in_3_1 in_3_0)) (+ in_2_2 in_2_1)) (+ (+ in_2_0 in_1_2) (+ in_1_1 in_1_0))) (+ (+ (+ in_3_3 (+ in_3_2 in_3_1)) (+ in_2_3 in_2_2)) (+ (+ in_2_1 in_1_3) (+ in_1_2 in_1_1))) (+ (+ (+ in_3_4 (+ in_3_3 in_3_2)) (+ in_2_4 in_2_3)) (+ (+ in_2_2 in_1_4) (+ in_1_3 in_1_2))) (+ (+ (+ in_3_4 in_3_3) (+ in_2_4 in_2_3)) (+ in_1_4 in_1_3)) (+ (+ (+ in_4_1 in_4_0) (+ in_3_1 in_3_0)) (+ in_2_1 in_2_0)) (+ (+ (+ in_4_2 (+ in_4_1 in_4_0)) (+ in_3_2 in_3_1)) (+ (+ in_3_0 in_2_2) (+ in_2_1 in_2_0))) (+ (+ (+ in_4_3 (+ in_4_2 in_4_1)) (+ in_3_3 in_3_2)) (+ (+ in_3_1 in_2_3) (+ in_2_2 in_2_1))) (+ (+ (+ in_4_4 (+ in_4_3 in_4_2)) (+ in_3_4 in_3_3)) (+ (+ in_3_2 in_2_4) (+ in_2_3 in_2_2))) (+ (+ (+ in_4_4 in_4_3) (+ in_3_4 in_3_3)) (+ in_2_4 in_2_3)) (+ (+ in_4_1 in_4_0) (+ in_3_1 in_3_0)) (+ (+ (+ in_4_2 in_4_1) (+ in_4_0 in_3_2)) (+ in_3_1 in_3_0)) (+ (+ (+ in_4_3 in_4_2) (+ in_4_1 in_3_3)) (+ in_3_2 in_3_1)) (+ (+ (+ in_4_4 in_4_3) (+ in_4_2 in_3_4)) (+ in_3_3 in_3_2)) (+ (+ in_4_4 in_4_3) (+ in_3_4 in_3_3)))</t>
         </is>
       </c>
       <c r="E3" t="n">
         <v>36006</v>
       </c>
       <c r="F3" t="n">
-        <v>54653</v>
+        <v>54580</v>
       </c>
       <c r="G3" t="n">
-        <v>-51.79</v>
+        <v>-51.59</v>
       </c>
       <c r="H3" t="n">
         <v>7.19</v>
       </c>
       <c r="I3" t="n">
-        <v>2564.98</v>
+        <v>95.84</v>
       </c>
       <c r="J3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K3" t="n">
-        <v>-2264.98</v>
+        <v>204.16</v>
       </c>
       <c r="L3" t="n">
         <v>75</v>
@@ -589,17 +589,17 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>(VecAdd (Vec v2_0 v2_1 v2_2 v2_3 v2_4 v2_5 v2_6 v2_7) (VecAdd (Vec 2 2 2 2 2 2 2 2) (Vec (* v1_0 5) (* v1_1 5) (* v1_2 5) (* v1_3 5) (* v1_4 5) (* v1_5 5) (* v1_6 5) (* v1_7 5))))</t>
+          <t>(Vec ( + v2_0 ( + 2 ( * v1_0 5 ) ) ) ( + v2_1 ( + 2 ( * v1_1 5 ) ) ) ( + v2_2 ( + 2 ( * v1_2 5 ) ) ) ( + v2_3 ( + 2 ( * v1_3 5 ) ) ) ( + v2_4 ( + 2 ( * v1_4 5 ) ) ) ( + v2_5 ( + 2 ( * v1_5 5 ) ) ) ( + v2_6 ( + 2 ( * v1_6 5 ) ) ) ( + v2_7 ( + 2 ( * v1_7 5 ) ) ) )</t>
         </is>
       </c>
       <c r="E4" t="n">
         <v>6006</v>
       </c>
       <c r="F4" t="n">
-        <v>2008</v>
+        <v>6006</v>
       </c>
       <c r="G4" t="n">
-        <v>66.56999999999999</v>
+        <v>0</v>
       </c>
       <c r="H4" t="n">
         <v>39.37</v>
@@ -614,7 +614,7 @@
         <v>260.63</v>
       </c>
       <c r="L4" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5">
@@ -631,29 +631,29 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>(Vec (+ v2_0 (+ 2 (* v1_0 5))) (+ v2_1 (+ 2 (* v1_1 5))) (+ v2_2 (+ 2 (* v1_2 5))) (+ v2_3 (+ 2 (* v1_3 5))) (+ v2_4 (+ 2 (* v1_4 5))) (+ v2_5 (+ 2 (* v1_5 5))) (+ v2_6 (+ 2 (* v1_6 5))) (+ v2_7 (+ 2 (* v1_7 5))) (+ v2_8 (+ 2 (* v1_8 5))) (+ v2_9 (+ 2 (* v1_9 5))) (+ v2_10 (+ 2 (* v1_10 5))) (+ v2_11 (+ 2 (* v1_11 5))) (+ v2_12 (+ 2 (* v1_12 5))) (+ v2_13 (+ 2 (* v1_13 5))) (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (+ v2_14 (+ 2 (* v1_14 5))) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) (+ v2_15 (+ 2 (* v1_15 5))) (+ v2_16 (+ 2 (* v1_16 5))) (+ v2_17 (+ 2 (* v1_17 5))) (+ v2_18 (+ 2 (* v1_18 5))) (+ v2_19 (+ 2 (* v1_19 5))) (+ v2_20 (+ 2 (* v1_20 5))) (+ v2_21 (+ 2 (* v1_21 5))) (+ v2_22 (+ 2 (* v1_22 5))) (+ v2_23 (+ 2 (* v1_23 5))) (+ v2_24 (+ 2 (* v1_24 5))) (+ v2_25 (+ 2 (* v1_25 5))) (+ v2_26 (+ 2 (* v1_26 5))) (+ v2_27 (+ 2 (* v1_27 5))) (+ v2_28 (+ 2 (* v1_28 5))) (+ v2_29 (+ 2 (* v1_29 5))) (+ v2_30 (+ 2 (* v1_30 5))) (+ v2_31 (+ 2 (* v1_31 5))))</t>
+          <t>(Vec (+ v2_0 (+ 2 (* v1_0 5))) (+ v2_1 (+ 2 (* v1_1 5))) (+ v2_2 (+ 2 (* v1_2 5))) (+ v2_3 (+ 2 (* v1_3 5))) (+ v2_4 (+ 2 (* v1_4 5))) (+ v2_5 (+ 2 (+ 0 (+ 0 (+ 0 (* v1_5 5)))))) (+ v2_6 (+ 2 (+ 0 (+ 0 (+ 0 (* v1_6 5)))))) (+ v2_7 (+ 2 (+ 0 (+ 0 (+ 0 (* v1_7 5)))))) (+ v2_8 (+ 2 (+ 0 (+ 0 (+ 0 (* v1_8 5)))))) (+ v2_9 (+ 2 (+ 0 (+ 0 (+ 0 (* v1_9 5)))))) (+ v2_10 (+ 2 (+ 0 (+ 0 (+ 0 (* v1_10 5)))))) (+ v2_11 (+ 2 (+ 0 (+ 0 (+ 0 (* v1_11 5)))))) (+ v2_12 (+ 2 (+ 0 (+ 0 (+ 0 (* v1_12 5)))))) (+ v2_13 (+ 2 (+ 0 (+ 0 (+ 0 (* v1_13 5)))))) (+ v2_14 (+ 2 (+ 0 (+ 0 (+ 0 (* v1_14 5)))))) (+ v2_15 (+ 2 (+ 0 (+ 0 (+ 0 (* v1_15 5)))))) (+ v2_16 (+ 2 (+ 0 (+ 0 (+ 0 (* v1_16 5)))))) (+ v2_17 (+ 2 (+ 0 (+ 0 (+ 0 (* v1_17 5)))))) (+ v2_18 (+ 2 (+ 0 (+ 0 (+ 0 (* v1_18 5)))))) (+ v2_19 (+ 2 (+ 0 (+ 0 (+ 0 (* v1_19 5)))))) (+ v2_20 (+ 2 (+ 0 (+ 0 (+ 0 (* v1_20 5)))))) (+ v2_21 (+ 2 (+ 0 (+ 0 (+ 0 (* v1_21 5)))))) (+ v2_22 (+ 2 (+ 0 (+ 0 (+ 0 (* v1_22 5)))))) (+ v2_23 (+ 2 (+ 0 (+ 0 (+ 0 (* v1_23 5)))))) (+ v2_24 (+ 2 (+ 0 (+ 0 (+ 0 (* v1_24 5)))))) (+ v2_25 (+ 2 (+ 0 (+ 0 (* v1_25 5))))) (+ v2_26 (+ 2 (+ 0 (+ 0 (* v1_26 5))))) (+ v2_27 (+ 2 (+ 0 (+ 0 (* v1_27 5))))) (+ v2_28 (+ 2 (+ 0 (+ 0 (* v1_28 5))))) (+ v2_29 (+ 2 (+ 0 (+ 0 (* v1_29 5))))) (+ v2_30 (+ 2 (+ 0 (+ 0 (* v1_30 5))))) (+ v2_31 (+ 2 (+ 0 (+ 0 (* v1_31 5))))))</t>
         </is>
       </c>
       <c r="E5" t="n">
         <v>24006</v>
       </c>
       <c r="F5" t="n">
-        <v>42654</v>
+        <v>42509</v>
       </c>
       <c r="G5" t="n">
-        <v>-77.68000000000001</v>
+        <v>-77.08</v>
       </c>
       <c r="H5" t="n">
         <v>39.37</v>
       </c>
       <c r="I5" t="n">
-        <v>2598.36</v>
+        <v>42.97</v>
       </c>
       <c r="J5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>-2298.36</v>
+        <v>257.03</v>
       </c>
       <c r="L5" t="n">
         <v>75</v>
@@ -673,29 +673,29 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>(Vec (+ (+ (- (+ v1_0 v2_0) (* (* v1_0 v2_0) 2)) (- (+ v1_1 v2_1) (* 2 (* v1_1 v2_1)))) (+ (- (+ v1_2 v2_2) (* 2 (* v1_2 v2_2))) (- (+ v1_3 v2_3) (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* 2 (* v1_3 v2_3)) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1)))))</t>
+          <t>(Vec (+ (+ (- (+ v1_0 v2_0) (* (* v1_0 v2_0) 2)) (- (+ v1_1 v2_1) (* 2 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (* v1_1 v2_1))))))))))))))))))))))))))))) (+ (- (+ v1_2 v2_2) (* 2 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (* v1_2 v2_2)))))))))))))))))))))))))))) (- (+ v1_3 v2_3) (* 2 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (* v1_3 v2_3))))))))))))))))))))))))))))))</t>
         </is>
       </c>
       <c r="E6" t="n">
         <v>4759</v>
       </c>
       <c r="F6" t="n">
-        <v>23407</v>
+        <v>23284</v>
       </c>
       <c r="G6" t="n">
-        <v>-391.85</v>
+        <v>-389.26</v>
       </c>
       <c r="H6" t="n">
         <v>75.15000000000001</v>
       </c>
       <c r="I6" t="n">
-        <v>2634.14</v>
+        <v>105.1</v>
       </c>
       <c r="J6" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>-2334.14</v>
+        <v>194.9</v>
       </c>
       <c r="L6" t="n">
         <v>75</v>
@@ -715,32 +715,32 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>(Vec (+ (+ (+ (- (+ v1_0 v2_0) (* (* v1_0 v2_0) 2)) (- (+ v1_1 v2_1) (* 2 (* v1_1 v2_1)))) (+ (- (+ v1_2 v2_2) (* 2 (* v1_2 v2_2))) (- (+ v1_3 v2_3) (* 2 (* v1_3 v2_3))))) (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (- (+ v1_4 v2_4) (* 2 (* v1_4 v2_4))) (- (+ v1_5 v2_5) (* 2 (* v1_5 v2_5)))) (+ (- (+ v1_6 v2_6) (* 2 (* v1_6 v2_6))) (- (+ v1_7 v2_7) (* 2 (* v1_7 v2_7))))) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0)))</t>
+          <t>(Vec ( + ( + ( + ( - ( + v1_0 v2_0 ) ( * ( * v1_0 v2_0 ) 2 ) ) ( - ( + v1_1 v2_1 ) ( * 2 ( * v1_1 v2_1 ) ) ) ) ( + ( - ( + v1_2 v2_2 ) ( * 2 ( * v1_2 v2_2 ) ) ) ( - ( + v1_3 v2_3 ) ( * 2 ( * v1_3 v2_3 ) ) ) ) ) ( + ( + ( - ( + v1_4 v2_4 ) ( * 2 ( * v1_4 v2_4 ) ) ) ( - ( + v1_5 v2_5 ) ( * 2 ( * v1_5 v2_5 ) ) ) ) ( + ( - ( + v1_6 v2_6 ) ( * 2 ( * v1_6 v2_6 ) ) ) ( - ( + v1_7 v2_7 ) ( * 2 ( * v1_7 v2_7 ) ) ) ) ) ) )</t>
         </is>
       </c>
       <c r="E7" t="n">
         <v>9760</v>
       </c>
       <c r="F7" t="n">
-        <v>28334</v>
+        <v>9760</v>
       </c>
       <c r="G7" t="n">
-        <v>-190.31</v>
+        <v>0</v>
       </c>
       <c r="H7" t="n">
         <v>76.34999999999999</v>
       </c>
       <c r="I7" t="n">
-        <v>165</v>
+        <v>76.34999999999999</v>
       </c>
       <c r="J7" t="b">
         <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>135</v>
+        <v>223.65</v>
       </c>
       <c r="L7" t="n">
-        <v>75</v>
+        <v>1</v>
       </c>
     </row>
     <row r="8">
@@ -799,32 +799,32 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>(Vec (+ c1_0 (+ c2_0 (* c0_0 (+ c3_0 (* c0_0 c4_0))))) (+ c1_1 (+ c2_1 (* c0_1 (+ c3_1 (* c0_1 c4_1))))) (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ c1_2 (+ c2_2 (* c0_2 (+ c3_2 (* c0_2 c4_2))))) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) (+ c1_3 (+ c2_3 (* c0_3 (+ c3_3 (* c0_3 c4_3))))) (+ c1_4 (+ c2_4 (* c0_4 (+ c3_4 (* c0_4 c4_4))))) (+ c1_5 (+ c2_5 (* c0_5 (+ c3_5 (* c0_5 c4_5))))) (+ c1_6 (+ c2_6 (* c0_6 (+ c3_6 (* c0_6 c4_6))))) (+ c1_7 (+ c2_7 (* c0_7 (+ c3_7 (* c0_7 c4_7))))))</t>
+          <t>(Vec ( + c1_0 ( + c2_0 ( * c0_0 ( + c3_0 ( * c0_0 c4_0 ) ) ) ) ) ( + c1_1 ( + c2_1 ( * c0_1 ( + c3_1 ( * c0_1 c4_1 ) ) ) ) ) ( + c1_2 ( + c2_2 ( * c0_2 ( + c3_2 ( * c0_2 c4_2 ) ) ) ) ) ( + c1_3 ( + c2_3 ( * c0_3 ( + c3_3 ( * c0_3 c4_3 ) ) ) ) ) ( + c1_4 ( + c2_4 ( * c0_4 ( + c3_4 ( * c0_4 c4_4 ) ) ) ) ) ( + c1_5 ( + c2_5 ( * c0_5 ( + c3_5 ( * c0_5 c4_5 ) ) ) ) ) ( + c1_6 ( + c2_6 ( * c0_6 ( + c3_6 ( * c0_6 c4_6 ) ) ) ) ) ( + c1_7 ( + c2_7 ( * c0_7 ( + c3_7 ( * c0_7 c4_7 ) ) ) ) ) )</t>
         </is>
       </c>
       <c r="E9" t="n">
         <v>10009</v>
       </c>
       <c r="F9" t="n">
-        <v>28583</v>
+        <v>10009</v>
       </c>
       <c r="G9" t="n">
-        <v>-185.57</v>
+        <v>0</v>
       </c>
       <c r="H9" t="n">
         <v>75.15000000000001</v>
       </c>
       <c r="I9" t="n">
-        <v>163.8</v>
+        <v>75.15000000000001</v>
       </c>
       <c r="J9" t="b">
         <v>0</v>
       </c>
       <c r="K9" t="n">
-        <v>136.2</v>
+        <v>224.85</v>
       </c>
       <c r="L9" t="n">
-        <v>75</v>
+        <v>1</v>
       </c>
     </row>
     <row r="10">
@@ -841,29 +841,29 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>(Vec (+ c1_0 (+ c2_0 (* c0_0 (+ c3_0 (* c0_0 c4_0))))) (+ c1_1 (+ c2_1 (* c0_1 (+ c3_1 (* c0_1 c4_1))))) (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ c1_2 (+ c2_2 (* c0_2 (+ c3_2 (* c0_2 c4_2))))) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) (+ c1_3 (+ c2_3 (* c0_3 (+ c3_3 (* c0_3 c4_3))))) (+ c1_4 (+ c2_4 (* c0_4 (+ c3_4 (* c0_4 c4_4))))) (+ c1_5 (+ c2_5 (* c0_5 (+ c3_5 (* c0_5 c4_5))))) (+ c1_6 (+ c2_6 (* c0_6 (+ c3_6 (* c0_6 c4_6))))) (+ c1_7 (+ c2_7 (* c0_7 (+ c3_7 (* c0_7 c4_7))))) (+ c1_8 (+ c2_8 (* c0_8 (+ c3_8 (* c0_8 c4_8))))) (+ c1_9 (+ c2_9 (* c0_9 (+ c3_9 (* c0_9 c4_9))))) (+ c1_10 (+ c2_10 (* c0_10 (+ c3_10 (* c0_10 c4_10))))) (+ c1_11 (+ c2_11 (* c0_11 (+ c3_11 (* c0_11 c4_11))))) (+ c1_12 (+ c2_12 (* c0_12 (+ c3_12 (* c0_12 c4_12))))) (+ c1_13 (+ c2_13 (* c0_13 (+ c3_13 (* c0_13 c4_13))))) (+ c1_14 (+ c2_14 (* c0_14 (+ c3_14 (* c0_14 c4_14))))) (+ c1_15 (+ c2_15 (* c0_15 (+ c3_15 (* c0_15 c4_15))))) (+ c1_16 (+ c2_16 (* c0_16 (+ c3_16 (* c0_16 c4_16))))) (+ c1_17 (+ c2_17 (* c0_17 (+ c3_17 (* c0_17 c4_17))))) (+ c1_18 (+ c2_18 (* c0_18 (+ c3_18 (* c0_18 c4_18))))) (+ c1_19 (+ c2_19 (* c0_19 (+ c3_19 (* c0_19 c4_19))))) (+ c1_20 (+ c2_20 (* c0_20 (+ c3_20 (* c0_20 c4_20))))) (+ c1_21 (+ c2_21 (* c0_21 (+ c3_21 (* c0_21 c4_21))))) (+ c1_22 (+ c2_22 (* c0_22 (+ c3_22 (* c0_22 c4_22))))) (+ c1_23 (+ c2_23 (* c0_23 (+ c3_23 (* c0_23 c4_23))))) (+ c1_24 (+ c2_24 (* c0_24 (+ c3_24 (* c0_24 c4_24))))) (+ c1_25 (+ c2_25 (* c0_25 (+ c3_25 (* c0_25 c4_25))))) (+ c1_26 (+ c2_26 (* c0_26 (+ c3_26 (* c0_26 c4_26))))) (+ c1_27 (+ c2_27 (* c0_27 (+ c3_27 (* c0_27 c4_27))))) (+ c1_28 (+ c2_28 (* c0_28 (+ c3_28 (* c0_28 c4_28))))) (+ c1_29 (+ c2_29 (* c0_29 (+ c3_29 (* c0_29 c4_29))))) (+ c1_30 (+ c2_30 (* c0_30 (+ c3_30 (* c0_30 c4_30))))) (+ c1_31 (+ c2_31 (* c0_31 (+ c3_31 (* c0_31 c4_31))))))</t>
+          <t>(Vec (+ c1_0 (+ c2_0 (* c0_0 (+ c3_0 (+ 0 (* c0_0 c4_0)))))) (+ c1_1 (+ c2_1 (* c0_1 (+ c3_1 (+ 0 (* c0_1 c4_1)))))) (+ c1_2 (+ c2_2 (* c0_2 (+ c3_2 (+ 0 (* c0_2 c4_2)))))) (+ c1_3 (+ c2_3 (* c0_3 (+ c3_3 (+ 0 (* c0_3 c4_3)))))) (+ c1_4 (+ c2_4 (* c0_4 (+ c3_4 (+ 0 (* c0_4 c4_4)))))) (+ c1_5 (+ c2_5 (* c0_5 (+ c3_5 (+ 0 (* c0_5 c4_5)))))) (+ c1_6 (+ c2_6 (* c0_6 (+ c3_6 (+ 0 (* c0_6 c4_6)))))) (+ c1_7 (+ c2_7 (* c0_7 (+ c3_7 (+ 0 (* c0_7 c4_7)))))) (+ c1_8 (+ c2_8 (* c0_8 (+ c3_8 (+ 0 (* c0_8 c4_8)))))) (+ c1_9 (+ c2_9 (* c0_9 (+ c3_9 (+ 0 (* c0_9 c4_9)))))) (+ c1_10 (+ c2_10 (* c0_10 (+ c3_10 (+ 0 (* c0_10 c4_10)))))) (+ c1_11 (+ c2_11 (+ 0 (+ 0 (+ 0 (* c0_11 (+ c3_11 (* c0_11 c4_11)))))))) (+ c1_12 (+ c2_12 (+ 0 (+ 0 (+ 0 (* c0_12 (+ c3_12 (* c0_12 c4_12)))))))) (+ c1_13 (+ c2_13 (+ 0 (+ 0 (+ 0 (* c0_13 (+ c3_13 (* c0_13 c4_13)))))))) (+ c1_14 (+ c2_14 (+ 0 (+ 0 (+ 0 (* c0_14 (+ c3_14 (* c0_14 c4_14)))))))) (+ c1_15 (+ c2_15 (+ 0 (+ 0 (+ 0 (* c0_15 (+ c3_15 (* c0_15 c4_15)))))))) (+ c1_16 (+ c2_16 (+ 0 (+ 0 (+ 0 (* c0_16 (+ c3_16 (* c0_16 c4_16)))))))) (+ c1_17 (+ c2_17 (+ 0 (+ 0 (+ 0 (* c0_17 (+ c3_17 (* c0_17 c4_17)))))))) (+ c1_18 (+ c2_18 (+ 0 (+ 0 (+ 0 (* c0_18 (+ c3_18 (* c0_18 c4_18)))))))) (+ c1_19 (+ c2_19 (+ 0 (+ 0 (+ 0 (* c0_19 (+ c3_19 (* c0_19 c4_19)))))))) (+ c1_20 (+ c2_20 (+ 0 (+ 0 (+ 0 (* c0_20 (+ c3_20 (* c0_20 c4_20)))))))) (+ c1_21 (+ c2_21 (+ 0 (+ 0 (+ 0 (* c0_21 (+ c3_21 (* c0_21 c4_21)))))))) (+ c1_22 (+ c2_22 (+ 0 (+ 0 (+ 0 (* c0_22 (+ c3_22 (* c0_22 c4_22)))))))) (+ c1_23 (+ c2_23 (+ 0 (+ 0 (+ 0 (* c0_23 (+ c3_23 (* c0_23 c4_23)))))))) (+ c1_24 (+ c2_24 (+ 0 (+ 0 (+ 0 (* c0_24 (+ c3_24 (* c0_24 c4_24)))))))) (+ c1_25 (+ c2_25 (+ 0 (+ 0 (+ 0 (* c0_25 (+ c3_25 (* c0_25 c4_25)))))))) (+ c1_26 (+ c2_26 (+ 0 (+ 0 (+ 0 (* c0_26 (+ c3_26 (* c0_26 c4_26)))))))) (+ c1_27 (+ c2_27 (+ 0 (+ 0 (+ 0 (* c0_27 (+ c3_27 (* c0_27 c4_27)))))))) (+ c1_28 (+ c2_28 (+ 0 (+ 0 (+ 0 (* c0_28 (+ c3_28 (* c0_28 c4_28)))))))) (+ c1_29 (+ c2_29 (+ 0 (+ 0 (+ 0 (* c0_29 (+ c3_29 (* c0_29 c4_29)))))))) (+ c1_30 (+ c2_30 (+ 0 (+ 0 (+ 0 (* c0_30 (+ c3_30 (* c0_30 c4_30)))))))) (+ c1_31 (+ c2_31 (+ 0 (+ 0 (+ 0 (* c0_31 (+ c3_31 (* c0_31 c4_31)))))))))</t>
         </is>
       </c>
       <c r="E10" t="n">
         <v>40009</v>
       </c>
       <c r="F10" t="n">
-        <v>58583</v>
+        <v>58512</v>
       </c>
       <c r="G10" t="n">
-        <v>-46.42</v>
+        <v>-46.25</v>
       </c>
       <c r="H10" t="n">
         <v>75.15000000000001</v>
       </c>
       <c r="I10" t="n">
-        <v>163.8</v>
+        <v>78.75</v>
       </c>
       <c r="J10" t="b">
         <v>0</v>
       </c>
       <c r="K10" t="n">
-        <v>136.2</v>
+        <v>221.25</v>
       </c>
       <c r="L10" t="n">
         <v>75</v>
@@ -883,29 +883,29 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>(Vec (+ (+ (* (- c2_0 c1_0) (- c2_0 c1_0)) (* (- c2_1 c1_1) (- c2_1 c1_1))) (+ (* (- c2_2 c1_2) (- c2_2 c1_2)) (* (- c2_3 c1_3) (- c2_3 c1_3)))))</t>
+          <t>(Vec (+ (+ (* (- c2_0 c1_0) (- c2_0 c1_0)) (* (- c2_1 c1_1) (- c2_1 c1_1))) (+ (* (- c2_2 c1_2) (- c2_2 c1_2)) (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (* (- c2_3 c1_3) (- c2_3 c1_3)))))))))))))))))))))))))))))))))))))))))))))))))))))))))))))))))))))))))))))))</t>
         </is>
       </c>
       <c r="E11" t="n">
         <v>3757</v>
       </c>
       <c r="F11" t="n">
-        <v>3757</v>
+        <v>22331</v>
       </c>
       <c r="G11" t="n">
-        <v>0</v>
+        <v>-494.38</v>
       </c>
       <c r="H11" t="n">
         <v>40.57</v>
       </c>
       <c r="I11" t="n">
-        <v>40.57</v>
+        <v>129.22</v>
       </c>
       <c r="J11" t="b">
         <v>0</v>
       </c>
       <c r="K11" t="n">
-        <v>259.43</v>
+        <v>170.78</v>
       </c>
       <c r="L11" t="n">
         <v>75</v>
@@ -925,29 +925,29 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>(Vec (+ (+ (+ (* (- c2_0 c1_0) (- c2_0 c1_0)) (* (- c2_1 c1_1) (- c2_1 c1_1))) (+ (* (- c2_2 c1_2) (- c2_2 c1_2)) (* (- c2_3 c1_3) (- c2_3 c1_3)))) (+ (+ (* (- c2_4 c1_4) (- c2_4 c1_4)) (* (- c2_5 c1_5) (- c2_5 c1_5))) (+ (* (- c2_6 c1_6) (- c2_6 c1_6)) (* (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (- c2_7 c1_7)))))))))))))))))))))))))))))))))))))) (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (- c2_7 c1_7)))))))))))))))))))))))))))))))))))))))))))</t>
+          <t>(Vec (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (+ (+ (* 1 (+ (* (- c2_0 c1_0) (- c2_0 c1_0)) (* (- c2_1 c1_1) (- c2_1 c1_1)))) (+ (* (- c2_2 c1_2) (- c2_2 c1_2)) (* (- c2_3 c1_3) (- c2_3 c1_3)))) (+ (+ (+ (+ (+ (+ (+ (* 1 (* 1 (* 1 (+ (+ (* (- c2_4 c1_4) (- c2_4 c1_4)) 0) 0)))) 0) 0) 0) 0) 0) (* (- c2_5 c1_5) (- c2_5 c1_5))) (+ (* (- c2_6 c1_6) (- c2_6 c1_6)) (* (- c2_7 c1_7) (- c2_7 c1_7)))))))))))))))</t>
         </is>
       </c>
       <c r="E12" t="n">
         <v>7758</v>
       </c>
       <c r="F12" t="n">
-        <v>26332</v>
+        <v>12789</v>
       </c>
       <c r="G12" t="n">
-        <v>-239.42</v>
+        <v>-64.84999999999999</v>
       </c>
       <c r="H12" t="n">
         <v>41.77</v>
       </c>
       <c r="I12" t="n">
-        <v>1321.26</v>
+        <v>465.13</v>
       </c>
       <c r="J12" t="b">
         <v>1</v>
       </c>
       <c r="K12" t="n">
-        <v>-1021.26</v>
+        <v>-165.13</v>
       </c>
       <c r="L12" t="n">
         <v>75</v>
@@ -967,29 +967,29 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>(Vec (+ (+ (+ (+ (+ (* (- c2_0 c1_0) (- c2_0 c1_0)) (* (- c2_1 c1_1) (- c2_1 c1_1))) (+ (* (- c2_2 c1_2) (- c2_2 c1_2)) (* (- c2_3 c1_3) (- c2_3 c1_3)))) (+ (+ (* (- c2_4 c1_4) (- c2_4 c1_4)) (* (- c2_5 c1_5) (- c2_5 c1_5))) (+ (* (- c2_6 c1_6) (- c2_6 c1_6)) (* (- c2_7 c1_7) (- c2_7 c1_7))))) (+ (+ (+ (* (- c2_8 c1_8) (- c2_8 c1_8)) (* (- c2_9 c1_9) (- c2_9 c1_9))) (+ (* (- c2_10 c1_10) (- c2_10 c1_10)) (* (- c2_11 c1_11) (- c2_11 c1_11)))) (+ (+ (* (- c2_12 c1_12) (- c2_12 c1_12)) (* (- c2_13 c1_13) (- c2_13 c1_13))) (+ (* (- c2_14 c1_14) (- c2_14 c1_14)) (* (- c2_15 c1_15) (- c2_15 c1_15)))))) (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (* (- c2_16 c1_16) (- c2_16 c1_16)) (* (- c2_17 c1_17) (- c2_17 c1_17))) (+ (* (- c2_18 c1_18) (- c2_18 c1_18)) (* (- c2_19 c1_19) (- c2_19 c1_19)))) (+ (+ (* (- c2_20 c1_20) (- c2_20 c1_20)) (* (- c2_21 c1_21) (- c2_21 c1_21))) (+ (* (- c2_22 c1_22) (- c2_22 c1_22)) (* (- c2_23 c1_23) (- c2_23 c1_23))))) (+ (+ (+ (* (- c2_24 c1_24) (- c2_24 c1_24)) (* (- c2_25 c1_25) (- c2_25 c1_25))) (+ (* (- c2_26 c1_26) (- c2_26 c1_26)) (* (- c2_27 c1_27) (- c2_27 c1_27)))) (+ (+ (* (- c2_28 c1_28) (- c2_28 c1_28)) (* (- c2_29 c1_29) (- c2_29 c1_29))) (+ (* (- c2_30 c1_30) (- c2_30 c1_30)) (* (- c2_31 c1_31) (- c2_31 c1_31)))))) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0)))</t>
+          <t>(Vec (+ (+ (+ (+ (+ (* (- c2_0 c1_0) (- c2_0 c1_0)) (* (- c2_1 c1_1) (- c2_1 c1_1))) (+ (* (- c2_2 c1_2) (- c2_2 c1_2)) (* (- c2_3 c1_3) (- c2_3 c1_3)))) (+ (+ (* (- c2_4 c1_4) (- c2_4 c1_4)) (* (- c2_5 c1_5) (- c2_5 c1_5))) (+ (* (- c2_6 c1_6) (- c2_6 c1_6)) (* (- c2_7 c1_7) (- c2_7 c1_7))))) (+ (+ (+ (* (- c2_8 c1_8) (- c2_8 c1_8)) (* (- c2_9 c1_9) (- c2_9 c1_9))) (+ (* (- c2_10 c1_10) (- c2_10 c1_10)) (+ 0 (+ 0 (+ 0 (+ 0 (* (- c2_11 c1_11) (- c2_11 c1_11)))))))) (+ (+ (+ 0 (+ 0 (+ 0 (+ 0 (* (- c2_12 c1_12) (- c2_12 c1_12)))))) (+ 0 (+ 0 (+ 0 (+ 0 (* (- c2_13 c1_13) (- c2_13 c1_13))))))) (+ (+ 0 (+ 0 (+ 0 (+ 0 (* (- c2_14 c1_14) (- c2_14 c1_14)))))) (+ 0 (+ 0 (+ 0 (+ 0 (* (- c2_15 c1_15) (- c2_15 c1_15)))))))))) (+ (+ (+ (+ (+ 0 (+ 0 (+ 0 (+ 0 (* (- c2_16 c1_16) (- c2_16 c1_16)))))) (+ 0 (+ 0 (+ 0 (+ 0 (* (- c2_17 c1_17) (- c2_17 c1_17))))))) (+ (+ 0 (+ 0 (+ 0 (+ 0 (* (- c2_18 c1_18) (- c2_18 c1_18)))))) (+ 0 (+ 0 (+ 0 (+ 0 (* (- c2_19 c1_19) (- c2_19 c1_19)))))))) (+ (+ (+ 0 (+ 0 (+ 0 (+ 0 (* (- c2_20 c1_20) (- c2_20 c1_20)))))) (+ 0 (+ 0 (+ 0 (+ 0 (* (- c2_21 c1_21) (- c2_21 c1_21))))))) (+ (+ 0 (+ 0 (+ 0 (* (- c2_22 c1_22) (- c2_22 c1_22))))) (+ 0 (+ 0 (+ 0 (* (- c2_23 c1_23) (- c2_23 c1_23)))))))) (+ (+ (+ (+ 0 (+ 0 (+ 0 (* (- c2_24 c1_24) (- c2_24 c1_24))))) (+ 0 (+ 0 (+ 0 (* (- c2_25 c1_25) (- c2_25 c1_25)))))) (+ (+ 0 (+ 0 (+ 0 (* (- c2_26 c1_26) (- c2_26 c1_26))))) (+ 0 (+ 0 (+ 0 (* (- c2_27 c1_27) (- c2_27 c1_27))))))) (+ (+ (+ 0 (+ 0 (+ 0 (* (- c2_28 c1_28) (- c2_28 c1_28))))) (+ 0 (+ 0 (+ 0 (* (- c2_29 c1_29) (- c2_29 c1_29)))))) (+ (+ 0 (+ 0 (+ 0 (* (- c2_30 c1_30) (- c2_30 c1_30))))) (+ 0 (+ 0 (+ 0 (* (- c2_31 c1_31) (- c2_31 c1_31)))))))))))</t>
         </is>
       </c>
       <c r="E13" t="n">
         <v>31760</v>
       </c>
       <c r="F13" t="n">
-        <v>50334</v>
+        <v>50264</v>
       </c>
       <c r="G13" t="n">
-        <v>-58.48</v>
+        <v>-58.26</v>
       </c>
       <c r="H13" t="n">
         <v>44.16</v>
       </c>
       <c r="I13" t="n">
-        <v>132.82</v>
+        <v>48.96</v>
       </c>
       <c r="J13" t="b">
         <v>0</v>
       </c>
       <c r="K13" t="n">
-        <v>167.18</v>
+        <v>251.04</v>
       </c>
       <c r="L13" t="n">
         <v>75</v>
@@ -1009,29 +1009,29 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>(Vec (+ (+ (* v1_0 v2_0) (* v1_1 v2_1)) (+ (* v1_2 v2_2) (* v1_3 v2_3))))</t>
+          <t>(Vec (+ (+ (* v1_0 v2_0) (* v1_1 v2_1)) (+ (* v1_2 v2_2) (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (* v1_3 v2_3))))))))))))))))))))))))))))))))))))))))))))))))))))))))))))))))))))))))))))))</t>
         </is>
       </c>
       <c r="E14" t="n">
         <v>1756</v>
       </c>
       <c r="F14" t="n">
-        <v>1756</v>
+        <v>20330</v>
       </c>
       <c r="G14" t="n">
-        <v>0</v>
+        <v>-1057.74</v>
       </c>
       <c r="H14" t="n">
         <v>39.37</v>
       </c>
       <c r="I14" t="n">
-        <v>39.37</v>
+        <v>128.02</v>
       </c>
       <c r="J14" t="b">
         <v>0</v>
       </c>
       <c r="K14" t="n">
-        <v>260.63</v>
+        <v>171.98</v>
       </c>
       <c r="L14" t="n">
         <v>75</v>
@@ -1051,29 +1051,29 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>(Vec (+ (+ (+ (* v1_0 v2_0) (* v1_1 v2_1)) (+ (* v1_2 v2_2) (* v1_3 v2_3))) (+ (+ (* v1_4 v2_4) (* v1_5 v2_5)) (+ (* v1_6 v2_6) (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* v1_7 v2_7) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1)))))</t>
+          <t>(Vec (+ (+ (+ (* v1_0 v2_0) (* v1_1 v2_1)) (+ (* v1_2 v2_2) (* v1_3 v2_3))) (+ (+ (* v1_4 v2_4) (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (* v1_5 v2_5))))))))))))))))))))))))))) (+ (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (* v1_6 v2_6)))))))))))))))))))))))))) (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (* v1_7 v2_7)))))))))))))))))))))))))))))</t>
         </is>
       </c>
       <c r="E15" t="n">
         <v>3757</v>
       </c>
       <c r="F15" t="n">
-        <v>22405</v>
+        <v>22282</v>
       </c>
       <c r="G15" t="n">
-        <v>-496.35</v>
+        <v>-493.08</v>
       </c>
       <c r="H15" t="n">
         <v>40.57</v>
       </c>
       <c r="I15" t="n">
-        <v>2599.56</v>
+        <v>70.52</v>
       </c>
       <c r="J15" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K15" t="n">
-        <v>-2299.56</v>
+        <v>229.48</v>
       </c>
       <c r="L15" t="n">
         <v>75</v>
@@ -1093,32 +1093,32 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>(Vec (+ (+ (+ (+ (+ (* v1_0 v2_0) (* v1_1 v2_1)) (+ (* v1_2 v2_2) (* v1_3 v2_3))) (+ (+ (* v1_4 v2_4) (* v1_5 v2_5)) (+ (* v1_6 v2_6) (* v1_7 v2_7)))) (+ (+ (+ (* v1_8 v2_8) (* v1_9 v2_9)) (+ (* v1_10 v2_10) (* v1_11 v2_11))) (+ (+ (* v1_12 v2_12) (* v1_13 v2_13)) (+ (* v1_14 v2_14) (* v1_15 v2_15))))) (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (* v1_16 v2_16) (* v1_17 v2_17)) (+ (* v1_18 v2_18) (* v1_19 v2_19))) (+ (+ (* v1_20 v2_20) (* v1_21 v2_21)) (+ (* v1_22 v2_22) (* v1_23 v2_23)))) (+ (+ (+ (* v1_24 v2_24) (* v1_25 v2_25)) (+ (* v1_26 v2_26) (* v1_27 v2_27))) (+ (+ (* v1_28 v2_28) (* v1_29 v2_29)) (+ (* v1_30 v2_30) (* v1_31 v2_31))))) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0)))</t>
+          <t>(Vec ( + ( + ( + ( + ( + ( * v1_0 v2_0 ) ( * v1_1 v2_1 ) ) ( + ( * v1_2 v2_2 ) ( * v1_3 v2_3 ) ) ) ( + ( + ( * v1_4 v2_4 ) ( * v1_5 v2_5 ) ) ( + ( * v1_6 v2_6 ) ( * v1_7 v2_7 ) ) ) ) ( + ( + ( + ( * v1_8 v2_8 ) ( * v1_9 v2_9 ) ) ( + ( * v1_10 v2_10 ) ( * v1_11 v2_11 ) ) ) ( + ( + ( * v1_12 v2_12 ) ( * v1_13 v2_13 ) ) ( + ( * v1_14 v2_14 ) ( * v1_15 v2_15 ) ) ) ) ) ( + ( + ( + ( + ( * v1_16 v2_16 ) ( * v1_17 v2_17 ) ) ( + ( * v1_18 v2_18 ) ( * v1_19 v2_19 ) ) ) ( + ( + ( * v1_20 v2_20 ) ( * v1_21 v2_21 ) ) ( + ( * v1_22 v2_22 ) ( * v1_23 v2_23 ) ) ) ) ( + ( + ( + ( * v1_24 v2_24 ) ( * v1_25 v2_25 ) ) ( + ( * v1_26 v2_26 ) ( * v1_27 v2_27 ) ) ) ( + ( + ( * v1_28 v2_28 ) ( * v1_29 v2_29 ) ) ( + ( * v1_30 v2_30 ) ( * v1_31 v2_31 ) ) ) ) ) ) )</t>
         </is>
       </c>
       <c r="E16" t="n">
         <v>15759</v>
       </c>
       <c r="F16" t="n">
-        <v>34333</v>
+        <v>15759</v>
       </c>
       <c r="G16" t="n">
-        <v>-117.86</v>
+        <v>0</v>
       </c>
       <c r="H16" t="n">
         <v>42.97</v>
       </c>
       <c r="I16" t="n">
-        <v>131.62</v>
+        <v>42.97</v>
       </c>
       <c r="J16" t="b">
         <v>0</v>
       </c>
       <c r="K16" t="n">
-        <v>168.38</v>
+        <v>257.03</v>
       </c>
       <c r="L16" t="n">
-        <v>75</v>
+        <v>1</v>
       </c>
     </row>
     <row r="17">
@@ -1135,29 +1135,29 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>(Vec (+ in_1_1 (* in_0_1 2)) (+ (+ in_1_2 (- in_1_0)) (+ (* in_0_2 2) (* in_0_0 -2))) (+ (+ in_1_3 (- in_1_1)) (+ (* in_0_3 2) (* in_0_1 -2))) (+ (- in_1_2) (* in_0_2 -2)) (+ in_2_1 (+ in_0_1 (* in_1_1 2))) (+ (+ in_2_2 (- in_2_0)) (+ (+ in_0_2 (- in_0_0)) (+ (* in_1_2 2) (* in_1_0 -2)))) (+ (+ in_2_3 (- in_2_1)) (+ (+ in_0_3 (- in_0_1)) (+ (* in_1_3 2) (* in_1_1 -2)))) (+ (- in_2_2) (+ (- in_0_2) (* in_1_2 -2))) (+ in_3_1 (+ in_1_1 (* in_2_1 2))) (+ (+ in_3_2 (- in_3_0)) (+ (+ in_1_2 (- in_1_0)) (+ (* in_2_2 2) (* in_2_0 -2)))) (+ (+ in_3_3 (- in_3_1)) (+ (+ in_1_3 (- in_1_1)) (+ (* in_2_3 2) (* in_2_1 -2)))) (+ (- in_3_2) (+ (- in_1_2) (* in_2_2 -2))) (+ in_2_1 (* in_3_1 2)) (+ (+ in_2_2 (- in_2_0)) (+ (* in_3_2 2) (* in_3_0 -2))) (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (+ (+ in_2_3 (- in_2_1)) (+ (* in_3_3 2) (* in_3_1 -2))) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) (+ (- in_2_2) (* in_3_2 -2)))</t>
+          <t>(Vec (+ in_1_1 (* in_0_1 2)) (+ (+ in_1_2 (- in_1_0)) (+ (* in_0_2 2) (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (* in_0_0 -2)))))))) (+ (+ in_1_3 (- in_1_1)) (+ (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (* in_0_3 2)))))) (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (* in_0_1 -2)))))))) (+ (- in_1_2) (* in_0_2 -2)) (+ in_2_1 (+ in_0_1 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (* in_1_1 2)))))))) (+ (+ in_2_2 (- in_2_0)) (+ (+ in_0_2 (- in_0_0)) (+ (+ 0 (+ 0 (+ 0 (+ 0 (* in_1_2 2))))) (+ 0 (+ 0 (+ 0 (+ 0 (* in_1_0 -2)))))))) (+ (+ in_2_3 (- in_2_1)) (+ (+ in_0_3 (- in_0_1)) (+ (+ 0 (+ 0 (+ 0 (* in_1_3 2)))) (+ 0 (+ 0 (+ 0 (* in_1_1 -2))))))) (+ (- in_2_2) (+ (- in_0_2) (+ 0 (+ 0 (+ 0 (+ 0 (* in_1_2 -2))))))) (+ in_3_1 (+ in_1_1 (+ 0 (+ 0 (+ 0 (+ 0 (* in_2_1 2))))))) (+ (+ in_3_2 (- in_3_0)) (+ (+ in_1_2 (- in_1_0)) (+ (+ 0 (+ 0 (+ 0 (* in_2_2 2)))) (+ 0 (+ 0 (+ 0 (* in_2_0 -2))))))) (+ (+ in_3_3 (- in_3_1)) (+ (+ in_1_3 (- in_1_1)) (+ (+ 0 (+ 0 (+ 0 (* in_2_3 2)))) (+ 0 (+ 0 (+ 0 (* in_2_1 -2))))))) (+ (- in_3_2) (+ (- in_1_2) (+ 0 (+ 0 (+ 0 (+ 0 (* in_2_2 -2))))))) (+ in_2_1 (* in_3_1 2)) (+ (+ in_2_2 (- in_2_0)) (+ (+ 0 (+ 0 (+ 0 (+ 0 (* in_3_2 2))))) (+ 0 (+ 0 (+ 0 (+ 0 (* in_3_0 -2))))))) (+ (+ in_2_3 (- in_2_1)) (+ (+ 0 (+ 0 (+ 0 (+ 0 (* in_3_3 2))))) (+ 0 (+ 0 (+ 0 (+ 0 (* in_3_1 -2))))))) (+ (- in_2_2) (* in_3_2 -2)))</t>
         </is>
       </c>
       <c r="E17" t="n">
         <v>21507</v>
       </c>
       <c r="F17" t="n">
-        <v>40154</v>
+        <v>40011</v>
       </c>
       <c r="G17" t="n">
-        <v>-86.7</v>
+        <v>-86.04000000000001</v>
       </c>
       <c r="H17" t="n">
         <v>40.57</v>
       </c>
       <c r="I17" t="n">
-        <v>2598.36</v>
+        <v>45.36</v>
       </c>
       <c r="J17" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K17" t="n">
-        <v>-2298.36</v>
+        <v>254.64</v>
       </c>
       <c r="L17" t="n">
         <v>75</v>
@@ -1177,32 +1177,32 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>(Vec (+ (+ (* a_0_0 b_0_0) (* a_0_1 b_1_0)) (* a_0_2 b_2_0)) (+ (+ (* a_0_0 b_0_1) (* a_0_1 b_1_1)) (* a_0_2 b_2_1)) (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (* a_0_0 b_0_2) (* a_0_1 b_1_2)) (* a_0_2 b_2_2)) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) (+ (+ (* a_1_0 b_0_0) (* a_1_1 b_1_0)) (* a_1_2 b_2_0)) (+ (+ (* a_1_0 b_0_1) (* a_1_1 b_1_1)) (* a_1_2 b_2_1)) (+ (+ (* a_1_0 b_0_2) (* a_1_1 b_1_2)) (* a_1_2 b_2_2)) (+ (+ (* a_2_0 b_0_0) (* a_2_1 b_1_0)) (* a_2_2 b_2_0)) (+ (+ (* a_2_0 b_0_1) (* a_2_1 b_1_1)) (* a_2_2 b_2_1)) (+ (+ (* a_2_0 b_0_2) (* a_2_1 b_1_2)) (* a_2_2 b_2_2)))</t>
+          <t>(Vec ( + ( + ( * a_0_0 b_0_0 ) ( * a_0_1 b_1_0 ) ) ( * a_0_2 b_2_0 ) ) ( + ( + ( * a_0_0 b_0_1 ) ( * a_0_1 b_1_1 ) ) ( * a_0_2 b_2_1 ) ) ( + ( + ( * a_0_0 b_0_2 ) ( * a_0_1 b_1_2 ) ) ( * a_0_2 b_2_2 ) ) ( + ( + ( * a_1_0 b_0_0 ) ( * a_1_1 b_1_0 ) ) ( * a_1_2 b_2_0 ) ) ( + ( + ( * a_1_0 b_0_1 ) ( * a_1_1 b_1_1 ) ) ( * a_1_2 b_2_1 ) ) ( + ( + ( * a_1_0 b_0_2 ) ( * a_1_1 b_1_2 ) ) ( * a_1_2 b_2_2 ) ) ( + ( + ( * a_2_0 b_0_0 ) ( * a_2_1 b_1_0 ) ) ( * a_2_2 b_2_0 ) ) ( + ( + ( * a_2_0 b_0_1 ) ( * a_2_1 b_1_1 ) ) ( * a_2_2 b_2_1 ) ) ( + ( + ( * a_2_0 b_0_2 ) ( * a_2_1 b_1_2 ) ) ( * a_2_2 b_2_2 ) ) )</t>
         </is>
       </c>
       <c r="E18" t="n">
         <v>11256</v>
       </c>
       <c r="F18" t="n">
-        <v>29830</v>
+        <v>11256</v>
       </c>
       <c r="G18" t="n">
-        <v>-165.01</v>
+        <v>0</v>
       </c>
       <c r="H18" t="n">
         <v>39.37</v>
       </c>
       <c r="I18" t="n">
-        <v>128.02</v>
+        <v>39.37</v>
       </c>
       <c r="J18" t="b">
         <v>0</v>
       </c>
       <c r="K18" t="n">
-        <v>171.98</v>
+        <v>260.63</v>
       </c>
       <c r="L18" t="n">
-        <v>75</v>
+        <v>1</v>
       </c>
     </row>
     <row r="19">
@@ -1219,29 +1219,29 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>(Vec (+ (* (+ (* o3 (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (- 1 c23) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1)) (* c23 o2)) (- 1 c12)) (* c12 (+ (* o3 (- 1 c13)) (* c13 o1)))))</t>
+          <t>(Vec (+ (* (+ (* o3 (- 1 c23)) (* c23 o2)) (- 1 c12)) (* c12 (+ (* o3 (- 1 c13)) (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (* c13 o1)))))))))))))))))))))))))))))))))))))))))))))))))))))))))))))))))))))))))))))))</t>
         </is>
       </c>
       <c r="E19" t="n">
         <v>3009</v>
       </c>
       <c r="F19" t="n">
-        <v>21657</v>
+        <v>21582</v>
       </c>
       <c r="G19" t="n">
-        <v>-619.74</v>
+        <v>-617.25</v>
       </c>
       <c r="H19" t="n">
         <v>75.15000000000001</v>
       </c>
       <c r="I19" t="n">
-        <v>2634.14</v>
+        <v>162.61</v>
       </c>
       <c r="J19" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K19" t="n">
-        <v>-2334.14</v>
+        <v>137.39</v>
       </c>
       <c r="L19" t="n">
         <v>75</v>
@@ -1261,29 +1261,29 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>(Vec (+ (* (+ (* (+ (* o321 (- 1 c23)) (* c23 o231)) (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (- 1 c13) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1)) (* c13 o213)) (- 1 c12)) (* c12 (+ (* (- 1 c23) (+ (* o312 (- 1 c13)) (* c13 o132))) (* c23 o123)))))</t>
+          <t>(Vec (+ (* (+ (* (+ (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (* o321 (- 1 c23))))))))))))))))) (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (* c23 o231))))))))))))))))) (- 1 c13)) (* c13 o213)) (- 1 c12)) (* c12 (+ (* (- 1 c23) (+ (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (* o312 (- 1 c13)))))))))))))))) (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (* c13 o132))))))))))))))))) (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (* c23 o123)))))))))))))))))))))</t>
         </is>
       </c>
       <c r="E20" t="n">
         <v>5012</v>
       </c>
       <c r="F20" t="n">
-        <v>23657</v>
+        <v>23527</v>
       </c>
       <c r="G20" t="n">
-        <v>-372.01</v>
+        <v>-369.41</v>
       </c>
       <c r="H20" t="n">
         <v>110.93</v>
       </c>
       <c r="I20" t="n">
-        <v>2634.14</v>
+        <v>128.9</v>
       </c>
       <c r="J20" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K20" t="n">
-        <v>-2334.14</v>
+        <v>171.1</v>
       </c>
       <c r="L20" t="n">
         <v>75</v>
@@ -1303,29 +1303,29 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>(VecMul (Vec (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ x9602 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) x9604) (+ (+ x9608 x9610) (+ x9617 (* x9613 x9615)))) (&lt;&lt; (Vec (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ x9602 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) x9604) (+ (+ x9608 x9610) (+ x9617 (* x9613 x9615)))) 1))</t>
+          <t>(Vec (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (* (+ x9602 x9604) (+ (+ x9608 x9610) (+ (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (* x9613 x9615))))))))))))))))))))))))))))))))))))))))))))))) x9617))))))))))))))))))))))))))))))))</t>
         </is>
       </c>
       <c r="E21" t="n">
         <v>1508</v>
       </c>
       <c r="F21" t="n">
-        <v>19480</v>
+        <v>20082</v>
       </c>
       <c r="G21" t="n">
-        <v>-1191.78</v>
+        <v>-1231.7</v>
       </c>
       <c r="H21" t="n">
         <v>73.95</v>
       </c>
       <c r="I21" t="n">
-        <v>159.01</v>
+        <v>162.61</v>
       </c>
       <c r="J21" t="b">
         <v>0</v>
       </c>
       <c r="K21" t="n">
-        <v>140.99</v>
+        <v>137.39</v>
       </c>
       <c r="L21" t="n">
         <v>75</v>
@@ -1345,32 +1345,32 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>(Vec (+ (+ (* (+ (* x9604 x9605) (+ x9607 x9608)) (+ (+ x9611 x9612) (+ x9614 x9615))) (* (* (* x9619 x9620) (* x9622 x9623)) (* (+ x9626 x9627) (* x9629 x9630)))) (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (* (+ (+ (* x9634 x9635) (+ x9637 x9638)) (+ (* x9641 x9642) (* x9644 x9645))) (+ (* (+ x9649 x9650) (+ x9652 x9653)) (+ (* x9656 x9657) (* x9659 x9660)))) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0)))</t>
+          <t>(Vec ( + ( + ( * ( + ( * x9604 x9605 ) ( + x9607 x9608 ) ) ( + ( + x9611 x9612 ) ( + x9614 x9615 ) ) ) ( * ( * ( * x9619 x9620 ) ( * x9622 x9623 ) ) ( * ( + x9626 x9627 ) ( * x9629 x9630 ) ) ) ) ( * ( + ( + ( * x9634 x9635 ) ( + x9637 x9638 ) ) ( + ( * x9641 x9642 ) ( * x9644 x9645 ) ) ) ( + ( * ( + x9649 x9650 ) ( + x9652 x9653 ) ) ( + ( * x9656 x9657 ) ( * x9659 x9660 ) ) ) ) ) )</t>
         </is>
       </c>
       <c r="E22" t="n">
         <v>7760</v>
       </c>
       <c r="F22" t="n">
-        <v>26334</v>
+        <v>7760</v>
       </c>
       <c r="G22" t="n">
-        <v>-239.36</v>
+        <v>0</v>
       </c>
       <c r="H22" t="n">
         <v>108.53</v>
       </c>
       <c r="I22" t="n">
-        <v>197.19</v>
+        <v>108.53</v>
       </c>
       <c r="J22" t="b">
         <v>0</v>
       </c>
       <c r="K22" t="n">
-        <v>102.81</v>
+        <v>191.47</v>
       </c>
       <c r="L22" t="n">
-        <v>75</v>
+        <v>1</v>
       </c>
     </row>
     <row r="23">
@@ -1387,32 +1387,32 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>(Vec (+ (* (+ (* (+ (* (+ (* o5 (- 1 c45)) (* c45 o4)) (- 1 c34)) (* c34 (+ (* o5 (- 1 c35)) (* c35 o3)))) (- 1 c23)) (* c23 (+ (* (+ (* o5 (- 1 c45)) (* c45 o4)) (- 1 c24)) (* c24 (+ (* o5 (- 1 c25)) (* c25 o2)))))) (- 1 c12)) (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (* c12 (+ (* (+ (* (+ (* o5 (- 1 c45)) (* c45 o4)) (- 1 c34)) (* c34 (+ (* o5 (- 1 c35)) (* c35 o3)))) (- 1 c13)) (* c13 (+ (* (+ (* o5 (- 1 c45)) (* c45 o4)) (- 1 c14)) (* c14 (+ (* o5 (- 1 c15)) (* c15 o1))))))) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0)))</t>
+          <t>(Vec ( + ( * ( + ( * ( + ( * ( + ( * o5 ( - 1 c45 ) ) ( * c45 o4 ) ) ( - 1 c34 ) ) ( * c34 ( + ( * o5 ( - 1 c35 ) ) ( * c35 o3 ) ) ) ) ( - 1 c23 ) ) ( * c23 ( + ( * ( + ( * o5 ( - 1 c45 ) ) ( * c45 o4 ) ) ( - 1 c24 ) ) ( * c24 ( + ( * o5 ( - 1 c25 ) ) ( * c25 o2 ) ) ) ) ) ) ( - 1 c12 ) ) ( * c12 ( + ( * ( + ( * ( + ( * o5 ( - 1 c45 ) ) ( * c45 o4 ) ) ( - 1 c34 ) ) ( * c34 ( + ( * o5 ( - 1 c35 ) ) ( * c35 o3 ) ) ) ) ( - 1 c13 ) ) ( * c13 ( + ( * ( + ( * o5 ( - 1 c45 ) ) ( * c45 o4 ) ) ( - 1 c14 ) ) ( * c14 ( + ( * o5 ( - 1 c15 ) ) ( * c15 o1 ) ) ) ) ) ) ) ) )</t>
         </is>
       </c>
       <c r="E23" t="n">
         <v>15015</v>
       </c>
       <c r="F23" t="n">
-        <v>33589</v>
+        <v>15015</v>
       </c>
       <c r="G23" t="n">
-        <v>-123.7</v>
+        <v>0</v>
       </c>
       <c r="H23" t="n">
         <v>146.71</v>
       </c>
       <c r="I23" t="n">
-        <v>235.36</v>
+        <v>146.71</v>
       </c>
       <c r="J23" t="b">
         <v>0</v>
       </c>
       <c r="K23" t="n">
-        <v>64.64</v>
+        <v>153.29</v>
       </c>
       <c r="L23" t="n">
-        <v>75</v>
+        <v>1</v>
       </c>
     </row>
     <row r="24">
@@ -1429,29 +1429,29 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>(Vec (+ (+ in_1_1 in_1_0) (+ in_0_1 in_0_0)) (+ (+ (+ in_1_2 in_1_1) (+ in_1_0 in_0_2)) (+ in_0_1 in_0_0)) (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ in_1_3 in_1_2) (+ in_1_1 in_0_3)) (+ in_0_2 in_0_1)) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) (- 0)) 0) 0) 0) (- 0)) 0) 0) 0) 0) (+ (+ in_1_3 in_1_2) (+ in_0_3 in_0_2)) (+ (+ (+ in_2_1 in_2_0) (+ in_1_1 in_1_0)) (+ in_0_1 in_0_0)) (+ (+ (+ in_2_2 (+ in_2_1 in_2_0)) (+ in_1_2 in_1_1)) (+ (+ in_1_0 in_0_2) (+ in_0_1 in_0_0))) (+ (+ (+ in_2_3 (+ in_2_2 in_2_1)) (+ in_1_3 in_1_2)) (+ (+ in_1_1 in_0_3) (+ in_0_2 in_0_1))) (+ (+ (+ in_2_3 in_2_2) (+ in_1_3 in_1_2)) (+ in_0_3 in_0_2)) (+ (+ in_3_1 in_3_0) (+ (+ in_2_1 in_2_0) (+ in_1_1 in_1_0))) (+ (+ (+ in_3_2 (+ in_3_1 in_3_0)) (+ in_2_2 in_2_1)) (+ (+ in_2_0 in_1_2) (+ in_1_1 in_1_0))) (+ (+ (+ in_3_3 (+ in_3_2 in_3_1)) (+ in_2_3 in_2_2)) (+ (+ in_2_1 in_1_3) (+ in_1_2 in_1_1))) (+ (+ (+ in_3_3 in_3_2) (+ in_2_3 in_2_2)) (+ in_1_3 in_1_2)) (+ (+ in_3_1 in_3_0) (+ in_2_1 in_2_0)) (+ (+ (+ in_3_2 in_3_1) (+ in_3_0 in_2_2)) (+ in_2_1 in_2_0)) (+ (+ (+ in_3_3 in_3_2) (+ in_3_1 in_2_3)) (+ in_2_2 in_2_1)) (+ (+ in_3_3 in_3_2) (+ in_2_3 in_2_2)))</t>
+          <t>(Vec (* 1 (* 1 (* 1 (+ (+ in_1_1 in_1_0) (+ in_0_1 in_0_0))))) (* 1 (* 1 (* 1 (+ (+ (+ in_1_2 in_1_1) (+ in_1_0 in_0_2)) (+ in_0_1 in_0_0))))) (* 1 (* 1 (* 1 (+ (+ (+ in_1_3 in_1_2) (+ in_1_1 in_0_3)) (+ in_0_2 in_0_1))))) (* 1 (* 1 (* 1 (* 1 (+ (+ in_1_3 in_1_2) (+ in_0_3 in_0_2)))))) (* 1 (* 1 (* 1 (* 1 (+ (+ (+ in_2_1 in_2_0) (+ in_1_1 in_1_0)) (+ in_0_1 in_0_0)))))) (* 1 (* 1 (* 1 (* 1 (+ (+ (+ in_2_2 (+ in_2_1 in_2_0)) (+ in_1_2 in_1_1)) (+ (+ in_1_0 in_0_2) (+ in_0_1 in_0_0))))))) (* 1 (* 1 (* 1 (* 1 (+ (+ (+ in_2_3 (+ in_2_2 in_2_1)) (+ in_1_3 in_1_2)) (+ (+ in_1_1 in_0_3) (+ in_0_2 in_0_1))))))) (* 1 (* 1 (* 1 (* 1 (+ (+ (+ in_2_3 in_2_2) (+ in_1_3 in_1_2)) (+ in_0_3 in_0_2)))))) (* 1 (* 1 (* 1 (* 1 (+ (+ in_3_1 in_3_0) (+ (+ in_2_1 in_2_0) (+ in_1_1 in_1_0))))))) (* 1 (* 1 (* 1 (* 1 (+ (+ (+ in_3_2 (+ in_3_1 in_3_0)) (+ in_2_2 in_2_1)) (+ (+ in_2_0 in_1_2) (+ in_1_1 in_1_0))))))) (* 1 (* 1 (* 1 (* 1 (+ (+ (+ in_3_3 (+ in_3_2 in_3_1)) (+ in_2_3 in_2_2)) (+ (+ in_2_1 in_1_3) (+ in_1_2 in_1_1))))))) (* 1 (* 1 (* 1 (+ (+ (+ in_3_3 in_3_2) (+ in_2_3 in_2_2)) (+ in_1_3 in_1_2))))) (* 1 (* 1 (* 1 (+ (+ in_3_1 in_3_0) (+ in_2_1 in_2_0))))) (* 1 (* 1 (* 1 (+ (+ (+ in_3_2 in_3_1) (+ in_3_0 in_2_2)) (+ in_2_1 in_2_0))))) (* 1 (* 1 (* 1 (+ (+ (+ in_3_3 in_3_2) (+ in_3_1 in_2_3)) (+ in_2_2 in_2_1))))) (* 1 (* 1 (* 1 (+ (+ in_3_3 in_3_2) (+ in_2_3 in_2_2))))))</t>
         </is>
       </c>
       <c r="E24" t="n">
         <v>21006</v>
       </c>
       <c r="F24" t="n">
-        <v>39577</v>
+        <v>35014</v>
       </c>
       <c r="G24" t="n">
-        <v>-88.41</v>
+        <v>-66.69</v>
       </c>
       <c r="H24" t="n">
         <v>7.19</v>
       </c>
       <c r="I24" t="n">
-        <v>92.25</v>
+        <v>145.51</v>
       </c>
       <c r="J24" t="b">
         <v>0</v>
       </c>
       <c r="K24" t="n">
-        <v>207.75</v>
+        <v>154.49</v>
       </c>
       <c r="L24" t="n">
         <v>75</v>
@@ -1471,29 +1471,29 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>(Vec (+ v2_0 (+ 2 (* v1_0 5))) (+ v2_1 (+ 2 (* v1_1 5))) (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ v2_2 (+ 2 (* v1_2 5))) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) (+ v2_3 (+ 2 (* v1_3 5))))</t>
+          <t>(Vec (+ v2_0 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (+ 2 (* v1_0 5))))))))))))))) (+ v2_1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (+ 2 (* v1_1 5))))))))))))))) (+ v2_2 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (+ 2 (* v1_2 5))))))))))))))) (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (+ v2_3 (+ (+ (+ (+ (+ (* 1 (* 1 (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ 2 (* v1_3 5)) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0))) 0) 0) 0) 0) 0))))))))))))))))</t>
         </is>
       </c>
       <c r="E25" t="n">
         <v>3006</v>
       </c>
       <c r="F25" t="n">
-        <v>21580</v>
+        <v>21559</v>
       </c>
       <c r="G25" t="n">
-        <v>-617.9</v>
+        <v>-617.2</v>
       </c>
       <c r="H25" t="n">
         <v>39.37</v>
       </c>
       <c r="I25" t="n">
-        <v>128.02</v>
+        <v>585.64</v>
       </c>
       <c r="J25" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K25" t="n">
-        <v>171.98</v>
+        <v>-285.64</v>
       </c>
       <c r="L25" t="n">
         <v>75</v>
@@ -1513,29 +1513,29 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>(Vec (+ v2_0 (+ 2 (* v1_0 5))) (+ v2_1 (+ 2 (* v1_1 5))) (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ v2_2 (+ 2 (* v1_2 5))) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) (- 0)) 0) 0) 0) 0) 0) (- 0)) (- 0)) (- (- 0))) (- (- (- 0)))) (- (- (- (- 0))))) (- (- 0))) 0) 0) 0) (+ v2_3 (+ 2 (* v1_3 5))) (+ v2_4 (+ 2 (* v1_4 5))) (+ v2_5 (+ 2 (* v1_5 5))) (+ v2_6 (+ 2 (* v1_6 5))) (+ v2_7 (+ 2 (* v1_7 5))) (+ v2_8 (+ 2 (* v1_8 5))) (+ v2_9 (+ 2 (* v1_9 5))) (+ v2_10 (+ 2 (* v1_10 5))) (+ v2_11 (+ 2 (* v1_11 5))) (+ v2_12 (+ 2 (* v1_12 5))) (+ v2_13 (+ 2 (* v1_13 5))) (+ v2_14 (+ 2 (* v1_14 5))) (+ v2_15 (+ 2 (* v1_15 5))))</t>
+          <t>(Vec (+ v2_0 (* 1 (* 1 (* 1 (* 1 (+ 2 (* v1_0 5))))))) (+ v2_1 (* 1 (* 1 (* 1 (* 1 (+ 2 (* v1_1 5))))))) (+ v2_2 (* 1 (* 1 (* 1 (* 1 (+ 2 (* v1_2 5))))))) (* 1 (* 1 (* 1 (* 1 (* 1 (+ v2_3 (+ 2 (* v1_3 5)))))))) (* 1 (* 1 (* 1 (* 1 (* 1 (+ v2_4 (+ 2 (* v1_4 5)))))))) (* 1 (* 1 (* 1 (* 1 (* 1 (+ v2_5 (+ 2 (* v1_5 5)))))))) (* 1 (* 1 (* 1 (* 1 (* 1 (+ v2_6 (+ 2 (* v1_6 5)))))))) (* 1 (* 1 (* 1 (* 1 (* 1 (+ v2_7 (+ 2 (* v1_7 5)))))))) (* 1 (* 1 (* 1 (* 1 (* 1 (+ v2_8 (+ 2 (* v1_8 5)))))))) (* 1 (* 1 (* 1 (* 1 (* 1 (+ v2_9 (+ 2 (* v1_9 5)))))))) (* 1 (* 1 (* 1 (* 1 (* 1 (+ v2_10 (+ 2 (* v1_10 5)))))))) (* 1 (* 1 (* 1 (* 1 (* 1 (+ v2_11 (+ 2 (* v1_11 5)))))))) (* 1 (* 1 (* 1 (* 1 (* 1 (+ v2_12 (+ 2 (* v1_12 5)))))))) (* 1 (* 1 (* 1 (* 1 (+ v2_13 (+ 2 (* v1_13 5))))))) (* 1 (* 1 (* 1 (* 1 (+ v2_14 (+ 2 (* v1_14 5))))))) (* 1 (* 1 (* 1 (* 1 (+ v2_15 (+ 2 (* v1_15 5))))))))</t>
         </is>
       </c>
       <c r="E26" t="n">
         <v>12006</v>
       </c>
       <c r="F26" t="n">
-        <v>30566</v>
+        <v>30516</v>
       </c>
       <c r="G26" t="n">
-        <v>-154.59</v>
+        <v>-154.17</v>
       </c>
       <c r="H26" t="n">
         <v>39.37</v>
       </c>
       <c r="I26" t="n">
-        <v>111.25</v>
+        <v>212.28</v>
       </c>
       <c r="J26" t="b">
         <v>0</v>
       </c>
       <c r="K26" t="n">
-        <v>188.75</v>
+        <v>87.72</v>
       </c>
       <c r="L26" t="n">
         <v>75</v>
@@ -1555,32 +1555,32 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>(Vec (+ (+ (- (+ v1_0 v2_0) (* (* v1_0 v2_0) 2)) (- (+ v1_1 v2_1) (* 2 (* v1_1 v2_1)))) (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (- (+ v1_2 v2_2) (* 2 (* v1_2 v2_2))) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0)))</t>
+          <t>(Vec ( + ( + ( - ( + v1_0 v2_0 ) ( * ( * v1_0 v2_0 ) 2 ) ) ( - ( + v1_1 v2_1 ) ( * 2 ( * v1_1 v2_1 ) ) ) ) ( - ( + v1_2 v2_2 ) ( * 2 ( * v1_2 v2_2 ) ) ) ) )</t>
         </is>
       </c>
       <c r="E27" t="n">
         <v>3509</v>
       </c>
       <c r="F27" t="n">
-        <v>22082</v>
+        <v>3509</v>
       </c>
       <c r="G27" t="n">
-        <v>-529.3</v>
+        <v>0</v>
       </c>
       <c r="H27" t="n">
         <v>75.15000000000001</v>
       </c>
       <c r="I27" t="n">
-        <v>162.61</v>
+        <v>75.15000000000001</v>
       </c>
       <c r="J27" t="b">
         <v>0</v>
       </c>
       <c r="K27" t="n">
-        <v>137.39</v>
+        <v>224.85</v>
       </c>
       <c r="L27" t="n">
-        <v>75</v>
+        <v>1</v>
       </c>
     </row>
     <row r="28">
@@ -1597,32 +1597,32 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>(Vec (+ (+ (- (+ v1_0 v2_0) (* (* v1_0 v2_0) 2)) (- (+ v1_1 v2_1) (* 2 (* v1_1 v2_1)))) (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (- (+ v1_2 v2_2) (* 2 (* v1_2 v2_2))) (- (+ v1_3 v2_3) (* 2 (* v1_3 v2_3)))) (- (+ v1_4 v2_4) (* 2 (* v1_4 v2_4)))) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0)))</t>
+          <t>(Vec ( + ( + ( - ( + v1_0 v2_0 ) ( * ( * v1_0 v2_0 ) 2 ) ) ( - ( + v1_1 v2_1 ) ( * 2 ( * v1_1 v2_1 ) ) ) ) ( + ( + ( - ( + v1_2 v2_2 ) ( * 2 ( * v1_2 v2_2 ) ) ) ( - ( + v1_3 v2_3 ) ( * 2 ( * v1_3 v2_3 ) ) ) ) ( - ( + v1_4 v2_4 ) ( * 2 ( * v1_4 v2_4 ) ) ) ) ) )</t>
         </is>
       </c>
       <c r="E28" t="n">
         <v>6010</v>
       </c>
       <c r="F28" t="n">
-        <v>24584</v>
+        <v>6010</v>
       </c>
       <c r="G28" t="n">
-        <v>-309.05</v>
+        <v>0</v>
       </c>
       <c r="H28" t="n">
         <v>76.34999999999999</v>
       </c>
       <c r="I28" t="n">
-        <v>165</v>
+        <v>76.34999999999999</v>
       </c>
       <c r="J28" t="b">
         <v>0</v>
       </c>
       <c r="K28" t="n">
-        <v>135</v>
+        <v>223.65</v>
       </c>
       <c r="L28" t="n">
-        <v>75</v>
+        <v>1</v>
       </c>
     </row>
     <row r="29">
@@ -1639,29 +1639,29 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>(Vec (+ (+ (+ (+ (- (+ v1_0 v2_0) (* (* v1_0 v2_0) 2)) (- (+ v1_1 v2_1) (* 2 (* v1_1 v2_1)))) (+ (- (+ v1_2 v2_2) (* 2 (* v1_2 v2_2))) (- (+ v1_3 v2_3) (* 2 (* v1_3 v2_3))))) (+ (+ (- (+ v1_4 v2_4) (* 2 (* v1_4 v2_4))) (- (+ v1_5 v2_5) (* 2 (* v1_5 v2_5)))) (+ (- (+ v1_6 v2_6) (* 2 (* v1_6 v2_6))) (- (+ v1_7 v2_7) (* 2 (* v1_7 v2_7)))))) (+ (+ (+ (- (+ v1_8 v2_8) (* 2 (* v1_8 v2_8))) (- (+ v1_9 v2_9) (* 2 (* v1_9 v2_9)))) (+ (- (+ v1_10 v2_10) (* 2 (* v1_10 v2_10))) (- (+ v1_11 v2_11) (* 2 (* v1_11 v2_11))))) (+ (+ (- (+ v1_12 v2_12) (* 2 (* v1_12 v2_12))) (- (+ v1_13 v2_13) (* 2 (* v1_13 v2_13)))) (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (+ (- (+ v1_14 v2_14) (* 2 (* v1_14 v2_14))) (- (+ v1_15 v2_15) (* 2 (* v1_15 v2_15)))) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1)))))</t>
+          <t>(Vec (+ (+ (+ (+ (- (+ v1_0 v2_0) (* (+ 0 (+ 0 (+ 0 (+ 0 (* v1_0 v2_0))))) 2)) (- (+ v1_1 v2_1) (* 2 (+ 0 (+ 0 (+ 0 (+ 0 (* v1_1 v2_1)))))))) (+ (- (+ v1_2 v2_2) (* 2 (+ 0 (+ 0 (+ 0 (+ 0 (* v1_2 v2_2))))))) (- (+ v1_3 v2_3) (* 2 (+ 0 (+ 0 (+ 0 (+ 0 (* v1_3 v2_3))))))))) (+ (+ (- (+ v1_4 v2_4) (* 2 (+ 0 (+ 0 (+ 0 (+ 0 (* v1_4 v2_4))))))) (- (+ v1_5 v2_5) (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (* 2 (* v1_5 v2_5))))))))) (+ (- (+ v1_6 v2_6) (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (* 2 (* v1_6 v2_6)))))))) (- (+ v1_7 v2_7) (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (* 2 (* v1_7 v2_7))))))))))) (+ (+ (+ (- (+ v1_8 v2_8) (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (* 2 (* v1_8 v2_8)))))))) (- (+ v1_9 v2_9) (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (* 2 (* v1_9 v2_9))))))))) (+ (- (+ v1_10 v2_10) (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (* 2 (* v1_10 v2_10)))))))) (- (+ v1_11 v2_11) (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (* 2 (* v1_11 v2_11)))))))))) (+ (+ (- (+ v1_12 v2_12) (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (* 2 (* v1_12 v2_12)))))))) (- (+ v1_13 v2_13) (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (* 2 (* v1_13 v2_13))))))))) (+ (- (+ v1_14 v2_14) (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (* 2 (* v1_14 v2_14)))))))) (- (+ v1_15 v2_15) (+ 0 (+ 0 (+ 0 (+ 0 (* 2 (* v1_15 v2_15))))))))))))</t>
         </is>
       </c>
       <c r="E29" t="n">
         <v>19761</v>
       </c>
       <c r="F29" t="n">
-        <v>38409</v>
+        <v>38266</v>
       </c>
       <c r="G29" t="n">
-        <v>-94.37</v>
+        <v>-93.64</v>
       </c>
       <c r="H29" t="n">
         <v>77.55</v>
       </c>
       <c r="I29" t="n">
-        <v>2636.54</v>
+        <v>83.54000000000001</v>
       </c>
       <c r="J29" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K29" t="n">
-        <v>-2336.54</v>
+        <v>216.46</v>
       </c>
       <c r="L29" t="n">
         <v>75</v>
@@ -1681,32 +1681,32 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>(Vec (+ c1_0 (+ c2_0 (* c0_0 (+ c3_0 (* c0_0 c4_0))))) (+ c1_1 (+ c2_1 (* c0_1 (+ c3_1 (* c0_1 c4_1))))) (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ c1_2 (+ c2_2 (* c0_2 (+ c3_2 (* c0_2 c4_2))))) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) (+ c1_3 (+ c2_3 (* c0_3 (+ c3_3 (* c0_3 c4_3))))))</t>
+          <t>(Vec ( + c1_0 ( + c2_0 ( * c0_0 ( + c3_0 ( * c0_0 c4_0 ) ) ) ) ) ( + c1_1 ( + c2_1 ( * c0_1 ( + c3_1 ( * c0_1 c4_1 ) ) ) ) ) ( + c1_2 ( + c2_2 ( * c0_2 ( + c3_2 ( * c0_2 c4_2 ) ) ) ) ) ( + c1_3 ( + c2_3 ( * c0_3 ( + c3_3 ( * c0_3 c4_3 ) ) ) ) ) )</t>
         </is>
       </c>
       <c r="E30" t="n">
         <v>5009</v>
       </c>
       <c r="F30" t="n">
-        <v>23583</v>
+        <v>5009</v>
       </c>
       <c r="G30" t="n">
-        <v>-370.81</v>
+        <v>0</v>
       </c>
       <c r="H30" t="n">
         <v>75.15000000000001</v>
       </c>
       <c r="I30" t="n">
-        <v>163.8</v>
+        <v>75.15000000000001</v>
       </c>
       <c r="J30" t="b">
         <v>0</v>
       </c>
       <c r="K30" t="n">
-        <v>136.2</v>
+        <v>224.85</v>
       </c>
       <c r="L30" t="n">
-        <v>75</v>
+        <v>1</v>
       </c>
     </row>
     <row r="31">
@@ -1723,29 +1723,29 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>(Vec (+ c1_0 (+ c2_0 (* c0_0 (+ c3_0 (* c0_0 c4_0))))) (+ c1_1 (+ c2_1 (* c0_1 (+ c3_1 (* c0_1 c4_1))))) (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ c1_2 (+ c2_2 (* c0_2 (+ c3_2 (* c0_2 c4_2))))) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) (+ c1_3 (+ c2_3 (* c0_3 (+ c3_3 (* c0_3 c4_3))))) (+ c1_4 (+ c2_4 (* c0_4 (+ c3_4 (* c0_4 c4_4))))) (+ c1_5 (+ c2_5 (* c0_5 (+ c3_5 (* c0_5 c4_5))))) (+ c1_6 (+ c2_6 (* c0_6 (+ c3_6 (* c0_6 c4_6))))) (+ c1_7 (+ c2_7 (* c0_7 (+ c3_7 (* c0_7 c4_7))))) (+ c1_8 (+ c2_8 (* c0_8 (+ c3_8 (* c0_8 c4_8))))) (+ c1_9 (+ c2_9 (* c0_9 (+ c3_9 (* c0_9 c4_9))))) (+ c1_10 (+ c2_10 (* c0_10 (+ c3_10 (* c0_10 c4_10))))) (+ c1_11 (+ c2_11 (* c0_11 (+ c3_11 (* c0_11 c4_11))))) (+ c1_12 (+ c2_12 (* c0_12 (+ c3_12 (* c0_12 c4_12))))) (+ c1_13 (+ c2_13 (* c0_13 (+ c3_13 (* c0_13 c4_13))))) (+ c1_14 (+ c2_14 (* c0_14 (+ c3_14 (* c0_14 c4_14))))) (+ c1_15 (+ c2_15 (* c0_15 (+ c3_15 (* c0_15 c4_15))))))</t>
+          <t>(Vec (+ c1_0 (+ c2_0 (* c0_0 (+ c3_0 (+ 0 (+ 0 (+ 0 (+ 0 (* c0_0 c4_0))))))))) (+ c1_1 (+ c2_1 (* c0_1 (+ c3_1 (+ 0 (+ 0 (+ 0 (+ 0 (* c0_1 c4_1))))))))) (+ c1_2 (+ c2_2 (* c0_2 (+ c3_2 (+ 0 (+ 0 (+ 0 (+ 0 (* c0_2 c4_2))))))))) (+ c1_3 (+ c2_3 (* c0_3 (+ c3_3 (+ 0 (+ 0 (+ 0 (+ 0 (* c0_3 c4_3))))))))) (+ c1_4 (+ c2_4 (* c0_4 (+ c3_4 (+ 0 (+ 0 (+ 0 (+ 0 (* c0_4 c4_4))))))))) (+ c1_5 (+ c2_5 (* c0_5 (+ c3_5 (+ 0 (+ 0 (+ 0 (+ 0 (* c0_5 c4_5))))))))) (+ c1_6 (+ c2_6 (* c0_6 (+ c3_6 (+ 0 (+ 0 (+ 0 (+ 0 (* c0_6 c4_6))))))))) (+ c1_7 (+ c2_7 (* c0_7 (+ c3_7 (+ 0 (+ 0 (+ 0 (+ 0 (* c0_7 c4_7))))))))) (+ c1_8 (+ c2_8 (* c0_8 (+ c3_8 (+ 0 (+ 0 (+ 0 (+ 0 (* c0_8 c4_8))))))))) (+ c1_9 (+ c2_9 (* c0_9 (+ c3_9 (+ 0 (+ 0 (+ 0 (+ 0 (* c0_9 c4_9))))))))) (+ c1_10 (+ c2_10 (* c0_10 (+ c3_10 (+ 0 (+ 0 (+ 0 (+ 0 (* c0_10 c4_10))))))))) (+ c1_11 (+ c2_11 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (* c0_11 (+ c3_11 (* c0_11 c4_11))))))))))) (+ c1_12 (+ c2_12 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (* c0_12 (+ c3_12 (* c0_12 c4_12))))))))))) (+ c1_13 (+ c2_13 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (* c0_13 (+ c3_13 (* c0_13 c4_13))))))))))) (+ c1_14 (+ c2_14 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (* c0_14 (+ c3_14 (* c0_14 c4_14))))))))))) (+ c1_15 (+ c2_15 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (* c0_15 (+ c3_15 (* c0_15 c4_15))))))))))))</t>
         </is>
       </c>
       <c r="E31" t="n">
         <v>20009</v>
       </c>
       <c r="F31" t="n">
-        <v>38583</v>
+        <v>38515</v>
       </c>
       <c r="G31" t="n">
-        <v>-92.83</v>
+        <v>-92.48999999999999</v>
       </c>
       <c r="H31" t="n">
         <v>75.15000000000001</v>
       </c>
       <c r="I31" t="n">
-        <v>163.8</v>
+        <v>82.34</v>
       </c>
       <c r="J31" t="b">
         <v>0</v>
       </c>
       <c r="K31" t="n">
-        <v>136.2</v>
+        <v>217.66</v>
       </c>
       <c r="L31" t="n">
         <v>75</v>
@@ -1765,29 +1765,29 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>(Vec (+ (+ (* (- c2_0 c1_0) (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (- c2_0 c1_0))))))))))))))))))))))))))) (* (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (- c2_1 c1_1)))))))))))))))))))))))))) (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (- c2_1 c1_1))))))))))))))))))))))))))) (* (- c2_2 c1_2) (- c2_2 c1_2))))</t>
+          <t>(Vec (+ (+ (* (- c2_0 c1_0) (- c2_0 c1_0)) (* (- c2_1 c1_1) (- c2_1 c1_1))) (* (- (+ (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (+ (+ (+ (+ (+ (+ (+ (+ (+ (* 1 (* 1 (* 1 (* 1 (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ c2_2 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0))))) 0) 0) 0) 0) 0) 0) 0) 0) 0))))))))))))))))))))))))))))))))))))))))))))))))) 0) c1_2) (- c2_2 c1_2))))</t>
         </is>
       </c>
       <c r="E32" t="n">
         <v>2757</v>
       </c>
       <c r="F32" t="n">
-        <v>21307</v>
+        <v>21382</v>
       </c>
       <c r="G32" t="n">
-        <v>-672.83</v>
+        <v>-675.55</v>
       </c>
       <c r="H32" t="n">
         <v>40.57</v>
       </c>
       <c r="I32" t="n">
-        <v>905.09</v>
+        <v>1863.94</v>
       </c>
       <c r="J32" t="b">
         <v>1</v>
       </c>
       <c r="K32" t="n">
-        <v>-605.09</v>
+        <v>-1563.94</v>
       </c>
       <c r="L32" t="n">
         <v>75</v>
@@ -1807,32 +1807,32 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>(Vec (+ (+ (* (- c2_0 c1_0) (- c2_0 c1_0)) (* (- c2_1 c1_1) (- c2_1 c1_1))) (+ (+ (* (* 1 (* 1 (* 1 (* 1 (- c2_2 c1_2))))) (* 1 (* 1 (* 1 (* 1 (- c2_2 c1_2)))))) (* (* 1 (* 1 (* 1 (- c2_3 c1_3)))) (* 1 (* 1 (* 1 (- c2_3 c1_3)))))) (* (- c2_4 c1_4) (* 1 (* 1 (* 1 (* 1 (- c2_4 c1_4)))))))))</t>
+          <t>(Vec ( + ( + ( * ( - c2_0 c1_0 ) ( - c2_0 c1_0 ) ) ( * ( - c2_1 c1_1 ) ( - c2_1 c1_1 ) ) ) ( + ( + ( * ( - c2_2 c1_2 ) ( - c2_2 c1_2 ) ) ( * ( - c2_3 c1_3 ) ( - c2_3 c1_3 ) ) ) ( * ( - c2_4 c1_4 ) ( - c2_4 c1_4 ) ) ) ) )</t>
         </is>
       </c>
       <c r="E33" t="n">
         <v>4758</v>
       </c>
       <c r="F33" t="n">
-        <v>9266</v>
+        <v>4758</v>
       </c>
       <c r="G33" t="n">
-        <v>-94.75</v>
+        <v>0</v>
       </c>
       <c r="H33" t="n">
         <v>41.77</v>
       </c>
       <c r="I33" t="n">
-        <v>180.09</v>
+        <v>41.77</v>
       </c>
       <c r="J33" t="b">
         <v>0</v>
       </c>
       <c r="K33" t="n">
-        <v>119.91</v>
+        <v>258.23</v>
       </c>
       <c r="L33" t="n">
-        <v>19</v>
+        <v>1</v>
       </c>
     </row>
     <row r="34">
@@ -1849,29 +1849,29 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>(Vec (+ (+ (+ (+ (* (- c2_0 c1_0) (- c2_0 c1_0)) (* (- c2_1 c1_1) (- c2_1 c1_1))) (+ (* (- c2_2 c1_2) (- c2_2 c1_2)) (* (- c2_3 c1_3) (- c2_3 c1_3)))) (+ (+ (* (- c2_4 c1_4) (- c2_4 c1_4)) (* (- c2_5 c1_5) (- c2_5 c1_5))) (+ (* (- c2_6 c1_6) (- c2_6 c1_6)) (* (* 1 (* 1 (* 1 (* 1 (* 1 (- c2_7 c1_7)))))) (* 1 (* 1 (* 1 (* 1 (* 1 (- c2_7 c1_7)))))))))) (+ (+ (+ (* (* 1 (* 1 (* 1 (* 1 (- c2_8 c1_8))))) (* 1 (* 1 (* 1 (* 1 (- c2_8 c1_8)))))) (* (* 1 (* 1 (* 1 (* 1 (- c2_9 c1_9))))) (* 1 (* 1 (* 1 (* 1 (- c2_9 c1_9))))))) (+ (* (* 1 (* 1 (* 1 (* 1 (- c2_10 c1_10))))) (* 1 (* 1 (* 1 (* 1 (- c2_10 c1_10)))))) (* (* 1 (* 1 (* 1 (* 1 (- c2_11 c1_11))))) (* 1 (* 1 (* 1 (* 1 (- c2_11 c1_11)))))))) (+ (+ (* (* 1 (* 1 (* 1 (* 1 (- c2_12 c1_12))))) (* 1 (* 1 (* 1 (* 1 (- c2_12 c1_12)))))) (* (* 1 (* 1 (* 1 (* 1 (- c2_13 c1_13))))) (* 1 (* 1 (* 1 (* 1 (- c2_13 c1_13))))))) (+ (* (* 1 (* 1 (* 1 (* 1 (- c2_14 c1_14))))) (* 1 (* 1 (* 1 (* 1 (- c2_14 c1_14)))))) (* (* 1 (* 1 (* 1 (* 1 (- c2_15 c1_15))))) (* 1 (* 1 (* 1 (* 1 (- c2_15 c1_15)))))))))))</t>
+          <t>(Vec (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (+ (* 1 (+ (+ (+ (* (- c2_0 c1_0) (- c2_0 c1_0)) (* (- c2_1 c1_1) (- c2_1 c1_1))) (+ (* (- c2_2 c1_2) (- c2_2 c1_2)) (* (- c2_3 c1_3) (- c2_3 c1_3)))) (+ (+ (* (- c2_4 c1_4) (- c2_4 c1_4)) (* (- c2_5 c1_5) (- c2_5 c1_5))) (+ (* (- c2_6 c1_6) (- c2_6 c1_6)) (* (- c2_7 c1_7) (- c2_7 c1_7)))))) (+ (* 1 (+ (+ (* (- c2_8 c1_8) (- c2_8 c1_8)) (* (- c2_9 c1_9) (- c2_9 c1_9))) (+ (* (- c2_10 c1_10) (- c2_10 c1_10)) (* (- c2_11 c1_11) (- c2_11 c1_11))))) (+ (+ (* (- c2_12 c1_12) (- c2_12 c1_12)) (* (- c2_13 c1_13) (- c2_13 c1_13))) (+ (* (- c2_14 c1_14) (- c2_14 c1_14)) (* (- c2_15 c1_15) (- c2_15 c1_15)))))))))))))))))</t>
         </is>
       </c>
       <c r="E34" t="n">
         <v>15759</v>
       </c>
       <c r="F34" t="n">
-        <v>34269</v>
+        <v>18781</v>
       </c>
       <c r="G34" t="n">
-        <v>-117.46</v>
+        <v>-19.18</v>
       </c>
       <c r="H34" t="n">
         <v>42.97</v>
       </c>
       <c r="I34" t="n">
-        <v>215.87</v>
+        <v>423.36</v>
       </c>
       <c r="J34" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K34" t="n">
-        <v>84.13</v>
+        <v>-123.36</v>
       </c>
       <c r="L34" t="n">
         <v>75</v>
@@ -1891,29 +1891,29 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>(Vec (+ (+ (* v1_0 v2_0) (* v1_1 v2_1)) (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (* v1_2 v2_2) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0)))</t>
+          <t>(Vec (+ (+ (* v1_0 v2_0) (+ (* (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (+ (+ (+ (+ (+ (+ (+ (+ (+ (* 1 (* 1 (* 1 (* 1 (* 1 (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ v1_1 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0)))))) 0) 0) 0) 0) 0) 0) 0) 0) 0)))))))))))))))))))))))))))))))))))))))))))) v2_1) 0)) (* v1_2 v2_2)))</t>
         </is>
       </c>
       <c r="E35" t="n">
         <v>1256</v>
       </c>
       <c r="F35" t="n">
-        <v>19829</v>
+        <v>19878</v>
       </c>
       <c r="G35" t="n">
-        <v>-1478.74</v>
+        <v>-1482.64</v>
       </c>
       <c r="H35" t="n">
         <v>39.37</v>
       </c>
       <c r="I35" t="n">
-        <v>126.83</v>
+        <v>1730.41</v>
       </c>
       <c r="J35" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K35" t="n">
-        <v>173.17</v>
+        <v>-1430.41</v>
       </c>
       <c r="L35" t="n">
         <v>75</v>
@@ -1933,32 +1933,32 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>(Vec (+ (+ (* v1_0 v2_0) (* v1_1 v2_1)) (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (* v1_2 v2_2) (* v1_3 v2_3)) (* v1_4 v2_4)) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0)))</t>
+          <t>(Vec ( + ( + ( * v1_0 v2_0 ) ( * v1_1 v2_1 ) ) ( + ( + ( * v1_2 v2_2 ) ( * v1_3 v2_3 ) ) ( * v1_4 v2_4 ) ) ) )</t>
         </is>
       </c>
       <c r="E36" t="n">
         <v>2257</v>
       </c>
       <c r="F36" t="n">
-        <v>20831</v>
+        <v>2257</v>
       </c>
       <c r="G36" t="n">
-        <v>-822.95</v>
+        <v>0</v>
       </c>
       <c r="H36" t="n">
         <v>40.57</v>
       </c>
       <c r="I36" t="n">
-        <v>129.22</v>
+        <v>40.57</v>
       </c>
       <c r="J36" t="b">
         <v>0</v>
       </c>
       <c r="K36" t="n">
-        <v>170.78</v>
+        <v>259.43</v>
       </c>
       <c r="L36" t="n">
-        <v>75</v>
+        <v>1</v>
       </c>
     </row>
     <row r="37">
@@ -1975,29 +1975,29 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>(Vec (+ (+ (+ (+ (* v1_0 v2_0) (* v1_1 v2_1)) (+ (* v1_2 v2_2) (* v1_3 v2_3))) (+ (+ (* v1_4 v2_4) (* v1_5 v2_5)) (+ (* v1_6 v2_6) (* v1_7 v2_7)))) (+ (+ (+ (* v1_8 v2_8) (* v1_9 v2_9)) (+ (* v1_10 v2_10) (* v1_11 v2_11))) (+ (+ (* v1_12 v2_12) (* v1_13 v2_13)) (+ (* v1_14 v2_14) (* v1_15 v2_15))))))</t>
+          <t>(Vec (+ (+ (+ (+ (* v1_0 v2_0) (* v1_1 v2_1)) (+ (* v1_2 v2_2) (* v1_3 v2_3))) (+ (+ (* v1_4 v2_4) (* v1_5 v2_5)) (+ (* v1_6 v2_6) (* v1_7 v2_7)))) (+ (+ (+ (* v1_8 v2_8) (* v1_9 v2_9)) (+ (* v1_10 v2_10) (* v1_11 v2_11))) (+ (+ (* v1_12 v2_12) (* v1_13 v2_13)) (+ (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (* v1_14 v2_14)))))))))))))))))))))))))))))))))))))) (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (* v1_15 v2_15)))))))))))))))))))))))))))))))))))))))))))</t>
         </is>
       </c>
       <c r="E37" t="n">
         <v>7758</v>
       </c>
       <c r="F37" t="n">
-        <v>7758</v>
+        <v>26295</v>
       </c>
       <c r="G37" t="n">
-        <v>0</v>
+        <v>-238.94</v>
       </c>
       <c r="H37" t="n">
         <v>41.77</v>
       </c>
       <c r="I37" t="n">
-        <v>41.77</v>
+        <v>86.09</v>
       </c>
       <c r="J37" t="b">
         <v>0</v>
       </c>
       <c r="K37" t="n">
-        <v>258.23</v>
+        <v>213.91</v>
       </c>
       <c r="L37" t="n">
         <v>75</v>
@@ -2017,32 +2017,32 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>(Vec (+ in_1_1 (* in_0_1 2)) (+ (+ in_1_2 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (- in_1_0))))))))))))) (+ (* in_0_2 2) (* in_0_0 -2))) (+ (- in_1_1) (* in_0_1 -2)) (+ in_2_1 (+ in_0_1 (* in_1_1 2))) (+ (+ in_2_2 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (- in_2_0))))))))))))) (+ (+ in_0_2 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (- in_0_0)))))))))))) (+ (* in_1_2 2) (* in_1_0 -2)))) (+ (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (- in_2_1)))))))))))) (+ (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (- in_0_1))))))))))) (* in_1_1 -2))) (+ in_1_1 (* in_2_1 2)) (+ (+ in_1_2 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (- in_1_0)))))))))))) (+ (* in_2_2 2) (* in_2_0 -2))) (+ (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (- in_1_1)))))))))))) (* in_2_1 -2)))</t>
+          <t>(Vec ( + in_1_1 ( * in_0_1 2 ) ) ( + ( + in_1_2 ( - in_1_0 ) ) ( + ( * in_0_2 2 ) ( * in_0_0 -2 ) ) ) ( + ( - in_1_1 ) ( * in_0_1 -2 ) ) ( + in_2_1 ( + in_0_1 ( * in_1_1 2 ) ) ) ( + ( + in_2_2 ( - in_2_0 ) ) ( + ( + in_0_2 ( - in_0_0 ) ) ( + ( * in_1_2 2 ) ( * in_1_0 -2 ) ) ) ) ( + ( - in_2_1 ) ( + ( - in_0_1 ) ( * in_1_1 -2 ) ) ) ( + in_1_1 ( * in_2_1 2 ) ) ( + ( + in_1_2 ( - in_1_0 ) ) ( + ( * in_2_2 2 ) ( * in_2_0 -2 ) ) ) ( + ( - in_1_1 ) ( * in_2_1 -2 ) ) )</t>
         </is>
       </c>
       <c r="E38" t="n">
         <v>9757</v>
       </c>
       <c r="F38" t="n">
-        <v>28267</v>
+        <v>9757</v>
       </c>
       <c r="G38" t="n">
-        <v>-189.71</v>
+        <v>0</v>
       </c>
       <c r="H38" t="n">
         <v>40.57</v>
       </c>
       <c r="I38" t="n">
-        <v>52.55</v>
+        <v>40.57</v>
       </c>
       <c r="J38" t="b">
         <v>0</v>
       </c>
       <c r="K38" t="n">
-        <v>247.45</v>
+        <v>259.43</v>
       </c>
       <c r="L38" t="n">
-        <v>75</v>
+        <v>1</v>
       </c>
     </row>
     <row r="39">
@@ -2059,32 +2059,32 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>(Vec (+ in_1_1 (* in_0_1 2)) (+ (+ in_1_2 (+ 0 (+ 0 (+ 0 (- in_1_0))))) (+ (* in_0_2 2) (* in_0_0 -2))) (+ (+ in_1_3 (+ 0 (+ 0 (+ 0 (- in_1_1))))) (+ (* in_0_3 2) (* in_0_1 -2))) (+ (+ in_1_4 (+ 0 (+ 0 (+ 0 (- in_1_2))))) (+ (* in_0_4 2) (* in_0_2 -2))) (+ (- in_1_3) (* in_0_3 -2)) (+ in_2_1 (+ in_0_1 (* in_1_1 2))) (+ (+ in_2_2 (+ 0 (+ 0 (+ 0 (- in_2_0))))) (+ (+ in_0_2 (+ 0 (+ 0 (- in_0_0)))) (+ (* in_1_2 2) (* in_1_0 -2)))) (+ (+ in_2_3 (+ 0 (+ 0 (+ 0 (- in_2_1))))) (+ (+ in_0_3 (+ 0 (+ 0 (- in_0_1)))) (+ (* in_1_3 2) (* in_1_1 -2)))) (+ (+ in_2_4 (+ 0 (+ 0 (+ 0 (- in_2_2))))) (+ (+ in_0_4 (+ 0 (+ 0 (- in_0_2)))) (+ (* in_1_4 2) (* in_1_2 -2)))) (+ (+ 0 (+ 0 (+ 0 (+ 0 (- in_2_3))))) (+ (+ 0 (+ 0 (+ 0 (- in_0_3)))) (* in_1_3 -2))) (+ in_3_1 (+ in_1_1 (* in_2_1 2))) (+ (+ in_3_2 (+ 0 (+ 0 (+ 0 (- in_3_0))))) (+ (+ in_1_2 (+ 0 (+ 0 (- in_1_0)))) (+ (* in_2_2 2) (* in_2_0 -2)))) (+ (+ in_3_3 (+ 0 (+ 0 (+ 0 (- in_3_1))))) (+ (+ in_1_3 (+ 0 (+ 0 (- in_1_1)))) (+ (* in_2_3 2) (* in_2_1 -2)))) (+ (+ in_3_4 (+ 0 (+ 0 (+ 0 (- in_3_2))))) (+ (+ in_1_4 (+ 0 (+ 0 (- in_1_2)))) (+ (* in_2_4 2) (* in_2_2 -2)))) (+ (+ 0 (+ 0 (+ 0 (- in_3_3)))) (+ (+ 0 (+ 0 (- in_1_3))) (* in_2_3 -2))) (+ in_4_1 (+ in_2_1 (* in_3_1 2))) (+ (+ in_4_2 (+ 0 (+ 0 (- in_4_0)))) (+ (+ in_2_2 (+ 0 (- in_2_0))) (+ (* in_3_2 2) (* in_3_0 -2)))) (+ (+ in_4_3 (+ 0 (+ 0 (- in_4_1)))) (+ (+ in_2_3 (+ 0 (- in_2_1))) (+ (* in_3_3 2) (* in_3_1 -2)))) (+ (+ in_4_4 (+ 0 (+ 0 (- in_4_2)))) (+ (+ in_2_4 (+ 0 (- in_2_2))) (+ (* in_3_4 2) (* in_3_2 -2)))) (+ (+ 0 (+ 0 (+ 0 (- in_4_3)))) (+ (+ 0 (+ 0 (- in_2_3))) (* in_3_3 -2))) (+ in_3_1 (* in_4_1 2)) (+ (+ in_3_2 (+ 0 (+ 0 (- in_3_0)))) (+ (* in_4_2 2) (* in_4_0 -2))) (+ (+ in_3_3 (+ 0 (+ 0 (- in_3_1)))) (+ (* in_4_3 2) (* in_4_1 -2))) (+ (+ in_3_4 (+ 0 (+ 0 (- in_3_2)))) (+ (* in_4_4 2) (* in_4_2 -2))) (+ (+ 0 (+ 0 (+ 0 (- in_3_3)))) (* in_4_3 -2)))</t>
+          <t>(Vec ( + in_1_1 ( * in_0_1 2 ) ) ( + ( + in_1_2 ( - in_1_0 ) ) ( + ( * in_0_2 2 ) ( * in_0_0 -2 ) ) ) ( + ( + in_1_3 ( - in_1_1 ) ) ( + ( * in_0_3 2 ) ( * in_0_1 -2 ) ) ) ( + ( + in_1_4 ( - in_1_2 ) ) ( + ( * in_0_4 2 ) ( * in_0_2 -2 ) ) ) ( + ( - in_1_3 ) ( * in_0_3 -2 ) ) ( + in_2_1 ( + in_0_1 ( * in_1_1 2 ) ) ) ( + ( + in_2_2 ( - in_2_0 ) ) ( + ( + in_0_2 ( - in_0_0 ) ) ( + ( * in_1_2 2 ) ( * in_1_0 -2 ) ) ) ) ( + ( + in_2_3 ( - in_2_1 ) ) ( + ( + in_0_3 ( - in_0_1 ) ) ( + ( * in_1_3 2 ) ( * in_1_1 -2 ) ) ) ) ( + ( + in_2_4 ( - in_2_2 ) ) ( + ( + in_0_4 ( - in_0_2 ) ) ( + ( * in_1_4 2 ) ( * in_1_2 -2 ) ) ) ) ( + ( - in_2_3 ) ( + ( - in_0_3 ) ( * in_1_3 -2 ) ) ) ( + in_3_1 ( + in_1_1 ( * in_2_1 2 ) ) ) ( + ( + in_3_2 ( - in_3_0 ) ) ( + ( + in_1_2 ( - in_1_0 ) ) ( + ( * in_2_2 2 ) ( * in_2_0 -2 ) ) ) ) ( + ( + in_3_3 ( - in_3_1 ) ) ( + ( + in_1_3 ( - in_1_1 ) ) ( + ( * in_2_3 2 ) ( * in_2_1 -2 ) ) ) ) ( + ( + in_3_4 ( - in_3_2 ) ) ( + ( + in_1_4 ( - in_1_2 ) ) ( + ( * in_2_4 2 ) ( * in_2_2 -2 ) ) ) ) ( + ( - in_3_3 ) ( + ( - in_1_3 ) ( * in_2_3 -2 ) ) ) ( + in_4_1 ( + in_2_1 ( * in_3_1 2 ) ) ) ( + ( + in_4_2 ( - in_4_0 ) ) ( + ( + in_2_2 ( - in_2_0 ) ) ( + ( * in_3_2 2 ) ( * in_3_0 -2 ) ) ) ) ( + ( + in_4_3 ( - in_4_1 ) ) ( + ( + in_2_3 ( - in_2_1 ) ) ( + ( * in_3_3 2 ) ( * in_3_1 -2 ) ) ) ) ( + ( + in_4_4 ( - in_4_2 ) ) ( + ( + in_2_4 ( - in_2_2 ) ) ( + ( * in_3_4 2 ) ( * in_3_2 -2 ) ) ) ) ( + ( - in_4_3 ) ( + ( - in_2_3 ) ( * in_3_3 -2 ) ) ) ( + in_3_1 ( * in_4_1 2 ) ) ( + ( + in_3_2 ( - in_3_0 ) ) ( + ( * in_4_2 2 ) ( * in_4_0 -2 ) ) ) ( + ( + in_3_3 ( - in_3_1 ) ) ( + ( * in_4_3 2 ) ( * in_4_1 -2 ) ) ) ( + ( + in_3_4 ( - in_3_2 ) ) ( + ( * in_4_4 2 ) ( * in_4_2 -2 ) ) ) ( + ( - in_3_3 ) ( * in_4_3 -2 ) ) )</t>
         </is>
       </c>
       <c r="E39" t="n">
         <v>37757</v>
       </c>
       <c r="F39" t="n">
-        <v>56259</v>
+        <v>37757</v>
       </c>
       <c r="G39" t="n">
-        <v>-49</v>
+        <v>0</v>
       </c>
       <c r="H39" t="n">
         <v>40.57</v>
       </c>
       <c r="I39" t="n">
-        <v>42.97</v>
+        <v>40.57</v>
       </c>
       <c r="J39" t="b">
         <v>0</v>
       </c>
       <c r="K39" t="n">
-        <v>257.03</v>
+        <v>259.43</v>
       </c>
       <c r="L39" t="n">
-        <v>75</v>
+        <v>1</v>
       </c>
     </row>
     <row r="40">
@@ -2101,29 +2101,29 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>(Vec (+ (+ (* a_0_0 b_0_0) (* a_0_1 b_1_0)) (+ (* a_0_2 b_2_0) (* a_0_3 b_3_0))) (+ (+ (* a_0_0 b_0_1) (* a_0_1 b_1_1)) (+ (* a_0_2 b_2_1) (* a_0_3 b_3_1))) (+ (+ (* a_0_0 b_0_2) (* a_0_1 b_1_2)) (+ (* a_0_2 b_2_2) (* a_0_3 b_3_2))) (+ (+ (* a_0_0 b_0_3) (* a_0_1 b_1_3)) (+ (* a_0_2 b_2_3) (* a_0_3 b_3_3))) (+ (+ (* a_1_0 b_0_0) (* a_1_1 b_1_0)) (+ (* a_1_2 b_2_0) (* a_1_3 b_3_0))) (+ (+ (* a_1_0 b_0_1) (* a_1_1 b_1_1)) (+ (* a_1_2 b_2_1) (* a_1_3 b_3_1))) (+ (+ (* a_1_0 b_0_2) (* a_1_1 b_1_2)) (+ (* a_1_2 b_2_2) (* a_1_3 b_3_2))) (+ (+ (* a_1_0 b_0_3) (* a_1_1 b_1_3)) (+ (* a_1_2 b_2_3) (* a_1_3 b_3_3))) (+ (+ (* a_2_0 b_0_0) (* a_2_1 b_1_0)) (+ (* a_2_2 b_2_0) (* a_2_3 b_3_0))) (+ (+ (* a_2_0 b_0_1) (* a_2_1 b_1_1)) (+ (* a_2_2 b_2_1) (* a_2_3 b_3_1))) (+ (+ (* a_2_0 b_0_2) (* a_2_1 b_1_2)) (+ (* a_2_2 b_2_2) (* a_2_3 b_3_2))) (+ (+ (* a_2_0 b_0_3) (* a_2_1 b_1_3)) (+ (* a_2_2 b_2_3) (* a_2_3 b_3_3))) (+ (+ (* a_3_0 b_0_0) (* a_3_1 b_1_0)) (+ (* a_3_2 b_2_0) (* a_3_3 b_3_0))) (+ (+ (* a_3_0 b_0_1) (* a_3_1 b_1_1)) (+ (* a_3_2 b_2_1) (* a_3_3 b_3_1))) (+ (+ (* a_3_0 b_0_2) (* a_3_1 b_1_2)) (+ (* a_3_2 b_2_2) (* a_3_3 b_3_2))) (+ (+ (* a_3_0 b_0_3) (* a_3_1 b_1_3)) (+ (* a_3_2 b_2_3) (* a_3_3 b_3_3))))</t>
+          <t>(Vec (+ (+ (* a_0_0 b_0_0) (* a_0_1 b_1_0)) (+ (* a_0_2 b_2_0) (* a_0_3 b_3_0))) (+ (+ (* a_0_0 b_0_1) (* a_0_1 b_1_1)) (+ (* a_0_2 b_2_1) (* a_0_3 b_3_1))) (+ (+ (* a_0_0 b_0_2) (* a_0_1 b_1_2)) (+ (* a_0_2 b_2_2) (* a_0_3 b_3_2))) (+ (+ (* a_0_0 b_0_3) (* a_0_1 b_1_3)) (+ (+ 0 (+ 0 (* a_0_2 b_2_3))) (+ 0 (+ 0 (* a_0_3 b_3_3))))) (+ (+ (+ 0 (+ 0 (* a_1_0 b_0_0))) (+ 0 (+ 0 (* a_1_1 b_1_0)))) (+ (+ 0 (+ 0 (* a_1_2 b_2_0))) (+ 0 (+ 0 (* a_1_3 b_3_0))))) (+ (+ (+ 0 (+ 0 (* a_1_0 b_0_1))) (+ 0 (+ 0 (* a_1_1 b_1_1)))) (+ (+ 0 (+ 0 (* a_1_2 b_2_1))) (+ 0 (+ 0 (* a_1_3 b_3_1))))) (+ (+ (+ 0 (+ 0 (* a_1_0 b_0_2))) (+ 0 (+ 0 (* a_1_1 b_1_2)))) (+ (+ 0 (+ 0 (* a_1_2 b_2_2))) (+ 0 (+ 0 (* a_1_3 b_3_2))))) (+ (+ (+ 0 (+ 0 (* a_1_0 b_0_3))) (+ 0 (+ 0 (* a_1_1 b_1_3)))) (+ (+ 0 (+ 0 (* a_1_2 b_2_3))) (+ 0 (+ 0 (* a_1_3 b_3_3))))) (+ (+ (+ 0 (+ 0 (* a_2_0 b_0_0))) (+ 0 (+ 0 (* a_2_1 b_1_0)))) (+ (+ 0 (+ 0 (* a_2_2 b_2_0))) (+ 0 (+ 0 (* a_2_3 b_3_0))))) (+ (+ (+ 0 (+ 0 (* a_2_0 b_0_1))) (+ 0 (+ 0 (* a_2_1 b_1_1)))) (+ (+ 0 (* a_2_2 b_2_1)) (+ 0 (* a_2_3 b_3_1)))) (+ (+ (+ 0 (* a_2_0 b_0_2)) (+ 0 (* a_2_1 b_1_2))) (+ (+ 0 (* a_2_2 b_2_2)) (+ 0 (* a_2_3 b_3_2)))) (+ (+ (+ 0 (* a_2_0 b_0_3)) (+ 0 (* a_2_1 b_1_3))) (+ (+ 0 (* a_2_2 b_2_3)) (+ 0 (* a_2_3 b_3_3)))) (+ (+ (+ 0 (* a_3_0 b_0_0)) (+ 0 (* a_3_1 b_1_0))) (+ (+ 0 (* a_3_2 b_2_0)) (+ 0 (* a_3_3 b_3_0)))) (+ (+ (+ 0 (* a_3_0 b_0_1)) (+ 0 (* a_3_1 b_1_1))) (+ (+ 0 (* a_3_2 b_2_1)) (+ 0 (* a_3_3 b_3_1)))) (+ (+ (+ 0 (* a_3_0 b_0_2)) (+ 0 (* a_3_1 b_1_2))) (+ (+ 0 (* a_3_2 b_2_2)) (+ 0 (* a_3_3 b_3_2)))) (+ (+ (+ 0 (* a_3_0 b_0_3)) (+ 0 (* a_3_1 b_1_3))) (+ (+ 0 (* a_3_2 b_2_3)) (+ 0 (* a_3_3 b_3_3)))))</t>
         </is>
       </c>
       <c r="E40" t="n">
         <v>28006</v>
       </c>
       <c r="F40" t="n">
-        <v>28006</v>
+        <v>46508</v>
       </c>
       <c r="G40" t="n">
-        <v>0</v>
+        <v>-66.06</v>
       </c>
       <c r="H40" t="n">
         <v>39.37</v>
       </c>
       <c r="I40" t="n">
-        <v>39.37</v>
+        <v>41.77</v>
       </c>
       <c r="J40" t="b">
         <v>0</v>
       </c>
       <c r="K40" t="n">
-        <v>260.63</v>
+        <v>258.23</v>
       </c>
       <c r="L40" t="n">
         <v>75</v>
@@ -2143,32 +2143,32 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>(Vec (+ (* (+ (* (+ (* o4 (- 1 c34)) (* c34 o3)) (- 1 c23)) (* c23 (+ (* o4 (- 1 c24)) (* c24 o2)))) (- 1 c12)) (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (* c12 (+ (* (+ (* o4 (- 1 c34)) (* c34 o3)) (- 1 c13)) (* c13 (+ (* o4 (- 1 c14)) (* c14 o1))))) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0)))</t>
+          <t>(Vec ( + ( * ( + ( * ( + ( * o4 ( - 1 c34 ) ) ( * c34 o3 ) ) ( - 1 c23 ) ) ( * c23 ( + ( * o4 ( - 1 c24 ) ) ( * c24 o2 ) ) ) ) ( - 1 c12 ) ) ( * c12 ( + ( * ( + ( * o4 ( - 1 c34 ) ) ( * c34 o3 ) ) ( - 1 c13 ) ) ( * c13 ( + ( * o4 ( - 1 c14 ) ) ( * c14 o1 ) ) ) ) ) ) )</t>
         </is>
       </c>
       <c r="E41" t="n">
         <v>7012</v>
       </c>
       <c r="F41" t="n">
-        <v>25586</v>
+        <v>7012</v>
       </c>
       <c r="G41" t="n">
-        <v>-264.89</v>
+        <v>0</v>
       </c>
       <c r="H41" t="n">
         <v>110.93</v>
       </c>
       <c r="I41" t="n">
-        <v>199.58</v>
+        <v>110.93</v>
       </c>
       <c r="J41" t="b">
         <v>0</v>
       </c>
       <c r="K41" t="n">
-        <v>100.42</v>
+        <v>189.07</v>
       </c>
       <c r="L41" t="n">
-        <v>75</v>
+        <v>1</v>
       </c>
     </row>
     <row r="42">
@@ -2269,29 +2269,29 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>(VecMul (Vec (+ (* (* (* x9604 x9605) (* x9607 x9608)) (* (* x9611 x9612) (* x9614 x9615))) (* (* (* x9619 x9620) (* x9622 x9623)) (* (* x9626 x9627) (* x9629 x9630)))) (+ (* (* (* x9649 x9650) (* x9652 x9653)) (* (* x9656 x9657) (* x9659 x9660))) (* (* (* x9634 x9635) (* x9637 x9638)) (* (* x9641 x9642) (* x9644 x9645))))) (&lt;&lt; (Vec (+ (* (* (* x9604 x9605) (* x9607 x9608)) (* (* x9611 x9612) (* x9614 x9615))) (* (* (* x9619 x9620) (* x9622 x9623)) (* (* x9626 x9627) (* x9629 x9630)))) (+ (* (* (* x9649 x9650) (* x9652 x9653)) (* (* x9656 x9657) (* x9659 x9660))) (* (* (* x9634 x9635) (* x9637 x9638)) (* (* x9641 x9642) (* x9644 x9645))))) 1))</t>
+          <t>(Vec (* (+ (* (* (* x9604 x9605) (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (* x9607 x9608))))))) (* (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (* x9611 x9612)))))) (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (* x9614 x9615)))))))) (* (* (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (* x9619 x9620)))))) (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (* x9622 x9623))))))) (* (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (* x9626 x9627)))))) (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (* x9629 x9630))))))))) (+ (* (* (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (* x9634 x9635)))))) (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (* x9637 x9638))))))) (* (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (* x9641 x9642)))))) (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (* x9644 x9645)))))))) (* (* (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (* x9649 x9650)))))) (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (* x9652 x9653))))))) (* (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (* x9656 x9657)))))) (+ 0 (+ 0 (+ 0 (+ 0 (* x9659 x9660))))))))))</t>
         </is>
       </c>
       <c r="E44" t="n">
         <v>7761</v>
       </c>
       <c r="F44" t="n">
-        <v>7663</v>
+        <v>26266</v>
       </c>
       <c r="G44" t="n">
-        <v>1.26</v>
+        <v>-238.44</v>
       </c>
       <c r="H44" t="n">
         <v>141.92</v>
       </c>
       <c r="I44" t="n">
-        <v>143.12</v>
+        <v>147.91</v>
       </c>
       <c r="J44" t="b">
         <v>0</v>
       </c>
       <c r="K44" t="n">
-        <v>156.88</v>
+        <v>152.09</v>
       </c>
       <c r="L44" t="n">
         <v>75</v>
@@ -2311,29 +2311,29 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>(Vec (+ (+ in_1_1 in_1_0) (+ in_0_1 in_0_0)) (+ (+ (+ in_1_2 in_1_1) (+ in_1_0 in_0_2)) (+ in_0_1 in_0_0)) (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ in_1_2 in_1_1) (+ in_0_2 in_0_1)) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) (+ (+ (+ in_2_1 in_2_0) (+ in_1_1 in_1_0)) (+ in_0_1 in_0_0)) (+ (+ (+ in_2_2 (+ in_2_1 in_2_0)) (+ in_1_2 in_1_1)) (+ (+ in_1_0 in_0_2) (+ in_0_1 in_0_0))) (+ (+ (+ in_2_2 in_2_1) (+ in_1_2 in_1_1)) (+ in_0_2 in_0_1)) (+ (+ in_2_1 in_2_0) (+ in_1_1 in_1_0)) (+ (+ (+ in_2_2 in_2_1) (+ in_2_0 in_1_2)) (+ in_1_1 in_1_0)) (+ (+ in_2_2 in_2_1) (+ in_1_2 in_1_1)))</t>
+          <t>(Vec (* 1 (* 1 (* 1 (* 1 (* 1 (+ (+ in_1_1 in_1_0) (+ in_0_1 in_0_0))))))) (* 1 (* 1 (* 1 (* 1 (* 1 (+ (+ (+ in_1_2 in_1_1) (+ in_1_0 in_0_2)) (+ in_0_1 in_0_0))))))) (* 1 (* 1 (* 1 (* 1 (+ (* 1 (+ in_1_2 in_1_1)) (* 1 (+ in_0_2 in_0_1))))))) (* 1 (* 1 (* 1 (* 1 (* 1 (+ (+ (+ in_2_1 in_2_0) (+ in_1_1 in_1_0)) (+ in_0_1 in_0_0))))))) (* 1 (* 1 (* 1 (* 1 (* 1 (+ (+ (+ in_2_2 (+ in_2_1 in_2_0)) (+ in_1_2 in_1_1)) (+ (+ in_1_0 in_0_2) (+ in_0_1 in_0_0)))))))) (* 1 (* 1 (* 1 (* 1 (* 1 (+ (+ (+ in_2_2 in_2_1) (+ in_1_2 in_1_1)) (+ in_0_2 in_0_1))))))) (* 1 (* 1 (* 1 (* 1 (* 1 (+ (+ in_2_1 in_2_0) (+ in_1_1 in_1_0))))))) (* 1 (* 1 (* 1 (* 1 (* 1 (+ (+ (+ in_2_2 in_2_1) (+ in_2_0 in_1_2)) (+ in_1_1 in_1_0))))))) (* 1 (* 1 (* 1 (* 1 (* 1 (+ (+ in_2_2 in_2_1) (+ in_1_2 in_1_1))))))))</t>
         </is>
       </c>
       <c r="E45" t="n">
         <v>10006</v>
       </c>
       <c r="F45" t="n">
-        <v>28578</v>
+        <v>21516</v>
       </c>
       <c r="G45" t="n">
-        <v>-185.61</v>
+        <v>-115.03</v>
       </c>
       <c r="H45" t="n">
         <v>7.19</v>
       </c>
       <c r="I45" t="n">
-        <v>93.44</v>
+        <v>180.09</v>
       </c>
       <c r="J45" t="b">
         <v>0</v>
       </c>
       <c r="K45" t="n">
-        <v>306.56</v>
+        <v>219.91</v>
       </c>
       <c r="L45" t="n">
         <v>75</v>
@@ -2353,32 +2353,32 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>(Vec (+ (+ in_1_1 in_1_0) (+ in_0_1 in_0_0)) (+ (+ (+ in_1_2 in_1_1) (+ in_1_0 in_0_2)) (+ in_0_1 in_0_0)) (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ in_1_3 in_1_2) (+ in_1_1 in_0_3)) (+ in_0_2 in_0_1)) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) (+ (+ (+ in_1_4 in_1_3) (+ in_1_2 in_0_4)) (+ in_0_3 in_0_2)) (+ (+ in_1_4 in_1_3) (+ in_0_4 in_0_3)) (+ (+ (+ in_2_1 in_2_0) (+ in_1_1 in_1_0)) (+ in_0_1 in_0_0)) (+ (+ (+ in_2_2 (+ in_2_1 in_2_0)) (+ in_1_2 in_1_1)) (+ (+ in_1_0 in_0_2) (+ in_0_1 in_0_0))) (+ (+ (+ in_2_3 (+ in_2_2 in_2_1)) (+ in_1_3 in_1_2)) (+ (+ in_1_1 in_0_3) (+ in_0_2 in_0_1))) (+ (+ (+ in_2_4 (+ in_2_3 in_2_2)) (+ in_1_4 in_1_3)) (+ (+ in_1_2 in_0_4) (+ in_0_3 in_0_2))) (+ (+ (+ in_2_4 in_2_3) (+ in_1_4 in_1_3)) (+ in_0_4 in_0_3)) (+ (+ (+ in_3_1 in_3_0) (+ in_2_1 in_2_0)) (+ in_1_1 in_1_0)) (+ (+ (+ in_3_2 (+ in_3_1 in_3_0)) (+ in_2_2 in_2_1)) (+ (+ in_2_0 in_1_2) (+ in_1_1 in_1_0))) (+ (+ (+ in_3_3 (+ in_3_2 in_3_1)) (+ in_2_3 in_2_2)) (+ (+ in_2_1 in_1_3) (+ in_1_2 in_1_1))) (+ (+ (+ in_3_4 (+ in_3_3 in_3_2)) (+ in_2_4 in_2_3)) (+ (+ in_2_2 in_1_4) (+ in_1_3 in_1_2))) (+ (+ (+ in_3_4 in_3_3) (+ in_2_4 in_2_3)) (+ in_1_4 in_1_3)) (+ (+ (+ in_4_1 in_4_0) (+ in_3_1 in_3_0)) (+ in_2_1 in_2_0)) (+ (+ (+ in_4_2 (+ in_4_1 in_4_0)) (+ in_3_2 in_3_1)) (+ (+ in_3_0 in_2_2) (+ in_2_1 in_2_0))) (+ (+ (+ in_4_3 (+ in_4_2 in_4_1)) (+ in_3_3 in_3_2)) (+ (+ in_3_1 in_2_3) (+ in_2_2 in_2_1))) (+ (+ (+ in_4_4 (+ in_4_3 in_4_2)) (+ in_3_4 in_3_3)) (+ (+ in_3_2 in_2_4) (+ in_2_3 in_2_2))) (+ (+ (+ in_4_4 in_4_3) (+ in_3_4 in_3_3)) (+ in_2_4 in_2_3)) (+ (+ in_4_1 in_4_0) (+ in_3_1 in_3_0)) (+ (+ (+ in_4_2 in_4_1) (+ in_4_0 in_3_2)) (+ in_3_1 in_3_0)) (+ (+ (+ in_4_3 in_4_2) (+ in_4_1 in_3_3)) (+ in_3_2 in_3_1)) (+ (+ (+ in_4_4 in_4_3) (+ in_4_2 in_3_4)) (+ in_3_3 in_3_2)) (+ (+ in_4_4 in_4_3) (+ in_3_4 in_3_3)))</t>
+          <t>(Vec ( + ( + in_1_1 in_1_0 ) ( + in_0_1 in_0_0 ) ) ( + ( + ( + in_1_2 in_1_1 ) ( + in_1_0 in_0_2 ) ) ( + in_0_1 in_0_0 ) ) ( + ( + ( + in_1_3 in_1_2 ) ( + in_1_1 in_0_3 ) ) ( + in_0_2 in_0_1 ) ) ( + ( + ( + in_1_4 in_1_3 ) ( + in_1_2 in_0_4 ) ) ( + in_0_3 in_0_2 ) ) ( + ( + in_1_4 in_1_3 ) ( + in_0_4 in_0_3 ) ) ( + ( + ( + in_2_1 in_2_0 ) ( + in_1_1 in_1_0 ) ) ( + in_0_1 in_0_0 ) ) ( + ( + ( + in_2_2 ( + in_2_1 in_2_0 ) ) ( + in_1_2 in_1_1 ) ) ( + ( + in_1_0 in_0_2 ) ( + in_0_1 in_0_0 ) ) ) ( + ( + ( + in_2_3 ( + in_2_2 in_2_1 ) ) ( + in_1_3 in_1_2 ) ) ( + ( + in_1_1 in_0_3 ) ( + in_0_2 in_0_1 ) ) ) ( + ( + ( + in_2_4 ( + in_2_3 in_2_2 ) ) ( + in_1_4 in_1_3 ) ) ( + ( + in_1_2 in_0_4 ) ( + in_0_3 in_0_2 ) ) ) ( + ( + ( + in_2_4 in_2_3 ) ( + in_1_4 in_1_3 ) ) ( + in_0_4 in_0_3 ) ) ( + ( + ( + in_3_1 in_3_0 ) ( + in_2_1 in_2_0 ) ) ( + in_1_1 in_1_0 ) ) ( + ( + ( + in_3_2 ( + in_3_1 in_3_0 ) ) ( + in_2_2 in_2_1 ) ) ( + ( + in_2_0 in_1_2 ) ( + in_1_1 in_1_0 ) ) ) ( + ( + ( + in_3_3 ( + in_3_2 in_3_1 ) ) ( + in_2_3 in_2_2 ) ) ( + ( + in_2_1 in_1_3 ) ( + in_1_2 in_1_1 ) ) ) ( + ( + ( + in_3_4 ( + in_3_3 in_3_2 ) ) ( + in_2_4 in_2_3 ) ) ( + ( + in_2_2 in_1_4 ) ( + in_1_3 in_1_2 ) ) ) ( + ( + ( + in_3_4 in_3_3 ) ( + in_2_4 in_2_3 ) ) ( + in_1_4 in_1_3 ) ) ( + ( + ( + in_4_1 in_4_0 ) ( + in_3_1 in_3_0 ) ) ( + in_2_1 in_2_0 ) ) ( + ( + ( + in_4_2 ( + in_4_1 in_4_0 ) ) ( + in_3_2 in_3_1 ) ) ( + ( + in_3_0 in_2_2 ) ( + in_2_1 in_2_0 ) ) ) ( + ( + ( + in_4_3 ( + in_4_2 in_4_1 ) ) ( + in_3_3 in_3_2 ) ) ( + ( + in_3_1 in_2_3 ) ( + in_2_2 in_2_1 ) ) ) ( + ( + ( + in_4_4 ( + in_4_3 in_4_2 ) ) ( + in_3_4 in_3_3 ) ) ( + ( + in_3_2 in_2_4 ) ( + in_2_3 in_2_2 ) ) ) ( + ( + ( + in_4_4 in_4_3 ) ( + in_3_4 in_3_3 ) ) ( + in_2_4 in_2_3 ) ) ( + ( + in_4_1 in_4_0 ) ( + in_3_1 in_3_0 ) ) ( + ( + ( + in_4_2 in_4_1 ) ( + in_4_0 in_3_2 ) ) ( + in_3_1 in_3_0 ) ) ( + ( + ( + in_4_3 in_4_2 ) ( + in_4_1 in_3_3 ) ) ( + in_3_2 in_3_1 ) ) ( + ( + ( + in_4_4 in_4_3 ) ( + in_4_2 in_3_4 ) ) ( + in_3_3 in_3_2 ) ) ( + ( + in_4_4 in_4_3 ) ( + in_3_4 in_3_3 ) ) )</t>
         </is>
       </c>
       <c r="E46" t="n">
         <v>36006</v>
       </c>
       <c r="F46" t="n">
-        <v>54579</v>
+        <v>36006</v>
       </c>
       <c r="G46" t="n">
-        <v>-51.58</v>
+        <v>0</v>
       </c>
       <c r="H46" t="n">
         <v>7.19</v>
       </c>
       <c r="I46" t="n">
-        <v>94.64</v>
+        <v>7.19</v>
       </c>
       <c r="J46" t="b">
         <v>0</v>
       </c>
       <c r="K46" t="n">
-        <v>305.36</v>
+        <v>392.81</v>
       </c>
       <c r="L46" t="n">
-        <v>75</v>
+        <v>1</v>
       </c>
     </row>
     <row r="47">
@@ -2395,29 +2395,29 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>(Vec (+ v2_0 (+ 2 (* v1_0 5))) (+ v2_1 (+ 2 (* v1_1 5))) (+ v2_2 (+ 2 (* v1_2 5))) (+ (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* v2_3 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) (+ 2 (* v1_3 5))) (+ v2_4 (+ 2 (* v1_4 5))) (+ v2_5 (+ 2 (* v1_5 5))) (+ v2_6 (+ 2 (* v1_6 5))) (+ v2_7 (+ 2 (* v1_7 5))))</t>
+          <t>(Vec (+ v2_0 (+ 2 (* v1_0 5))) (+ v2_1 (+ 2 (* v1_1 5))) (+ v2_2 (+ 2 (* v1_2 5))) (+ v2_3 (+ 2 (* v1_3 5))) (+ v2_4 (+ 2 (* v1_4 5))) (+ v2_5 (+ 2 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (* v1_5 5)))))))))))))))))))))))))))) (+ v2_6 (+ 2 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (* v1_6 5)))))))))))))))))))))))))))) (+ v2_7 (+ 2 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (* v1_7 5))))))))))))))))))))))))))))</t>
         </is>
       </c>
       <c r="E47" t="n">
         <v>6006</v>
       </c>
       <c r="F47" t="n">
-        <v>24651</v>
+        <v>24531</v>
       </c>
       <c r="G47" t="n">
-        <v>-310.44</v>
+        <v>-308.44</v>
       </c>
       <c r="H47" t="n">
         <v>39.37</v>
       </c>
       <c r="I47" t="n">
-        <v>2562.58</v>
+        <v>69.31999999999999</v>
       </c>
       <c r="J47" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K47" t="n">
-        <v>-2162.58</v>
+        <v>330.68</v>
       </c>
       <c r="L47" t="n">
         <v>75</v>
@@ -2437,29 +2437,29 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>(Vec (+ v2_0 (+ 2 (* v1_0 5))) (+ v2_1 (+ 2 (* v1_1 5))) (+ v2_2 (+ 2 (* v1_2 5))) (+ v2_3 (+ 2 (* v1_3 5))) (+ v2_4 (+ 2 (* v1_4 5))) (+ v2_5 (+ 2 (* v1_5 5))) (+ v2_6 (+ 2 (* v1_6 5))) (+ v2_7 (+ 2 (* v1_7 5))) (+ v2_8 (+ 2 (* v1_8 5))) (+ v2_9 (+ 2 (* v1_9 5))) (+ v2_10 (+ 2 (* v1_10 5))) (+ v2_11 (+ 2 (* v1_11 5))) (+ v2_12 (+ 2 (* v1_12 5))) (+ v2_13 (+ 2 (* v1_13 5))) (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (+ v2_14 (+ 2 (* v1_14 5))) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) (+ v2_15 (+ 2 (* v1_15 5))) (+ v2_16 (+ 2 (* v1_16 5))) (+ v2_17 (+ 2 (* v1_17 5))) (+ v2_18 (+ 2 (* v1_18 5))) (+ v2_19 (+ 2 (* v1_19 5))) (+ v2_20 (+ 2 (* v1_20 5))) (+ v2_21 (+ 2 (* v1_21 5))) (+ v2_22 (+ 2 (* v1_22 5))) (+ v2_23 (+ 2 (* v1_23 5))) (+ v2_24 (+ 2 (* v1_24 5))) (+ v2_25 (+ 2 (* v1_25 5))) (+ v2_26 (+ 2 (* v1_26 5))) (+ v2_27 (+ 2 (* v1_27 5))) (+ v2_28 (+ 2 (* v1_28 5))) (+ v2_29 (+ 2 (* v1_29 5))) (+ v2_30 (+ 2 (* v1_30 5))) (+ v2_31 (+ 2 (* v1_31 5))))</t>
+          <t>(Vec (+ v2_0 (+ 2 (* v1_0 5))) (+ v2_1 (+ 2 (* v1_1 5))) (+ v2_2 (+ 2 (* v1_2 5))) (+ v2_3 (+ 2 (* v1_3 5))) (+ v2_4 (+ 2 (* v1_4 5))) (+ v2_5 (+ 2 (+ 0 (+ 0 (+ 0 (* v1_5 5)))))) (+ v2_6 (+ 2 (+ 0 (+ 0 (+ 0 (* v1_6 5)))))) (+ v2_7 (+ 2 (+ 0 (+ 0 (+ 0 (* v1_7 5)))))) (+ v2_8 (+ 2 (+ 0 (+ 0 (+ 0 (* v1_8 5)))))) (+ v2_9 (+ 2 (+ 0 (+ 0 (+ 0 (* v1_9 5)))))) (+ v2_10 (+ 2 (+ 0 (+ 0 (+ 0 (* v1_10 5)))))) (+ v2_11 (+ 2 (+ 0 (+ 0 (+ 0 (* v1_11 5)))))) (+ v2_12 (+ 2 (+ 0 (+ 0 (+ 0 (* v1_12 5)))))) (+ v2_13 (+ 2 (+ 0 (+ 0 (+ 0 (* v1_13 5)))))) (+ v2_14 (+ 2 (+ 0 (+ 0 (+ 0 (* v1_14 5)))))) (+ v2_15 (+ 2 (+ 0 (+ 0 (+ 0 (* v1_15 5)))))) (+ v2_16 (+ 2 (+ 0 (+ 0 (+ 0 (* v1_16 5)))))) (+ v2_17 (+ 2 (+ 0 (+ 0 (+ 0 (* v1_17 5)))))) (+ v2_18 (+ 2 (+ 0 (+ 0 (+ 0 (* v1_18 5)))))) (+ v2_19 (+ 2 (+ 0 (+ 0 (+ 0 (* v1_19 5)))))) (+ v2_20 (+ 2 (+ 0 (+ 0 (+ 0 (* v1_20 5)))))) (+ v2_21 (+ 2 (+ 0 (+ 0 (+ 0 (* v1_21 5)))))) (+ v2_22 (+ 2 (+ 0 (+ 0 (+ 0 (* v1_22 5)))))) (+ v2_23 (+ 2 (+ 0 (+ 0 (+ 0 (* v1_23 5)))))) (+ v2_24 (+ 2 (+ 0 (+ 0 (+ 0 (* v1_24 5)))))) (+ v2_25 (+ 2 (+ 0 (+ 0 (* v1_25 5))))) (+ v2_26 (+ 2 (+ 0 (+ 0 (* v1_26 5))))) (+ v2_27 (+ 2 (+ 0 (+ 0 (* v1_27 5))))) (+ v2_28 (+ 2 (+ 0 (+ 0 (* v1_28 5))))) (+ v2_29 (+ 2 (+ 0 (+ 0 (* v1_29 5))))) (+ v2_30 (+ 2 (+ 0 (+ 0 (* v1_30 5))))) (+ v2_31 (+ 2 (+ 0 (+ 0 (* v1_31 5))))))</t>
         </is>
       </c>
       <c r="E48" t="n">
         <v>24006</v>
       </c>
       <c r="F48" t="n">
-        <v>42654</v>
+        <v>42509</v>
       </c>
       <c r="G48" t="n">
-        <v>-77.68000000000001</v>
+        <v>-77.08</v>
       </c>
       <c r="H48" t="n">
         <v>39.37</v>
       </c>
       <c r="I48" t="n">
-        <v>2598.36</v>
+        <v>42.97</v>
       </c>
       <c r="J48" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K48" t="n">
-        <v>-2198.36</v>
+        <v>357.03</v>
       </c>
       <c r="L48" t="n">
         <v>75</v>
@@ -2479,29 +2479,29 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>(Vec (+ (+ (- (+ v1_0 v2_0) (* (* v1_0 v2_0) 2)) (- (+ v1_1 v2_1) (* 2 (* v1_1 v2_1)))) (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (- (+ v1_2 v2_2) (* 2 (* v1_2 v2_2))) (- (+ v1_3 v2_3) (* 2 (* v1_3 v2_3)))) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0)))</t>
+          <t>(Vec (+ (+ (- (+ v1_0 v2_0) (* (* v1_0 v2_0) 2)) (- (+ v1_1 v2_1) (* 2 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (* v1_1 v2_1)))))))))))))))))))))))))))))))))))))))))))))))))))))))) (+ (- (+ v1_2 v2_2) (* 2 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (* v1_2 v2_2)))))))))))))) (- (+ v1_3 v2_3) (* 2 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (* v1_3 v2_3)))))))))))))))))</t>
         </is>
       </c>
       <c r="E49" t="n">
         <v>4759</v>
       </c>
       <c r="F49" t="n">
-        <v>23333</v>
+        <v>23311</v>
       </c>
       <c r="G49" t="n">
-        <v>-390.29</v>
+        <v>-389.83</v>
       </c>
       <c r="H49" t="n">
         <v>75.15000000000001</v>
       </c>
       <c r="I49" t="n">
-        <v>163.8</v>
+        <v>137.45</v>
       </c>
       <c r="J49" t="b">
         <v>0</v>
       </c>
       <c r="K49" t="n">
-        <v>236.2</v>
+        <v>262.55</v>
       </c>
       <c r="L49" t="n">
         <v>75</v>
@@ -2521,32 +2521,32 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>(Vec (+ (+ (+ (- (+ v1_0 v2_0) (* (* v1_0 v2_0) 2)) (- (+ v1_1 v2_1) (* 2 (* v1_1 v2_1)))) (+ (- (+ v1_2 v2_2) (* 2 (* v1_2 v2_2))) (- (+ v1_3 v2_3) (* 2 (* v1_3 v2_3))))) (+ (+ (- (+ v1_4 v2_4) (* 2 (* v1_4 v2_4))) (* 1 (* 1 (* 1 (* 1 (- (+ v1_5 v2_5) (* 2 (* v1_5 v2_5)))))))) (* 1 (* 1 (* 1 (+ (- (+ v1_6 v2_6) (* 2 (* v1_6 v2_6))) (- (+ v1_7 v2_7) (* 2 (* v1_7 v2_7))))))))))</t>
+          <t>(Vec ( + ( + ( + ( - ( + v1_0 v2_0 ) ( * ( * v1_0 v2_0 ) 2 ) ) ( - ( + v1_1 v2_1 ) ( * 2 ( * v1_1 v2_1 ) ) ) ) ( + ( - ( + v1_2 v2_2 ) ( * 2 ( * v1_2 v2_2 ) ) ) ( - ( + v1_3 v2_3 ) ( * 2 ( * v1_3 v2_3 ) ) ) ) ) ( + ( + ( - ( + v1_4 v2_4 ) ( * 2 ( * v1_4 v2_4 ) ) ) ( - ( + v1_5 v2_5 ) ( * 2 ( * v1_5 v2_5 ) ) ) ) ( + ( - ( + v1_6 v2_6 ) ( * 2 ( * v1_6 v2_6 ) ) ) ( - ( + v1_7 v2_7 ) ( * 2 ( * v1_7 v2_7 ) ) ) ) ) ) )</t>
         </is>
       </c>
       <c r="E50" t="n">
         <v>9760</v>
       </c>
       <c r="F50" t="n">
-        <v>11518</v>
+        <v>9760</v>
       </c>
       <c r="G50" t="n">
-        <v>-18.01</v>
+        <v>0</v>
       </c>
       <c r="H50" t="n">
         <v>76.34999999999999</v>
       </c>
       <c r="I50" t="n">
-        <v>214.67</v>
+        <v>76.34999999999999</v>
       </c>
       <c r="J50" t="b">
         <v>0</v>
       </c>
       <c r="K50" t="n">
-        <v>185.33</v>
+        <v>323.65</v>
       </c>
       <c r="L50" t="n">
-        <v>14</v>
+        <v>1</v>
       </c>
     </row>
     <row r="51">
@@ -2563,29 +2563,29 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>(Vec (+ (+ (+ (+ (+ (- (+ v1_0 v2_0) (* (* v1_0 v2_0) 2)) (- (+ v1_1 v2_1) (* 2 (* v1_1 v2_1)))) (+ (- (+ v1_2 v2_2) (* 2 (* v1_2 v2_2))) (- (+ v1_3 v2_3) (* 2 (* v1_3 v2_3))))) (+ (+ (- (+ v1_4 v2_4) (* 2 (* v1_4 v2_4))) (- (+ v1_5 v2_5) (* 2 (* v1_5 v2_5)))) (+ (- (+ v1_6 v2_6) (* 2 (* v1_6 v2_6))) (- (+ v1_7 v2_7) (* 2 (* v1_7 v2_7)))))) (+ (+ (+ (- (+ v1_8 v2_8) (* 2 (* v1_8 v2_8))) (- (+ v1_9 v2_9) (* 2 (* v1_9 v2_9)))) (+ (- (+ v1_10 v2_10) (* 2 (* v1_10 v2_10))) (- (+ v1_11 v2_11) (* 2 (* v1_11 v2_11))))) (+ (+ (- (+ v1_12 v2_12) (* 2 (* v1_12 v2_12))) (- (+ v1_13 v2_13) (* 2 (* v1_13 v2_13)))) (* 1 (* 1 (* 1 (+ (- (+ v1_14 v2_14) (* 2 (* v1_14 v2_14))) (- (+ v1_15 v2_15) (* 2 (* v1_15 v2_15)))))))))) (* 1 (* 1 (+ (+ (+ (* 1 (+ (- (+ v1_16 v2_16) (* 2 (* v1_16 v2_16))) (- (+ v1_17 v2_17) (* 2 (* v1_17 v2_17))))) (+ (- (+ v1_18 v2_18) (* 2 (* v1_18 v2_18))) (- (+ v1_19 v2_19) (* 2 (* v1_19 v2_19))))) (+ (+ (- (+ v1_20 v2_20) (* 2 (* v1_20 v2_20))) (- (+ v1_21 v2_21) (* 2 (* v1_21 v2_21)))) (+ (- (+ v1_22 v2_22) (* 2 (* v1_22 v2_22))) (- (+ v1_23 v2_23) (* 2 (* v1_23 v2_23)))))) (+ (+ (+ (- (+ v1_24 v2_24) (* 2 (* v1_24 v2_24))) (- (+ v1_25 v2_25) (* 2 (* v1_25 v2_25)))) (+ (- (+ v1_26 v2_26) (* 2 (* v1_26 v2_26))) (- (+ v1_27 v2_27) (* 2 (* v1_27 v2_27))))) (+ (+ (- (+ v1_28 v2_28) (* 2 (* v1_28 v2_28))) (- (+ v1_29 v2_29) (* 2 (* v1_29 v2_29)))) (+ (- (+ v1_30 v2_30) (* 2 (* v1_30 v2_30))) (- (+ v1_31 v2_31) (* 2 (* v1_31 v2_31)))))))))))</t>
+          <t>(Vec (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (+ (* 1 (+ (+ (+ (+ (- (+ v1_0 v2_0) (* (* v1_0 v2_0) 2)) (- (+ v1_1 v2_1) (* 2 (* v1_1 v2_1)))) (+ (- (+ v1_2 v2_2) (* 2 (* v1_2 v2_2))) (- (+ v1_3 v2_3) (* 2 (* v1_3 v2_3))))) (+ (+ (- (+ v1_4 v2_4) (* 2 (* v1_4 v2_4))) (- (+ v1_5 v2_5) (* 2 (* v1_5 v2_5)))) (+ (- (+ v1_6 v2_6) (* 2 (* v1_6 v2_6))) (- (+ v1_7 v2_7) (* 2 (* v1_7 v2_7)))))) (+ (+ (+ (- (+ v1_8 v2_8) (* 2 (* v1_8 v2_8))) (- (+ v1_9 v2_9) (* 2 (* v1_9 v2_9)))) (+ (- (+ v1_10 v2_10) (* 2 (* v1_10 v2_10))) (- (+ v1_11 v2_11) (* 2 (* v1_11 v2_11))))) (+ (+ (- (+ v1_12 v2_12) (* 2 (* v1_12 v2_12))) (- (+ v1_13 v2_13) (* 2 (* v1_13 v2_13)))) (+ (- (+ v1_14 v2_14) (* 2 (* v1_14 v2_14))) (- (+ v1_15 v2_15) (* 2 (* v1_15 v2_15)))))))) (+ (* 1 (+ (+ (+ (- (+ v1_16 v2_16) (* 2 (* v1_16 v2_16))) (- (+ v1_17 v2_17) (* 2 (* v1_17 v2_17)))) (+ (- (+ v1_18 v2_18) (* 2 (* v1_18 v2_18))) (- (+ v1_19 v2_19) (* 2 (* v1_19 v2_19))))) (+ (+ (- (+ v1_20 v2_20) (* 2 (* v1_20 v2_20))) (- (+ v1_21 v2_21) (* 2 (* v1_21 v2_21)))) (+ (- (+ v1_22 v2_22) (* 2 (* v1_22 v2_22))) (- (+ v1_23 v2_23) (* 2 (* v1_23 v2_23))))))) (+ (+ (+ (- (+ v1_24 v2_24) (* 2 (* v1_24 v2_24))) (- (+ v1_25 v2_25) (* 2 (* v1_25 v2_25)))) (+ (- (+ v1_26 v2_26) (* 2 (* v1_26 v2_26))) (- (+ v1_27 v2_27) (* 2 (* v1_27 v2_27))))) (+ (+ (- (+ v1_28 v2_28) (* 2 (* v1_28 v2_28))) (- (+ v1_29 v2_29) (* 2 (* v1_29 v2_29)))) (+ (- (+ v1_30 v2_30) (* 2 (* v1_30 v2_30))) (- (+ v1_31 v2_31) (* 2 (* v1_31 v2_31)))))))))))))))))))</t>
         </is>
       </c>
       <c r="E51" t="n">
         <v>39762</v>
       </c>
       <c r="F51" t="n">
-        <v>41268</v>
+        <v>42784</v>
       </c>
       <c r="G51" t="n">
-        <v>-3.79</v>
+        <v>-7.6</v>
       </c>
       <c r="H51" t="n">
         <v>78.75</v>
       </c>
       <c r="I51" t="n">
-        <v>182.49</v>
+        <v>459.14</v>
       </c>
       <c r="J51" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K51" t="n">
-        <v>217.51</v>
+        <v>-59.14</v>
       </c>
       <c r="L51" t="n">
         <v>75</v>
@@ -2605,32 +2605,32 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>(Vec (+ c1_0 (+ c2_0 (* c0_0 (+ c3_0 (* c0_0 c4_0))))) (+ c1_1 (+ c2_1 (* c0_1 (+ c3_1 (* c0_1 c4_1))))) (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ c1_2 (+ c2_2 (* c0_2 (+ c3_2 (* c0_2 c4_2))))) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) (+ c1_3 (+ c2_3 (* c0_3 (+ c3_3 (* c0_3 c4_3))))) (+ c1_4 (+ c2_4 (* c0_4 (+ c3_4 (* c0_4 c4_4))))) (+ c1_5 (+ c2_5 (* c0_5 (+ c3_5 (* c0_5 c4_5))))) (+ c1_6 (+ c2_6 (* c0_6 (+ c3_6 (* c0_6 c4_6))))) (+ c1_7 (+ c2_7 (* c0_7 (+ c3_7 (* c0_7 c4_7))))))</t>
+          <t>(Vec ( + c1_0 ( + c2_0 ( * c0_0 ( + c3_0 ( * c0_0 c4_0 ) ) ) ) ) ( + c1_1 ( + c2_1 ( * c0_1 ( + c3_1 ( * c0_1 c4_1 ) ) ) ) ) ( + c1_2 ( + c2_2 ( * c0_2 ( + c3_2 ( * c0_2 c4_2 ) ) ) ) ) ( + c1_3 ( + c2_3 ( * c0_3 ( + c3_3 ( * c0_3 c4_3 ) ) ) ) ) ( + c1_4 ( + c2_4 ( * c0_4 ( + c3_4 ( * c0_4 c4_4 ) ) ) ) ) ( + c1_5 ( + c2_5 ( * c0_5 ( + c3_5 ( * c0_5 c4_5 ) ) ) ) ) ( + c1_6 ( + c2_6 ( * c0_6 ( + c3_6 ( * c0_6 c4_6 ) ) ) ) ) ( + c1_7 ( + c2_7 ( * c0_7 ( + c3_7 ( * c0_7 c4_7 ) ) ) ) ) )</t>
         </is>
       </c>
       <c r="E52" t="n">
         <v>10009</v>
       </c>
       <c r="F52" t="n">
-        <v>28583</v>
+        <v>10009</v>
       </c>
       <c r="G52" t="n">
-        <v>-185.57</v>
+        <v>0</v>
       </c>
       <c r="H52" t="n">
         <v>75.15000000000001</v>
       </c>
       <c r="I52" t="n">
-        <v>163.8</v>
+        <v>75.15000000000001</v>
       </c>
       <c r="J52" t="b">
         <v>0</v>
       </c>
       <c r="K52" t="n">
-        <v>236.2</v>
+        <v>324.85</v>
       </c>
       <c r="L52" t="n">
-        <v>75</v>
+        <v>1</v>
       </c>
     </row>
     <row r="53">
@@ -2647,29 +2647,29 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>(Vec (+ c1_0 (+ c2_0 (* c0_0 (+ c3_0 (* c0_0 c4_0))))) (+ c1_1 (+ c2_1 (* c0_1 (+ c3_1 (* c0_1 c4_1))))) (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ c1_2 (+ c2_2 (* c0_2 (+ c3_2 (* c0_2 c4_2))))) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) (+ c1_3 (+ c2_3 (* c0_3 (+ c3_3 (* c0_3 c4_3))))) (+ c1_4 (+ c2_4 (* c0_4 (+ c3_4 (* c0_4 c4_4))))) (+ c1_5 (+ c2_5 (* c0_5 (+ c3_5 (* c0_5 c4_5))))) (+ c1_6 (+ c2_6 (* c0_6 (+ c3_6 (* c0_6 c4_6))))) (+ c1_7 (+ c2_7 (* c0_7 (+ c3_7 (* c0_7 c4_7))))) (+ c1_8 (+ c2_8 (* c0_8 (+ c3_8 (* c0_8 c4_8))))) (+ c1_9 (+ c2_9 (* c0_9 (+ c3_9 (* c0_9 c4_9))))) (+ c1_10 (+ c2_10 (* c0_10 (+ c3_10 (* c0_10 c4_10))))) (+ c1_11 (+ c2_11 (* c0_11 (+ c3_11 (* c0_11 c4_11))))) (+ c1_12 (+ c2_12 (* c0_12 (+ c3_12 (* c0_12 c4_12))))) (+ c1_13 (+ c2_13 (* c0_13 (+ c3_13 (* c0_13 c4_13))))) (+ c1_14 (+ c2_14 (* c0_14 (+ c3_14 (* c0_14 c4_14))))) (+ c1_15 (+ c2_15 (* c0_15 (+ c3_15 (* c0_15 c4_15))))) (+ c1_16 (+ c2_16 (* c0_16 (+ c3_16 (* c0_16 c4_16))))) (+ c1_17 (+ c2_17 (* c0_17 (+ c3_17 (* c0_17 c4_17))))) (+ c1_18 (+ c2_18 (* c0_18 (+ c3_18 (* c0_18 c4_18))))) (+ c1_19 (+ c2_19 (* c0_19 (+ c3_19 (* c0_19 c4_19))))) (+ c1_20 (+ c2_20 (* c0_20 (+ c3_20 (* c0_20 c4_20))))) (+ c1_21 (+ c2_21 (* c0_21 (+ c3_21 (* c0_21 c4_21))))) (+ c1_22 (+ c2_22 (* c0_22 (+ c3_22 (* c0_22 c4_22))))) (+ c1_23 (+ c2_23 (* c0_23 (+ c3_23 (* c0_23 c4_23))))) (+ c1_24 (+ c2_24 (* c0_24 (+ c3_24 (* c0_24 c4_24))))) (+ c1_25 (+ c2_25 (* c0_25 (+ c3_25 (* c0_25 c4_25))))) (+ c1_26 (+ c2_26 (* c0_26 (+ c3_26 (* c0_26 c4_26))))) (+ c1_27 (+ c2_27 (* c0_27 (+ c3_27 (* c0_27 c4_27))))) (+ c1_28 (+ c2_28 (* c0_28 (+ c3_28 (* c0_28 c4_28))))) (+ c1_29 (+ c2_29 (* c0_29 (+ c3_29 (* c0_29 c4_29))))) (+ c1_30 (+ c2_30 (* c0_30 (+ c3_30 (* c0_30 c4_30))))) (+ c1_31 (+ c2_31 (* c0_31 (+ c3_31 (* c0_31 c4_31))))))</t>
+          <t>(Vec (+ c1_0 (+ c2_0 (* c0_0 (+ c3_0 (+ 0 (* c0_0 c4_0)))))) (+ c1_1 (+ c2_1 (* c0_1 (+ c3_1 (+ 0 (* c0_1 c4_1)))))) (+ c1_2 (+ c2_2 (* c0_2 (+ c3_2 (+ 0 (* c0_2 c4_2)))))) (+ c1_3 (+ c2_3 (* c0_3 (+ c3_3 (+ 0 (* c0_3 c4_3)))))) (+ c1_4 (+ c2_4 (* c0_4 (+ c3_4 (+ 0 (* c0_4 c4_4)))))) (+ c1_5 (+ c2_5 (* c0_5 (+ c3_5 (+ 0 (* c0_5 c4_5)))))) (+ c1_6 (+ c2_6 (* c0_6 (+ c3_6 (+ 0 (* c0_6 c4_6)))))) (+ c1_7 (+ c2_7 (* c0_7 (+ c3_7 (+ 0 (* c0_7 c4_7)))))) (+ c1_8 (+ c2_8 (* c0_8 (+ c3_8 (+ 0 (* c0_8 c4_8)))))) (+ c1_9 (+ c2_9 (* c0_9 (+ c3_9 (+ 0 (* c0_9 c4_9)))))) (+ c1_10 (+ c2_10 (* c0_10 (+ c3_10 (+ 0 (* c0_10 c4_10)))))) (+ c1_11 (+ c2_11 (+ 0 (+ 0 (+ 0 (* c0_11 (+ c3_11 (* c0_11 c4_11)))))))) (+ c1_12 (+ c2_12 (+ 0 (+ 0 (+ 0 (* c0_12 (+ c3_12 (* c0_12 c4_12)))))))) (+ c1_13 (+ c2_13 (+ 0 (+ 0 (+ 0 (* c0_13 (+ c3_13 (* c0_13 c4_13)))))))) (+ c1_14 (+ c2_14 (+ 0 (+ 0 (+ 0 (* c0_14 (+ c3_14 (* c0_14 c4_14)))))))) (+ c1_15 (+ c2_15 (+ 0 (+ 0 (+ 0 (* c0_15 (+ c3_15 (* c0_15 c4_15)))))))) (+ c1_16 (+ c2_16 (+ 0 (+ 0 (+ 0 (* c0_16 (+ c3_16 (* c0_16 c4_16)))))))) (+ c1_17 (+ c2_17 (+ 0 (+ 0 (+ 0 (* c0_17 (+ c3_17 (* c0_17 c4_17)))))))) (+ c1_18 (+ c2_18 (+ 0 (+ 0 (+ 0 (* c0_18 (+ c3_18 (* c0_18 c4_18)))))))) (+ c1_19 (+ c2_19 (+ 0 (+ 0 (+ 0 (* c0_19 (+ c3_19 (* c0_19 c4_19)))))))) (+ c1_20 (+ c2_20 (+ 0 (+ 0 (+ 0 (* c0_20 (+ c3_20 (* c0_20 c4_20)))))))) (+ c1_21 (+ c2_21 (+ 0 (+ 0 (+ 0 (* c0_21 (+ c3_21 (* c0_21 c4_21)))))))) (+ c1_22 (+ c2_22 (+ 0 (+ 0 (+ 0 (* c0_22 (+ c3_22 (* c0_22 c4_22)))))))) (+ c1_23 (+ c2_23 (+ 0 (+ 0 (+ 0 (* c0_23 (+ c3_23 (* c0_23 c4_23)))))))) (+ c1_24 (+ c2_24 (+ 0 (+ 0 (+ 0 (* c0_24 (+ c3_24 (* c0_24 c4_24)))))))) (+ c1_25 (+ c2_25 (+ 0 (+ 0 (+ 0 (* c0_25 (+ c3_25 (* c0_25 c4_25)))))))) (+ c1_26 (+ c2_26 (+ 0 (+ 0 (+ 0 (* c0_26 (+ c3_26 (* c0_26 c4_26)))))))) (+ c1_27 (+ c2_27 (+ 0 (+ 0 (+ 0 (* c0_27 (+ c3_27 (* c0_27 c4_27)))))))) (+ c1_28 (+ c2_28 (+ 0 (+ 0 (+ 0 (* c0_28 (+ c3_28 (* c0_28 c4_28)))))))) (+ c1_29 (+ c2_29 (+ 0 (+ 0 (+ 0 (* c0_29 (+ c3_29 (* c0_29 c4_29)))))))) (+ c1_30 (+ c2_30 (+ 0 (+ 0 (+ 0 (* c0_30 (+ c3_30 (* c0_30 c4_30)))))))) (+ c1_31 (+ c2_31 (+ 0 (+ 0 (+ 0 (* c0_31 (+ c3_31 (* c0_31 c4_31)))))))))</t>
         </is>
       </c>
       <c r="E53" t="n">
         <v>40009</v>
       </c>
       <c r="F53" t="n">
-        <v>58583</v>
+        <v>58512</v>
       </c>
       <c r="G53" t="n">
-        <v>-46.42</v>
+        <v>-46.25</v>
       </c>
       <c r="H53" t="n">
         <v>75.15000000000001</v>
       </c>
       <c r="I53" t="n">
-        <v>163.8</v>
+        <v>78.75</v>
       </c>
       <c r="J53" t="b">
         <v>0</v>
       </c>
       <c r="K53" t="n">
-        <v>236.2</v>
+        <v>321.25</v>
       </c>
       <c r="L53" t="n">
         <v>75</v>
@@ -2689,29 +2689,29 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>(Vec (+ (+ (* (- c2_0 c1_0) (- c2_0 c1_0)) (* (- c2_1 c1_1) (- c2_1 c1_1))) (+ (* (- c2_2 c1_2) (- c2_2 c1_2)) (* (- c2_3 c1_3) (- c2_3 c1_3)))))</t>
+          <t>(Vec (+ (+ (* (- c2_0 c1_0) (- c2_0 c1_0)) (* (- c2_1 c1_1) (- c2_1 c1_1))) (+ (* (- c2_2 c1_2) (- c2_2 c1_2)) (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (* (- c2_3 c1_3) (- c2_3 c1_3)))))))))))))))))))))))))))))))))))))))))))))))))))))))))))))))))))))))))))))))</t>
         </is>
       </c>
       <c r="E54" t="n">
         <v>3757</v>
       </c>
       <c r="F54" t="n">
-        <v>3757</v>
+        <v>22331</v>
       </c>
       <c r="G54" t="n">
-        <v>0</v>
+        <v>-494.38</v>
       </c>
       <c r="H54" t="n">
         <v>40.57</v>
       </c>
       <c r="I54" t="n">
-        <v>40.57</v>
+        <v>129.22</v>
       </c>
       <c r="J54" t="b">
         <v>0</v>
       </c>
       <c r="K54" t="n">
-        <v>359.43</v>
+        <v>270.78</v>
       </c>
       <c r="L54" t="n">
         <v>75</v>
@@ -2731,29 +2731,29 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>(Vec (+ (+ (+ (* (- c2_0 c1_0) (- c2_0 c1_0)) (* (- c2_1 c1_1) (- c2_1 c1_1))) (+ (* (- c2_2 c1_2) (- c2_2 c1_2)) (* (- c2_3 c1_3) (- c2_3 c1_3)))) (+ (+ (* (- c2_4 c1_4) (- c2_4 c1_4)) (* (- c2_5 c1_5) (- c2_5 c1_5))) (+ (* (- c2_6 c1_6) (- c2_6 c1_6)) (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (- c2_7 c1_7) (- c2_7 c1_7)) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1)))))</t>
+          <t>(Vec (+ (+ (+ (* (- c2_0 c1_0) (- c2_0 c1_0)) (* (- c2_1 c1_1) (- c2_1 c1_1))) (+ (* (- c2_2 c1_2) (- c2_2 c1_2)) (* (- c2_3 c1_3) (- c2_3 c1_3)))) (+ (+ (* (- c2_4 c1_4) (- c2_4 c1_4)) (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (* (- c2_5 c1_5) (- c2_5 c1_5)))))))))))))))))))))))))))) (+ (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (* (- c2_6 c1_6) (- c2_6 c1_6))))))))))))))))))))))))))) (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (* (- c2_7 c1_7) (- c2_7 c1_7))))))))))))))))))))))))))))))</t>
         </is>
       </c>
       <c r="E55" t="n">
         <v>7758</v>
       </c>
       <c r="F55" t="n">
-        <v>26406</v>
+        <v>26283</v>
       </c>
       <c r="G55" t="n">
-        <v>-240.37</v>
+        <v>-238.79</v>
       </c>
       <c r="H55" t="n">
         <v>41.77</v>
       </c>
       <c r="I55" t="n">
-        <v>2600.76</v>
+        <v>71.72</v>
       </c>
       <c r="J55" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K55" t="n">
-        <v>-2200.76</v>
+        <v>328.28</v>
       </c>
       <c r="L55" t="n">
         <v>75</v>
@@ -2773,29 +2773,29 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>(Vec (+ (+ (+ (+ (+ (* (- c2_0 c1_0) (- c2_0 c1_0)) (* (- c2_1 c1_1) (- c2_1 c1_1))) (+ (* (- c2_2 c1_2) (- c2_2 c1_2)) (* (- c2_3 c1_3) (- c2_3 c1_3)))) (+ (+ (* (- c2_4 c1_4) (- c2_4 c1_4)) (* (- c2_5 c1_5) (- c2_5 c1_5))) (+ (* (- c2_6 c1_6) (- c2_6 c1_6)) (* (- c2_7 c1_7) (- c2_7 c1_7))))) (+ (+ (+ (* (- c2_8 c1_8) (- c2_8 c1_8)) (* (- c2_9 c1_9) (- c2_9 c1_9))) (+ (* (- c2_10 c1_10) (- c2_10 c1_10)) (* (- c2_11 c1_11) (- c2_11 c1_11)))) (+ (+ (* (- c2_12 c1_12) (- c2_12 c1_12)) (* (- c2_13 c1_13) (- c2_13 c1_13))) (+ (* (- c2_14 c1_14) (- c2_14 c1_14)) (* (- c2_15 c1_15) (- c2_15 c1_15)))))) (+ (+ (+ (+ (* (- c2_16 c1_16) (- c2_16 c1_16)) (* (- c2_17 c1_17) (- c2_17 c1_17))) (+ (* (- c2_18 c1_18) (- c2_18 c1_18)) (* (- c2_19 c1_19) (- c2_19 c1_19)))) (+ (+ (* (- c2_20 c1_20) (- c2_20 c1_20)) (* (- c2_21 c1_21) (- c2_21 c1_21))) (+ (* (- c2_22 c1_22) (- c2_22 c1_22)) (* (- c2_23 c1_23) (- c2_23 c1_23))))) (+ (+ (+ (* (- c2_24 c1_24) (- c2_24 c1_24)) (* (- c2_25 c1_25) (- c2_25 c1_25))) (+ (* (- c2_26 c1_26) (- c2_26 c1_26)) (* (- c2_27 c1_27) (- c2_27 c1_27)))) (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (+ (+ (* (- c2_28 c1_28) (- c2_28 c1_28)) (* (- c2_29 c1_29) (- c2_29 c1_29))) (+ (* (- c2_30 c1_30) (- c2_30 c1_30)) (* (- c2_31 c1_31) (- c2_31 c1_31)))) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1)))))</t>
+          <t>(Vec (+ (+ (+ (+ (+ (* (- c2_0 c1_0) (- c2_0 c1_0)) (* (- c2_1 c1_1) (- c2_1 c1_1))) (+ (* (- c2_2 c1_2) (- c2_2 c1_2)) (* (- c2_3 c1_3) (- c2_3 c1_3)))) (+ (+ (* (- c2_4 c1_4) (- c2_4 c1_4)) (+ 0 (+ 0 (+ 0 (* (- c2_5 c1_5) (- c2_5 c1_5)))))) (+ (+ 0 (+ 0 (+ 0 (* (- c2_6 c1_6) (- c2_6 c1_6))))) (+ 0 (+ 0 (+ 0 (* (- c2_7 c1_7) (- c2_7 c1_7)))))))) (+ (+ (+ (+ 0 (+ 0 (+ 0 (* (- c2_8 c1_8) (- c2_8 c1_8))))) (+ 0 (+ 0 (+ 0 (* (- c2_9 c1_9) (- c2_9 c1_9)))))) (+ (+ 0 (+ 0 (+ 0 (* (- c2_10 c1_10) (- c2_10 c1_10))))) (+ 0 (+ 0 (+ 0 (* (- c2_11 c1_11) (- c2_11 c1_11))))))) (+ (+ (+ 0 (+ 0 (+ 0 (* (- c2_12 c1_12) (- c2_12 c1_12))))) (+ 0 (+ 0 (+ 0 (* (- c2_13 c1_13) (- c2_13 c1_13)))))) (+ (+ 0 (+ 0 (+ 0 (* (- c2_14 c1_14) (- c2_14 c1_14))))) (+ 0 (+ 0 (+ 0 (* (- c2_15 c1_15) (- c2_15 c1_15))))))))) (+ (+ (+ (+ (+ 0 (+ 0 (+ 0 (* (- c2_16 c1_16) (- c2_16 c1_16))))) (+ 0 (+ 0 (+ 0 (* (- c2_17 c1_17) (- c2_17 c1_17)))))) (+ (+ 0 (+ 0 (+ 0 (* (- c2_18 c1_18) (- c2_18 c1_18))))) (+ 0 (+ 0 (+ 0 (* (- c2_19 c1_19) (- c2_19 c1_19))))))) (+ (+ (+ 0 (+ 0 (+ 0 (* (- c2_20 c1_20) (- c2_20 c1_20))))) (+ 0 (+ 0 (+ 0 (* (- c2_21 c1_21) (- c2_21 c1_21)))))) (+ (+ 0 (+ 0 (+ 0 (* (- c2_22 c1_22) (- c2_22 c1_22))))) (+ 0 (+ 0 (+ 0 (* (- c2_23 c1_23) (- c2_23 c1_23)))))))) (+ (+ (+ (+ 0 (+ 0 (+ 0 (* (- c2_24 c1_24) (- c2_24 c1_24))))) (+ 0 (+ 0 (* (- c2_25 c1_25) (- c2_25 c1_25))))) (+ (+ 0 (+ 0 (* (- c2_26 c1_26) (- c2_26 c1_26)))) (+ 0 (+ 0 (* (- c2_27 c1_27) (- c2_27 c1_27)))))) (+ (+ (+ 0 (+ 0 (* (- c2_28 c1_28) (- c2_28 c1_28)))) (+ 0 (+ 0 (* (- c2_29 c1_29) (- c2_29 c1_29))))) (+ (+ 0 (+ 0 (* (- c2_30 c1_30) (- c2_30 c1_30)))) (+ 0 (+ 0 (* (- c2_31 c1_31) (- c2_31 c1_31))))))))))</t>
         </is>
       </c>
       <c r="E56" t="n">
         <v>31760</v>
       </c>
       <c r="F56" t="n">
-        <v>50408</v>
+        <v>50263</v>
       </c>
       <c r="G56" t="n">
-        <v>-58.72</v>
+        <v>-58.26</v>
       </c>
       <c r="H56" t="n">
         <v>44.16</v>
       </c>
       <c r="I56" t="n">
-        <v>2603.16</v>
+        <v>47.76</v>
       </c>
       <c r="J56" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K56" t="n">
-        <v>-2203.16</v>
+        <v>352.24</v>
       </c>
       <c r="L56" t="n">
         <v>75</v>
@@ -2815,29 +2815,29 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>(Vec (+ (+ (* v1_0 v2_0) (* v1_1 v2_1)) (+ (* v1_2 v2_2) (* v1_3 v2_3))))</t>
+          <t>(Vec (+ (+ (* v1_0 v2_0) (* v1_1 v2_1)) (+ (* v1_2 v2_2) (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (* v1_3 v2_3))))))))))))))))))))))))))))))))))))))))))))))))))))))))))))))))))))))))))))))</t>
         </is>
       </c>
       <c r="E57" t="n">
         <v>1756</v>
       </c>
       <c r="F57" t="n">
-        <v>1756</v>
+        <v>20330</v>
       </c>
       <c r="G57" t="n">
-        <v>0</v>
+        <v>-1057.74</v>
       </c>
       <c r="H57" t="n">
         <v>39.37</v>
       </c>
       <c r="I57" t="n">
-        <v>39.37</v>
+        <v>128.02</v>
       </c>
       <c r="J57" t="b">
         <v>0</v>
       </c>
       <c r="K57" t="n">
-        <v>360.63</v>
+        <v>271.98</v>
       </c>
       <c r="L57" t="n">
         <v>75</v>
@@ -2899,29 +2899,29 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>(Vec (+ (+ (+ (+ (+ (* v1_0 v2_0) (* v1_1 v2_1)) (+ (* v1_2 v2_2) (* v1_3 v2_3))) (+ (+ (* v1_4 v2_4) (* v1_5 v2_5)) (+ (* v1_6 v2_6) (* v1_7 v2_7)))) (+ (+ (+ (* v1_8 v2_8) (* v1_9 v2_9)) (+ (* v1_10 v2_10) (* v1_11 v2_11))) (+ (+ (* v1_12 v2_12) (* v1_13 v2_13)) (+ (* v1_14 v2_14) (* v1_15 v2_15))))) (+ (+ (+ (+ (* v1_16 v2_16) (* v1_17 v2_17)) (+ (* v1_18 v2_18) (* v1_19 v2_19))) (+ (+ (* v1_20 v2_20) (* v1_21 v2_21)) (+ (* v1_22 v2_22) (* v1_23 v2_23)))) (+ (+ (+ (* v1_24 v2_24) (* v1_25 v2_25)) (+ (* v1_26 v2_26) (* v1_27 v2_27))) (+ (+ (* v1_28 v2_28) (* v1_29 v2_29)) (+ (* v1_30 v2_30) (* v1_31 v2_31)))))))</t>
+          <t>(Vec (+ (+ (+ (+ (+ (* v1_0 v2_0) (* v1_1 v2_1)) (+ (* v1_2 v2_2) (* v1_3 v2_3))) (+ (+ (* v1_4 v2_4) (* v1_5 v2_5)) (+ (* v1_6 v2_6) (* v1_7 v2_7)))) (+ (+ (+ (* v1_8 v2_8) (* v1_9 v2_9)) (+ (* v1_10 v2_10) (* v1_11 v2_11))) (+ (+ (* v1_12 v2_12) (* v1_13 v2_13)) (+ (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (* v1_14 v2_14)))))) (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (* v1_15 v2_15)))))))))) (+ (+ (+ (+ (+ 0 (+ 0 (+ 0 (+ 0 (* v1_16 v2_16))))) (+ 0 (+ 0 (+ 0 (+ 0 (* v1_17 v2_17)))))) (+ (+ 0 (+ 0 (+ 0 (+ 0 (* v1_18 v2_18))))) (+ 0 (+ 0 (+ 0 (+ 0 (* v1_19 v2_19))))))) (+ (+ (+ 0 (+ 0 (+ 0 (+ 0 (* v1_20 v2_20))))) (+ 0 (+ 0 (+ 0 (+ 0 (* v1_21 v2_21)))))) (+ (+ 0 (+ 0 (+ 0 (+ 0 (* v1_22 v2_22))))) (+ 0 (+ 0 (+ 0 (+ 0 (* v1_23 v2_23)))))))) (+ (+ (+ (+ 0 (+ 0 (+ 0 (+ 0 (* v1_24 v2_24))))) (+ 0 (+ 0 (+ 0 (+ 0 (* v1_25 v2_25)))))) (+ (+ 0 (+ 0 (+ 0 (+ 0 (* v1_26 v2_26))))) (+ 0 (+ 0 (+ 0 (+ 0 (* v1_27 v2_27))))))) (+ (+ (+ 0 (+ 0 (+ 0 (+ 0 (* v1_28 v2_28))))) (+ 0 (+ 0 (+ 0 (+ 0 (* v1_29 v2_29)))))) (+ (+ 0 (+ 0 (+ 0 (+ 0 (* v1_30 v2_30))))) (+ 0 (+ 0 (+ 0 (+ 0 (* v1_31 v2_31)))))))))))</t>
         </is>
       </c>
       <c r="E59" t="n">
         <v>15759</v>
       </c>
       <c r="F59" t="n">
-        <v>15759</v>
+        <v>34264</v>
       </c>
       <c r="G59" t="n">
-        <v>0</v>
+        <v>-117.42</v>
       </c>
       <c r="H59" t="n">
         <v>42.97</v>
       </c>
       <c r="I59" t="n">
-        <v>42.97</v>
+        <v>48.96</v>
       </c>
       <c r="J59" t="b">
         <v>0</v>
       </c>
       <c r="K59" t="n">
-        <v>357.03</v>
+        <v>351.04</v>
       </c>
       <c r="L59" t="n">
         <v>75</v>
@@ -2941,29 +2941,29 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>(Vec (+ in_1_1 (* in_0_1 2)) (+ (+ in_1_2 (- in_1_0)) (+ (* in_0_2 2) (* in_0_0 -2))) (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ in_1_3 (- in_1_1)) (+ (* in_0_3 2) (* in_0_1 -2))) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) (- 0)) (- (- 0))) (- (- 0))) (- (- (- 0)))) (- (- (- (- 0))))) (- (- (- (- (- 0)))))) (- (- (- (- (- (- 0))))))) (- (- (- (- (- (- (- 0)))))))) 0) 0) 0) (+ (- in_1_2) (* in_0_2 -2)) (+ in_2_1 (+ in_0_1 (* in_1_1 2))) (+ (+ in_2_2 (- in_2_0)) (+ (+ in_0_2 (- in_0_0)) (+ (* in_1_2 2) (* in_1_0 -2)))) (+ (+ in_2_3 (- in_2_1)) (+ (+ in_0_3 (- in_0_1)) (+ (* in_1_3 2) (* in_1_1 -2)))) (+ (- in_2_2) (+ (- in_0_2) (* in_1_2 -2))) (+ in_3_1 (+ in_1_1 (* in_2_1 2))) (+ (+ in_3_2 (- in_3_0)) (+ (+ in_1_2 (- in_1_0)) (+ (* in_2_2 2) (* in_2_0 -2)))) (+ (+ in_3_3 (- in_3_1)) (+ (+ in_1_3 (- in_1_1)) (+ (* in_2_3 2) (* in_2_1 -2)))) (+ (- in_3_2) (+ (- in_1_2) (* in_2_2 -2))) (+ in_2_1 (* in_3_1 2)) (+ (+ in_2_2 (- in_2_0)) (+ (* in_3_2 2) (* in_3_0 -2))) (+ (+ in_2_3 (- in_2_1)) (+ (* in_3_3 2) (* in_3_1 -2))) (+ (- in_2_2) (* in_3_2 -2)))</t>
+          <t>(Vec (+ in_1_1 (* in_0_1 2)) (* 1 (* 1 (* 1 (* 1 (+ (+ in_1_2 (- in_1_0)) (+ (* in_0_2 2) (* in_0_0 -2))))))) (* 1 (* 1 (* 1 (+ (* 1 (+ in_1_3 (- in_1_1))) (+ (* in_0_3 2) (* in_0_1 -2)))))) (* 1 (* 1 (* 1 (* 1 (+ (- in_1_2) (* in_0_2 -2)))))) (* 1 (* 1 (* 1 (* 1 (+ in_2_1 (+ in_0_1 (* in_1_1 2))))))) (* 1 (* 1 (* 1 (* 1 (+ (+ in_2_2 (- in_2_0)) (+ (+ in_0_2 (- in_0_0)) (+ (* in_1_2 2) (* in_1_0 -2)))))))) (* 1 (* 1 (* 1 (* 1 (+ (+ in_2_3 (- in_2_1)) (+ (+ in_0_3 (- in_0_1)) (+ (* in_1_3 2) (* in_1_1 -2)))))))) (* 1 (* 1 (* 1 (* 1 (+ (- in_2_2) (+ (- in_0_2) (* in_1_2 -2))))))) (* 1 (* 1 (* 1 (* 1 (+ in_3_1 (+ in_1_1 (* in_2_1 2))))))) (* 1 (* 1 (* 1 (* 1 (+ (+ in_3_2 (- in_3_0)) (+ (+ in_1_2 (- in_1_0)) (+ (* in_2_2 2) (* in_2_0 -2)))))))) (* 1 (* 1 (* 1 (* 1 (+ (+ in_3_3 (- in_3_1)) (+ (+ in_1_3 (- in_1_1)) (+ (* in_2_3 2) (* in_2_1 -2)))))))) (* 1 (* 1 (* 1 (* 1 (+ (- in_3_2) (+ (- in_1_2) (* in_2_2 -2))))))) (* 1 (* 1 (* 1 (* 1 (+ in_2_1 (* in_3_1 2)))))) (* 1 (* 1 (* 1 (* 1 (+ (+ in_2_2 (- in_2_0)) (+ (* in_3_2 2) (* in_3_0 -2))))))) (* 1 (* 1 (* 1 (* 1 (+ (+ in_2_3 (- in_2_1)) (+ (* in_3_3 2) (* in_3_1 -2))))))) (* 1 (* 1 (* 1 (* 1 (+ (- in_2_2) (* in_3_2 -2)))))))</t>
         </is>
       </c>
       <c r="E60" t="n">
         <v>21507</v>
       </c>
       <c r="F60" t="n">
-        <v>40050</v>
+        <v>36515</v>
       </c>
       <c r="G60" t="n">
-        <v>-86.22</v>
+        <v>-69.78</v>
       </c>
       <c r="H60" t="n">
         <v>40.57</v>
       </c>
       <c r="I60" t="n">
-        <v>92.08</v>
+        <v>178.89</v>
       </c>
       <c r="J60" t="b">
         <v>0</v>
       </c>
       <c r="K60" t="n">
-        <v>307.92</v>
+        <v>221.11</v>
       </c>
       <c r="L60" t="n">
         <v>75</v>
@@ -2983,29 +2983,29 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>(Vec (+ (+ (* a_0_0 b_0_0) (* a_0_1 b_1_0)) (* a_0_2 b_2_0)) (+ (+ (* a_0_0 b_0_1) (* a_0_1 b_1_1)) (* a_0_2 b_2_1)) (+ (+ (* a_0_0 b_0_2) (* a_0_1 b_1_2)) (* a_0_2 b_2_2)) (+ (+ (* a_1_0 b_0_0) (* a_1_1 b_1_0)) (* a_1_2 b_2_0)) (+ (+ (* a_1_0 b_0_1) (* a_1_1 b_1_1)) (* a_1_2 b_2_1)) (+ (+ (* a_1_0 b_0_2) (* a_1_1 b_1_2)) (* a_1_2 b_2_2)) (+ (+ (* a_2_0 b_0_0) (* a_2_1 b_1_0)) (* a_2_2 b_2_0)) (+ (+ (* a_2_0 b_0_1) (* a_2_1 b_1_1)) (* a_2_2 b_2_1)) (+ (+ (* a_2_0 b_0_2) (* a_2_1 b_1_2)) (* a_2_2 b_2_2)))</t>
+          <t>(Vec (+ (+ (* a_0_0 b_0_0) (* a_0_1 b_1_0)) (* a_0_2 b_2_0)) (+ (+ (* a_0_0 b_0_1) (* a_0_1 b_1_1)) (* a_0_2 b_2_1)) (+ (+ (* a_0_0 b_0_2) (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (* a_0_1 b_1_2)))))))) (* a_0_2 b_2_2)) (+ (+ (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (* a_1_0 b_0_0))))))) (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (* a_1_1 b_1_0)))))))) (* a_1_2 b_2_0)) (+ (+ (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (* a_1_0 b_0_1))))))) (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (* a_1_1 b_1_1)))))))) (* a_1_2 b_2_1)) (+ (+ (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (* a_1_0 b_0_2))))))) (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (* a_1_1 b_1_2)))))))) (* a_1_2 b_2_2)) (+ (+ (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (* a_2_0 b_0_0))))))) (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (* a_2_1 b_1_0)))))))) (* a_2_2 b_2_0)) (+ (+ (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (* a_2_0 b_0_1)))))) (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (* a_2_1 b_1_1))))))) (* a_2_2 b_2_1)) (+ (+ (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (* a_2_0 b_0_2)))))) (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (* a_2_1 b_1_2))))))) (* a_2_2 b_2_2)))</t>
         </is>
       </c>
       <c r="E61" t="n">
         <v>11256</v>
       </c>
       <c r="F61" t="n">
-        <v>11256</v>
+        <v>29762</v>
       </c>
       <c r="G61" t="n">
-        <v>0</v>
+        <v>-164.41</v>
       </c>
       <c r="H61" t="n">
         <v>39.37</v>
       </c>
       <c r="I61" t="n">
-        <v>39.37</v>
+        <v>46.56</v>
       </c>
       <c r="J61" t="b">
         <v>0</v>
       </c>
       <c r="K61" t="n">
-        <v>360.63</v>
+        <v>353.44</v>
       </c>
       <c r="L61" t="n">
         <v>75</v>
@@ -3025,29 +3025,29 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>(Vec (+ (* (+ (* o3 (- 1 c23)) (* c23 o2)) (- 1 c12)) (* c12 (+ (* o3 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (- 1 c13)))))))))))))))))))))))))))))))))))))))))))))))))))))))))))))))))))))))))))) (* c13 o1)))))</t>
+          <t>(Vec (+ (* (+ (* o3 (- 1 c23)) (* c23 o2)) (- 1 c12)) (* c12 (+ (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (+ (+ (+ (+ (+ (+ (+ (+ (+ (* 1 (* 1 (+ (+ (* 1 (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (* o3 (- 1 c13)) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0)) 0) 0))) 0) 0) 0) 0) 0) 0) 0) 0) 0))))))))))))))))))))))))))))))))))))))))))))))))))) (* c13 o1)))))</t>
         </is>
       </c>
       <c r="E62" t="n">
         <v>3009</v>
       </c>
       <c r="F62" t="n">
-        <v>21657</v>
+        <v>21636</v>
       </c>
       <c r="G62" t="n">
-        <v>-619.74</v>
+        <v>-619.04</v>
       </c>
       <c r="H62" t="n">
         <v>75.15000000000001</v>
       </c>
       <c r="I62" t="n">
-        <v>2634.14</v>
+        <v>1933.1</v>
       </c>
       <c r="J62" t="b">
         <v>1</v>
       </c>
       <c r="K62" t="n">
-        <v>-2234.14</v>
+        <v>-1533.1</v>
       </c>
       <c r="L62" t="n">
         <v>75</v>
@@ -3067,32 +3067,32 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>(Vec (+ (* (+ (* (+ (* o321 (* 1 (* 1 (* 1 (* 1 (- 1 c23)))))) (* c23 o231)) (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (- 1 c13)))))))) (* c13 o213)) (- 1 c12)) (* c12 (+ (* (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (- 1 c23))))))) (+ (* o312 (* 1 (* 1 (* 1 (- 1 c13))))) (* c13 o132))) (* c23 o123)))))</t>
+          <t>(Vec ( + ( * ( + ( * ( + ( * o321 ( - 1 c23 ) ) ( * c23 o231 ) ) ( - 1 c13 ) ) ( * c13 o213 ) ) ( - 1 c12 ) ) ( * c12 ( + ( * ( - 1 c23 ) ( + ( * o312 ( - 1 c13 ) ) ( * c13 o132 ) ) ) ( * c23 o123 ) ) ) ) )</t>
         </is>
       </c>
       <c r="E63" t="n">
         <v>5012</v>
       </c>
       <c r="F63" t="n">
-        <v>9771</v>
+        <v>5012</v>
       </c>
       <c r="G63" t="n">
-        <v>-94.95</v>
+        <v>0</v>
       </c>
       <c r="H63" t="n">
         <v>110.93</v>
       </c>
       <c r="I63" t="n">
-        <v>282.64</v>
+        <v>110.93</v>
       </c>
       <c r="J63" t="b">
         <v>0</v>
       </c>
       <c r="K63" t="n">
-        <v>117.36</v>
+        <v>289.07</v>
       </c>
       <c r="L63" t="n">
-        <v>20</v>
+        <v>1</v>
       </c>
     </row>
     <row r="64">
@@ -3109,29 +3109,29 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>(VecMul (Vec (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ x9602 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) x9604) (+ (+ x9608 x9610) (+ x9617 (* x9613 x9615)))) (&lt;&lt; (Vec (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ x9602 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) x9604) (+ (+ x9608 x9610) (+ x9617 (* x9613 x9615)))) 1))</t>
+          <t>(Vec (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (* (+ x9602 x9604) (+ (+ x9608 x9610) (+ (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (* x9613 x9615))))))))))))))))))))))))))))))))))))))))))))))) x9617))))))))))))))))))))))))))))))))</t>
         </is>
       </c>
       <c r="E64" t="n">
         <v>1508</v>
       </c>
       <c r="F64" t="n">
-        <v>19480</v>
+        <v>20082</v>
       </c>
       <c r="G64" t="n">
-        <v>-1191.78</v>
+        <v>-1231.7</v>
       </c>
       <c r="H64" t="n">
         <v>73.95</v>
       </c>
       <c r="I64" t="n">
-        <v>159.01</v>
+        <v>162.61</v>
       </c>
       <c r="J64" t="b">
         <v>0</v>
       </c>
       <c r="K64" t="n">
-        <v>240.99</v>
+        <v>237.39</v>
       </c>
       <c r="L64" t="n">
         <v>75</v>
@@ -3235,29 +3235,29 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>(Vec (+ (+ in_1_1 in_1_0) (+ in_0_1 in_0_0)) (+ (+ (+ in_1_2 in_1_1) (+ in_1_0 in_0_2)) (+ in_0_1 in_0_0)) (+ (+ (+ in_1_3 in_1_2) (+ in_1_1 in_0_3)) (+ in_0_2 in_0_1)) (+ (+ in_1_3 in_1_2) (+ in_0_3 in_0_2)) (+ (+ (+ in_2_1 in_2_0) (+ in_1_1 in_1_0)) (+ in_0_1 in_0_0)) (+ (+ (+ in_2_2 (+ in_2_1 in_2_0)) (+ in_1_2 in_1_1)) (+ (+ in_1_0 in_0_2) (+ in_0_1 in_0_0))) (+ (+ (+ in_2_3 (+ in_2_2 in_2_1)) (+ in_1_3 in_1_2)) (+ (+ in_1_1 in_0_3) (+ in_0_2 in_0_1))) (+ (+ (+ in_2_3 in_2_2) (+ in_1_3 in_1_2)) (+ in_0_3 in_0_2)) (+ (+ in_3_1 in_3_0) (+ (+ in_2_1 in_2_0) (+ in_1_1 in_1_0))) (+ (+ (+ in_3_2 (+ in_3_1 in_3_0)) (+ in_2_2 in_2_1)) (+ (+ in_2_0 in_1_2) (+ in_1_1 in_1_0))) (+ (+ (+ in_3_3 (+ in_3_2 in_3_1)) (+ in_2_3 in_2_2)) (+ (+ in_2_1 in_1_3) (+ in_1_2 in_1_1))) (+ (+ (+ in_3_3 in_3_2) (+ in_2_3 in_2_2)) (+ in_1_3 in_1_2)) (+ (+ in_3_1 in_3_0) (+ in_2_1 in_2_0)) (+ (+ (+ in_3_2 in_3_1) (+ in_3_0 in_2_2)) (+ in_2_1 in_2_0)) (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (+ (+ (+ in_3_3 in_3_2) (+ in_3_1 in_2_3)) (+ in_2_2 in_2_1)) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) (+ (+ in_3_3 in_3_2) (+ in_2_3 in_2_2)))</t>
+          <t>(Vec (+ (+ in_1_1 in_1_0) (+ in_0_1 in_0_0)) (+ (+ (+ in_1_2 in_1_1) (+ in_1_0 in_0_2)) (+ in_0_1 in_0_0)) (+ (+ (+ in_1_3 in_1_2) (+ in_1_1 in_0_3)) (+ in_0_2 in_0_1)) (+ (+ in_1_3 in_1_2) (+ in_0_3 in_0_2)) (+ (+ (+ in_2_1 in_2_0) (+ in_1_1 in_1_0)) (+ in_0_1 in_0_0)) (+ (+ (+ in_2_2 (+ in_2_1 in_2_0)) (+ in_1_2 in_1_1)) (+ (+ in_1_0 in_0_2) (+ in_0_1 in_0_0))) (+ (+ (+ in_2_3 (+ in_2_2 in_2_1)) (+ in_1_3 in_1_2)) (+ (+ in_1_1 in_0_3) (+ in_0_2 in_0_1))) (+ (+ (+ in_2_3 in_2_2) (+ in_1_3 in_1_2)) (+ in_0_3 in_0_2)) (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (+ (+ in_3_1 in_3_0) (+ (+ in_2_1 in_2_0) (+ in_1_1 in_1_0))) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) (+ (+ (+ in_3_2 (+ in_3_1 in_3_0)) (+ in_2_2 in_2_1)) (+ (+ in_2_0 in_1_2) (+ in_1_1 in_1_0))) (+ (+ (+ in_3_3 (+ in_3_2 in_3_1)) (+ in_2_3 in_2_2)) (+ (+ in_2_1 in_1_3) (+ in_1_2 in_1_1))) (+ (+ (+ in_3_3 in_3_2) (+ in_2_3 in_2_2)) (+ in_1_3 in_1_2)) (+ (+ in_3_1 in_3_0) (+ in_2_1 in_2_0)) (+ (+ (+ in_3_2 in_3_1) (+ in_3_0 in_2_2)) (+ in_2_1 in_2_0)) (+ (+ (+ in_3_3 in_3_2) (+ in_3_1 in_2_3)) (+ in_2_2 in_2_1)) (+ (+ in_3_3 in_3_2) (+ in_2_3 in_2_2)))</t>
         </is>
       </c>
       <c r="E67" t="n">
         <v>21006</v>
       </c>
       <c r="F67" t="n">
-        <v>39653</v>
+        <v>39579</v>
       </c>
       <c r="G67" t="n">
-        <v>-88.77</v>
+        <v>-88.42</v>
       </c>
       <c r="H67" t="n">
         <v>7.19</v>
       </c>
       <c r="I67" t="n">
-        <v>2564.98</v>
+        <v>94.64</v>
       </c>
       <c r="J67" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K67" t="n">
-        <v>-2164.98</v>
+        <v>305.36</v>
       </c>
       <c r="L67" t="n">
         <v>75</v>
@@ -3277,32 +3277,32 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>(Vec (+ v2_0 (+ 2 (* v1_0 5))) (+ v2_1 (+ 2 (* v1_1 5))) (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ v2_2 (+ 2 (* v1_2 5))) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) (+ v2_3 (+ 2 (* v1_3 5))))</t>
+          <t>(Vec ( + v2_0 ( + 2 ( * v1_0 5 ) ) ) ( + v2_1 ( + 2 ( * v1_1 5 ) ) ) ( + v2_2 ( + 2 ( * v1_2 5 ) ) ) ( + v2_3 ( + 2 ( * v1_3 5 ) ) ) )</t>
         </is>
       </c>
       <c r="E68" t="n">
         <v>3006</v>
       </c>
       <c r="F68" t="n">
-        <v>21580</v>
+        <v>3006</v>
       </c>
       <c r="G68" t="n">
-        <v>-617.9</v>
+        <v>0</v>
       </c>
       <c r="H68" t="n">
         <v>39.37</v>
       </c>
       <c r="I68" t="n">
-        <v>128.02</v>
+        <v>39.37</v>
       </c>
       <c r="J68" t="b">
         <v>0</v>
       </c>
       <c r="K68" t="n">
-        <v>271.98</v>
+        <v>360.63</v>
       </c>
       <c r="L68" t="n">
-        <v>75</v>
+        <v>1</v>
       </c>
     </row>
     <row r="69">
@@ -3319,29 +3319,29 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>(Vec (+ v2_0 (+ 2 (* v1_0 5))) (+ v2_1 (+ 2 (* v1_1 5))) (+ v2_2 (+ 2 (* v1_2 5))) (+ v2_3 (+ 2 (* v1_3 5))) (+ v2_4 (+ 2 (* v1_4 5))) (+ v2_5 (+ 2 (* v1_5 5))) (+ v2_6 (+ 2 (* v1_6 5))) (+ v2_7 (+ 2 (* v1_7 5))) (+ v2_8 (+ 2 (* v1_8 5))) (+ v2_9 (+ 2 (* v1_9 5))) (+ v2_10 (+ 2 (* v1_10 5))) (+ v2_11 (+ 2 (* v1_11 5))) (+ v2_12 (+ 2 (* v1_12 5))) (+ v2_13 (+ 2 (* v1_13 5))) (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (+ v2_14 (+ 2 (* v1_14 5))) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) (+ v2_15 (+ 2 (* v1_15 5))))</t>
+          <t>(Vec (+ v2_0 (+ 2 (* v1_0 5))) (+ v2_1 (+ 2 (* v1_1 5))) (+ v2_2 (+ 2 (* v1_2 5))) (+ v2_3 (+ 2 (* v1_3 5))) (+ v2_4 (+ 2 (* v1_4 5))) (+ v2_5 (+ 2 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (* v1_5 5)))))))))) (+ v2_6 (+ 2 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (* v1_6 5)))))))))) (+ v2_7 (+ 2 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (* v1_7 5)))))))))) (+ v2_8 (+ 2 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (* v1_8 5)))))))))) (+ v2_9 (+ 2 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (* v1_9 5)))))))))) (+ v2_10 (+ 2 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (* v1_10 5)))))))))) (+ v2_11 (+ 2 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (* v1_11 5)))))))))) (+ v2_12 (+ 2 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (* v1_12 5)))))))))) (+ v2_13 (+ 2 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (* v1_13 5))))))))) (+ v2_14 (+ 2 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (* v1_14 5))))))))) (+ v2_15 (+ 2 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (* v1_15 5))))))))))</t>
         </is>
       </c>
       <c r="E69" t="n">
         <v>12006</v>
       </c>
       <c r="F69" t="n">
-        <v>30654</v>
+        <v>30513</v>
       </c>
       <c r="G69" t="n">
-        <v>-155.32</v>
+        <v>-154.15</v>
       </c>
       <c r="H69" t="n">
         <v>39.37</v>
       </c>
       <c r="I69" t="n">
-        <v>2598.36</v>
+        <v>47.76</v>
       </c>
       <c r="J69" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K69" t="n">
-        <v>-2198.36</v>
+        <v>352.24</v>
       </c>
       <c r="L69" t="n">
         <v>75</v>
@@ -3361,32 +3361,32 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>(Vec (+ (+ (- (+ v1_0 v2_0) (* (* v1_0 v2_0) 2)) (- (+ v1_1 v2_1) (* 2 (* v1_1 v2_1)))) (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (- (+ v1_2 v2_2) (* 2 (* v1_2 v2_2))) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0)))</t>
+          <t>(Vec ( + ( + ( - ( + v1_0 v2_0 ) ( * ( * v1_0 v2_0 ) 2 ) ) ( - ( + v1_1 v2_1 ) ( * 2 ( * v1_1 v2_1 ) ) ) ) ( - ( + v1_2 v2_2 ) ( * 2 ( * v1_2 v2_2 ) ) ) ) )</t>
         </is>
       </c>
       <c r="E70" t="n">
         <v>3509</v>
       </c>
       <c r="F70" t="n">
-        <v>22082</v>
+        <v>3509</v>
       </c>
       <c r="G70" t="n">
-        <v>-529.3</v>
+        <v>0</v>
       </c>
       <c r="H70" t="n">
         <v>75.15000000000001</v>
       </c>
       <c r="I70" t="n">
-        <v>162.61</v>
+        <v>75.15000000000001</v>
       </c>
       <c r="J70" t="b">
         <v>0</v>
       </c>
       <c r="K70" t="n">
-        <v>237.39</v>
+        <v>324.85</v>
       </c>
       <c r="L70" t="n">
-        <v>75</v>
+        <v>1</v>
       </c>
     </row>
     <row r="71">
@@ -3403,29 +3403,29 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>(Vec (+ (+ (- (+ v1_0 v2_0) (* (* v1_0 v2_0) 2)) (- (+ v1_1 v2_1) (* 2 (* v1_1 v2_1)))) (+ (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (+ (* 1 (- (+ v1_2 v2_2) (* 2 (* v1_2 v2_2)))) (* 1 (- (+ v1_3 v2_3) (* 2 (* v1_3 v2_3))))))))))))))))))))))))))))) (- (+ v1_4 v2_4) (* 2 (* v1_4 v2_4))))))</t>
+          <t>(Vec (+ (+ (- (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (+ v1_0 v2_0)))))))))))))))) (* (* v1_0 v2_0) 2)) (- (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (+ v1_1 v2_1)))))))))))))))) (* 2 (* v1_1 v2_1)))) (+ (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (+ (+ (+ (+ (+ (* 1 (* 1 (* 1 (+ (+ (+ (+ (+ (+ (+ (+ (- (+ v1_2 v2_2) (* 2 (* v1_2 v2_2))) 0) 0) 0) 0) 0) 0) 0) 0)))) 0) 0) 0) 0) (- (+ v1_3 v2_3) (* 2 (* v1_3 v2_3))))))))))))))))))) (- (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (+ v1_4 v2_4))))))))))))))) (* 2 (* v1_4 v2_4))))))</t>
         </is>
       </c>
       <c r="E71" t="n">
         <v>6010</v>
       </c>
       <c r="F71" t="n">
-        <v>12560</v>
+        <v>24558</v>
       </c>
       <c r="G71" t="n">
-        <v>-108.99</v>
+        <v>-308.62</v>
       </c>
       <c r="H71" t="n">
         <v>76.34999999999999</v>
       </c>
       <c r="I71" t="n">
-        <v>940.87</v>
+        <v>713.1799999999999</v>
       </c>
       <c r="J71" t="b">
         <v>1</v>
       </c>
       <c r="K71" t="n">
-        <v>-540.87</v>
+        <v>-313.18</v>
       </c>
       <c r="L71" t="n">
         <v>75</v>
@@ -3445,29 +3445,29 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>(Vec (+ (+ (+ (+ (- (+ v1_0 v2_0) (* (* v1_0 v2_0) 2)) (- (+ v1_1 v2_1) (* 2 (* v1_1 v2_1)))) (+ (- (+ v1_2 v2_2) (* 2 (* v1_2 v2_2))) (- (+ v1_3 v2_3) (* 2 (* v1_3 v2_3))))) (+ (+ (- (+ v1_4 v2_4) (* 2 (* v1_4 v2_4))) (- (+ v1_5 v2_5) (* 2 (* v1_5 v2_5)))) (+ (- (+ v1_6 v2_6) (* 2 (* v1_6 v2_6))) (- (+ v1_7 v2_7) (* 2 (* v1_7 v2_7)))))) (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (- (+ v1_8 v2_8) (* 2 (* v1_8 v2_8))) (- (+ v1_9 v2_9) (* 2 (* v1_9 v2_9)))) (+ (- (+ v1_10 v2_10) (* 2 (* v1_10 v2_10))) (- (+ v1_11 v2_11) (* 2 (* v1_11 v2_11))))) (+ (+ (- (+ v1_12 v2_12) (* 2 (* v1_12 v2_12))) (- (+ v1_13 v2_13) (* 2 (* v1_13 v2_13)))) (+ (- (+ v1_14 v2_14) (* 2 (* v1_14 v2_14))) (- (+ v1_15 v2_15) (* 2 (* v1_15 v2_15)))))) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0)))</t>
+          <t>(Vec (+ (+ (+ (+ (- (+ v1_0 v2_0) (* (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (* v1_0 v2_0)))))) 2)) (- (+ v1_1 v2_1) (* 2 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (* v1_1 v2_1))))))))) (+ (- (+ v1_2 v2_2) (* 2 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (* v1_2 v2_2)))))))) (- (+ v1_3 v2_3) (* 2 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (* v1_3 v2_3)))))))))) (+ (+ (- (+ v1_4 v2_4) (* 2 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (* v1_4 v2_4)))))))) (- (+ v1_5 v2_5) (* 2 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (* v1_5 v2_5))))))))) (+ (- (+ v1_6 v2_6) (* 2 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (* v1_6 v2_6)))))))) (- (+ v1_7 v2_7) (* 2 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (* v1_7 v2_7))))))))))) (+ (+ (+ (- (+ v1_8 v2_8) (* 2 (+ 0 (+ 0 (+ 0 (+ 0 (* v1_8 v2_8))))))) (- (+ v1_9 v2_9) (* 2 (+ 0 (+ 0 (+ 0 (+ 0 (* v1_9 v2_9)))))))) (+ (- (+ v1_10 v2_10) (* 2 (+ 0 (+ 0 (+ 0 (+ 0 (* v1_10 v2_10))))))) (- (+ v1_11 v2_11) (* 2 (+ 0 (+ 0 (+ 0 (+ 0 (* v1_11 v2_11))))))))) (+ (+ (- (+ v1_12 v2_12) (* 2 (+ 0 (+ 0 (+ 0 (+ 0 (* v1_12 v2_12))))))) (- (+ v1_13 v2_13) (* 2 (+ 0 (+ 0 (+ 0 (+ 0 (* v1_13 v2_13)))))))) (+ (- (+ v1_14 v2_14) (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (* 2 (* v1_14 v2_14)))))))) (- (+ v1_15 v2_15) (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (* 2 (* v1_15 v2_15)))))))))))))</t>
         </is>
       </c>
       <c r="E72" t="n">
         <v>19761</v>
       </c>
       <c r="F72" t="n">
-        <v>38335</v>
+        <v>38266</v>
       </c>
       <c r="G72" t="n">
-        <v>-93.98999999999999</v>
+        <v>-93.64</v>
       </c>
       <c r="H72" t="n">
         <v>77.55</v>
       </c>
       <c r="I72" t="n">
-        <v>166.2</v>
+        <v>83.54000000000001</v>
       </c>
       <c r="J72" t="b">
         <v>0</v>
       </c>
       <c r="K72" t="n">
-        <v>233.8</v>
+        <v>316.46</v>
       </c>
       <c r="L72" t="n">
         <v>75</v>
@@ -3487,32 +3487,32 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>(Vec (+ c1_0 (+ c2_0 (* c0_0 (+ c3_0 (* c0_0 c4_0))))) (+ c1_1 (+ c2_1 (* c0_1 (+ c3_1 (* c0_1 c4_1))))) (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ c1_2 (+ c2_2 (* c0_2 (+ c3_2 (* c0_2 c4_2))))) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) (+ c1_3 (+ c2_3 (* c0_3 (+ c3_3 (* c0_3 c4_3))))))</t>
+          <t>(Vec ( + c1_0 ( + c2_0 ( * c0_0 ( + c3_0 ( * c0_0 c4_0 ) ) ) ) ) ( + c1_1 ( + c2_1 ( * c0_1 ( + c3_1 ( * c0_1 c4_1 ) ) ) ) ) ( + c1_2 ( + c2_2 ( * c0_2 ( + c3_2 ( * c0_2 c4_2 ) ) ) ) ) ( + c1_3 ( + c2_3 ( * c0_3 ( + c3_3 ( * c0_3 c4_3 ) ) ) ) ) )</t>
         </is>
       </c>
       <c r="E73" t="n">
         <v>5009</v>
       </c>
       <c r="F73" t="n">
-        <v>23583</v>
+        <v>5009</v>
       </c>
       <c r="G73" t="n">
-        <v>-370.81</v>
+        <v>0</v>
       </c>
       <c r="H73" t="n">
         <v>75.15000000000001</v>
       </c>
       <c r="I73" t="n">
-        <v>163.8</v>
+        <v>75.15000000000001</v>
       </c>
       <c r="J73" t="b">
         <v>0</v>
       </c>
       <c r="K73" t="n">
-        <v>236.2</v>
+        <v>324.85</v>
       </c>
       <c r="L73" t="n">
-        <v>75</v>
+        <v>1</v>
       </c>
     </row>
     <row r="74">
@@ -3529,29 +3529,29 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>(Vec (+ c1_0 (+ c2_0 (* c0_0 (+ c3_0 (* c0_0 c4_0))))) (+ c1_1 (+ c2_1 (* c0_1 (+ c3_1 (* c0_1 c4_1))))) (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ c1_2 (+ c2_2 (* c0_2 (+ c3_2 (* c0_2 c4_2))))) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) (+ c1_3 (+ c2_3 (* c0_3 (+ c3_3 (* c0_3 c4_3))))) (+ c1_4 (+ c2_4 (* c0_4 (+ c3_4 (* c0_4 c4_4))))) (+ c1_5 (+ c2_5 (* c0_5 (+ c3_5 (* c0_5 c4_5))))) (+ c1_6 (+ c2_6 (* c0_6 (+ c3_6 (* c0_6 c4_6))))) (+ c1_7 (+ c2_7 (* c0_7 (+ c3_7 (* c0_7 c4_7))))) (+ c1_8 (+ c2_8 (* c0_8 (+ c3_8 (* c0_8 c4_8))))) (+ c1_9 (+ c2_9 (* c0_9 (+ c3_9 (* c0_9 c4_9))))) (+ c1_10 (+ c2_10 (* c0_10 (+ c3_10 (* c0_10 c4_10))))) (+ c1_11 (+ c2_11 (* c0_11 (+ c3_11 (* c0_11 c4_11))))) (+ c1_12 (+ c2_12 (* c0_12 (+ c3_12 (* c0_12 c4_12))))) (+ c1_13 (+ c2_13 (* c0_13 (+ c3_13 (* c0_13 c4_13))))) (+ c1_14 (+ c2_14 (* c0_14 (+ c3_14 (* c0_14 c4_14))))) (+ c1_15 (+ c2_15 (* c0_15 (+ c3_15 (* c0_15 c4_15))))))</t>
+          <t>(Vec (+ c1_0 (+ c2_0 (* c0_0 (+ c3_0 (+ 0 (+ 0 (+ 0 (+ 0 (* c0_0 c4_0))))))))) (+ c1_1 (+ c2_1 (* c0_1 (+ c3_1 (+ 0 (+ 0 (+ 0 (+ 0 (* c0_1 c4_1))))))))) (+ c1_2 (+ c2_2 (* c0_2 (+ c3_2 (+ 0 (+ 0 (+ 0 (+ 0 (* c0_2 c4_2))))))))) (+ c1_3 (+ c2_3 (* c0_3 (+ c3_3 (+ 0 (+ 0 (+ 0 (+ 0 (* c0_3 c4_3))))))))) (+ c1_4 (+ c2_4 (* c0_4 (+ c3_4 (+ 0 (+ 0 (+ 0 (+ 0 (* c0_4 c4_4))))))))) (+ c1_5 (+ c2_5 (* c0_5 (+ c3_5 (+ 0 (+ 0 (+ 0 (+ 0 (* c0_5 c4_5))))))))) (+ c1_6 (+ c2_6 (* c0_6 (+ c3_6 (+ 0 (+ 0 (+ 0 (+ 0 (* c0_6 c4_6))))))))) (+ c1_7 (+ c2_7 (* c0_7 (+ c3_7 (+ 0 (+ 0 (+ 0 (+ 0 (* c0_7 c4_7))))))))) (+ c1_8 (+ c2_8 (* c0_8 (+ c3_8 (+ 0 (+ 0 (+ 0 (+ 0 (* c0_8 c4_8))))))))) (+ c1_9 (+ c2_9 (* c0_9 (+ c3_9 (+ 0 (+ 0 (+ 0 (+ 0 (* c0_9 c4_9))))))))) (+ c1_10 (+ c2_10 (* c0_10 (+ c3_10 (+ 0 (+ 0 (+ 0 (+ 0 (* c0_10 c4_10))))))))) (+ c1_11 (+ c2_11 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (* c0_11 (+ c3_11 (* c0_11 c4_11))))))))))) (+ c1_12 (+ c2_12 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (* c0_12 (+ c3_12 (* c0_12 c4_12))))))))))) (+ c1_13 (+ c2_13 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (* c0_13 (+ c3_13 (* c0_13 c4_13))))))))))) (+ c1_14 (+ c2_14 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (* c0_14 (+ c3_14 (* c0_14 c4_14))))))))))) (+ c1_15 (+ c2_15 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (* c0_15 (+ c3_15 (* c0_15 c4_15))))))))))))</t>
         </is>
       </c>
       <c r="E74" t="n">
         <v>20009</v>
       </c>
       <c r="F74" t="n">
-        <v>38583</v>
+        <v>38515</v>
       </c>
       <c r="G74" t="n">
-        <v>-92.83</v>
+        <v>-92.48999999999999</v>
       </c>
       <c r="H74" t="n">
         <v>75.15000000000001</v>
       </c>
       <c r="I74" t="n">
-        <v>163.8</v>
+        <v>82.34</v>
       </c>
       <c r="J74" t="b">
         <v>0</v>
       </c>
       <c r="K74" t="n">
-        <v>236.2</v>
+        <v>317.66</v>
       </c>
       <c r="L74" t="n">
         <v>75</v>
@@ -3571,32 +3571,32 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>(Vec (+ (+ (* (- c2_0 c1_0) (- c2_0 c1_0)) (* (- c2_1 c1_1) (- c2_1 c1_1))) (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (* (- c2_2 c1_2) (- c2_2 c1_2)) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0)))</t>
+          <t>(Vec ( + ( + ( * ( - c2_0 c1_0 ) ( - c2_0 c1_0 ) ) ( * ( - c2_1 c1_1 ) ( - c2_1 c1_1 ) ) ) ( * ( - c2_2 c1_2 ) ( - c2_2 c1_2 ) ) ) )</t>
         </is>
       </c>
       <c r="E75" t="n">
         <v>2757</v>
       </c>
       <c r="F75" t="n">
-        <v>21330</v>
+        <v>2757</v>
       </c>
       <c r="G75" t="n">
-        <v>-673.67</v>
+        <v>0</v>
       </c>
       <c r="H75" t="n">
         <v>40.57</v>
       </c>
       <c r="I75" t="n">
-        <v>128.02</v>
+        <v>40.57</v>
       </c>
       <c r="J75" t="b">
         <v>0</v>
       </c>
       <c r="K75" t="n">
-        <v>271.98</v>
+        <v>359.43</v>
       </c>
       <c r="L75" t="n">
-        <v>75</v>
+        <v>1</v>
       </c>
     </row>
     <row r="76">
@@ -3613,29 +3613,29 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>(Vec (+ (+ (* (- c2_0 c1_0) (- c2_0 c1_0)) (* (- c2_1 c1_1) (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (- c2_1 c1_1))))))))))))))) (+ (+ (* (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (- c2_2 c1_2))))))))))) (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (- c2_2 c1_2)))))))))))) (* (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (- c2_3 c1_3))))))))))) (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (- c2_3 c1_3))))))))))))) (* (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (- c2_4 c1_4)))))))))))) (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (- c2_4 c1_4))))))))))))))))</t>
+          <t>(Vec (+ (+ (* (- c2_0 c1_0) (- c2_0 c1_0)) (* (- c2_1 c1_1) (- c2_1 c1_1))) (+ (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (+ (+ (+ (+ (+ (+ (+ (+ (+ (* 1 (* 1 (* 1 (* 1 (+ (+ (+ (+ (+ (+ (+ (+ (+ (* (- c2_2 c1_2) (- c2_2 c1_2)) 0) 0) 0) 0) 0) 0) 0) 0) 0))))) 0) 0) 0) 0) 0) 0) 0) 0) (* (- c2_3 c1_3) (- c2_3 c1_3)))))))))))))))))))))))))))))))))))))))))))))))))))))))) (* (- c2_4 c1_4) (- c2_4 c1_4)))))</t>
         </is>
       </c>
       <c r="E76" t="n">
         <v>4758</v>
       </c>
       <c r="F76" t="n">
-        <v>23281</v>
+        <v>23389</v>
       </c>
       <c r="G76" t="n">
-        <v>-389.3</v>
+        <v>-391.57</v>
       </c>
       <c r="H76" t="n">
         <v>41.77</v>
       </c>
       <c r="I76" t="n">
-        <v>455.54</v>
+        <v>2033.25</v>
       </c>
       <c r="J76" t="b">
         <v>1</v>
       </c>
       <c r="K76" t="n">
-        <v>-55.54</v>
+        <v>-1633.25</v>
       </c>
       <c r="L76" t="n">
         <v>75</v>
@@ -3655,29 +3655,29 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>(Vec (+ (+ (+ (+ (* (- c2_0 c1_0) (- c2_0 c1_0)) (* (- c2_1 c1_1) (- c2_1 c1_1))) (+ (* (- c2_2 c1_2) (- c2_2 c1_2)) (* (- c2_3 c1_3) (- c2_3 c1_3)))) (+ (+ (* (- c2_4 c1_4) (- c2_4 c1_4)) (* (- c2_5 c1_5) (- c2_5 c1_5))) (+ (* (- c2_6 c1_6) (- c2_6 c1_6)) (* (- c2_7 c1_7) (- c2_7 c1_7))))) (+ (+ (+ (* (- c2_8 c1_8) (- c2_8 c1_8)) (* (- c2_9 c1_9) (- c2_9 c1_9))) (+ (* (- c2_10 c1_10) (- c2_10 c1_10)) (* (- c2_11 c1_11) (- c2_11 c1_11)))) (+ (+ (* (- c2_12 c1_12) (- c2_12 c1_12)) (* (- c2_13 c1_13) (- c2_13 c1_13))) (+ (* (- c2_14 c1_14) (- c2_14 c1_14)) (* (- c2_15 c1_15) (- c2_15 c1_15)))))))</t>
+          <t>(Vec (+ (+ (+ (+ (* (- c2_0 c1_0) (- c2_0 c1_0)) (* (- c2_1 c1_1) (- c2_1 c1_1))) (+ (* (- c2_2 c1_2) (- c2_2 c1_2)) (* (- c2_3 c1_3) (- c2_3 c1_3)))) (+ (+ (* (- c2_4 c1_4) (- c2_4 c1_4)) (* (- c2_5 c1_5) (- c2_5 c1_5))) (+ (* (- c2_6 c1_6) (- c2_6 c1_6)) (* (- c2_7 c1_7) (- c2_7 c1_7))))) (+ (+ (+ (* (- c2_8 c1_8) (- c2_8 c1_8)) (* (- c2_9 c1_9) (- c2_9 c1_9))) (+ (* (- c2_10 c1_10) (- c2_10 c1_10)) (* (- c2_11 c1_11) (- c2_11 c1_11)))) (+ (+ (* (- c2_12 c1_12) (- c2_12 c1_12)) (* (- c2_13 c1_13) (- c2_13 c1_13))) (+ (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (* (- c2_14 c1_14) (- c2_14 c1_14))))))))))))))))))))))))))))))))))))))) (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (* (- c2_15 c1_15) (- c2_15 c1_15))))))))))))))))))))))))))))))))))))))))))))</t>
         </is>
       </c>
       <c r="E77" t="n">
         <v>15759</v>
       </c>
       <c r="F77" t="n">
-        <v>15759</v>
+        <v>34296</v>
       </c>
       <c r="G77" t="n">
-        <v>0</v>
+        <v>-117.63</v>
       </c>
       <c r="H77" t="n">
         <v>42.97</v>
       </c>
       <c r="I77" t="n">
-        <v>42.97</v>
+        <v>87.29000000000001</v>
       </c>
       <c r="J77" t="b">
         <v>0</v>
       </c>
       <c r="K77" t="n">
-        <v>357.03</v>
+        <v>312.71</v>
       </c>
       <c r="L77" t="n">
         <v>75</v>
@@ -3697,29 +3697,29 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>(Vec (+ (+ (* v1_0 v2_0) (* v1_1 v2_1)) (* v1_2 v2_2)))</t>
+          <t>(Vec (+ (+ (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (* v1_0 v2_0)))))))))))))))))))))))))) (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (* v1_1 v2_1)))))))))))))))))))))))))) (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (* v1_2 v2_2))))))))))))))))))))))))))))</t>
         </is>
       </c>
       <c r="E78" t="n">
         <v>1256</v>
       </c>
       <c r="F78" t="n">
-        <v>1256</v>
+        <v>19781</v>
       </c>
       <c r="G78" t="n">
-        <v>0</v>
+        <v>-1474.92</v>
       </c>
       <c r="H78" t="n">
         <v>39.37</v>
       </c>
       <c r="I78" t="n">
-        <v>39.37</v>
+        <v>69.31999999999999</v>
       </c>
       <c r="J78" t="b">
         <v>0</v>
       </c>
       <c r="K78" t="n">
-        <v>360.63</v>
+        <v>330.68</v>
       </c>
       <c r="L78" t="n">
         <v>75</v>
@@ -3739,29 +3739,29 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>(Vec (+ (+ (* v1_0 v2_0) (* v1_1 v2_1)) (+ (+ (* v1_2 v2_2) (* v1_3 v2_3)) (* v1_4 (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* v2_4 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1)))))</t>
+          <t>(Vec (+ (+ (* v1_0 v2_0) (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (* v1_1 v2_1))))))))))))))))))))))) (+ (+ (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (* v1_2 v2_2))))))))))))))) (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (* v1_3 v2_3))))))))))))))))))))) (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (* v1_4 v2_4))))))))))))))))))))))))</t>
         </is>
       </c>
       <c r="E79" t="n">
         <v>2257</v>
       </c>
       <c r="F79" t="n">
-        <v>20904</v>
+        <v>20777</v>
       </c>
       <c r="G79" t="n">
-        <v>-826.1900000000001</v>
+        <v>-820.5599999999999</v>
       </c>
       <c r="H79" t="n">
         <v>40.57</v>
       </c>
       <c r="I79" t="n">
-        <v>2598.36</v>
+        <v>64.53</v>
       </c>
       <c r="J79" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K79" t="n">
-        <v>-2198.36</v>
+        <v>335.47</v>
       </c>
       <c r="L79" t="n">
         <v>75</v>
@@ -3781,32 +3781,32 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>(Vec (+ (+ (+ (+ (* v1_0 v2_0) (* v1_1 v2_1)) (+ (* v1_2 v2_2) (* v1_3 v2_3))) (+ (+ (* v1_4 v2_4) (* v1_5 v2_5)) (+ (* v1_6 v2_6) (* v1_7 v2_7)))) (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (* v1_8 v2_8) (* v1_9 v2_9)) (+ (* v1_10 v2_10) (* v1_11 v2_11))) (+ (+ (* v1_12 v2_12) (* v1_13 v2_13)) (+ (* v1_14 v2_14) (* v1_15 v2_15)))) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0)))</t>
+          <t>(Vec ( + ( + ( + ( + ( * v1_0 v2_0 ) ( * v1_1 v2_1 ) ) ( + ( * v1_2 v2_2 ) ( * v1_3 v2_3 ) ) ) ( + ( + ( * v1_4 v2_4 ) ( * v1_5 v2_5 ) ) ( + ( * v1_6 v2_6 ) ( * v1_7 v2_7 ) ) ) ) ( + ( + ( + ( * v1_8 v2_8 ) ( * v1_9 v2_9 ) ) ( + ( * v1_10 v2_10 ) ( * v1_11 v2_11 ) ) ) ( + ( + ( * v1_12 v2_12 ) ( * v1_13 v2_13 ) ) ( + ( * v1_14 v2_14 ) ( * v1_15 v2_15 ) ) ) ) ) )</t>
         </is>
       </c>
       <c r="E80" t="n">
         <v>7758</v>
       </c>
       <c r="F80" t="n">
-        <v>26332</v>
+        <v>7758</v>
       </c>
       <c r="G80" t="n">
-        <v>-239.42</v>
+        <v>0</v>
       </c>
       <c r="H80" t="n">
         <v>41.77</v>
       </c>
       <c r="I80" t="n">
-        <v>130.42</v>
+        <v>41.77</v>
       </c>
       <c r="J80" t="b">
         <v>0</v>
       </c>
       <c r="K80" t="n">
-        <v>269.58</v>
+        <v>358.23</v>
       </c>
       <c r="L80" t="n">
-        <v>75</v>
+        <v>1</v>
       </c>
     </row>
     <row r="81">
@@ -3823,29 +3823,29 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>(Vec (+ in_1_1 (* in_0_1 2)) (+ (+ in_1_2 (- in_1_0)) (+ (* in_0_2 2) (* in_0_0 -2))) (+ (- in_1_1) (* in_0_1 -2)) (+ in_2_1 (+ in_0_1 (* in_1_1 2))) (+ (+ in_2_2 (- in_2_0)) (+ (+ in_0_2 (- in_0_0)) (+ (* in_1_2 2) (* in_1_0 -2)))) (+ (- in_2_1) (+ (- in_0_1) (* in_1_1 -2))) (+ in_1_1 (* in_2_1 2)) (+ (+ in_1_2 (- in_1_0)) (+ (* in_2_2 2) (* in_2_0 -2))) (+ (- in_1_1) (* in_2_1 -2)))</t>
+          <t>(Vec (+ in_1_1 (* in_0_1 2)) (+ (+ in_1_2 (- in_1_0)) (+ (* in_0_2 2) (* in_0_0 -2))) (+ (- in_1_1) (* in_0_1 -2)) (+ in_2_1 (+ in_0_1 (* in_1_1 2))) (+ (+ in_2_2 (- in_2_0)) (+ (+ in_0_2 (- in_0_0)) (+ (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (* in_1_2 2)))))))))))))))))))))))))))))))))))))) (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (* in_1_0 -2))))))))))))))))))))))))))))))))))))))))) (+ (- in_2_1) (+ (- in_0_1) (* in_1_1 -2))) (+ in_1_1 (* in_2_1 2)) (+ (+ in_1_2 (- in_1_0)) (+ (* in_2_2 2) (* in_2_0 -2))) (+ (- in_1_1) (* in_2_1 -2)))</t>
         </is>
       </c>
       <c r="E81" t="n">
         <v>9757</v>
       </c>
       <c r="F81" t="n">
-        <v>9757</v>
+        <v>28294</v>
       </c>
       <c r="G81" t="n">
-        <v>0</v>
+        <v>-189.99</v>
       </c>
       <c r="H81" t="n">
         <v>40.57</v>
       </c>
       <c r="I81" t="n">
-        <v>40.57</v>
+        <v>84.90000000000001</v>
       </c>
       <c r="J81" t="b">
         <v>0</v>
       </c>
       <c r="K81" t="n">
-        <v>359.43</v>
+        <v>315.1</v>
       </c>
       <c r="L81" t="n">
         <v>75</v>
@@ -3865,29 +3865,29 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>(Vec (+ in_1_1 (* in_0_1 2)) (+ (+ in_1_2 (- in_1_0)) (+ (* in_0_2 2) (* in_0_0 -2))) (+ (+ in_1_3 (- in_1_1)) (+ (* in_0_3 2) (* in_0_1 -2))) (+ (+ in_1_4 (- in_1_2)) (+ (* in_0_4 2) (* in_0_2 -2))) (+ (- in_1_3) (* in_0_3 -2)) (+ in_2_1 (+ in_0_1 (* in_1_1 2))) (+ (+ in_2_2 (- in_2_0)) (+ (+ in_0_2 (- in_0_0)) (+ (* in_1_2 2) (* in_1_0 -2)))) (+ (+ in_2_3 (- in_2_1)) (+ (+ in_0_3 (- in_0_1)) (+ (* in_1_3 2) (* in_1_1 -2)))) (+ (+ in_2_4 (- in_2_2)) (+ (+ in_0_4 (- in_0_2)) (+ (* in_1_4 2) (* in_1_2 -2)))) (+ (- in_2_3) (+ (- in_0_3) (* in_1_3 -2))) (+ in_3_1 (+ in_1_1 (* in_2_1 2))) (+ (+ in_3_2 (- in_3_0)) (+ (+ in_1_2 (- in_1_0)) (+ (* in_2_2 2) (* in_2_0 -2)))) (+ (+ in_3_3 (- in_3_1)) (+ (+ in_1_3 (- in_1_1)) (+ (* in_2_3 2) (* in_2_1 -2)))) (+ (+ in_3_4 (- in_3_2)) (+ (+ in_1_4 (- in_1_2)) (+ (* in_2_4 2) (* in_2_2 -2)))) (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (+ (- in_3_3) (+ (- in_1_3) (* in_2_3 -2))) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) (+ in_4_1 (+ in_2_1 (* in_3_1 2))) (+ (+ in_4_2 (- in_4_0)) (+ (+ in_2_2 (- in_2_0)) (+ (* in_3_2 2) (* in_3_0 -2)))) (+ (+ in_4_3 (- in_4_1)) (+ (+ in_2_3 (- in_2_1)) (+ (* in_3_3 2) (* in_3_1 -2)))) (+ (+ in_4_4 (- in_4_2)) (+ (+ in_2_4 (- in_2_2)) (+ (* in_3_4 2) (* in_3_2 -2)))) (+ (- in_4_3) (+ (- in_2_3) (* in_3_3 -2))) (+ in_3_1 (* in_4_1 2)) (+ (+ in_3_2 (- in_3_0)) (+ (* in_4_2 2) (* in_4_0 -2))) (+ (+ in_3_3 (- in_3_1)) (+ (* in_4_3 2) (* in_4_1 -2))) (+ (+ in_3_4 (- in_3_2)) (+ (* in_4_4 2) (* in_4_2 -2))) (+ (- in_3_3) (* in_4_3 -2)))</t>
+          <t>(Vec (+ in_1_1 (* in_0_1 2)) (+ (+ in_1_2 (- in_1_0)) (+ (* in_0_2 2) (+ 0 (+ 0 (+ 0 (* in_0_0 -2)))))) (+ (+ in_1_3 (- in_1_1)) (+ (+ 0 (+ 0 (+ 0 (* in_0_3 2)))) (+ 0 (+ 0 (+ 0 (* in_0_1 -2)))))) (+ (+ in_1_4 (- in_1_2)) (+ (+ 0 (+ 0 (+ 0 (* in_0_4 2)))) (+ 0 (+ 0 (+ 0 (* in_0_2 -2)))))) (+ (- in_1_3) (* in_0_3 -2)) (+ in_2_1 (+ in_0_1 (+ 0 (+ 0 (+ 0 (* in_1_1 2)))))) (+ (+ in_2_2 (- in_2_0)) (+ (+ in_0_2 (- in_0_0)) (+ (+ 0 (+ 0 (* in_1_2 2))) (+ 0 (+ 0 (* in_1_0 -2)))))) (+ (+ in_2_3 (- in_2_1)) (+ (+ in_0_3 (- in_0_1)) (+ (+ 0 (+ 0 (* in_1_3 2))) (+ 0 (+ 0 (* in_1_1 -2)))))) (+ (+ in_2_4 (- in_2_2)) (+ (+ in_0_4 (- in_0_2)) (+ (+ 0 (+ 0 (* in_1_4 2))) (+ 0 (+ 0 (* in_1_2 -2)))))) (+ (- in_2_3) (+ (- in_0_3) (+ 0 (+ 0 (+ 0 (* in_1_3 -2)))))) (+ in_3_1 (+ in_1_1 (+ 0 (+ 0 (+ 0 (* in_2_1 2)))))) (+ (+ in_3_2 (- in_3_0)) (+ (+ in_1_2 (- in_1_0)) (+ (+ 0 (+ 0 (* in_2_2 2))) (+ 0 (+ 0 (* in_2_0 -2)))))) (+ (+ in_3_3 (- in_3_1)) (+ (+ in_1_3 (- in_1_1)) (+ (+ 0 (+ 0 (* in_2_3 2))) (+ 0 (+ 0 (* in_2_1 -2)))))) (+ (+ in_3_4 (- in_3_2)) (+ (+ in_1_4 (- in_1_2)) (+ (+ 0 (+ 0 (* in_2_4 2))) (+ 0 (+ 0 (* in_2_2 -2)))))) (+ (- in_3_3) (+ (- in_1_3) (+ 0 (+ 0 (+ 0 (* in_2_3 -2)))))) (+ in_4_1 (+ in_2_1 (+ 0 (+ 0 (+ 0 (* in_3_1 2)))))) (+ (+ in_4_2 (- in_4_0)) (+ (+ in_2_2 (- in_2_0)) (+ (+ 0 (* in_3_2 2)) (+ 0 (* in_3_0 -2))))) (+ (+ in_4_3 (- in_4_1)) (+ (+ in_2_3 (- in_2_1)) (+ (+ 0 (* in_3_3 2)) (+ 0 (* in_3_1 -2))))) (+ (+ in_4_4 (- in_4_2)) (+ (+ in_2_4 (- in_2_2)) (+ (+ 0 (* in_3_4 2)) (+ 0 (* in_3_2 -2))))) (+ (- in_4_3) (+ (- in_2_3) (+ 0 (+ 0 (* in_3_3 -2))))) (+ in_3_1 (* in_4_1 2)) (+ (+ in_3_2 (- in_3_0)) (+ (+ 0 (+ 0 (* in_4_2 2))) (+ 0 (+ 0 (* in_4_0 -2))))) (+ (+ in_3_3 (- in_3_1)) (+ (+ 0 (+ 0 (* in_4_3 2))) (+ 0 (+ 0 (* in_4_1 -2))))) (+ (+ in_3_4 (- in_3_2)) (+ (+ 0 (+ 0 (* in_4_4 2))) (+ 0 (+ 0 (* in_4_2 -2))))) (+ (- in_3_3) (* in_4_3 -2)))</t>
         </is>
       </c>
       <c r="E82" t="n">
         <v>37757</v>
       </c>
       <c r="F82" t="n">
-        <v>56404</v>
+        <v>56259</v>
       </c>
       <c r="G82" t="n">
-        <v>-49.39</v>
+        <v>-49</v>
       </c>
       <c r="H82" t="n">
         <v>40.57</v>
       </c>
       <c r="I82" t="n">
-        <v>2598.36</v>
+        <v>42.97</v>
       </c>
       <c r="J82" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K82" t="n">
-        <v>-2198.36</v>
+        <v>357.03</v>
       </c>
       <c r="L82" t="n">
         <v>75</v>
@@ -3907,17 +3907,17 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>(VecAdd (VecAdd (Vec (* a_0_0 b_0_0) (* a_0_0 b_0_1) (* a_0_0 b_0_2) (* a_0_0 b_0_3) (* a_1_0 b_0_0) (* a_1_0 b_0_1) (* a_1_0 b_0_2) (* a_1_0 b_0_3) (* a_2_0 b_0_0) (* a_2_0 b_0_1) (* a_2_0 b_0_2) (* a_2_0 b_0_3) (* a_3_0 b_0_0) (* a_3_0 b_0_1) (* a_3_0 b_0_2) (* a_3_0 b_0_3)) (Vec (* a_0_1 b_1_0) (* a_0_1 b_1_1) (* a_0_1 b_1_2) (* a_0_1 b_1_3) (* a_1_1 b_1_0) (* a_1_1 b_1_1) (* a_1_1 b_1_2) (* a_1_1 b_1_3) (* a_2_1 b_1_0) (* a_2_1 b_1_1) (* a_2_1 b_1_2) (* a_2_1 b_1_3) (* a_3_1 b_1_0) (* a_3_1 b_1_1) (* a_3_1 b_1_2) (* a_3_1 b_1_3))) (VecAdd (Vec (* a_0_2 b_2_0) (* a_0_2 b_2_1) (* a_0_2 b_2_2) (* a_0_2 b_2_3) (* a_1_2 b_2_0) (* a_1_2 b_2_1) (* a_1_2 b_2_2) (* a_1_2 b_2_3) (* a_2_2 b_2_0) (* a_2_2 b_2_1) (* a_2_2 b_2_2) (* a_2_2 b_2_3) (* a_3_2 b_2_0) (* a_3_2 b_2_1) (* a_3_2 b_2_2) (* a_3_2 b_2_3)) (Vec (* a_0_3 b_3_0) (* a_0_3 b_3_1) (* a_0_3 b_3_2) (* a_0_3 b_3_3) (* a_1_3 b_3_0) (* a_1_3 b_3_1) (* a_1_3 b_3_2) (* a_1_3 b_3_3) (* a_2_3 b_3_0) (* a_2_3 b_3_1) (* a_2_3 b_3_2) (* a_2_3 b_3_3) (* a_3_3 b_3_0) (* a_3_3 b_3_1) (* a_3_3 b_3_2) (* a_3_3 b_3_3))))</t>
+          <t>(Vec ( + ( + ( * a_0_0 b_0_0 ) ( * a_0_1 b_1_0 ) ) ( + ( * a_0_2 b_2_0 ) ( * a_0_3 b_3_0 ) ) ) ( + ( + ( * a_0_0 b_0_1 ) ( * a_0_1 b_1_1 ) ) ( + ( * a_0_2 b_2_1 ) ( * a_0_3 b_3_1 ) ) ) ( + ( + ( * a_0_0 b_0_2 ) ( * a_0_1 b_1_2 ) ) ( + ( * a_0_2 b_2_2 ) ( * a_0_3 b_3_2 ) ) ) ( + ( + ( * a_0_0 b_0_3 ) ( * a_0_1 b_1_3 ) ) ( + ( * a_0_2 b_2_3 ) ( * a_0_3 b_3_3 ) ) ) ( + ( + ( * a_1_0 b_0_0 ) ( * a_1_1 b_1_0 ) ) ( + ( * a_1_2 b_2_0 ) ( * a_1_3 b_3_0 ) ) ) ( + ( + ( * a_1_0 b_0_1 ) ( * a_1_1 b_1_1 ) ) ( + ( * a_1_2 b_2_1 ) ( * a_1_3 b_3_1 ) ) ) ( + ( + ( * a_1_0 b_0_2 ) ( * a_1_1 b_1_2 ) ) ( + ( * a_1_2 b_2_2 ) ( * a_1_3 b_3_2 ) ) ) ( + ( + ( * a_1_0 b_0_3 ) ( * a_1_1 b_1_3 ) ) ( + ( * a_1_2 b_2_3 ) ( * a_1_3 b_3_3 ) ) ) ( + ( + ( * a_2_0 b_0_0 ) ( * a_2_1 b_1_0 ) ) ( + ( * a_2_2 b_2_0 ) ( * a_2_3 b_3_0 ) ) ) ( + ( + ( * a_2_0 b_0_1 ) ( * a_2_1 b_1_1 ) ) ( + ( * a_2_2 b_2_1 ) ( * a_2_3 b_3_1 ) ) ) ( + ( + ( * a_2_0 b_0_2 ) ( * a_2_1 b_1_2 ) ) ( + ( * a_2_2 b_2_2 ) ( * a_2_3 b_3_2 ) ) ) ( + ( + ( * a_2_0 b_0_3 ) ( * a_2_1 b_1_3 ) ) ( + ( * a_2_2 b_2_3 ) ( * a_2_3 b_3_3 ) ) ) ( + ( + ( * a_3_0 b_0_0 ) ( * a_3_1 b_1_0 ) ) ( + ( * a_3_2 b_2_0 ) ( * a_3_3 b_3_0 ) ) ) ( + ( + ( * a_3_0 b_0_1 ) ( * a_3_1 b_1_1 ) ) ( + ( * a_3_2 b_2_1 ) ( * a_3_3 b_3_1 ) ) ) ( + ( + ( * a_3_0 b_0_2 ) ( * a_3_1 b_1_2 ) ) ( + ( * a_3_2 b_2_2 ) ( * a_3_3 b_3_2 ) ) ) ( + ( + ( * a_3_0 b_0_3 ) ( * a_3_1 b_1_3 ) ) ( + ( * a_3_2 b_2_3 ) ( * a_3_3 b_3_3 ) ) ) )</t>
         </is>
       </c>
       <c r="E83" t="n">
         <v>28006</v>
       </c>
       <c r="F83" t="n">
-        <v>16009</v>
+        <v>28006</v>
       </c>
       <c r="G83" t="n">
-        <v>42.84</v>
+        <v>0</v>
       </c>
       <c r="H83" t="n">
         <v>39.37</v>
@@ -3932,7 +3932,7 @@
         <v>360.63</v>
       </c>
       <c r="L83" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="84">
@@ -3949,29 +3949,29 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>(Vec (+ (* (+ (* (+ (* o4 (- 1 c34)) (* c34 o3)) (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (- 1 c23) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1)) (* c23 (+ (* o4 (- 1 c24)) (* c24 o2)))) (- 1 c12)) (* c12 (+ (* (+ (* o4 (- 1 c34)) (* c34 o3)) (- 1 c13)) (* c13 (+ (* o4 (- 1 c14)) (* c14 o1)))))))</t>
+          <t>(Vec (+ (* (+ (* (+ (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (* o4 (- 1 c34))))))))))))) (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (* c34 o3))))))))))))) (- 1 c23)) (* c23 (+ (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (* o4 (- 1 c24)))))))))))) (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (* c24 o2)))))))))))))) (- 1 c12)) (* c12 (+ (* (+ (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (* o4 (- 1 c34)))))))))))) (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (* c34 o3)))))))))))) (- 1 c13)) (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (* c13 (+ (* o4 (- 1 c14)) (* c14 o1)))))))))))))))))))</t>
         </is>
       </c>
       <c r="E84" t="n">
         <v>7012</v>
       </c>
       <c r="F84" t="n">
-        <v>25657</v>
+        <v>25524</v>
       </c>
       <c r="G84" t="n">
-        <v>-265.9</v>
+        <v>-264</v>
       </c>
       <c r="H84" t="n">
         <v>110.93</v>
       </c>
       <c r="I84" t="n">
-        <v>2634.14</v>
+        <v>125.31</v>
       </c>
       <c r="J84" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K84" t="n">
-        <v>-2234.14</v>
+        <v>274.69</v>
       </c>
       <c r="L84" t="n">
         <v>75</v>
@@ -3991,29 +3991,29 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>(Vec (+ (* (+ (* (+ (* o3214 (- 1 c34)) (* c34 (+ (* (+ (* o4321 (- 1 c34)) (* c34 o3421)) (- 1 c24)) (* c24 (+ (* o3241 (- 1 c14)) (* c14 o3214)))))) (- 1 c23)) (* c23 (+ (* (+ (* o2314 (- 1 c24)) (* c24 (+ (* (- 1 c34) (+ (* o4231 (- 1 c24)) (* c24 o2431))) (* c34 (+ (* o2341 (- 1 c14)) (* c14 o2314)))))) (- 1 c13)) (* c13 (+ (* o2134 (- 1 c24)) (* c24 (+ (* (- 1 c14) (+ (* o4213 (- 1 c24)) (* c24 o2413))) (* c14 (+ (* o2143 (- 1 c34)) (* c34 o2134)))))))))) (- 1 c12)) (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (* c12 (+ (* (- 1 c13) (+ (* o3124 (- 1 c34)) (* c34 (+ (* (- 1 c14) (+ (* o4312 (- 1 c34)) (* c34 o3412))) (* c14 (+ (* o3142 (- 1 c24)) (* c24 o3124))))))) (* c13 (+ (* (- 1 c23) (+ (* o1324 (- 1 c14)) (* c14 (+ (* (- 1 c34) (+ (* o4132 (- 1 c14)) (* c14 o1432))) (* c34 (+ (* o1342 (- 1 c24)) (* c24 o1324))))))) (* c23 (+ (* o1234 (- 1 c14)) (* c14 (+ (* (- 1 c24) (+ (* o4123 (- 1 c14)) (* c14 o1423))) (* c24 (+ (* o1243 (- 1 c34)) (* c34 o1234))))))))))) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0)))</t>
+          <t>(Vec (+ (* (+ (* (+ (* o3214 (- 1 c34)) (* c34 (+ (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (* (+ (* o4321 (- 1 c34)) (* c34 o3421)) (- 1 c24)))))))))) (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (* c24 (+ (* o3241 (- 1 c14)) (* c14 o3214)))))))))))))) (- 1 c23)) (* c23 (+ (* (+ (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (* o2314 (- 1 c24)))))))))) (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (* c24 (+ (* (- 1 c34) (+ (* o4231 (- 1 c24)) (* c24 o2431))) (* c34 (+ (* o2341 (- 1 c14)) (* c14 o2314)))))))))))))) (- 1 c13)) (* c13 (+ (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (* o2134 (- 1 c24)))))))))) (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (* c24 (+ (* (- 1 c14) (+ (* o4213 (- 1 c24)) (* c24 o2413))) (* c14 (+ (* o2143 (- 1 c34)) (* c34 o2134))))))))))))))))) (- 1 c12)) (* c12 (+ (* (- 1 c13) (+ (* o3124 (- 1 c34)) (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (* c34 (+ (* (- 1 c14) (+ (* o4312 (- 1 c34)) (* c34 o3412))) (* c14 (+ (* o3142 (- 1 c24)) (* c24 o3124)))))))))))))))) (* c13 (+ (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (* (- 1 c23) (+ (* o1324 (- 1 c14)) (* c14 (+ (* (- 1 c34) (+ (* o4132 (- 1 c14)) (* c14 o1432))) (* c34 (+ (* o1342 (- 1 c24)) (* c24 o1324)))))))))))))))) (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (* c23 (+ (* o1234 (- 1 c14)) (* c14 (+ (* (- 1 c24) (+ (* o4123 (- 1 c14)) (* c14 o1423))) (* c24 (+ (* o1243 (- 1 c34)) (* c34 o1234))))))))))))))))))))))</t>
         </is>
       </c>
       <c r="E85" t="n">
         <v>29021</v>
       </c>
       <c r="F85" t="n">
-        <v>47595</v>
+        <v>47530</v>
       </c>
       <c r="G85" t="n">
-        <v>-64</v>
+        <v>-63.78</v>
       </c>
       <c r="H85" t="n">
         <v>218.27</v>
       </c>
       <c r="I85" t="n">
-        <v>306.92</v>
+        <v>229.05</v>
       </c>
       <c r="J85" t="b">
         <v>0</v>
       </c>
       <c r="K85" t="n">
-        <v>93.08</v>
+        <v>170.95</v>
       </c>
       <c r="L85" t="n">
         <v>75</v>
@@ -4033,29 +4033,29 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>(VecMul (Vec (* (* (+ (* (* x10106 x10108) x10110) x10112) x10115) (* x10117 x10119)) (+ (+ x10121 (* x10125 (+ (+ (* (* x10146 x10147) (* (+ x10149 x10150) x10152)) (* (* (* x10132 x10133) (+ x10135 x10136)) (+ (* x10139 x10140) x10142))) (+ (+ x10154 (* (* x10159 (+ (+ x10162 x10163) x10165)) x10167)) (+ (+ x10170 x10173) (+ x10176 x10178)))))) (+ x10181 x10183))) (&lt;&lt; (Vec (* (* (+ (* (* x10106 x10108) x10110) x10112) x10115) (* x10117 x10119)) (+ (+ x10121 (* x10125 (+ (+ (* (* x10146 x10147) (* (+ x10149 x10150) x10152)) (* (* (* x10132 x10133) (+ x10135 x10136)) (+ (* x10139 x10140) x10142))) (+ (+ x10154 (* (* x10159 (+ (+ x10162 x10163) x10165)) x10167)) (+ (+ x10170 x10173) (+ x10176 x10178)))))) (+ x10181 x10183))) 1))</t>
+          <t>(Vec (* (* (* (+ (* (* x10106 x10108) x10110) x10112) x10115) (* x10117 x10119)) (+ (+ x10121 (* x10125 (+ (+ (* (* (* x10132 x10133) (+ x10135 x10136)) (+ (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (* x10139 x10140)))))))))))))))))))))))))))))))))))))) x10142)) (* (* x10146 x10147) (* (+ x10149 x10150) x10152))) (+ (+ x10154 (* (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (* x10159 (+ (+ x10162 x10163) x10165))))))))))))))))))))))))))))))))))))))) x10167)) (+ (+ x10170 x10173) (+ x10176 x10178)))))) (+ x10181 x10183))))</t>
         </is>
       </c>
       <c r="E86" t="n">
         <v>8018</v>
       </c>
       <c r="F86" t="n">
-        <v>7920</v>
+        <v>26555</v>
       </c>
       <c r="G86" t="n">
-        <v>1.22</v>
+        <v>-231.19</v>
       </c>
       <c r="H86" t="n">
         <v>182.49</v>
       </c>
       <c r="I86" t="n">
-        <v>183.69</v>
+        <v>226.81</v>
       </c>
       <c r="J86" t="b">
         <v>0</v>
       </c>
       <c r="K86" t="n">
-        <v>216.31</v>
+        <v>173.19</v>
       </c>
       <c r="L86" t="n">
         <v>75</v>
@@ -4075,29 +4075,29 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>(VecMul (Vec (+ (* (* (* x9604 x9605) (* x9607 x9608)) (* (* x9611 x9612) (* x9614 x9615))) (* (* (* x9619 x9620) (* x9622 x9623)) (* (* x9626 x9627) (* x9629 x9630)))) (+ (* (* (* x9649 x9650) (* x9652 x9653)) (* (* x9656 x9657) (* x9659 x9660))) (* (* (* x9634 x9635) (* x9637 x9638)) (* (* x9641 x9642) (* x9644 x9645))))) (&lt;&lt; (Vec (+ (* (* (* x9604 x9605) (* x9607 x9608)) (* (* x9611 x9612) (* x9614 x9615))) (* (* (* x9619 x9620) (* x9622 x9623)) (* (* x9626 x9627) (* x9629 x9630)))) (+ (* (* (* x9649 x9650) (* x9652 x9653)) (* (* x9656 x9657) (* x9659 x9660))) (* (* (* x9634 x9635) (* x9637 x9638)) (* (* x9641 x9642) (* x9644 x9645))))) 1))</t>
+          <t>(Vec (* (+ (* (* (* x9604 x9605) (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (* x9607 x9608))))))) (* (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (* x9611 x9612)))))) (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (* x9614 x9615)))))))) (* (* (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (* x9619 x9620)))))) (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (* x9622 x9623))))))) (* (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (* x9626 x9627)))))) (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (* x9629 x9630))))))))) (+ (* (* (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (* x9634 x9635)))))) (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (* x9637 x9638))))))) (* (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (* x9641 x9642)))))) (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (* x9644 x9645)))))))) (* (* (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (* x9649 x9650)))))) (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (* x9652 x9653))))))) (* (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (* x9656 x9657)))))) (+ 0 (+ 0 (+ 0 (+ 0 (* x9659 x9660))))))))))</t>
         </is>
       </c>
       <c r="E87" t="n">
         <v>7761</v>
       </c>
       <c r="F87" t="n">
-        <v>7663</v>
+        <v>26266</v>
       </c>
       <c r="G87" t="n">
-        <v>1.26</v>
+        <v>-238.44</v>
       </c>
       <c r="H87" t="n">
         <v>141.92</v>
       </c>
       <c r="I87" t="n">
-        <v>143.12</v>
+        <v>147.91</v>
       </c>
       <c r="J87" t="b">
         <v>0</v>
       </c>
       <c r="K87" t="n">
-        <v>256.88</v>
+        <v>252.09</v>
       </c>
       <c r="L87" t="n">
         <v>75</v>
@@ -4117,29 +4117,29 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>(Vec (+ (+ in_1_1 in_1_0) (+ in_0_1 in_0_0)) (+ (+ (+ in_1_2 in_1_1) (+ in_1_0 in_0_2)) (+ in_0_1 in_0_0)) (+ (+ in_1_2 in_1_1) (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (+ in_0_2 in_0_1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1)) (+ (+ (+ in_2_1 in_2_0) (+ in_1_1 in_1_0)) (+ in_0_1 in_0_0)) (+ (+ (+ in_2_2 (+ in_2_1 in_2_0)) (+ in_1_2 in_1_1)) (+ (+ in_1_0 in_0_2) (+ in_0_1 in_0_0))) (+ (+ (+ in_2_2 in_2_1) (+ in_1_2 in_1_1)) (+ in_0_2 in_0_1)) (+ (+ in_2_1 in_2_0) (+ in_1_1 in_1_0)) (+ (+ (+ in_2_2 in_2_1) (+ in_2_0 in_1_2)) (+ in_1_1 in_1_0)) (+ (+ in_2_2 in_2_1) (+ in_1_2 in_1_1)))</t>
+          <t>(Vec (+ (+ in_1_1 in_1_0) (+ in_0_1 in_0_0)) (- (- (- (- (- (- (- (- (- (- (+ (+ (+ in_1_2 in_1_1) (+ in_1_0 in_0_2)) (+ in_0_1 in_0_0)) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) (+ (+ in_1_2 in_1_1) (+ in_0_2 in_0_1)) (+ (+ (+ in_2_1 in_2_0) (+ in_1_1 in_1_0)) (+ in_0_1 in_0_0)) (+ (+ (+ in_2_2 (+ in_2_1 in_2_0)) (+ in_1_2 in_1_1)) (+ (+ in_1_0 in_0_2) (+ in_0_1 in_0_0))) (+ (+ (+ in_2_2 in_2_1) (+ in_1_2 in_1_1)) (+ in_0_2 in_0_1)) (+ (+ in_2_1 in_2_0) (+ in_1_1 in_1_0)) (+ (+ (+ in_2_2 in_2_1) (+ in_2_0 in_1_2)) (+ in_1_1 in_1_0)) (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (+ (+ in_2_2 in_2_1) (+ in_1_2 in_1_1)) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0))</t>
         </is>
       </c>
       <c r="E88" t="n">
         <v>10006</v>
       </c>
       <c r="F88" t="n">
-        <v>28652</v>
+        <v>28568</v>
       </c>
       <c r="G88" t="n">
-        <v>-186.35</v>
+        <v>-185.51</v>
       </c>
       <c r="H88" t="n">
         <v>7.19</v>
       </c>
       <c r="I88" t="n">
-        <v>2563.78</v>
+        <v>81.45999999999999</v>
       </c>
       <c r="J88" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K88" t="n">
-        <v>-2063.78</v>
+        <v>418.54</v>
       </c>
       <c r="L88" t="n">
         <v>75</v>
@@ -4159,32 +4159,32 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>(Vec (+ (+ in_1_1 in_1_0) (+ in_0_1 in_0_0)) (+ (+ (+ in_1_2 in_1_1) (+ in_1_0 in_0_2)) (+ in_0_1 in_0_0)) (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ in_1_3 in_1_2) (+ in_1_1 in_0_3)) (+ in_0_2 in_0_1)) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) (+ (+ (+ in_1_4 in_1_3) (+ in_1_2 in_0_4)) (+ in_0_3 in_0_2)) (+ (+ in_1_4 in_1_3) (+ in_0_4 in_0_3)) (+ (+ (+ in_2_1 in_2_0) (+ in_1_1 in_1_0)) (+ in_0_1 in_0_0)) (+ (+ (+ in_2_2 (+ in_2_1 in_2_0)) (+ in_1_2 in_1_1)) (+ (+ in_1_0 in_0_2) (+ in_0_1 in_0_0))) (+ (+ (+ in_2_3 (+ in_2_2 in_2_1)) (+ in_1_3 in_1_2)) (+ (+ in_1_1 in_0_3) (+ in_0_2 in_0_1))) (+ (+ (+ in_2_4 (+ in_2_3 in_2_2)) (+ in_1_4 in_1_3)) (+ (+ in_1_2 in_0_4) (+ in_0_3 in_0_2))) (+ (+ (+ in_2_4 in_2_3) (+ in_1_4 in_1_3)) (+ in_0_4 in_0_3)) (+ (+ (+ in_3_1 in_3_0) (+ in_2_1 in_2_0)) (+ in_1_1 in_1_0)) (+ (+ (+ in_3_2 (+ in_3_1 in_3_0)) (+ in_2_2 in_2_1)) (+ (+ in_2_0 in_1_2) (+ in_1_1 in_1_0))) (+ (+ (+ in_3_3 (+ in_3_2 in_3_1)) (+ in_2_3 in_2_2)) (+ (+ in_2_1 in_1_3) (+ in_1_2 in_1_1))) (+ (+ (+ in_3_4 (+ in_3_3 in_3_2)) (+ in_2_4 in_2_3)) (+ (+ in_2_2 in_1_4) (+ in_1_3 in_1_2))) (+ (+ (+ in_3_4 in_3_3) (+ in_2_4 in_2_3)) (+ in_1_4 in_1_3)) (+ (+ (+ in_4_1 in_4_0) (+ in_3_1 in_3_0)) (+ in_2_1 in_2_0)) (+ (+ (+ in_4_2 (+ in_4_1 in_4_0)) (+ in_3_2 in_3_1)) (+ (+ in_3_0 in_2_2) (+ in_2_1 in_2_0))) (+ (+ (+ in_4_3 (+ in_4_2 in_4_1)) (+ in_3_3 in_3_2)) (+ (+ in_3_1 in_2_3) (+ in_2_2 in_2_1))) (+ (+ (+ in_4_4 (+ in_4_3 in_4_2)) (+ in_3_4 in_3_3)) (+ (+ in_3_2 in_2_4) (+ in_2_3 in_2_2))) (+ (+ (+ in_4_4 in_4_3) (+ in_3_4 in_3_3)) (+ in_2_4 in_2_3)) (+ (+ in_4_1 in_4_0) (+ in_3_1 in_3_0)) (+ (+ (+ in_4_2 in_4_1) (+ in_4_0 in_3_2)) (+ in_3_1 in_3_0)) (+ (+ (+ in_4_3 in_4_2) (+ in_4_1 in_3_3)) (+ in_3_2 in_3_1)) (+ (+ (+ in_4_4 in_4_3) (+ in_4_2 in_3_4)) (+ in_3_3 in_3_2)) (+ (+ in_4_4 in_4_3) (+ in_3_4 in_3_3)))</t>
+          <t>(Vec ( + ( + in_1_1 in_1_0 ) ( + in_0_1 in_0_0 ) ) ( + ( + ( + in_1_2 in_1_1 ) ( + in_1_0 in_0_2 ) ) ( + in_0_1 in_0_0 ) ) ( + ( + ( + in_1_3 in_1_2 ) ( + in_1_1 in_0_3 ) ) ( + in_0_2 in_0_1 ) ) ( + ( + ( + in_1_4 in_1_3 ) ( + in_1_2 in_0_4 ) ) ( + in_0_3 in_0_2 ) ) ( + ( + in_1_4 in_1_3 ) ( + in_0_4 in_0_3 ) ) ( + ( + ( + in_2_1 in_2_0 ) ( + in_1_1 in_1_0 ) ) ( + in_0_1 in_0_0 ) ) ( + ( + ( + in_2_2 ( + in_2_1 in_2_0 ) ) ( + in_1_2 in_1_1 ) ) ( + ( + in_1_0 in_0_2 ) ( + in_0_1 in_0_0 ) ) ) ( + ( + ( + in_2_3 ( + in_2_2 in_2_1 ) ) ( + in_1_3 in_1_2 ) ) ( + ( + in_1_1 in_0_3 ) ( + in_0_2 in_0_1 ) ) ) ( + ( + ( + in_2_4 ( + in_2_3 in_2_2 ) ) ( + in_1_4 in_1_3 ) ) ( + ( + in_1_2 in_0_4 ) ( + in_0_3 in_0_2 ) ) ) ( + ( + ( + in_2_4 in_2_3 ) ( + in_1_4 in_1_3 ) ) ( + in_0_4 in_0_3 ) ) ( + ( + ( + in_3_1 in_3_0 ) ( + in_2_1 in_2_0 ) ) ( + in_1_1 in_1_0 ) ) ( + ( + ( + in_3_2 ( + in_3_1 in_3_0 ) ) ( + in_2_2 in_2_1 ) ) ( + ( + in_2_0 in_1_2 ) ( + in_1_1 in_1_0 ) ) ) ( + ( + ( + in_3_3 ( + in_3_2 in_3_1 ) ) ( + in_2_3 in_2_2 ) ) ( + ( + in_2_1 in_1_3 ) ( + in_1_2 in_1_1 ) ) ) ( + ( + ( + in_3_4 ( + in_3_3 in_3_2 ) ) ( + in_2_4 in_2_3 ) ) ( + ( + in_2_2 in_1_4 ) ( + in_1_3 in_1_2 ) ) ) ( + ( + ( + in_3_4 in_3_3 ) ( + in_2_4 in_2_3 ) ) ( + in_1_4 in_1_3 ) ) ( + ( + ( + in_4_1 in_4_0 ) ( + in_3_1 in_3_0 ) ) ( + in_2_1 in_2_0 ) ) ( + ( + ( + in_4_2 ( + in_4_1 in_4_0 ) ) ( + in_3_2 in_3_1 ) ) ( + ( + in_3_0 in_2_2 ) ( + in_2_1 in_2_0 ) ) ) ( + ( + ( + in_4_3 ( + in_4_2 in_4_1 ) ) ( + in_3_3 in_3_2 ) ) ( + ( + in_3_1 in_2_3 ) ( + in_2_2 in_2_1 ) ) ) ( + ( + ( + in_4_4 ( + in_4_3 in_4_2 ) ) ( + in_3_4 in_3_3 ) ) ( + ( + in_3_2 in_2_4 ) ( + in_2_3 in_2_2 ) ) ) ( + ( + ( + in_4_4 in_4_3 ) ( + in_3_4 in_3_3 ) ) ( + in_2_4 in_2_3 ) ) ( + ( + in_4_1 in_4_0 ) ( + in_3_1 in_3_0 ) ) ( + ( + ( + in_4_2 in_4_1 ) ( + in_4_0 in_3_2 ) ) ( + in_3_1 in_3_0 ) ) ( + ( + ( + in_4_3 in_4_2 ) ( + in_4_1 in_3_3 ) ) ( + in_3_2 in_3_1 ) ) ( + ( + ( + in_4_4 in_4_3 ) ( + in_4_2 in_3_4 ) ) ( + in_3_3 in_3_2 ) ) ( + ( + in_4_4 in_4_3 ) ( + in_3_4 in_3_3 ) ) )</t>
         </is>
       </c>
       <c r="E89" t="n">
         <v>36006</v>
       </c>
       <c r="F89" t="n">
-        <v>54579</v>
+        <v>36006</v>
       </c>
       <c r="G89" t="n">
-        <v>-51.58</v>
+        <v>0</v>
       </c>
       <c r="H89" t="n">
         <v>7.19</v>
       </c>
       <c r="I89" t="n">
-        <v>94.64</v>
+        <v>7.19</v>
       </c>
       <c r="J89" t="b">
         <v>0</v>
       </c>
       <c r="K89" t="n">
-        <v>405.36</v>
+        <v>492.81</v>
       </c>
       <c r="L89" t="n">
-        <v>75</v>
+        <v>1</v>
       </c>
     </row>
     <row r="90">
@@ -4201,29 +4201,29 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>(Vec (+ v2_0 (+ 2 (* v1_0 5))) (+ v2_1 (+ 2 (* v1_1 5))) (+ v2_2 (+ 2 (* v1_2 5))) (+ (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* v2_3 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) (+ 2 (* v1_3 5))) (+ v2_4 (+ 2 (* v1_4 5))) (+ v2_5 (+ 2 (* v1_5 5))) (+ v2_6 (+ 2 (* v1_6 5))) (+ v2_7 (+ 2 (* v1_7 5))))</t>
+          <t>(Vec (+ v2_0 (+ 2 (* v1_0 5))) (+ v2_1 (+ 2 (* v1_1 5))) (+ v2_2 (+ 2 (* v1_2 5))) (+ v2_3 (+ 2 (* v1_3 5))) (+ v2_4 (+ 2 (* v1_4 5))) (+ v2_5 (+ 2 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (* v1_5 5)))))))))))))))))))))))))))) (+ v2_6 (+ 2 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (* v1_6 5)))))))))))))))))))))))))))) (+ v2_7 (+ 2 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (* v1_7 5))))))))))))))))))))))))))))</t>
         </is>
       </c>
       <c r="E90" t="n">
         <v>6006</v>
       </c>
       <c r="F90" t="n">
-        <v>24651</v>
+        <v>24531</v>
       </c>
       <c r="G90" t="n">
-        <v>-310.44</v>
+        <v>-308.44</v>
       </c>
       <c r="H90" t="n">
         <v>39.37</v>
       </c>
       <c r="I90" t="n">
-        <v>2562.58</v>
+        <v>69.31999999999999</v>
       </c>
       <c r="J90" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K90" t="n">
-        <v>-2062.58</v>
+        <v>430.68</v>
       </c>
       <c r="L90" t="n">
         <v>75</v>
@@ -4243,17 +4243,17 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>(VecAdd (Vec v2_0 v2_1 v2_2 v2_3 v2_4 v2_5 v2_6 v2_7 v2_8 v2_9 v2_10 v2_11 v2_12 v2_13 v2_14 v2_15 v2_16 v2_17 v2_18 v2_19 v2_20 v2_21 v2_22 v2_23 v2_24 v2_25 v2_26 v2_27 v2_28 v2_29 v2_30 v2_31) (VecAdd (Vec 2 2 2 2 2 2 2 2 2 2 2 2 2 2 2 2 2 2 2 2 2 2 2 2 2 2 2 2 2 2 2 2) (Vec (* v1_0 5) (* v1_1 5) (* v1_2 5) (* v1_3 5) (* v1_4 5) (* v1_5 5) (* v1_6 5) (* v1_7 5) (* v1_8 5) (* v1_9 5) (* v1_10 5) (* v1_11 5) (* v1_12 5) (* v1_13 5) (* v1_14 5) (* v1_15 5) (* v1_16 5) (* v1_17 5) (* v1_18 5) (* v1_19 5) (* v1_20 5) (* v1_21 5) (* v1_22 5) (* v1_23 5) (* v1_24 5) (* v1_25 5) (* v1_26 5) (* v1_27 5) (* v1_28 5) (* v1_29 5) (* v1_30 5) (* v1_31 5))))</t>
+          <t>(Vec ( + v2_0 ( + 2 ( * v1_0 5 ) ) ) ( + v2_1 ( + 2 ( * v1_1 5 ) ) ) ( + v2_2 ( + 2 ( * v1_2 5 ) ) ) ( + v2_3 ( + 2 ( * v1_3 5 ) ) ) ( + v2_4 ( + 2 ( * v1_4 5 ) ) ) ( + v2_5 ( + 2 ( * v1_5 5 ) ) ) ( + v2_6 ( + 2 ( * v1_6 5 ) ) ) ( + v2_7 ( + 2 ( * v1_7 5 ) ) ) ( + v2_8 ( + 2 ( * v1_8 5 ) ) ) ( + v2_9 ( + 2 ( * v1_9 5 ) ) ) ( + v2_10 ( + 2 ( * v1_10 5 ) ) ) ( + v2_11 ( + 2 ( * v1_11 5 ) ) ) ( + v2_12 ( + 2 ( * v1_12 5 ) ) ) ( + v2_13 ( + 2 ( * v1_13 5 ) ) ) ( + v2_14 ( + 2 ( * v1_14 5 ) ) ) ( + v2_15 ( + 2 ( * v1_15 5 ) ) ) ( + v2_16 ( + 2 ( * v1_16 5 ) ) ) ( + v2_17 ( + 2 ( * v1_17 5 ) ) ) ( + v2_18 ( + 2 ( * v1_18 5 ) ) ) ( + v2_19 ( + 2 ( * v1_19 5 ) ) ) ( + v2_20 ( + 2 ( * v1_20 5 ) ) ) ( + v2_21 ( + 2 ( * v1_21 5 ) ) ) ( + v2_22 ( + 2 ( * v1_22 5 ) ) ) ( + v2_23 ( + 2 ( * v1_23 5 ) ) ) ( + v2_24 ( + 2 ( * v1_24 5 ) ) ) ( + v2_25 ( + 2 ( * v1_25 5 ) ) ) ( + v2_26 ( + 2 ( * v1_26 5 ) ) ) ( + v2_27 ( + 2 ( * v1_27 5 ) ) ) ( + v2_28 ( + 2 ( * v1_28 5 ) ) ) ( + v2_29 ( + 2 ( * v1_29 5 ) ) ) ( + v2_30 ( + 2 ( * v1_30 5 ) ) ) ( + v2_31 ( + 2 ( * v1_31 5 ) ) ) )</t>
         </is>
       </c>
       <c r="E91" t="n">
         <v>24006</v>
       </c>
       <c r="F91" t="n">
-        <v>8008</v>
+        <v>24006</v>
       </c>
       <c r="G91" t="n">
-        <v>66.64</v>
+        <v>0</v>
       </c>
       <c r="H91" t="n">
         <v>39.37</v>
@@ -4268,7 +4268,7 @@
         <v>460.63</v>
       </c>
       <c r="L91" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="92">
@@ -4285,29 +4285,29 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>(Vec (+ (+ (- (+ v1_0 v2_0) (* (* v1_0 v2_0) 2)) (- (+ v1_1 v2_1) (* 2 (* v1_1 v2_1)))) (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (- (+ v1_2 v2_2) (* 2 (* v1_2 v2_2))) (- (+ v1_3 v2_3) (* 2 (* v1_3 v2_3)))) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0)))</t>
+          <t>(Vec (+ (+ (- (+ v1_0 v2_0) (* (* v1_0 v2_0) 2)) (- (+ v1_1 v2_1) (* 2 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (* v1_1 v2_1)))))))))))))))))))))))))))))))))))))))))))))))))))))))) (+ (- (+ v1_2 v2_2) (* 2 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (* v1_2 v2_2)))))))))))))) (- (+ v1_3 v2_3) (* 2 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (* v1_3 v2_3)))))))))))))))))</t>
         </is>
       </c>
       <c r="E92" t="n">
         <v>4759</v>
       </c>
       <c r="F92" t="n">
-        <v>23333</v>
+        <v>23311</v>
       </c>
       <c r="G92" t="n">
-        <v>-390.29</v>
+        <v>-389.83</v>
       </c>
       <c r="H92" t="n">
         <v>75.15000000000001</v>
       </c>
       <c r="I92" t="n">
-        <v>163.8</v>
+        <v>137.45</v>
       </c>
       <c r="J92" t="b">
         <v>0</v>
       </c>
       <c r="K92" t="n">
-        <v>336.2</v>
+        <v>362.55</v>
       </c>
       <c r="L92" t="n">
         <v>75</v>
@@ -4327,29 +4327,29 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>(Vec (+ (+ (+ (- (+ v1_0 v2_0) (* (* v1_0 v2_0) 2)) (- (+ v1_1 v2_1) (* 2 (* v1_1 v2_1)))) (+ (- (+ v1_2 v2_2) (* 2 (* v1_2 v2_2))) (- (+ v1_3 v2_3) (* 2 (* v1_3 v2_3))))) (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (- (+ v1_4 v2_4) (* 2 (* v1_4 v2_4))) (- (+ v1_5 v2_5) (* 2 (* v1_5 v2_5)))) (+ (- (+ v1_6 v2_6) (* 2 (* v1_6 v2_6))) (- (+ v1_7 v2_7) (* 2 (* v1_7 v2_7))))) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0)))</t>
+          <t>(Vec (+ (+ (+ (- (+ v1_0 v2_0) (* (* v1_0 v2_0) 2)) (- (+ v1_1 v2_1) (* 2 (* v1_1 v2_1)))) (+ (- (+ v1_2 v2_2) (* 2 (* v1_2 v2_2))) (- (+ v1_3 v2_3) (* 2 (* v1_3 v2_3))))) (+ (+ (- (+ v1_4 v2_4) (* 2 (* v1_4 v2_4))) (- (+ v1_5 v2_5) (* 2 (* v1_5 v2_5)))) (+ (- (+ v1_6 v2_6) (* 2 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (* v1_6 v2_6)))))))))))))))))))))))))))))))))))))))) (- (+ v1_7 v2_7) (* 2 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (* v1_7 v2_7))))))))))))))))))))))))))))))))))))))))))))</t>
         </is>
       </c>
       <c r="E93" t="n">
         <v>9760</v>
       </c>
       <c r="F93" t="n">
-        <v>28334</v>
+        <v>28297</v>
       </c>
       <c r="G93" t="n">
-        <v>-190.31</v>
+        <v>-189.93</v>
       </c>
       <c r="H93" t="n">
         <v>76.34999999999999</v>
       </c>
       <c r="I93" t="n">
-        <v>165</v>
+        <v>120.68</v>
       </c>
       <c r="J93" t="b">
         <v>0</v>
       </c>
       <c r="K93" t="n">
-        <v>335</v>
+        <v>379.32</v>
       </c>
       <c r="L93" t="n">
         <v>75</v>
@@ -4369,29 +4369,29 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>(Vec (+ (+ (+ (+ (+ (- (+ v1_0 v2_0) (* (* v1_0 v2_0) 2)) (- (+ v1_1 v2_1) (* 2 (* v1_1 v2_1)))) (+ (- (+ v1_2 v2_2) (* 2 (* v1_2 v2_2))) (- (+ v1_3 v2_3) (* 2 (* v1_3 v2_3))))) (+ (+ (- (+ v1_4 v2_4) (* 2 (* v1_4 v2_4))) (- (+ v1_5 v2_5) (* 2 (* v1_5 v2_5)))) (+ (- (+ v1_6 v2_6) (* 2 (* v1_6 v2_6))) (- (+ v1_7 v2_7) (* 2 (* v1_7 v2_7)))))) (+ (+ (+ (- (+ v1_8 v2_8) (* 2 (* v1_8 v2_8))) (- (+ v1_9 v2_9) (* 2 (* v1_9 v2_9)))) (+ (- (+ v1_10 v2_10) (* 2 (* v1_10 v2_10))) (- (+ v1_11 v2_11) (* 2 (* v1_11 v2_11))))) (+ (+ (- (+ v1_12 v2_12) (* 2 (* v1_12 v2_12))) (- (+ v1_13 v2_13) (* 2 (* v1_13 v2_13)))) (* 1 (* 1 (* 1 (+ (- (+ v1_14 v2_14) (* 2 (* v1_14 v2_14))) (- (+ v1_15 v2_15) (* 2 (* v1_15 v2_15)))))))))) (* 1 (* 1 (+ (+ (+ (* 1 (+ (- (+ v1_16 v2_16) (* 2 (* v1_16 v2_16))) (- (+ v1_17 v2_17) (* 2 (* v1_17 v2_17))))) (+ (- (+ v1_18 v2_18) (* 2 (* v1_18 v2_18))) (- (+ v1_19 v2_19) (* 2 (* v1_19 v2_19))))) (+ (+ (- (+ v1_20 v2_20) (* 2 (* v1_20 v2_20))) (- (+ v1_21 v2_21) (* 2 (* v1_21 v2_21)))) (+ (- (+ v1_22 v2_22) (* 2 (* v1_22 v2_22))) (- (+ v1_23 v2_23) (* 2 (* v1_23 v2_23)))))) (+ (+ (+ (- (+ v1_24 v2_24) (* 2 (* v1_24 v2_24))) (- (+ v1_25 v2_25) (* 2 (* v1_25 v2_25)))) (+ (- (+ v1_26 v2_26) (* 2 (* v1_26 v2_26))) (- (+ v1_27 v2_27) (* 2 (* v1_27 v2_27))))) (+ (+ (- (+ v1_28 v2_28) (* 2 (* v1_28 v2_28))) (- (+ v1_29 v2_29) (* 2 (* v1_29 v2_29)))) (+ (- (+ v1_30 v2_30) (* 2 (* v1_30 v2_30))) (- (+ v1_31 v2_31) (* 2 (* v1_31 v2_31)))))))))))</t>
+          <t>(Vec (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (+ (* 1 (+ (+ (+ (+ (- (+ v1_0 v2_0) (* (* v1_0 v2_0) 2)) (- (+ v1_1 v2_1) (* 2 (* v1_1 v2_1)))) (+ (- (+ v1_2 v2_2) (* 2 (* v1_2 v2_2))) (- (+ v1_3 v2_3) (* 2 (* v1_3 v2_3))))) (+ (+ (- (+ v1_4 v2_4) (* 2 (* v1_4 v2_4))) (- (+ v1_5 v2_5) (* 2 (* v1_5 v2_5)))) (+ (- (+ v1_6 v2_6) (* 2 (* v1_6 v2_6))) (- (+ v1_7 v2_7) (* 2 (* v1_7 v2_7)))))) (+ (+ (+ (- (+ v1_8 v2_8) (* 2 (* v1_8 v2_8))) (- (+ v1_9 v2_9) (* 2 (* v1_9 v2_9)))) (+ (- (+ v1_10 v2_10) (* 2 (* v1_10 v2_10))) (- (+ v1_11 v2_11) (* 2 (* v1_11 v2_11))))) (+ (+ (- (+ v1_12 v2_12) (* 2 (* v1_12 v2_12))) (- (+ v1_13 v2_13) (* 2 (* v1_13 v2_13)))) (+ (- (+ v1_14 v2_14) (* 2 (* v1_14 v2_14))) (- (+ v1_15 v2_15) (* 2 (* v1_15 v2_15)))))))) (+ (* 1 (+ (+ (+ (- (+ v1_16 v2_16) (* 2 (* v1_16 v2_16))) (- (+ v1_17 v2_17) (* 2 (* v1_17 v2_17)))) (+ (- (+ v1_18 v2_18) (* 2 (* v1_18 v2_18))) (- (+ v1_19 v2_19) (* 2 (* v1_19 v2_19))))) (+ (+ (- (+ v1_20 v2_20) (* 2 (* v1_20 v2_20))) (- (+ v1_21 v2_21) (* 2 (* v1_21 v2_21)))) (+ (- (+ v1_22 v2_22) (* 2 (* v1_22 v2_22))) (- (+ v1_23 v2_23) (* 2 (* v1_23 v2_23))))))) (+ (+ (+ (- (+ v1_24 v2_24) (* 2 (* v1_24 v2_24))) (- (+ v1_25 v2_25) (* 2 (* v1_25 v2_25)))) (+ (- (+ v1_26 v2_26) (* 2 (* v1_26 v2_26))) (- (+ v1_27 v2_27) (* 2 (* v1_27 v2_27))))) (+ (+ (- (+ v1_28 v2_28) (* 2 (* v1_28 v2_28))) (- (+ v1_29 v2_29) (* 2 (* v1_29 v2_29)))) (+ (- (+ v1_30 v2_30) (* 2 (* v1_30 v2_30))) (- (+ v1_31 v2_31) (* 2 (* v1_31 v2_31)))))))))))))))))))</t>
         </is>
       </c>
       <c r="E94" t="n">
         <v>39762</v>
       </c>
       <c r="F94" t="n">
-        <v>41268</v>
+        <v>42784</v>
       </c>
       <c r="G94" t="n">
-        <v>-3.79</v>
+        <v>-7.6</v>
       </c>
       <c r="H94" t="n">
         <v>78.75</v>
       </c>
       <c r="I94" t="n">
-        <v>182.49</v>
+        <v>459.14</v>
       </c>
       <c r="J94" t="b">
         <v>0</v>
       </c>
       <c r="K94" t="n">
-        <v>317.51</v>
+        <v>40.86</v>
       </c>
       <c r="L94" t="n">
         <v>75</v>
@@ -4411,17 +4411,17 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>(VecAdd (Vec c1_0 c1_1 c1_2 c1_3 c1_4 c1_5 c1_6 c1_7) (VecAdd (Vec c2_0 c2_1 c2_2 c2_3 c2_4 c2_5 c2_6 c2_7) (Vec (* c0_0 (+ c3_0 (* c0_0 c4_0))) (* c0_1 (+ c3_1 (* c0_1 c4_1))) (* c0_2 (+ c3_2 (* c0_2 c4_2))) (* c0_3 (+ c3_3 (* c0_3 c4_3))) (* c0_4 (+ c3_4 (* c0_4 c4_4))) (* c0_5 (+ c3_5 (* c0_5 c4_5))) (* c0_6 (+ c3_6 (* c0_6 c4_6))) (* c0_7 (+ c3_7 (* c0_7 c4_7))))))</t>
+          <t>(Vec ( + c1_0 ( + c2_0 ( * c0_0 ( + c3_0 ( * c0_0 c4_0 ) ) ) ) ) ( + c1_1 ( + c2_1 ( * c0_1 ( + c3_1 ( * c0_1 c4_1 ) ) ) ) ) ( + c1_2 ( + c2_2 ( * c0_2 ( + c3_2 ( * c0_2 c4_2 ) ) ) ) ) ( + c1_3 ( + c2_3 ( * c0_3 ( + c3_3 ( * c0_3 c4_3 ) ) ) ) ) ( + c1_4 ( + c2_4 ( * c0_4 ( + c3_4 ( * c0_4 c4_4 ) ) ) ) ) ( + c1_5 ( + c2_5 ( * c0_5 ( + c3_5 ( * c0_5 c4_5 ) ) ) ) ) ( + c1_6 ( + c2_6 ( * c0_6 ( + c3_6 ( * c0_6 c4_6 ) ) ) ) ) ( + c1_7 ( + c2_7 ( * c0_7 ( + c3_7 ( * c0_7 c4_7 ) ) ) ) ) )</t>
         </is>
       </c>
       <c r="E95" t="n">
         <v>10009</v>
       </c>
       <c r="F95" t="n">
-        <v>6011</v>
+        <v>10009</v>
       </c>
       <c r="G95" t="n">
-        <v>39.94</v>
+        <v>0</v>
       </c>
       <c r="H95" t="n">
         <v>75.15000000000001</v>
@@ -4436,7 +4436,7 @@
         <v>424.85</v>
       </c>
       <c r="L95" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="96">
@@ -4453,29 +4453,29 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>(Vec (+ c1_0 (+ c2_0 (* c0_0 (+ c3_0 (* c0_0 c4_0))))) (+ c1_1 (+ c2_1 (* c0_1 (+ c3_1 (* c0_1 c4_1))))) (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ c1_2 (+ c2_2 (* c0_2 (+ c3_2 (* c0_2 c4_2))))) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) (+ c1_3 (+ c2_3 (* c0_3 (+ c3_3 (* c0_3 c4_3))))) (+ c1_4 (+ c2_4 (* c0_4 (+ c3_4 (* c0_4 c4_4))))) (+ c1_5 (+ c2_5 (* c0_5 (+ c3_5 (* c0_5 c4_5))))) (+ c1_6 (+ c2_6 (* c0_6 (+ c3_6 (* c0_6 c4_6))))) (+ c1_7 (+ c2_7 (* c0_7 (+ c3_7 (* c0_7 c4_7))))) (+ c1_8 (+ c2_8 (* c0_8 (+ c3_8 (* c0_8 c4_8))))) (+ c1_9 (+ c2_9 (* c0_9 (+ c3_9 (* c0_9 c4_9))))) (+ c1_10 (+ c2_10 (* c0_10 (+ c3_10 (* c0_10 c4_10))))) (+ c1_11 (+ c2_11 (* c0_11 (+ c3_11 (* c0_11 c4_11))))) (+ c1_12 (+ c2_12 (* c0_12 (+ c3_12 (* c0_12 c4_12))))) (+ c1_13 (+ c2_13 (* c0_13 (+ c3_13 (* c0_13 c4_13))))) (+ c1_14 (+ c2_14 (* c0_14 (+ c3_14 (* c0_14 c4_14))))) (+ c1_15 (+ c2_15 (* c0_15 (+ c3_15 (* c0_15 c4_15))))) (+ c1_16 (+ c2_16 (* c0_16 (+ c3_16 (* c0_16 c4_16))))) (+ c1_17 (+ c2_17 (* c0_17 (+ c3_17 (* c0_17 c4_17))))) (+ c1_18 (+ c2_18 (* c0_18 (+ c3_18 (* c0_18 c4_18))))) (+ c1_19 (+ c2_19 (* c0_19 (+ c3_19 (* c0_19 c4_19))))) (+ c1_20 (+ c2_20 (* c0_20 (+ c3_20 (* c0_20 c4_20))))) (+ c1_21 (+ c2_21 (* c0_21 (+ c3_21 (* c0_21 c4_21))))) (+ c1_22 (+ c2_22 (* c0_22 (+ c3_22 (* c0_22 c4_22))))) (+ c1_23 (+ c2_23 (* c0_23 (+ c3_23 (* c0_23 c4_23))))) (+ c1_24 (+ c2_24 (* c0_24 (+ c3_24 (* c0_24 c4_24))))) (+ c1_25 (+ c2_25 (* c0_25 (+ c3_25 (* c0_25 c4_25))))) (+ c1_26 (+ c2_26 (* c0_26 (+ c3_26 (* c0_26 c4_26))))) (+ c1_27 (+ c2_27 (* c0_27 (+ c3_27 (* c0_27 c4_27))))) (+ c1_28 (+ c2_28 (* c0_28 (+ c3_28 (* c0_28 c4_28))))) (+ c1_29 (+ c2_29 (* c0_29 (+ c3_29 (* c0_29 c4_29))))) (+ c1_30 (+ c2_30 (* c0_30 (+ c3_30 (* c0_30 c4_30))))) (+ c1_31 (+ c2_31 (* c0_31 (+ c3_31 (* c0_31 c4_31))))))</t>
+          <t>(Vec (+ c1_0 (+ c2_0 (* c0_0 (+ c3_0 (+ 0 (+ 0 (* c0_0 c4_0))))))) (+ c1_1 (+ c2_1 (* c0_1 (+ c3_1 (+ 0 (+ 0 (* c0_1 c4_1))))))) (+ c1_2 (+ c2_2 (* c0_2 (+ c3_2 (+ 0 (+ 0 (* c0_2 c4_2))))))) (+ c1_3 (+ c2_3 (* c0_3 (+ c3_3 (+ 0 (+ 0 (* c0_3 c4_3))))))) (+ c1_4 (+ c2_4 (* c0_4 (+ c3_4 (+ 0 (+ 0 (* c0_4 c4_4))))))) (+ c1_5 (+ c2_5 (* c0_5 (+ c3_5 (+ 0 (+ 0 (* c0_5 c4_5))))))) (+ c1_6 (+ c2_6 (* c0_6 (+ c3_6 (+ 0 (* c0_6 c4_6)))))) (+ c1_7 (+ c2_7 (* c0_7 (+ c3_7 (+ 0 (* c0_7 c4_7)))))) (+ c1_8 (+ c2_8 (* c0_8 (+ c3_8 (+ 0 (* c0_8 c4_8)))))) (+ c1_9 (+ c2_9 (* c0_9 (+ c3_9 (+ 0 (* c0_9 c4_9)))))) (+ c1_10 (+ c2_10 (* c0_10 (+ c3_10 (+ 0 (* c0_10 c4_10)))))) (+ c1_11 (+ c2_11 (* c0_11 (+ c3_11 (+ 0 (* c0_11 c4_11)))))) (+ c1_12 (+ c2_12 (* c0_12 (+ c3_12 (+ 0 (* c0_12 c4_12)))))) (+ c1_13 (+ c2_13 (* c0_13 (+ c3_13 (+ 0 (* c0_13 c4_13)))))) (+ c1_14 (+ c2_14 (+ 0 (+ 0 (+ 0 (* c0_14 (+ c3_14 (* c0_14 c4_14)))))))) (+ c1_15 (+ c2_15 (+ 0 (+ 0 (+ 0 (* c0_15 (+ c3_15 (* c0_15 c4_15)))))))) (+ c1_16 (+ c2_16 (+ 0 (+ 0 (+ 0 (* c0_16 (+ c3_16 (* c0_16 c4_16)))))))) (+ c1_17 (+ c2_17 (+ 0 (+ 0 (+ 0 (* c0_17 (+ c3_17 (* c0_17 c4_17)))))))) (+ c1_18 (+ c2_18 (+ 0 (+ 0 (+ 0 (* c0_18 (+ c3_18 (* c0_18 c4_18)))))))) (+ c1_19 (+ c2_19 (+ 0 (+ 0 (+ 0 (* c0_19 (+ c3_19 (* c0_19 c4_19)))))))) (+ c1_20 (+ c2_20 (+ 0 (+ 0 (+ 0 (* c0_20 (+ c3_20 (* c0_20 c4_20)))))))) (+ c1_21 (+ c2_21 (+ 0 (+ 0 (+ 0 (* c0_21 (+ c3_21 (* c0_21 c4_21)))))))) (+ c1_22 (+ c2_22 (+ 0 (+ 0 (+ 0 (* c0_22 (+ c3_22 (* c0_22 c4_22)))))))) (+ c1_23 (+ c2_23 (+ 0 (+ 0 (+ 0 (* c0_23 (+ c3_23 (* c0_23 c4_23)))))))) (+ c1_24 (+ c2_24 (+ 0 (+ 0 (+ 0 (* c0_24 (+ c3_24 (* c0_24 c4_24)))))))) (+ c1_25 (+ c2_25 (+ 0 (+ 0 (+ 0 (* c0_25 (+ c3_25 (* c0_25 c4_25)))))))) (+ c1_26 (+ c2_26 (+ 0 (+ 0 (+ 0 (* c0_26 (+ c3_26 (* c0_26 c4_26)))))))) (+ c1_27 (+ c2_27 (+ 0 (+ 0 (+ 0 (* c0_27 (+ c3_27 (* c0_27 c4_27)))))))) (+ c1_28 (+ c2_28 (+ 0 (+ 0 (+ 0 (* c0_28 (+ c3_28 (* c0_28 c4_28)))))))) (+ c1_29 (+ c2_29 (+ 0 (+ 0 (+ 0 (* c0_29 (+ c3_29 (* c0_29 c4_29)))))))) (+ c1_30 (+ c2_30 (+ 0 (+ 0 (+ 0 (* c0_30 (+ c3_30 (* c0_30 c4_30)))))))) (+ c1_31 (+ c2_31 (+ 0 (+ 0 (+ 0 (* c0_31 (+ c3_31 (* c0_31 c4_31)))))))))</t>
         </is>
       </c>
       <c r="E96" t="n">
         <v>40009</v>
       </c>
       <c r="F96" t="n">
-        <v>58583</v>
+        <v>58512</v>
       </c>
       <c r="G96" t="n">
-        <v>-46.42</v>
+        <v>-46.25</v>
       </c>
       <c r="H96" t="n">
         <v>75.15000000000001</v>
       </c>
       <c r="I96" t="n">
-        <v>163.8</v>
+        <v>78.75</v>
       </c>
       <c r="J96" t="b">
         <v>0</v>
       </c>
       <c r="K96" t="n">
-        <v>336.2</v>
+        <v>421.25</v>
       </c>
       <c r="L96" t="n">
         <v>75</v>
@@ -4495,29 +4495,29 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>(Vec (+ (+ (* (- c2_0 c1_0) (- c2_0 c1_0)) (* (- c2_1 c1_1) (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (- c2_1 c1_1)))))))))))))))))) (+ (* (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (- c2_2 c1_2)))))))))))))))) (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (- c2_2 c1_2))))))))))))))))) (* (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (- c2_3 c1_3)))))))))))))))) (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (- c2_3 c1_3)))))))))))))))))))</t>
+          <t>(Vec (+ (+ (* (- c2_0 c1_0) (- c2_0 c1_0)) (* (- c2_1 c1_1) (- c2_1 c1_1))) (+ (* (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (+ (+ (+ (+ (+ (+ (+ (+ (+ (* 1 (* 1 (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (- c2_2 c1_2) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0))) 0) 0) 0) 0) 0) 0) 0) 0) 0)))))))))))))))))))))))))))))))))))))))))))))))))))) (- c2_2 c1_2)) (* (- c2_3 c1_3) (- c2_3 c1_3)))))</t>
         </is>
       </c>
       <c r="E97" t="n">
         <v>3757</v>
       </c>
       <c r="F97" t="n">
-        <v>22287</v>
+        <v>22384</v>
       </c>
       <c r="G97" t="n">
-        <v>-493.21</v>
+        <v>-495.79</v>
       </c>
       <c r="H97" t="n">
         <v>40.57</v>
       </c>
       <c r="I97" t="n">
-        <v>559.29</v>
+        <v>1898.52</v>
       </c>
       <c r="J97" t="b">
         <v>1</v>
       </c>
       <c r="K97" t="n">
-        <v>-59.29</v>
+        <v>-1398.52</v>
       </c>
       <c r="L97" t="n">
         <v>75</v>
@@ -4537,32 +4537,32 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>(Vec (+ (+ (+ (* (- c2_0 c1_0) (- c2_0 c1_0)) (* (- c2_1 c1_1) (- c2_1 c1_1))) (+ (* (- c2_2 c1_2) (- c2_2 c1_2)) (* (- c2_3 c1_3) (- c2_3 c1_3)))) (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (* (- c2_4 c1_4) (- c2_4 c1_4)) (* (- c2_5 c1_5) (- c2_5 c1_5))) (+ (* (- c2_6 c1_6) (- c2_6 c1_6)) (* (- c2_7 c1_7) (- c2_7 c1_7)))) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0)))</t>
+          <t>(Vec ( + ( + ( + ( * ( - c2_0 c1_0 ) ( - c2_0 c1_0 ) ) ( * ( - c2_1 c1_1 ) ( - c2_1 c1_1 ) ) ) ( + ( * ( - c2_2 c1_2 ) ( - c2_2 c1_2 ) ) ( * ( - c2_3 c1_3 ) ( - c2_3 c1_3 ) ) ) ) ( + ( + ( * ( - c2_4 c1_4 ) ( - c2_4 c1_4 ) ) ( * ( - c2_5 c1_5 ) ( - c2_5 c1_5 ) ) ) ( + ( * ( - c2_6 c1_6 ) ( - c2_6 c1_6 ) ) ( * ( - c2_7 c1_7 ) ( - c2_7 c1_7 ) ) ) ) ) )</t>
         </is>
       </c>
       <c r="E98" t="n">
         <v>7758</v>
       </c>
       <c r="F98" t="n">
-        <v>26332</v>
+        <v>7758</v>
       </c>
       <c r="G98" t="n">
-        <v>-239.42</v>
+        <v>0</v>
       </c>
       <c r="H98" t="n">
         <v>41.77</v>
       </c>
       <c r="I98" t="n">
-        <v>130.42</v>
+        <v>41.77</v>
       </c>
       <c r="J98" t="b">
         <v>0</v>
       </c>
       <c r="K98" t="n">
-        <v>369.58</v>
+        <v>458.23</v>
       </c>
       <c r="L98" t="n">
-        <v>75</v>
+        <v>1</v>
       </c>
     </row>
     <row r="99">
@@ -4579,29 +4579,29 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>(Vec (+ (+ (+ (+ (+ (* (- c2_0 c1_0) (- c2_0 c1_0)) (* (- c2_1 c1_1) (- c2_1 c1_1))) (+ (* (- c2_2 c1_2) (- c2_2 c1_2)) (* (- c2_3 c1_3) (- c2_3 c1_3)))) (+ (+ (* (- c2_4 c1_4) (- c2_4 c1_4)) (* (- c2_5 c1_5) (- c2_5 c1_5))) (+ (* (- c2_6 c1_6) (- c2_6 c1_6)) (* (- c2_7 c1_7) (- c2_7 c1_7))))) (+ (+ (+ (* (- c2_8 c1_8) (- c2_8 c1_8)) (* (- c2_9 c1_9) (- c2_9 c1_9))) (+ (* (- c2_10 c1_10) (- c2_10 c1_10)) (* (- c2_11 c1_11) (- c2_11 c1_11)))) (+ (+ (* (- c2_12 c1_12) (- c2_12 c1_12)) (* (- c2_13 c1_13) (- c2_13 c1_13))) (+ (* (- c2_14 c1_14) (- c2_14 c1_14)) (* (- c2_15 c1_15) (- c2_15 c1_15)))))) (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (* (- c2_16 c1_16) (- c2_16 c1_16)) (* (- c2_17 c1_17) (- c2_17 c1_17))) (+ (* (- c2_18 c1_18) (- c2_18 c1_18)) (* (- c2_19 c1_19) (- c2_19 c1_19)))) (+ (+ (* (- c2_20 c1_20) (- c2_20 c1_20)) (* (- c2_21 c1_21) (- c2_21 c1_21))) (+ (* (- c2_22 c1_22) (- c2_22 c1_22)) (* (- c2_23 c1_23) (- c2_23 c1_23))))) (+ (+ (+ (* (- c2_24 c1_24) (- c2_24 c1_24)) (* (- c2_25 c1_25) (- c2_25 c1_25))) (+ (* (- c2_26 c1_26) (- c2_26 c1_26)) (* (- c2_27 c1_27) (- c2_27 c1_27)))) (+ (+ (* (- c2_28 c1_28) (- c2_28 c1_28)) (* (- c2_29 c1_29) (- c2_29 c1_29))) (+ (* (- c2_30 c1_30) (- c2_30 c1_30)) (* (- c2_31 c1_31) (- c2_31 c1_31)))))) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0)))</t>
+          <t>(Vec (+ (+ (+ (+ (+ (* (- c2_0 c1_0) (- c2_0 c1_0)) (* (- c2_1 c1_1) (- c2_1 c1_1))) (+ (* (- c2_2 c1_2) (- c2_2 c1_2)) (* (- c2_3 c1_3) (- c2_3 c1_3)))) (+ (+ (* (- c2_4 c1_4) (- c2_4 c1_4)) (* (- c2_5 c1_5) (- c2_5 c1_5))) (+ (* (- c2_6 c1_6) (- c2_6 c1_6)) (* (- c2_7 c1_7) (- c2_7 c1_7))))) (+ (+ (+ (* (- c2_8 c1_8) (- c2_8 c1_8)) (* (- c2_9 c1_9) (- c2_9 c1_9))) (+ (* (- c2_10 c1_10) (- c2_10 c1_10)) (+ 0 (+ 0 (+ 0 (+ 0 (* (- c2_11 c1_11) (- c2_11 c1_11)))))))) (+ (+ (+ 0 (+ 0 (+ 0 (+ 0 (* (- c2_12 c1_12) (- c2_12 c1_12)))))) (+ 0 (+ 0 (+ 0 (+ 0 (* (- c2_13 c1_13) (- c2_13 c1_13))))))) (+ (+ 0 (+ 0 (+ 0 (+ 0 (* (- c2_14 c1_14) (- c2_14 c1_14)))))) (+ 0 (+ 0 (+ 0 (+ 0 (* (- c2_15 c1_15) (- c2_15 c1_15)))))))))) (+ (+ (+ (+ (+ 0 (+ 0 (+ 0 (+ 0 (* (- c2_16 c1_16) (- c2_16 c1_16)))))) (+ 0 (+ 0 (+ 0 (+ 0 (* (- c2_17 c1_17) (- c2_17 c1_17))))))) (+ (+ 0 (+ 0 (+ 0 (+ 0 (* (- c2_18 c1_18) (- c2_18 c1_18)))))) (+ 0 (+ 0 (+ 0 (+ 0 (* (- c2_19 c1_19) (- c2_19 c1_19)))))))) (+ (+ (+ 0 (+ 0 (+ 0 (+ 0 (* (- c2_20 c1_20) (- c2_20 c1_20)))))) (+ 0 (+ 0 (+ 0 (+ 0 (* (- c2_21 c1_21) (- c2_21 c1_21))))))) (+ (+ 0 (+ 0 (+ 0 (* (- c2_22 c1_22) (- c2_22 c1_22))))) (+ 0 (+ 0 (+ 0 (* (- c2_23 c1_23) (- c2_23 c1_23)))))))) (+ (+ (+ (+ 0 (+ 0 (+ 0 (* (- c2_24 c1_24) (- c2_24 c1_24))))) (+ 0 (+ 0 (+ 0 (* (- c2_25 c1_25) (- c2_25 c1_25)))))) (+ (+ 0 (+ 0 (+ 0 (* (- c2_26 c1_26) (- c2_26 c1_26))))) (+ 0 (+ 0 (+ 0 (* (- c2_27 c1_27) (- c2_27 c1_27))))))) (+ (+ (+ 0 (+ 0 (+ 0 (* (- c2_28 c1_28) (- c2_28 c1_28))))) (+ 0 (+ 0 (+ 0 (* (- c2_29 c1_29) (- c2_29 c1_29)))))) (+ (+ 0 (+ 0 (+ 0 (* (- c2_30 c1_30) (- c2_30 c1_30))))) (+ 0 (+ 0 (+ 0 (* (- c2_31 c1_31) (- c2_31 c1_31)))))))))))</t>
         </is>
       </c>
       <c r="E99" t="n">
         <v>31760</v>
       </c>
       <c r="F99" t="n">
-        <v>50334</v>
+        <v>50264</v>
       </c>
       <c r="G99" t="n">
-        <v>-58.48</v>
+        <v>-58.26</v>
       </c>
       <c r="H99" t="n">
         <v>44.16</v>
       </c>
       <c r="I99" t="n">
-        <v>132.82</v>
+        <v>48.96</v>
       </c>
       <c r="J99" t="b">
         <v>0</v>
       </c>
       <c r="K99" t="n">
-        <v>367.18</v>
+        <v>451.04</v>
       </c>
       <c r="L99" t="n">
         <v>75</v>
@@ -4621,29 +4621,29 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>(Vec (+ (+ (* v1_0 v2_0) (* v1_1 v2_1)) (+ (* v1_2 v2_2) (* v1_3 (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* v2_3 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1)))))</t>
+          <t>(Vec (+ (+ (* v1_0 v2_0) (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (* v1_1 v2_1)))))))))))))))))))))) (+ (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (* v1_2 v2_2)))))))))))))))))))))))))))) (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (* v1_3 v2_3)))))))))))))))))))))))))))))))</t>
         </is>
       </c>
       <c r="E100" t="n">
         <v>1756</v>
       </c>
       <c r="F100" t="n">
-        <v>20404</v>
+        <v>20283</v>
       </c>
       <c r="G100" t="n">
-        <v>-1061.96</v>
+        <v>-1055.07</v>
       </c>
       <c r="H100" t="n">
         <v>39.37</v>
       </c>
       <c r="I100" t="n">
-        <v>2598.36</v>
+        <v>71.72</v>
       </c>
       <c r="J100" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K100" t="n">
-        <v>-2098.36</v>
+        <v>428.28</v>
       </c>
       <c r="L100" t="n">
         <v>75</v>
@@ -4705,29 +4705,29 @@
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>(Vec (+ (+ (+ (+ (+ (* v1_0 v2_0) (* v1_1 v2_1)) (+ (* v1_2 v2_2) (* v1_3 v2_3))) (+ (+ (* v1_4 v2_4) (* v1_5 v2_5)) (+ (* v1_6 v2_6) (* v1_7 v2_7)))) (+ (+ (+ (* v1_8 v2_8) (* v1_9 v2_9)) (+ (* v1_10 v2_10) (* v1_11 v2_11))) (+ (+ (* v1_12 v2_12) (* v1_13 v2_13)) (+ (* v1_14 v2_14) (* v1_15 v2_15))))) (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (* v1_16 v2_16) (* v1_17 v2_17)) (+ (* v1_18 v2_18) (* v1_19 v2_19))) (+ (+ (* v1_20 v2_20) (* v1_21 v2_21)) (+ (* v1_22 v2_22) (* v1_23 v2_23)))) (+ (+ (+ (* v1_24 v2_24) (* v1_25 v2_25)) (+ (* v1_26 v2_26) (* v1_27 v2_27))) (+ (+ (* v1_28 v2_28) (* v1_29 v2_29)) (+ (* v1_30 v2_30) (* v1_31 v2_31))))) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) (- 0)) (- (- 0))) (- (- (- 0)))) (- (- (- (- 0))))) (- (- (- (- (- 0)))))) (- (- (- (- (- (- 0))))))) (- (- (- (- (- (- (- 0)))))))) 0) 0) 0)))</t>
+          <t>(Vec (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (+ (* 1 (+ (+ (+ (+ (* v1_0 v2_0) (* v1_1 v2_1)) (+ (* v1_2 v2_2) (* v1_3 v2_3))) (+ (+ (* v1_4 v2_4) (* v1_5 v2_5)) (+ (* v1_6 v2_6) (* v1_7 v2_7)))) (+ (+ (+ (* v1_8 v2_8) (* v1_9 v2_9)) (+ (* v1_10 v2_10) (* v1_11 v2_11))) (+ (+ (* v1_12 v2_12) (* v1_13 v2_13)) (+ (* v1_14 v2_14) (* v1_15 v2_15)))))) (+ (* 1 (+ (+ (+ (* v1_16 v2_16) (* v1_17 v2_17)) (+ (* v1_18 v2_18) (* v1_19 v2_19))) (+ (+ (* v1_20 v2_20) (* v1_21 v2_21)) (+ (* v1_22 v2_22) (* v1_23 v2_23))))) (+ (+ (+ (* v1_24 v2_24) (* v1_25 v2_25)) (+ (* v1_26 v2_26) (* v1_27 v2_27))) (+ (+ (* v1_28 v2_28) (* v1_29 v2_29)) (+ (* v1_30 v2_30) (* v1_31 v2_31)))))))))))))))))</t>
         </is>
       </c>
       <c r="E102" t="n">
         <v>15759</v>
       </c>
       <c r="F102" t="n">
-        <v>34305</v>
+        <v>18781</v>
       </c>
       <c r="G102" t="n">
-        <v>-117.69</v>
+        <v>-19.18</v>
       </c>
       <c r="H102" t="n">
         <v>42.97</v>
       </c>
       <c r="I102" t="n">
-        <v>98.06999999999999</v>
+        <v>423.36</v>
       </c>
       <c r="J102" t="b">
         <v>0</v>
       </c>
       <c r="K102" t="n">
-        <v>401.93</v>
+        <v>76.64</v>
       </c>
       <c r="L102" t="n">
         <v>75</v>
@@ -4747,29 +4747,29 @@
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>(Vec (+ in_1_1 (* in_0_1 2)) (+ (+ in_1_2 (- in_1_0)) (+ (* in_0_2 2) (* in_0_0 -2))) (+ (+ in_1_3 (- in_1_1)) (+ (* in_0_3 2) (* in_0_1 -2))) (+ (- in_1_2) (* in_0_2 -2)) (+ in_2_1 (+ in_0_1 (* in_1_1 2))) (+ (+ in_2_2 (- in_2_0)) (+ (+ in_0_2 (- in_0_0)) (+ (* in_1_2 2) (* in_1_0 -2)))) (+ (+ in_2_3 (- in_2_1)) (+ (+ in_0_3 (- in_0_1)) (+ (* in_1_3 2) (* in_1_1 -2)))) (+ (- in_2_2) (+ (- in_0_2) (* in_1_2 -2))) (+ in_3_1 (+ in_1_1 (* in_2_1 2))) (+ (+ in_3_2 (- in_3_0)) (+ (+ in_1_2 (- in_1_0)) (+ (* in_2_2 2) (* in_2_0 -2)))) (+ (+ in_3_3 (- in_3_1)) (+ (+ in_1_3 (- in_1_1)) (+ (* in_2_3 2) (* in_2_1 -2)))) (+ (- in_3_2) (+ (- in_1_2) (* in_2_2 -2))) (+ in_2_1 (* in_3_1 2)) (+ (+ in_2_2 (- in_2_0)) (+ (* in_3_2 2) (* in_3_0 -2))) (+ (+ in_2_3 (- in_2_1)) (+ (* in_3_3 2) (* in_3_1 -2))) (+ (- in_2_2) (* in_3_2 -2)))</t>
+          <t>(Vec (+ in_1_1 (* in_0_1 2)) (+ (+ in_1_2 (- in_1_0)) (+ (* in_0_2 2) (* in_0_0 -2))) (+ (+ in_1_3 (- in_1_1)) (+ (* in_0_3 2) (* in_0_1 -2))) (+ (- in_1_2) (* in_0_2 -2)) (+ in_2_1 (+ in_0_1 (* in_1_1 2))) (+ (+ in_2_2 (- in_2_0)) (+ (+ in_0_2 (- in_0_0)) (+ (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (* in_1_2 2))))))))) (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (* in_1_0 -2)))))))))))) (+ (+ in_2_3 (- in_2_1)) (+ (+ in_0_3 (- in_0_1)) (+ (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (* in_1_3 2)))))))) (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (* in_1_1 -2))))))))))) (+ (- in_2_2) (+ (- in_0_2) (* in_1_2 -2))) (+ in_3_1 (+ in_1_1 (* in_2_1 2))) (+ (+ in_3_2 (- in_3_0)) (+ (+ in_1_2 (- in_1_0)) (+ (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (* in_2_2 2)))))))) (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (* in_2_0 -2))))))))))) (+ (+ in_3_3 (- in_3_1)) (+ (+ in_1_3 (- in_1_1)) (+ (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (* in_2_3 2)))))))) (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (* in_2_1 -2))))))))))) (+ (- in_3_2) (+ (- in_1_2) (* in_2_2 -2))) (+ in_2_1 (* in_3_1 2)) (+ (+ in_2_2 (- in_2_0)) (+ (* in_3_2 2) (* in_3_0 -2))) (+ (+ in_2_3 (- in_2_1)) (+ (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (* in_3_3 2))))))))) (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (* in_3_1 -2))))))))))) (+ (- in_2_2) (* in_3_2 -2)))</t>
         </is>
       </c>
       <c r="E103" t="n">
         <v>21507</v>
       </c>
       <c r="F103" t="n">
-        <v>21507</v>
+        <v>40015</v>
       </c>
       <c r="G103" t="n">
-        <v>0</v>
+        <v>-86.06</v>
       </c>
       <c r="H103" t="n">
         <v>40.57</v>
       </c>
       <c r="I103" t="n">
-        <v>40.57</v>
+        <v>50.15</v>
       </c>
       <c r="J103" t="b">
         <v>0</v>
       </c>
       <c r="K103" t="n">
-        <v>459.43</v>
+        <v>449.85</v>
       </c>
       <c r="L103" t="n">
         <v>75</v>
@@ -4789,32 +4789,32 @@
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>(Vec (+ (+ (* a_0_0 b_0_0) (* a_0_1 b_1_0)) (* a_0_2 b_2_0)) (+ (+ (* a_0_0 b_0_1) (* a_0_1 b_1_1)) (* a_0_2 b_2_1)) (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (* a_0_0 b_0_2) (* a_0_1 b_1_2)) (* a_0_2 b_2_2)) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) (+ (+ (* a_1_0 b_0_0) (* a_1_1 b_1_0)) (* a_1_2 b_2_0)) (+ (+ (* a_1_0 b_0_1) (* a_1_1 b_1_1)) (* a_1_2 b_2_1)) (+ (+ (* a_1_0 b_0_2) (* a_1_1 b_1_2)) (* a_1_2 b_2_2)) (+ (+ (* a_2_0 b_0_0) (* a_2_1 b_1_0)) (* a_2_2 b_2_0)) (+ (+ (* a_2_0 b_0_1) (* a_2_1 b_1_1)) (* a_2_2 b_2_1)) (+ (+ (* a_2_0 b_0_2) (* a_2_1 b_1_2)) (* a_2_2 b_2_2)))</t>
+          <t>(Vec ( + ( + ( * a_0_0 b_0_0 ) ( * a_0_1 b_1_0 ) ) ( * a_0_2 b_2_0 ) ) ( + ( + ( * a_0_0 b_0_1 ) ( * a_0_1 b_1_1 ) ) ( * a_0_2 b_2_1 ) ) ( + ( + ( * a_0_0 b_0_2 ) ( * a_0_1 b_1_2 ) ) ( * a_0_2 b_2_2 ) ) ( + ( + ( * a_1_0 b_0_0 ) ( * a_1_1 b_1_0 ) ) ( * a_1_2 b_2_0 ) ) ( + ( + ( * a_1_0 b_0_1 ) ( * a_1_1 b_1_1 ) ) ( * a_1_2 b_2_1 ) ) ( + ( + ( * a_1_0 b_0_2 ) ( * a_1_1 b_1_2 ) ) ( * a_1_2 b_2_2 ) ) ( + ( + ( * a_2_0 b_0_0 ) ( * a_2_1 b_1_0 ) ) ( * a_2_2 b_2_0 ) ) ( + ( + ( * a_2_0 b_0_1 ) ( * a_2_1 b_1_1 ) ) ( * a_2_2 b_2_1 ) ) ( + ( + ( * a_2_0 b_0_2 ) ( * a_2_1 b_1_2 ) ) ( * a_2_2 b_2_2 ) ) )</t>
         </is>
       </c>
       <c r="E104" t="n">
         <v>11256</v>
       </c>
       <c r="F104" t="n">
-        <v>29830</v>
+        <v>11256</v>
       </c>
       <c r="G104" t="n">
-        <v>-165.01</v>
+        <v>0</v>
       </c>
       <c r="H104" t="n">
         <v>39.37</v>
       </c>
       <c r="I104" t="n">
-        <v>128.02</v>
+        <v>39.37</v>
       </c>
       <c r="J104" t="b">
         <v>0</v>
       </c>
       <c r="K104" t="n">
-        <v>371.98</v>
+        <v>460.63</v>
       </c>
       <c r="L104" t="n">
-        <v>75</v>
+        <v>1</v>
       </c>
     </row>
     <row r="105">
@@ -4831,32 +4831,32 @@
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>(Vec (+ (* (+ (* o3 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (- 1 c23))))))))))))) (* c23 o2)) (- 1 c12)) (* c12 (+ (* o3 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (- 1 c13))))))))))))) (* c13 o1)))))</t>
+          <t>(Vec ( + ( * ( + ( * o3 ( - 1 c23 ) ) ( * c23 o2 ) ) ( - 1 c12 ) ) ( * c12 ( + ( * o3 ( - 1 c13 ) ) ( * c13 o1 ) ) ) ) )</t>
         </is>
       </c>
       <c r="E105" t="n">
         <v>3009</v>
       </c>
       <c r="F105" t="n">
-        <v>8531</v>
+        <v>3009</v>
       </c>
       <c r="G105" t="n">
-        <v>-183.52</v>
+        <v>0</v>
       </c>
       <c r="H105" t="n">
         <v>75.15000000000001</v>
       </c>
       <c r="I105" t="n">
-        <v>455.54</v>
+        <v>75.15000000000001</v>
       </c>
       <c r="J105" t="b">
         <v>0</v>
       </c>
       <c r="K105" t="n">
-        <v>44.46</v>
+        <v>424.85</v>
       </c>
       <c r="L105" t="n">
-        <v>23</v>
+        <v>1</v>
       </c>
     </row>
     <row r="106">
@@ -4873,32 +4873,32 @@
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>(Vec (+ (* (+ (* (+ (* o321 (- 1 c23)) (* c23 o231)) (- 1 c13)) (* c13 o213)) (- 1 c12)) (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (* c12 (+ (* (- 1 c23) (+ (* o312 (- 1 c13)) (* c13 o132))) (* c23 o123))) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0)))</t>
+          <t>(Vec ( + ( * ( + ( * ( + ( * o321 ( - 1 c23 ) ) ( * c23 o231 ) ) ( - 1 c13 ) ) ( * c13 o213 ) ) ( - 1 c12 ) ) ( * c12 ( + ( * ( - 1 c23 ) ( + ( * o312 ( - 1 c13 ) ) ( * c13 o132 ) ) ) ( * c23 o123 ) ) ) ) )</t>
         </is>
       </c>
       <c r="E106" t="n">
         <v>5012</v>
       </c>
       <c r="F106" t="n">
-        <v>23586</v>
+        <v>5012</v>
       </c>
       <c r="G106" t="n">
-        <v>-370.59</v>
+        <v>0</v>
       </c>
       <c r="H106" t="n">
         <v>110.93</v>
       </c>
       <c r="I106" t="n">
-        <v>199.58</v>
+        <v>110.93</v>
       </c>
       <c r="J106" t="b">
         <v>0</v>
       </c>
       <c r="K106" t="n">
-        <v>300.42</v>
+        <v>389.07</v>
       </c>
       <c r="L106" t="n">
-        <v>75</v>
+        <v>1</v>
       </c>
     </row>
     <row r="107">
@@ -4915,29 +4915,29 @@
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>(VecMul (Vec (+ x9602 x9604) (+ (+ x9608 x9610) (* (+ (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* x9613 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) x9615) x9617) 1))) (&lt;&lt; (Vec (+ x9602 x9604) (+ (+ x9608 x9610) (* (+ (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* x9613 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) x9615) x9617) 1))) 1))</t>
+          <t>(Vec (* (+ x9602 x9604) (+ (+ x9608 x9610) (+ (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (* x9613 x9615))))))))))))))))))))))))))))))))))))))))))))))))))))))))))))))))))))))))))) x9617))))</t>
         </is>
       </c>
       <c r="E107" t="n">
         <v>1508</v>
       </c>
       <c r="F107" t="n">
-        <v>19806</v>
+        <v>20082</v>
       </c>
       <c r="G107" t="n">
-        <v>-1213.4</v>
+        <v>-1231.7</v>
       </c>
       <c r="H107" t="n">
         <v>73.95</v>
       </c>
       <c r="I107" t="n">
-        <v>2599.56</v>
+        <v>162.61</v>
       </c>
       <c r="J107" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K107" t="n">
-        <v>-2099.56</v>
+        <v>337.39</v>
       </c>
       <c r="L107" t="n">
         <v>75</v>
@@ -4957,29 +4957,29 @@
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>(Vec (+ (+ (* (+ (* x9604 x9605) (+ x9607 x9608)) (+ (+ x9611 x9612) (+ x9614 x9615))) (* (* (* x9619 x9620) (* x9622 x9623)) (* (+ x9626 x9627) (* x9629 x9630)))) (* (+ (+ (* x9634 x9635) (+ x9637 x9638)) (+ (* x9641 x9642) (* x9644 x9645))) (+ (* (+ x9649 x9650) (+ x9652 x9653)) (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (+ (* x9656 x9657) (* x9659 x9660)) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1)))))</t>
+          <t>(Vec (+ (+ (* (+ (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (* x9604 x9605))))))))) (+ x9607 x9608)) (+ (+ x9611 x9612) (+ x9614 x9615))) (* (* (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (* x9619 x9620))))))))) (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (* x9622 x9623)))))))))) (* (+ x9626 x9627) (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (* x9629 x9630))))))))))) (* (+ (+ (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (* x9634 x9635)))))))) (+ x9637 x9638)) (+ (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (* x9641 x9642)))))))) (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (* x9644 x9645)))))))))) (+ (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (* (+ x9649 x9650) (+ x9652 x9653)))))))))) (+ (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (* x9656 x9657)))))))) (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (* x9659 x9660)))))))))))))</t>
         </is>
       </c>
       <c r="E108" t="n">
         <v>7760</v>
       </c>
       <c r="F108" t="n">
-        <v>26407</v>
+        <v>26268</v>
       </c>
       <c r="G108" t="n">
-        <v>-240.3</v>
+        <v>-238.51</v>
       </c>
       <c r="H108" t="n">
         <v>108.53</v>
       </c>
       <c r="I108" t="n">
-        <v>2634.14</v>
+        <v>118.12</v>
       </c>
       <c r="J108" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K108" t="n">
-        <v>-2134.14</v>
+        <v>381.88</v>
       </c>
       <c r="L108" t="n">
         <v>75</v>
@@ -4999,29 +4999,29 @@
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>(Vec (+ (* (+ (* (+ (* (+ (* o5 (- 1 c45)) (* c45 o4)) (- 1 c34)) (* c34 (+ (* o5 (- 1 c35)) (* c35 o3)))) (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (- 1 c23) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1)) (* c23 (+ (* (+ (* o5 (- 1 c45)) (* c45 o4)) (- 1 c24)) (* c24 (+ (* o5 (- 1 c25)) (* c25 o2)))))) (- 1 c12)) (* c12 (+ (* (+ (* (+ (* o5 (- 1 c45)) (* c45 o4)) (- 1 c34)) (* c34 (+ (* o5 (- 1 c35)) (* c35 o3)))) (- 1 c13)) (* c13 (+ (* (+ (* o5 (- 1 c45)) (* c45 o4)) (- 1 c14)) (* c14 (+ (* o5 (- 1 c15)) (* c15 o1)))))))))</t>
+          <t>(Vec (+ (* (+ (* (+ (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (* (+ (* o5 (- 1 c45)) (* c45 o4)) (- 1 c34))))))))))))) (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (* c34 (+ (* o5 (- 1 c35)) (* c35 o3))))))))))))))) (- 1 c23)) (* c23 (+ (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (* (+ (* o5 (- 1 c45)) (* c45 o4)) (- 1 c24)))))))))))) (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (* c24 (+ (* o5 (- 1 c25)) (* c25 o2)))))))))))))))) (- 1 c12)) (* c12 (+ (* (+ (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (* (+ (* o5 (- 1 c45)) (* c45 o4)) (- 1 c34)))))))))))) (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (* c34 (+ (* o5 (- 1 c35)) (* c35 o3)))))))))))))) (- 1 c13)) (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (* c13 (+ (* (+ (* o5 (- 1 c45)) (* c45 o4)) (- 1 c14)) (* c14 (+ (* o5 (- 1 c15)) (* c15 o1)))))))))))))))))))))</t>
         </is>
       </c>
       <c r="E109" t="n">
         <v>15015</v>
       </c>
       <c r="F109" t="n">
-        <v>33657</v>
+        <v>33527</v>
       </c>
       <c r="G109" t="n">
-        <v>-124.16</v>
+        <v>-123.29</v>
       </c>
       <c r="H109" t="n">
         <v>146.71</v>
       </c>
       <c r="I109" t="n">
-        <v>2634.14</v>
+        <v>161.09</v>
       </c>
       <c r="J109" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K109" t="n">
-        <v>-2134.14</v>
+        <v>338.91</v>
       </c>
       <c r="L109" t="n">
         <v>75</v>
@@ -5041,32 +5041,32 @@
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>(Vec (+ (+ in_1_1 in_1_0) (+ in_0_1 in_0_0)) (+ (+ (+ in_1_2 in_1_1) (+ in_1_0 in_0_2)) (+ in_0_1 in_0_0)) (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ in_1_3 in_1_2) (+ in_1_1 in_0_3)) (+ in_0_2 in_0_1)) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) (+ (+ in_1_3 in_1_2) (+ in_0_3 in_0_2)) (+ (+ (+ in_2_1 in_2_0) (+ in_1_1 in_1_0)) (+ in_0_1 in_0_0)) (+ (+ (+ in_2_2 (+ in_2_1 in_2_0)) (+ in_1_2 in_1_1)) (+ (+ in_1_0 in_0_2) (+ in_0_1 in_0_0))) (+ (+ (+ in_2_3 (+ in_2_2 in_2_1)) (+ in_1_3 in_1_2)) (+ (+ in_1_1 in_0_3) (+ in_0_2 in_0_1))) (+ (+ (+ in_2_3 in_2_2) (+ in_1_3 in_1_2)) (+ in_0_3 in_0_2)) (+ (+ in_3_1 in_3_0) (+ (+ in_2_1 in_2_0) (+ in_1_1 in_1_0))) (+ (+ (+ in_3_2 (+ in_3_1 in_3_0)) (+ in_2_2 in_2_1)) (+ (+ in_2_0 in_1_2) (+ in_1_1 in_1_0))) (+ (+ (+ in_3_3 (+ in_3_2 in_3_1)) (+ in_2_3 in_2_2)) (+ (+ in_2_1 in_1_3) (+ in_1_2 in_1_1))) (+ (+ (+ in_3_3 in_3_2) (+ in_2_3 in_2_2)) (+ in_1_3 in_1_2)) (+ (+ in_3_1 in_3_0) (+ in_2_1 in_2_0)) (+ (+ (+ in_3_2 in_3_1) (+ in_3_0 in_2_2)) (+ in_2_1 in_2_0)) (+ (+ (+ in_3_3 in_3_2) (+ in_3_1 in_2_3)) (+ in_2_2 in_2_1)) (+ (+ in_3_3 in_3_2) (+ in_2_3 in_2_2)))</t>
+          <t>(Vec ( + ( + in_1_1 in_1_0 ) ( + in_0_1 in_0_0 ) ) ( + ( + ( + in_1_2 in_1_1 ) ( + in_1_0 in_0_2 ) ) ( + in_0_1 in_0_0 ) ) ( + ( + ( + in_1_3 in_1_2 ) ( + in_1_1 in_0_3 ) ) ( + in_0_2 in_0_1 ) ) ( + ( + in_1_3 in_1_2 ) ( + in_0_3 in_0_2 ) ) ( + ( + ( + in_2_1 in_2_0 ) ( + in_1_1 in_1_0 ) ) ( + in_0_1 in_0_0 ) ) ( + ( + ( + in_2_2 ( + in_2_1 in_2_0 ) ) ( + in_1_2 in_1_1 ) ) ( + ( + in_1_0 in_0_2 ) ( + in_0_1 in_0_0 ) ) ) ( + ( + ( + in_2_3 ( + in_2_2 in_2_1 ) ) ( + in_1_3 in_1_2 ) ) ( + ( + in_1_1 in_0_3 ) ( + in_0_2 in_0_1 ) ) ) ( + ( + ( + in_2_3 in_2_2 ) ( + in_1_3 in_1_2 ) ) ( + in_0_3 in_0_2 ) ) ( + ( + in_3_1 in_3_0 ) ( + ( + in_2_1 in_2_0 ) ( + in_1_1 in_1_0 ) ) ) ( + ( + ( + in_3_2 ( + in_3_1 in_3_0 ) ) ( + in_2_2 in_2_1 ) ) ( + ( + in_2_0 in_1_2 ) ( + in_1_1 in_1_0 ) ) ) ( + ( + ( + in_3_3 ( + in_3_2 in_3_1 ) ) ( + in_2_3 in_2_2 ) ) ( + ( + in_2_1 in_1_3 ) ( + in_1_2 in_1_1 ) ) ) ( + ( + ( + in_3_3 in_3_2 ) ( + in_2_3 in_2_2 ) ) ( + in_1_3 in_1_2 ) ) ( + ( + in_3_1 in_3_0 ) ( + in_2_1 in_2_0 ) ) ( + ( + ( + in_3_2 in_3_1 ) ( + in_3_0 in_2_2 ) ) ( + in_2_1 in_2_0 ) ) ( + ( + ( + in_3_3 in_3_2 ) ( + in_3_1 in_2_3 ) ) ( + in_2_2 in_2_1 ) ) ( + ( + in_3_3 in_3_2 ) ( + in_2_3 in_2_2 ) ) )</t>
         </is>
       </c>
       <c r="E110" t="n">
         <v>21006</v>
       </c>
       <c r="F110" t="n">
-        <v>39579</v>
+        <v>21006</v>
       </c>
       <c r="G110" t="n">
-        <v>-88.42</v>
+        <v>0</v>
       </c>
       <c r="H110" t="n">
         <v>7.19</v>
       </c>
       <c r="I110" t="n">
-        <v>94.64</v>
+        <v>7.19</v>
       </c>
       <c r="J110" t="b">
         <v>0</v>
       </c>
       <c r="K110" t="n">
-        <v>405.36</v>
+        <v>492.81</v>
       </c>
       <c r="L110" t="n">
-        <v>75</v>
+        <v>1</v>
       </c>
     </row>
     <row r="111">
@@ -5083,7 +5083,7 @@
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>(Vec (+ v2_0 (+ 2 (* v1_0 5))) (+ v2_1 (+ 2 (* v1_1 5))) (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ v2_2 (+ 2 (* v1_2 5))) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) (+ v2_3 (+ 2 (* v1_3 5))))</t>
+          <t>(Vec (+ v2_0 (+ 2 (* v1_0 5))) (+ v2_1 (+ 2 (* v1_1 5))) (+ v2_2 (+ 2 (* v1_2 5))) (+ v2_3 (+ 2 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (* v1_3 5))))))))))))))))))))))))))))))))))))))))))))))))))))))))))))))))))))))))))))))</t>
         </is>
       </c>
       <c r="E111" t="n">
@@ -5125,29 +5125,29 @@
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>(Vec (+ v2_0 (+ 2 (* v1_0 5))) (+ v2_1 (+ 2 (* v1_1 5))) (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ v2_2 (+ 2 (* v1_2 5))) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) (- 0)) 0) 0) 0) 0) 0) (- 0)) (- 0)) (- (- 0))) (- (- (- 0)))) (- (- (- (- 0))))) (- (- 0))) 0) 0) 0) (+ v2_3 (+ 2 (* v1_3 5))) (+ v2_4 (+ 2 (* v1_4 5))) (+ v2_5 (+ 2 (* v1_5 5))) (+ v2_6 (+ 2 (* v1_6 5))) (+ v2_7 (+ 2 (* v1_7 5))) (+ v2_8 (+ 2 (* v1_8 5))) (+ v2_9 (+ 2 (* v1_9 5))) (+ v2_10 (+ 2 (* v1_10 5))) (+ v2_11 (+ 2 (* v1_11 5))) (+ v2_12 (+ 2 (* v1_12 5))) (+ v2_13 (+ 2 (* v1_13 5))) (+ v2_14 (+ 2 (* v1_14 5))) (+ v2_15 (+ 2 (* v1_15 5))))</t>
+          <t>(Vec (+ v2_0 (* 1 (* 1 (* 1 (* 1 (+ 2 (* v1_0 5))))))) (+ v2_1 (* 1 (* 1 (* 1 (* 1 (+ 2 (* v1_1 5))))))) (+ v2_2 (* 1 (* 1 (* 1 (* 1 (+ 2 (* v1_2 5))))))) (* 1 (* 1 (* 1 (* 1 (* 1 (+ v2_3 (+ 2 (* v1_3 5)))))))) (* 1 (* 1 (* 1 (* 1 (* 1 (+ v2_4 (+ 2 (* v1_4 5)))))))) (* 1 (* 1 (* 1 (* 1 (* 1 (+ v2_5 (+ 2 (* v1_5 5)))))))) (* 1 (* 1 (* 1 (* 1 (* 1 (+ v2_6 (+ 2 (* v1_6 5)))))))) (* 1 (* 1 (* 1 (* 1 (* 1 (+ v2_7 (+ 2 (* v1_7 5)))))))) (* 1 (* 1 (* 1 (* 1 (* 1 (+ v2_8 (+ 2 (* v1_8 5)))))))) (* 1 (* 1 (* 1 (* 1 (* 1 (+ v2_9 (+ 2 (* v1_9 5)))))))) (* 1 (* 1 (* 1 (* 1 (* 1 (+ v2_10 (+ 2 (* v1_10 5)))))))) (* 1 (* 1 (* 1 (* 1 (* 1 (+ v2_11 (+ 2 (* v1_11 5)))))))) (* 1 (* 1 (* 1 (* 1 (* 1 (+ v2_12 (+ 2 (* v1_12 5)))))))) (* 1 (* 1 (* 1 (* 1 (+ v2_13 (+ 2 (* v1_13 5))))))) (* 1 (* 1 (* 1 (* 1 (+ v2_14 (+ 2 (* v1_14 5))))))) (* 1 (* 1 (* 1 (* 1 (+ v2_15 (+ 2 (* v1_15 5))))))))</t>
         </is>
       </c>
       <c r="E112" t="n">
         <v>12006</v>
       </c>
       <c r="F112" t="n">
-        <v>30566</v>
+        <v>30516</v>
       </c>
       <c r="G112" t="n">
-        <v>-154.59</v>
+        <v>-154.17</v>
       </c>
       <c r="H112" t="n">
         <v>39.37</v>
       </c>
       <c r="I112" t="n">
-        <v>111.25</v>
+        <v>212.28</v>
       </c>
       <c r="J112" t="b">
         <v>0</v>
       </c>
       <c r="K112" t="n">
-        <v>388.75</v>
+        <v>287.72</v>
       </c>
       <c r="L112" t="n">
         <v>75</v>
@@ -5167,29 +5167,29 @@
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>(Vec (+ (+ (- (+ v1_0 v2_0) (* (* v1_0 v2_0) 2)) (- (+ v1_1 v2_1) (* 2 (* v1_1 v2_1)))) (- (+ v1_2 v2_2) (* 2 (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* v1_2 v2_2) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1)))))</t>
+          <t>(Vec (+ (+ (- (+ v1_0 v2_0) (* (* v1_0 v2_0) 2)) (- (+ v1_1 v2_1) (* 2 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (* v1_1 v2_1)))))))))))))))))))))))))))))))))))))))))))))))))))))))))))))))))))))))))))))) (- (+ v1_2 v2_2) (* 2 (* v1_2 v2_2)))))</t>
         </is>
       </c>
       <c r="E113" t="n">
         <v>3509</v>
       </c>
       <c r="F113" t="n">
-        <v>22156</v>
+        <v>22083</v>
       </c>
       <c r="G113" t="n">
-        <v>-531.4</v>
+        <v>-529.3200000000001</v>
       </c>
       <c r="H113" t="n">
         <v>75.15000000000001</v>
       </c>
       <c r="I113" t="n">
-        <v>2632.94</v>
+        <v>163.8</v>
       </c>
       <c r="J113" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K113" t="n">
-        <v>-2132.94</v>
+        <v>336.2</v>
       </c>
       <c r="L113" t="n">
         <v>75</v>
@@ -5209,29 +5209,29 @@
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>(Vec (+ (+ (- (+ v1_0 v2_0) (* (* v1_0 v2_0) 2)) (- (+ v1_1 v2_1) (* 2 (* v1_1 v2_1)))) (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (- (+ v1_2 v2_2) (* 2 (* v1_2 v2_2))) (- (+ v1_3 v2_3) (* 2 (* v1_3 v2_3)))) (- (+ v1_4 v2_4) (* 2 (* v1_4 v2_4)))) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0)))</t>
+          <t>(Vec (+ (+ (- (+ v1_0 v2_0) (* (* v1_0 v2_0) 2)) (- (+ v1_1 v2_1) (* 2 (* v1_1 v2_1)))) (+ (+ (- (+ v1_2 v2_2) (* 2 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (* v1_2 v2_2)))))))))))))))))))))))))))))))))))))))) (- (+ v1_3 v2_3) (* 2 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (* v1_3 v2_3))))))))))))))))))))))))))))))))))))))))) (- (+ v1_4 v2_4) (* 2 (* v1_4 v2_4))))))</t>
         </is>
       </c>
       <c r="E114" t="n">
         <v>6010</v>
       </c>
       <c r="F114" t="n">
-        <v>24584</v>
+        <v>24547</v>
       </c>
       <c r="G114" t="n">
-        <v>-309.05</v>
+        <v>-308.44</v>
       </c>
       <c r="H114" t="n">
         <v>76.34999999999999</v>
       </c>
       <c r="I114" t="n">
-        <v>165</v>
+        <v>120.68</v>
       </c>
       <c r="J114" t="b">
         <v>0</v>
       </c>
       <c r="K114" t="n">
-        <v>335</v>
+        <v>379.32</v>
       </c>
       <c r="L114" t="n">
         <v>75</v>
@@ -5251,29 +5251,29 @@
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>(Vec (+ (+ (+ (+ (- (+ v1_0 v2_0) (* (* v1_0 v2_0) 2)) (- (+ v1_1 v2_1) (* 2 (* v1_1 v2_1)))) (+ (- (+ v1_2 v2_2) (* 2 (* v1_2 v2_2))) (- (+ v1_3 v2_3) (* 2 (* v1_3 v2_3))))) (+ (+ (- (+ v1_4 v2_4) (* 2 (* v1_4 v2_4))) (- (+ v1_5 v2_5) (* 2 (* v1_5 v2_5)))) (+ (- (+ v1_6 v2_6) (* 2 (* v1_6 v2_6))) (- (+ v1_7 v2_7) (* 2 (* v1_7 v2_7)))))) (+ (+ (+ (- (+ v1_8 v2_8) (* 2 (* v1_8 v2_8))) (- (+ v1_9 v2_9) (* 2 (* v1_9 v2_9)))) (+ (- (+ v1_10 v2_10) (* 2 (* v1_10 v2_10))) (- (+ v1_11 v2_11) (* 2 (* v1_11 v2_11))))) (+ (+ (- (+ v1_12 v2_12) (* 2 (* v1_12 v2_12))) (- (+ v1_13 v2_13) (* 2 (* v1_13 v2_13)))) (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (+ (* 1 (- (+ v1_14 v2_14) (* 2 (* v1_14 v2_14)))) (* 1 (- (+ v1_15 v2_15) (* 2 (* v1_15 v2_15)))))))))))))))))))))))))))))))))</t>
+          <t>(Vec (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (+ (* 1 (+ (+ (+ (- (+ v1_0 v2_0) (* (* v1_0 v2_0) 2)) (- (+ v1_1 v2_1) (* 2 (* v1_1 v2_1)))) (+ (- (+ v1_2 v2_2) (* 2 (* v1_2 v2_2))) (- (+ v1_3 v2_3) (* 2 (* v1_3 v2_3))))) (+ (+ (- (+ v1_4 v2_4) (* 2 (* v1_4 v2_4))) (- (+ v1_5 v2_5) (* 2 (* v1_5 v2_5)))) (+ (- (+ v1_6 v2_6) (* 2 (* v1_6 v2_6))) (- (+ v1_7 v2_7) (* 2 (* v1_7 v2_7))))))) (+ (* 1 (+ (+ (- (+ v1_8 v2_8) (* 2 (* v1_8 v2_8))) (- (+ v1_9 v2_9) (* 2 (* v1_9 v2_9)))) (+ (- (+ v1_10 v2_10) (* 2 (* v1_10 v2_10))) (- (+ v1_11 v2_11) (* 2 (* v1_11 v2_11)))))) (+ (+ (- (+ v1_12 v2_12) (* 2 (* v1_12 v2_12))) (- (+ v1_13 v2_13) (* 2 (* v1_13 v2_13)))) (+ (- (+ v1_14 v2_14) (* 2 (* v1_14 v2_14))) (- (+ v1_15 v2_15) (* 2 (* v1_15 v2_15))))))))))))))))))</t>
         </is>
       </c>
       <c r="E115" t="n">
         <v>19761</v>
       </c>
       <c r="F115" t="n">
-        <v>26311</v>
+        <v>22783</v>
       </c>
       <c r="G115" t="n">
-        <v>-33.15</v>
+        <v>-15.29</v>
       </c>
       <c r="H115" t="n">
         <v>77.55</v>
       </c>
       <c r="I115" t="n">
-        <v>942.0700000000001</v>
+        <v>457.94</v>
       </c>
       <c r="J115" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K115" t="n">
-        <v>-442.07</v>
+        <v>42.06</v>
       </c>
       <c r="L115" t="n">
         <v>75</v>
@@ -5293,29 +5293,29 @@
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>(Vec (+ c1_0 (+ c2_0 (* c0_0 (+ c3_0 (* c0_0 c4_0))))) (+ c1_1 (+ (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* c2_1 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) (* c0_1 (+ c3_1 (* c0_1 c4_1))))) (+ c1_2 (+ c2_2 (* c0_2 (+ c3_2 (* c0_2 c4_2))))) (+ c1_3 (+ c2_3 (* c0_3 (+ c3_3 (* c0_3 c4_3))))))</t>
+          <t>(Vec (+ c1_0 (+ c2_0 (* c0_0 (+ c3_0 (* c0_0 c4_0))))) (+ c1_1 (+ c2_1 (* c0_1 (+ c3_1 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (* c0_1 c4_1)))))))))))))))))))))))))))))) (+ c1_2 (+ c2_2 (* c0_2 (+ c3_2 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (* c0_2 c4_2)))))))))))))))))))))))))))))) (+ c1_3 (+ c2_3 (* c0_3 (+ c3_3 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (* c0_3 c4_3))))))))))))))))))))))))))))))</t>
         </is>
       </c>
       <c r="E116" t="n">
         <v>5009</v>
       </c>
       <c r="F116" t="n">
-        <v>23652</v>
+        <v>23534</v>
       </c>
       <c r="G116" t="n">
-        <v>-372.19</v>
+        <v>-369.83</v>
       </c>
       <c r="H116" t="n">
         <v>75.15000000000001</v>
       </c>
       <c r="I116" t="n">
-        <v>2563.78</v>
+        <v>105.1</v>
       </c>
       <c r="J116" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K116" t="n">
-        <v>-2063.78</v>
+        <v>394.9</v>
       </c>
       <c r="L116" t="n">
         <v>75</v>
@@ -5335,29 +5335,29 @@
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>(Vec (+ c1_0 (+ c2_0 (* c0_0 (+ c3_0 (* c0_0 c4_0))))) (+ c1_1 (+ c2_1 (* c0_1 (+ c3_1 (* c0_1 c4_1))))) (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ c1_2 (+ c2_2 (* c0_2 (+ c3_2 (* c0_2 c4_2))))) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) (- 0)) (- 0)) (- (- 0))) (- (- (- 0)))) (- (- (- (- 0))))) (- (- (- (- (- 0)))))) (- (- (- (- (- (- 0))))))) (- (- (- (- (- (- (- 0)))))))) (- (- (- (- (- (- (- (- 0))))))))) 0) 0) 0) (+ c1_3 (+ c2_3 (* c0_3 (+ c3_3 (* c0_3 c4_3))))) (+ c1_4 (+ c2_4 (* c0_4 (+ c3_4 (* c0_4 c4_4))))) (+ c1_5 (+ c2_5 (* c0_5 (+ c3_5 (* c0_5 c4_5))))) (+ c1_6 (+ c2_6 (* c0_6 (+ c3_6 (* c0_6 c4_6))))) (+ c1_7 (+ c2_7 (* c0_7 (+ c3_7 (* c0_7 c4_7))))) (+ c1_8 (+ c2_8 (* c0_8 (+ c3_8 (* c0_8 c4_8))))) (+ c1_9 (+ c2_9 (* c0_9 (+ c3_9 (* c0_9 c4_9))))) (+ c1_10 (+ c2_10 (* c0_10 (+ c3_10 (* c0_10 c4_10))))) (+ c1_11 (+ c2_11 (* c0_11 (+ c3_11 (* c0_11 c4_11))))) (+ c1_12 (+ c2_12 (* c0_12 (+ c3_12 (* c0_12 c4_12))))) (+ c1_13 (+ c2_13 (* c0_13 (+ c3_13 (* c0_13 c4_13))))) (+ c1_14 (+ c2_14 (* c0_14 (+ c3_14 (* c0_14 c4_14))))) (+ c1_15 (+ c2_15 (* c0_15 (+ c3_15 (* c0_15 c4_15))))))</t>
+          <t>(Vec (+ c1_0 (* 1 (* 1 (* 1 (* 1 (+ c2_0 (* c0_0 (+ c3_0 (* c0_0 c4_0))))))))) (+ c1_1 (* 1 (* 1 (* 1 (* 1 (+ c2_1 (* c0_1 (+ c3_1 (* c0_1 c4_1))))))))) (+ c1_2 (* 1 (* 1 (* 1 (* 1 (+ c2_2 (* c0_2 (+ c3_2 (* c0_2 c4_2))))))))) (* 1 (* 1 (* 1 (* 1 (* 1 (+ c1_3 (+ c2_3 (* c0_3 (+ c3_3 (* c0_3 c4_3)))))))))) (* 1 (* 1 (* 1 (* 1 (* 1 (+ c1_4 (+ c2_4 (* c0_4 (+ c3_4 (* c0_4 c4_4)))))))))) (* 1 (* 1 (* 1 (* 1 (* 1 (+ c1_5 (+ c2_5 (* c0_5 (+ c3_5 (* c0_5 c4_5)))))))))) (* 1 (* 1 (* 1 (* 1 (* 1 (+ c1_6 (+ c2_6 (* c0_6 (+ c3_6 (* c0_6 c4_6)))))))))) (* 1 (* 1 (* 1 (* 1 (* 1 (+ c1_7 (+ c2_7 (* c0_7 (+ c3_7 (* c0_7 c4_7)))))))))) (* 1 (* 1 (* 1 (* 1 (* 1 (+ c1_8 (+ c2_8 (* c0_8 (+ c3_8 (* c0_8 c4_8)))))))))) (* 1 (* 1 (* 1 (* 1 (* 1 (+ c1_9 (+ c2_9 (* c0_9 (+ c3_9 (* c0_9 c4_9)))))))))) (* 1 (* 1 (* 1 (* 1 (* 1 (+ c1_10 (+ c2_10 (* c0_10 (+ c3_10 (* c0_10 c4_10)))))))))) (* 1 (* 1 (* 1 (* 1 (* 1 (+ c1_11 (+ c2_11 (* c0_11 (+ c3_11 (* c0_11 c4_11)))))))))) (* 1 (* 1 (* 1 (* 1 (* 1 (+ c1_12 (+ c2_12 (* c0_12 (+ c3_12 (* c0_12 c4_12)))))))))) (* 1 (* 1 (* 1 (* 1 (+ c1_13 (+ c2_13 (* c0_13 (+ c3_13 (* c0_13 c4_13))))))))) (* 1 (* 1 (* 1 (* 1 (+ c1_14 (+ c2_14 (* c0_14 (+ c3_14 (* c0_14 c4_14))))))))) (* 1 (* 1 (* 1 (* 1 (+ c1_15 (+ c2_15 (* c0_15 (+ c3_15 (* c0_15 c4_15))))))))))</t>
         </is>
       </c>
       <c r="E117" t="n">
         <v>20009</v>
       </c>
       <c r="F117" t="n">
-        <v>38546</v>
+        <v>38519</v>
       </c>
       <c r="G117" t="n">
-        <v>-92.64</v>
+        <v>-92.51000000000001</v>
       </c>
       <c r="H117" t="n">
         <v>75.15000000000001</v>
       </c>
       <c r="I117" t="n">
-        <v>119.48</v>
+        <v>248.06</v>
       </c>
       <c r="J117" t="b">
         <v>0</v>
       </c>
       <c r="K117" t="n">
-        <v>380.52</v>
+        <v>251.94</v>
       </c>
       <c r="L117" t="n">
         <v>75</v>
@@ -5377,32 +5377,32 @@
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>(Vec (+ (+ (* (- c2_0 c1_0) (- c2_0 c1_0)) (* (- c2_1 c1_1) (- c2_1 c1_1))) (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (* (- c2_2 c1_2) (- c2_2 c1_2)) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0)))</t>
+          <t>(Vec ( + ( + ( * ( - c2_0 c1_0 ) ( - c2_0 c1_0 ) ) ( * ( - c2_1 c1_1 ) ( - c2_1 c1_1 ) ) ) ( * ( - c2_2 c1_2 ) ( - c2_2 c1_2 ) ) ) )</t>
         </is>
       </c>
       <c r="E118" t="n">
         <v>2757</v>
       </c>
       <c r="F118" t="n">
-        <v>21330</v>
+        <v>2757</v>
       </c>
       <c r="G118" t="n">
-        <v>-673.67</v>
+        <v>0</v>
       </c>
       <c r="H118" t="n">
         <v>40.57</v>
       </c>
       <c r="I118" t="n">
-        <v>128.02</v>
+        <v>40.57</v>
       </c>
       <c r="J118" t="b">
         <v>0</v>
       </c>
       <c r="K118" t="n">
-        <v>371.98</v>
+        <v>459.43</v>
       </c>
       <c r="L118" t="n">
-        <v>75</v>
+        <v>1</v>
       </c>
     </row>
     <row r="119">
@@ -5419,29 +5419,29 @@
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>(Vec (+ (+ (* (- c2_0 c1_0) (- c2_0 c1_0)) (* (- c2_1 c1_1) (- c2_1 c1_1))) (+ (+ (* (- c2_2 c1_2) (- c2_2 c1_2)) (* (- c2_3 c1_3) (- c2_3 c1_3))) (* (- c2_4 c1_4) (- c2_4 c1_4)))))</t>
+          <t>(Vec (+ (+ (* (- c2_0 c1_0) (- c2_0 c1_0)) (* (- c2_1 c1_1) (- c2_1 c1_1))) (+ (+ (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (* (- c2_2 c1_2) (- c2_2 c1_2))))))))))))))))))))))))))))))))))))))) (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (* (- c2_3 c1_3) (- c2_3 c1_3)))))))))))))))))))))))))))))))))))))))) (* (- c2_4 c1_4) (- c2_4 c1_4)))))</t>
         </is>
       </c>
       <c r="E119" t="n">
         <v>4758</v>
       </c>
       <c r="F119" t="n">
-        <v>4758</v>
+        <v>23295</v>
       </c>
       <c r="G119" t="n">
-        <v>0</v>
+        <v>-389.6</v>
       </c>
       <c r="H119" t="n">
         <v>41.77</v>
       </c>
       <c r="I119" t="n">
-        <v>41.77</v>
+        <v>86.09</v>
       </c>
       <c r="J119" t="b">
         <v>0</v>
       </c>
       <c r="K119" t="n">
-        <v>458.23</v>
+        <v>413.91</v>
       </c>
       <c r="L119" t="n">
         <v>75</v>
@@ -5461,29 +5461,29 @@
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>(Vec (+ (+ (+ (+ (* (- c2_0 c1_0) (- c2_0 c1_0)) (* (- c2_1 c1_1) (- c2_1 c1_1))) (+ (* (- c2_2 c1_2) (- c2_2 c1_2)) (* (- c2_3 c1_3) (- c2_3 c1_3)))) (+ (+ (* (- c2_4 c1_4) (- c2_4 c1_4)) (* (- c2_5 c1_5) (- c2_5 c1_5))) (+ (* (- c2_6 c1_6) (- c2_6 c1_6)) (* (- c2_7 c1_7) (- c2_7 c1_7))))) (+ (+ (+ (* (- c2_8 c1_8) (- c2_8 c1_8)) (* (- c2_9 c1_9) (- c2_9 c1_9))) (+ (* (- c2_10 c1_10) (- c2_10 c1_10)) (* (- c2_11 c1_11) (- c2_11 c1_11)))) (+ (+ (* (- c2_12 c1_12) (- c2_12 c1_12)) (* (- c2_13 c1_13) (- c2_13 c1_13))) (+ (* (- c2_14 c1_14) (- c2_14 c1_14)) (* (- c2_15 c1_15) (- c2_15 c1_15)))))))</t>
+          <t>(Vec (+ (+ (+ (+ (* (- c2_0 c1_0) (- c2_0 c1_0)) (* (- c2_1 c1_1) (- c2_1 c1_1))) (+ (* (- c2_2 c1_2) (- c2_2 c1_2)) (* (- c2_3 c1_3) (- c2_3 c1_3)))) (+ (+ (* (- c2_4 c1_4) (- c2_4 c1_4)) (* (- c2_5 c1_5) (- c2_5 c1_5))) (+ (* (- c2_6 c1_6) (- c2_6 c1_6)) (* (- c2_7 c1_7) (- c2_7 c1_7))))) (+ (+ (+ (* (- c2_8 c1_8) (- c2_8 c1_8)) (* (- c2_9 c1_9) (- c2_9 c1_9))) (+ (* (- c2_10 c1_10) (- c2_10 c1_10)) (* (- c2_11 c1_11) (- c2_11 c1_11)))) (+ (+ (* (- c2_12 c1_12) (- c2_12 c1_12)) (* (- c2_13 c1_13) (- c2_13 c1_13))) (+ (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (* (- c2_14 c1_14) (- c2_14 c1_14))))))))))))))))))))))))))))))))))))))) (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (* (- c2_15 c1_15) (- c2_15 c1_15))))))))))))))))))))))))))))))))))))))))))))</t>
         </is>
       </c>
       <c r="E120" t="n">
         <v>15759</v>
       </c>
       <c r="F120" t="n">
-        <v>15759</v>
+        <v>34296</v>
       </c>
       <c r="G120" t="n">
-        <v>0</v>
+        <v>-117.63</v>
       </c>
       <c r="H120" t="n">
         <v>42.97</v>
       </c>
       <c r="I120" t="n">
-        <v>42.97</v>
+        <v>87.29000000000001</v>
       </c>
       <c r="J120" t="b">
         <v>0</v>
       </c>
       <c r="K120" t="n">
-        <v>457.03</v>
+        <v>412.71</v>
       </c>
       <c r="L120" t="n">
         <v>75</v>
@@ -5545,29 +5545,29 @@
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>(Vec (+ (+ (* v1_0 v2_0) (* v1_1 v2_1)) (+ (+ (* v1_2 v2_2) (* v1_3 v2_3)) (* v1_4 (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* v2_4 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1)))))</t>
+          <t>(Vec (+ (+ (* v1_0 v2_0) (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (* v1_1 v2_1))))))))))))))))))))))) (+ (+ (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (* v1_2 v2_2))))))))))))))) (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (* v1_3 v2_3))))))))))))))))))))) (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (* v1_4 v2_4))))))))))))))))))))))))</t>
         </is>
       </c>
       <c r="E122" t="n">
         <v>2257</v>
       </c>
       <c r="F122" t="n">
-        <v>20904</v>
+        <v>20777</v>
       </c>
       <c r="G122" t="n">
-        <v>-826.1900000000001</v>
+        <v>-820.5599999999999</v>
       </c>
       <c r="H122" t="n">
         <v>40.57</v>
       </c>
       <c r="I122" t="n">
-        <v>2598.36</v>
+        <v>64.53</v>
       </c>
       <c r="J122" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K122" t="n">
-        <v>-2098.36</v>
+        <v>435.47</v>
       </c>
       <c r="L122" t="n">
         <v>75</v>
@@ -5587,29 +5587,29 @@
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>(Vec (+ (+ (+ (+ (* v1_0 v2_0) (* v1_1 v2_1)) (+ (* v1_2 v2_2) (* v1_3 v2_3))) (+ (+ (* v1_4 v2_4) (* v1_5 v2_5)) (+ (* v1_6 v2_6) (* v1_7 v2_7)))) (+ (+ (+ (* v1_8 v2_8) (* v1_9 v2_9)) (+ (* v1_10 v2_10) (* v1_11 v2_11))) (+ (+ (* v1_12 v2_12) (* v1_13 v2_13)) (+ (* v1_14 v2_14) (* v1_15 v2_15))))))</t>
+          <t>(Vec (+ (+ (+ (+ (* v1_0 v2_0) (* v1_1 v2_1)) (+ (* v1_2 v2_2) (* v1_3 v2_3))) (+ (+ (* v1_4 v2_4) (* v1_5 v2_5)) (+ (* v1_6 v2_6) (* v1_7 v2_7)))) (+ (+ (+ (* v1_8 v2_8) (* v1_9 v2_9)) (+ (* v1_10 v2_10) (* v1_11 v2_11))) (+ (+ (* v1_12 v2_12) (* v1_13 v2_13)) (+ (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (* v1_14 v2_14)))))))))))))))))))))))))))))))))))))) (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (* v1_15 v2_15)))))))))))))))))))))))))))))))))))))))))))</t>
         </is>
       </c>
       <c r="E123" t="n">
         <v>7758</v>
       </c>
       <c r="F123" t="n">
-        <v>7758</v>
+        <v>26295</v>
       </c>
       <c r="G123" t="n">
-        <v>0</v>
+        <v>-238.94</v>
       </c>
       <c r="H123" t="n">
         <v>41.77</v>
       </c>
       <c r="I123" t="n">
-        <v>41.77</v>
+        <v>86.09</v>
       </c>
       <c r="J123" t="b">
         <v>0</v>
       </c>
       <c r="K123" t="n">
-        <v>458.23</v>
+        <v>413.91</v>
       </c>
       <c r="L123" t="n">
         <v>75</v>
@@ -5629,29 +5629,29 @@
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>(Vec (+ in_1_1 (* in_0_1 2)) (+ (+ in_1_2 (- in_1_0)) (+ (* in_0_2 2) (* in_0_0 -2))) (+ (- in_1_1) (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* in_0_1 -2) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1)) (+ in_2_1 (+ in_0_1 (* in_1_1 2))) (+ (+ in_2_2 (- in_2_0)) (+ (+ in_0_2 (- in_0_0)) (+ (* in_1_2 2) (* in_1_0 -2)))) (+ (- in_2_1) (+ (- in_0_1) (* in_1_1 -2))) (+ in_1_1 (* in_2_1 2)) (+ (+ in_1_2 (- in_1_0)) (+ (* in_2_2 2) (* in_2_0 -2))) (+ (- in_1_1) (* in_2_1 -2)))</t>
+          <t>(Vec (+ in_1_1 (* in_0_1 2)) (+ (+ in_1_2 (- in_1_0)) (+ (* in_0_2 2) (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (* in_0_0 -2)))))))))))))) (+ (- in_1_1) (* in_0_1 -2)) (+ in_2_1 (+ in_0_1 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (* in_1_1 2)))))))))))))) (+ (+ in_2_2 (- in_2_0)) (+ (+ in_0_2 (- in_0_0)) (+ (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (* in_1_2 2))))))))))) (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (* in_1_0 -2)))))))))))))) (+ (- in_2_1) (+ (- in_0_1) (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (* in_1_1 -2)))))))))))))) (+ in_1_1 (* in_2_1 2)) (+ (+ in_1_2 (- in_1_0)) (+ (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (* in_2_2 2)))))))))))) (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (* in_2_0 -2))))))))))))) (+ (- in_1_1) (* in_2_1 -2)))</t>
         </is>
       </c>
       <c r="E124" t="n">
         <v>9757</v>
       </c>
       <c r="F124" t="n">
-        <v>28403</v>
+        <v>28267</v>
       </c>
       <c r="G124" t="n">
-        <v>-191.1</v>
+        <v>-189.71</v>
       </c>
       <c r="H124" t="n">
         <v>40.57</v>
       </c>
       <c r="I124" t="n">
-        <v>2597.17</v>
+        <v>52.55</v>
       </c>
       <c r="J124" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K124" t="n">
-        <v>-2097.17</v>
+        <v>447.45</v>
       </c>
       <c r="L124" t="n">
         <v>75</v>
@@ -5671,29 +5671,29 @@
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>(Vec (+ in_1_1 (* in_0_1 2)) (+ (+ in_1_2 (- in_1_0)) (+ (* in_0_2 2) (* in_0_0 -2))) (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ in_1_3 (- in_1_1)) (+ (* in_0_3 2) (* in_0_1 -2))) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) (+ (+ in_1_4 (- in_1_2)) (+ (* in_0_4 2) (* in_0_2 -2))) (+ (- in_1_3) (* in_0_3 -2)) (+ in_2_1 (+ in_0_1 (* in_1_1 2))) (+ (+ in_2_2 (- in_2_0)) (+ (+ in_0_2 (- in_0_0)) (+ (* in_1_2 2) (* in_1_0 -2)))) (+ (+ in_2_3 (- in_2_1)) (+ (+ in_0_3 (- in_0_1)) (+ (* in_1_3 2) (* in_1_1 -2)))) (+ (+ in_2_4 (- in_2_2)) (+ (+ in_0_4 (- in_0_2)) (+ (* in_1_4 2) (* in_1_2 -2)))) (+ (- in_2_3) (+ (- in_0_3) (* in_1_3 -2))) (+ in_3_1 (+ in_1_1 (* in_2_1 2))) (+ (+ in_3_2 (- in_3_0)) (+ (+ in_1_2 (- in_1_0)) (+ (* in_2_2 2) (* in_2_0 -2)))) (+ (+ in_3_3 (- in_3_1)) (+ (+ in_1_3 (- in_1_1)) (+ (* in_2_3 2) (* in_2_1 -2)))) (+ (+ in_3_4 (- in_3_2)) (+ (+ in_1_4 (- in_1_2)) (+ (* in_2_4 2) (* in_2_2 -2)))) (+ (- in_3_3) (+ (- in_1_3) (* in_2_3 -2))) (+ in_4_1 (+ in_2_1 (* in_3_1 2))) (+ (+ in_4_2 (- in_4_0)) (+ (+ in_2_2 (- in_2_0)) (+ (* in_3_2 2) (* in_3_0 -2)))) (+ (+ in_4_3 (- in_4_1)) (+ (+ in_2_3 (- in_2_1)) (+ (* in_3_3 2) (* in_3_1 -2)))) (+ (+ in_4_4 (- in_4_2)) (+ (+ in_2_4 (- in_2_2)) (+ (* in_3_4 2) (* in_3_2 -2)))) (+ (- in_4_3) (+ (- in_2_3) (* in_3_3 -2))) (+ in_3_1 (* in_4_1 2)) (+ (+ in_3_2 (- in_3_0)) (+ (* in_4_2 2) (* in_4_0 -2))) (+ (+ in_3_3 (- in_3_1)) (+ (* in_4_3 2) (* in_4_1 -2))) (+ (+ in_3_4 (- in_3_2)) (+ (* in_4_4 2) (* in_4_2 -2))) (+ (- in_3_3) (* in_4_3 -2)))</t>
+          <t>(Vec (+ in_1_1 (* in_0_1 2)) (+ (+ in_1_2 (- in_1_0)) (+ (* in_0_2 2) (* in_0_0 -2))) (+ (+ in_1_3 (- in_1_1)) (+ (* in_0_3 2) (* in_0_1 -2))) (+ (+ in_1_4 (- in_1_2)) (+ (* in_0_4 2) (* in_0_2 -2))) (+ (- in_1_3) (* in_0_3 -2)) (+ in_2_1 (+ in_0_1 (* in_1_1 2))) (+ (+ in_2_2 (- in_2_0)) (+ (+ in_0_2 (- in_0_0)) (+ (+ 0 (+ 0 (+ 0 (* in_1_2 2)))) (+ 0 (+ 0 (+ 0 (* in_1_0 -2))))))) (+ (+ in_2_3 (- in_2_1)) (+ (+ in_0_3 (- in_0_1)) (+ (+ 0 (+ 0 (+ 0 (* in_1_3 2)))) (+ 0 (+ 0 (+ 0 (* in_1_1 -2))))))) (+ (+ in_2_4 (- in_2_2)) (+ (+ in_0_4 (- in_0_2)) (+ (+ 0 (+ 0 (+ 0 (* in_1_4 2)))) (+ 0 (+ 0 (* in_1_2 -2)))))) (+ (- in_2_3) (+ (- in_0_3) (+ 0 (+ 0 (+ 0 (* in_1_3 -2)))))) (+ in_3_1 (+ in_1_1 (+ 0 (+ 0 (+ 0 (* in_2_1 2)))))) (+ (+ in_3_2 (- in_3_0)) (+ (+ in_1_2 (- in_1_0)) (+ (+ 0 (+ 0 (* in_2_2 2))) (+ 0 (+ 0 (* in_2_0 -2)))))) (+ (+ in_3_3 (- in_3_1)) (+ (+ in_1_3 (- in_1_1)) (+ (+ 0 (+ 0 (* in_2_3 2))) (+ 0 (+ 0 (* in_2_1 -2)))))) (+ (+ in_3_4 (- in_3_2)) (+ (+ in_1_4 (- in_1_2)) (+ (+ 0 (+ 0 (* in_2_4 2))) (+ 0 (+ 0 (* in_2_2 -2)))))) (+ (- in_3_3) (+ (- in_1_3) (+ 0 (+ 0 (+ 0 (* in_2_3 -2)))))) (+ in_4_1 (+ in_2_1 (+ 0 (+ 0 (+ 0 (* in_3_1 2)))))) (+ (+ in_4_2 (- in_4_0)) (+ (+ in_2_2 (- in_2_0)) (+ (+ 0 (+ 0 (* in_3_2 2))) (+ 0 (+ 0 (* in_3_0 -2)))))) (+ (+ in_4_3 (- in_4_1)) (+ (+ in_2_3 (- in_2_1)) (+ (+ 0 (+ 0 (* in_3_3 2))) (+ 0 (+ 0 (* in_3_1 -2)))))) (+ (+ in_4_4 (- in_4_2)) (+ (+ in_2_4 (- in_2_2)) (+ (+ 0 (+ 0 (* in_3_4 2))) (+ 0 (+ 0 (* in_3_2 -2)))))) (+ (- in_4_3) (+ (- in_2_3) (+ 0 (+ 0 (+ 0 (* in_3_3 -2)))))) (+ in_3_1 (* in_4_1 2)) (+ (+ in_3_2 (- in_3_0)) (+ (+ 0 (+ 0 (+ 0 (* in_4_2 2)))) (+ 0 (+ 0 (+ 0 (* in_4_0 -2)))))) (+ (+ in_3_3 (- in_3_1)) (+ (+ 0 (+ 0 (+ 0 (* in_4_3 2)))) (+ 0 (+ 0 (+ 0 (* in_4_1 -2)))))) (+ (+ in_3_4 (- in_3_2)) (+ (+ 0 (+ 0 (+ 0 (* in_4_4 2)))) (+ 0 (+ 0 (+ 0 (* in_4_2 -2)))))) (+ (- in_3_3) (* in_4_3 -2)))</t>
         </is>
       </c>
       <c r="E125" t="n">
         <v>37757</v>
       </c>
       <c r="F125" t="n">
-        <v>56330</v>
+        <v>56260</v>
       </c>
       <c r="G125" t="n">
-        <v>-49.19</v>
+        <v>-49.01</v>
       </c>
       <c r="H125" t="n">
         <v>40.57</v>
       </c>
       <c r="I125" t="n">
-        <v>128.02</v>
+        <v>44.16</v>
       </c>
       <c r="J125" t="b">
         <v>0</v>
       </c>
       <c r="K125" t="n">
-        <v>371.98</v>
+        <v>455.84</v>
       </c>
       <c r="L125" t="n">
         <v>75</v>
@@ -5713,29 +5713,29 @@
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>(Vec (+ (+ (* a_0_0 b_0_0) (* a_0_1 b_1_0)) (+ (* a_0_2 b_2_0) (* a_0_3 b_3_0))) (+ (+ (* a_0_0 b_0_1) (* a_0_1 b_1_1)) (+ (* a_0_2 b_2_1) (* a_0_3 b_3_1))) (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (* a_0_0 b_0_2) (* a_0_1 b_1_2)) (+ (* a_0_2 b_2_2) (* a_0_3 b_3_2))) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) (+ (+ (* a_0_0 b_0_3) (* a_0_1 b_1_3)) (+ (* a_0_2 b_2_3) (* a_0_3 b_3_3))) (+ (+ (* a_1_0 b_0_0) (* a_1_1 b_1_0)) (+ (* a_1_2 b_2_0) (* a_1_3 b_3_0))) (+ (+ (* a_1_0 b_0_1) (* a_1_1 b_1_1)) (+ (* a_1_2 b_2_1) (* a_1_3 b_3_1))) (+ (+ (* a_1_0 b_0_2) (* a_1_1 b_1_2)) (+ (* a_1_2 b_2_2) (* a_1_3 b_3_2))) (+ (+ (* a_1_0 b_0_3) (* a_1_1 b_1_3)) (+ (* a_1_2 b_2_3) (* a_1_3 b_3_3))) (+ (+ (* a_2_0 b_0_0) (* a_2_1 b_1_0)) (+ (* a_2_2 b_2_0) (* a_2_3 b_3_0))) (+ (+ (* a_2_0 b_0_1) (* a_2_1 b_1_1)) (+ (* a_2_2 b_2_1) (* a_2_3 b_3_1))) (+ (+ (* a_2_0 b_0_2) (* a_2_1 b_1_2)) (+ (* a_2_2 b_2_2) (* a_2_3 b_3_2))) (+ (+ (* a_2_0 b_0_3) (* a_2_1 b_1_3)) (+ (* a_2_2 b_2_3) (* a_2_3 b_3_3))) (+ (+ (* a_3_0 b_0_0) (* a_3_1 b_1_0)) (+ (* a_3_2 b_2_0) (* a_3_3 b_3_0))) (+ (+ (* a_3_0 b_0_1) (* a_3_1 b_1_1)) (+ (* a_3_2 b_2_1) (* a_3_3 b_3_1))) (+ (+ (* a_3_0 b_0_2) (* a_3_1 b_1_2)) (+ (* a_3_2 b_2_2) (* a_3_3 b_3_2))) (+ (+ (* a_3_0 b_0_3) (* a_3_1 b_1_3)) (+ (* a_3_2 b_2_3) (* a_3_3 b_3_3))))</t>
+          <t>(Vec (+ (+ (* a_0_0 b_0_0) (* a_0_1 b_1_0)) (+ (* a_0_2 b_2_0) (* a_0_3 b_3_0))) (+ (+ (* a_0_0 b_0_1) (* a_0_1 b_1_1)) (+ (* a_0_2 b_2_1) (* a_0_3 b_3_1))) (+ (+ (* a_0_0 b_0_2) (* a_0_1 b_1_2)) (+ (* a_0_2 b_2_2) (+ 0 (+ 0 (* a_0_3 b_3_2))))) (+ (+ (+ 0 (+ 0 (* a_0_0 b_0_3))) (+ 0 (+ 0 (* a_0_1 b_1_3)))) (+ (+ 0 (+ 0 (* a_0_2 b_2_3))) (+ 0 (+ 0 (* a_0_3 b_3_3))))) (+ (+ (+ 0 (+ 0 (* a_1_0 b_0_0))) (+ 0 (+ 0 (* a_1_1 b_1_0)))) (+ (+ 0 (+ 0 (* a_1_2 b_2_0))) (+ 0 (+ 0 (* a_1_3 b_3_0))))) (+ (+ (+ 0 (+ 0 (* a_1_0 b_0_1))) (+ 0 (+ 0 (* a_1_1 b_1_1)))) (+ (+ 0 (+ 0 (* a_1_2 b_2_1))) (+ 0 (+ 0 (* a_1_3 b_3_1))))) (+ (+ (+ 0 (+ 0 (* a_1_0 b_0_2))) (+ 0 (+ 0 (* a_1_1 b_1_2)))) (+ (+ 0 (+ 0 (* a_1_2 b_2_2))) (+ 0 (+ 0 (* a_1_3 b_3_2))))) (+ (+ (+ 0 (+ 0 (* a_1_0 b_0_3))) (+ 0 (+ 0 (* a_1_1 b_1_3)))) (+ (+ 0 (+ 0 (* a_1_2 b_2_3))) (+ 0 (+ 0 (* a_1_3 b_3_3))))) (+ (+ (+ 0 (* a_2_0 b_0_0)) (+ 0 (* a_2_1 b_1_0))) (+ (+ 0 (* a_2_2 b_2_0)) (+ 0 (* a_2_3 b_3_0)))) (+ (+ (+ 0 (* a_2_0 b_0_1)) (+ 0 (* a_2_1 b_1_1))) (+ (+ 0 (* a_2_2 b_2_1)) (+ 0 (* a_2_3 b_3_1)))) (+ (+ (+ 0 (* a_2_0 b_0_2)) (+ 0 (* a_2_1 b_1_2))) (+ (+ 0 (* a_2_2 b_2_2)) (+ 0 (* a_2_3 b_3_2)))) (+ (+ (+ 0 (* a_2_0 b_0_3)) (+ 0 (* a_2_1 b_1_3))) (+ (+ 0 (* a_2_2 b_2_3)) (+ 0 (* a_2_3 b_3_3)))) (+ (+ (+ 0 (* a_3_0 b_0_0)) (+ 0 (* a_3_1 b_1_0))) (+ (+ 0 (* a_3_2 b_2_0)) (+ 0 (* a_3_3 b_3_0)))) (+ (+ (+ 0 (* a_3_0 b_0_1)) (+ 0 (* a_3_1 b_1_1))) (+ (+ 0 (* a_3_2 b_2_1)) (+ 0 (* a_3_3 b_3_1)))) (+ (+ (+ 0 (* a_3_0 b_0_2)) (+ 0 (* a_3_1 b_1_2))) (+ (+ 0 (* a_3_2 b_2_2)) (+ 0 (* a_3_3 b_3_2)))) (+ (+ (+ 0 (* a_3_0 b_0_3)) (+ 0 (* a_3_1 b_1_3))) (+ (+ 0 (* a_3_2 b_2_3)) (+ 0 (* a_3_3 b_3_3)))))</t>
         </is>
       </c>
       <c r="E126" t="n">
         <v>28006</v>
       </c>
       <c r="F126" t="n">
-        <v>46580</v>
+        <v>46508</v>
       </c>
       <c r="G126" t="n">
-        <v>-66.31999999999999</v>
+        <v>-66.06</v>
       </c>
       <c r="H126" t="n">
         <v>39.37</v>
       </c>
       <c r="I126" t="n">
-        <v>128.02</v>
+        <v>41.77</v>
       </c>
       <c r="J126" t="b">
         <v>0</v>
       </c>
       <c r="K126" t="n">
-        <v>371.98</v>
+        <v>458.23</v>
       </c>
       <c r="L126" t="n">
         <v>75</v>
@@ -5755,29 +5755,29 @@
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>(Vec (+ (* (+ (* (+ (* o4 (- 1 c34)) (* c34 o3)) (- 1 c23)) (* c23 (+ (* o4 (- 1 c24)) (* c24 o2)))) (- 1 c12)) (* c12 (+ (* (+ (* o4 (- 1 c34)) (* c34 o3)) (- 1 c13)) (* c13 (+ (* o4 (- 1 c14)) (* c14 o1)))))))</t>
+          <t>(Vec (+ (* (+ (* (+ (* o4 (- 1 c34)) (* c34 o3)) (- 1 c23)) (* c23 (+ (* o4 (- 1 c24)) (* c24 o2)))) (- 1 c12)) (* c12 (+ (* (+ (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (* o4 (- 1 c34))))))))))))))))))))) (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (* c34 o3))))))))))))))))))))) (- 1 c13)) (* c13 (+ (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (* o4 (- 1 c14)))))))))))))))))))) (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (* c14 o1)))))))))))))))))))))))))</t>
         </is>
       </c>
       <c r="E127" t="n">
         <v>7012</v>
       </c>
       <c r="F127" t="n">
-        <v>7012</v>
+        <v>25531</v>
       </c>
       <c r="G127" t="n">
-        <v>0</v>
+        <v>-264.1</v>
       </c>
       <c r="H127" t="n">
         <v>110.93</v>
       </c>
       <c r="I127" t="n">
-        <v>110.93</v>
+        <v>133.69</v>
       </c>
       <c r="J127" t="b">
         <v>0</v>
       </c>
       <c r="K127" t="n">
-        <v>389.07</v>
+        <v>366.31</v>
       </c>
       <c r="L127" t="n">
         <v>75</v>
@@ -5797,29 +5797,29 @@
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>(Vec (+ (* (+ (* (+ (* o3214 (- 1 c34)) (* c34 (+ (* (+ (* o4321 (- 1 c34)) (* c34 o3421)) (- 1 c24)) (* c24 (+ (* o3241 (- 1 c14)) (* c14 o3214)))))) (- 1 c23)) (* c23 (+ (* (+ (* o2314 (- 1 c24)) (* c24 (+ (* (- 1 c34) (+ (* o4231 (- 1 c24)) (* c24 o2431))) (* c34 (+ (* o2341 (- 1 c14)) (* c14 o2314)))))) (- 1 c13)) (* c13 (+ (* o2134 (- 1 c24)) (* c24 (+ (* (- 1 c14) (+ (* o4213 (- 1 c24)) (* c24 o2413))) (* c14 (+ (* o2143 (- 1 c34)) (* c34 o2134)))))))))) (- 1 c12)) (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (* c12 (+ (* (- 1 c13) (+ (* o3124 (- 1 c34)) (* c34 (+ (* (- 1 c14) (+ (* o4312 (- 1 c34)) (* c34 o3412))) (* c14 (+ (* o3142 (- 1 c24)) (* c24 o3124))))))) (* c13 (+ (* (- 1 c23) (+ (* o1324 (- 1 c14)) (* c14 (+ (* (- 1 c34) (+ (* o4132 (- 1 c14)) (* c14 o1432))) (* c34 (+ (* o1342 (- 1 c24)) (* c24 o1324))))))) (* c23 (+ (* o1234 (- 1 c14)) (* c14 (+ (* (- 1 c24) (+ (* o4123 (- 1 c14)) (* c14 o1423))) (* c24 (+ (* o1243 (- 1 c34)) (* c34 o1234))))))))))) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0)))</t>
+          <t>(Vec (+ (* (+ (* (+ (* o3214 (- 1 c34)) (* c34 (+ (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (* (+ (* o4321 (- 1 c34)) (* c34 o3421)) (- 1 c24)))))))))) (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (* c24 (+ (* o3241 (- 1 c14)) (* c14 o3214)))))))))))))) (- 1 c23)) (* c23 (+ (* (+ (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (* o2314 (- 1 c24)))))))))) (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (* c24 (+ (* (- 1 c34) (+ (* o4231 (- 1 c24)) (* c24 o2431))) (* c34 (+ (* o2341 (- 1 c14)) (* c14 o2314)))))))))))))) (- 1 c13)) (* c13 (+ (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (* o2134 (- 1 c24)))))))))) (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (* c24 (+ (* (- 1 c14) (+ (* o4213 (- 1 c24)) (* c24 o2413))) (* c14 (+ (* o2143 (- 1 c34)) (* c34 o2134))))))))))))))))) (- 1 c12)) (* c12 (+ (* (- 1 c13) (+ (* o3124 (- 1 c34)) (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (* c34 (+ (* (- 1 c14) (+ (* o4312 (- 1 c34)) (* c34 o3412))) (* c14 (+ (* o3142 (- 1 c24)) (* c24 o3124)))))))))))))))) (* c13 (+ (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (* (- 1 c23) (+ (* o1324 (- 1 c14)) (* c14 (+ (* (- 1 c34) (+ (* o4132 (- 1 c14)) (* c14 o1432))) (* c34 (+ (* o1342 (- 1 c24)) (* c24 o1324)))))))))))))))) (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (* c23 (+ (* o1234 (- 1 c14)) (* c14 (+ (* (- 1 c24) (+ (* o4123 (- 1 c14)) (* c14 o1423))) (* c24 (+ (* o1243 (- 1 c34)) (* c34 o1234))))))))))))))))))))))</t>
         </is>
       </c>
       <c r="E128" t="n">
         <v>29021</v>
       </c>
       <c r="F128" t="n">
-        <v>47595</v>
+        <v>47530</v>
       </c>
       <c r="G128" t="n">
-        <v>-64</v>
+        <v>-63.78</v>
       </c>
       <c r="H128" t="n">
         <v>218.27</v>
       </c>
       <c r="I128" t="n">
-        <v>306.92</v>
+        <v>229.05</v>
       </c>
       <c r="J128" t="b">
         <v>0</v>
       </c>
       <c r="K128" t="n">
-        <v>193.08</v>
+        <v>270.95</v>
       </c>
       <c r="L128" t="n">
         <v>75</v>
@@ -5839,29 +5839,29 @@
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>(VecMul (Vec (* (* (+ (* (* x10106 x10108) x10110) x10112) x10115) (* x10117 x10119)) (+ (+ x10121 (* x10125 (+ (+ (* (* x10146 x10147) (* (+ x10149 x10150) x10152)) (* (* (* x10132 x10133) (+ x10135 x10136)) (+ (* x10139 x10140) x10142))) (+ (+ x10154 (* (* x10159 (+ (+ x10162 x10163) x10165)) x10167)) (+ (+ x10170 x10173) (+ x10176 x10178)))))) (+ x10181 x10183))) (&lt;&lt; (Vec (* (* (+ (* (* x10106 x10108) x10110) x10112) x10115) (* x10117 x10119)) (+ (+ x10121 (* x10125 (+ (+ (* (* x10146 x10147) (* (+ x10149 x10150) x10152)) (* (* (* x10132 x10133) (+ x10135 x10136)) (+ (* x10139 x10140) x10142))) (+ (+ x10154 (* (* x10159 (+ (+ x10162 x10163) x10165)) x10167)) (+ (+ x10170 x10173) (+ x10176 x10178)))))) (+ x10181 x10183))) 1))</t>
+          <t>(Vec (* (* (* (+ (* (* x10106 x10108) x10110) x10112) x10115) (* x10117 x10119)) (+ (+ x10121 (* x10125 (+ (+ (* (* (* x10132 x10133) (+ x10135 x10136)) (+ (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (* x10139 x10140)))))))))))))))))))))))))))))))))))))) x10142)) (* (* x10146 x10147) (* (+ x10149 x10150) x10152))) (+ (+ x10154 (* (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (* x10159 (+ (+ x10162 x10163) x10165))))))))))))))))))))))))))))))))))))))) x10167)) (+ (+ x10170 x10173) (+ x10176 x10178)))))) (+ x10181 x10183))))</t>
         </is>
       </c>
       <c r="E129" t="n">
         <v>8018</v>
       </c>
       <c r="F129" t="n">
-        <v>7920</v>
+        <v>26555</v>
       </c>
       <c r="G129" t="n">
-        <v>1.22</v>
+        <v>-231.19</v>
       </c>
       <c r="H129" t="n">
         <v>182.49</v>
       </c>
       <c r="I129" t="n">
-        <v>183.69</v>
+        <v>226.81</v>
       </c>
       <c r="J129" t="b">
         <v>0</v>
       </c>
       <c r="K129" t="n">
-        <v>316.31</v>
+        <v>273.19</v>
       </c>
       <c r="L129" t="n">
         <v>75</v>
@@ -5881,29 +5881,29 @@
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>(VecMul (Vec (+ (* (* (* x9604 x9605) (* x9607 x9608)) (* (* x9611 x9612) (* x9614 x9615))) (* (* (* x9619 x9620) (* x9622 x9623)) (* (* x9626 x9627) (* x9629 x9630)))) (+ (* (* (* x9649 x9650) (* x9652 x9653)) (* (* x9656 x9657) (* x9659 x9660))) (* (* (* x9634 x9635) (* x9637 x9638)) (* (* x9641 x9642) (* x9644 x9645))))) (&lt;&lt; (Vec (+ (* (* (* x9604 x9605) (* x9607 x9608)) (* (* x9611 x9612) (* x9614 x9615))) (* (* (* x9619 x9620) (* x9622 x9623)) (* (* x9626 x9627) (* x9629 x9630)))) (+ (* (* (* x9649 x9650) (* x9652 x9653)) (* (* x9656 x9657) (* x9659 x9660))) (* (* (* x9634 x9635) (* x9637 x9638)) (* (* x9641 x9642) (* x9644 x9645))))) 1))</t>
+          <t>(Vec (* (+ (* (* (* x9604 x9605) (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (* x9607 x9608))))))) (* (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (* x9611 x9612)))))) (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (* x9614 x9615)))))))) (* (* (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (* x9619 x9620)))))) (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (* x9622 x9623))))))) (* (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (* x9626 x9627)))))) (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (* x9629 x9630))))))))) (+ (* (* (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (* x9634 x9635)))))) (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (* x9637 x9638))))))) (* (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (* x9641 x9642)))))) (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (* x9644 x9645)))))))) (* (* (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (* x9649 x9650)))))) (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (* x9652 x9653))))))) (* (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (* x9656 x9657)))))) (+ 0 (+ 0 (+ 0 (+ 0 (* x9659 x9660))))))))))</t>
         </is>
       </c>
       <c r="E130" t="n">
         <v>7761</v>
       </c>
       <c r="F130" t="n">
-        <v>7663</v>
+        <v>26266</v>
       </c>
       <c r="G130" t="n">
-        <v>1.26</v>
+        <v>-238.44</v>
       </c>
       <c r="H130" t="n">
         <v>141.92</v>
       </c>
       <c r="I130" t="n">
-        <v>143.12</v>
+        <v>147.91</v>
       </c>
       <c r="J130" t="b">
         <v>0</v>
       </c>
       <c r="K130" t="n">
-        <v>356.88</v>
+        <v>352.09</v>
       </c>
       <c r="L130" t="n">
         <v>75</v>
@@ -5923,32 +5923,32 @@
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>(Vec (+ (+ in_1_1 in_1_0) (+ in_0_1 in_0_0)) (+ (+ (+ in_1_2 in_1_1) (+ in_1_0 in_0_2)) (+ in_0_1 in_0_0)) (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ in_1_2 in_1_1) (+ in_0_2 in_0_1)) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) (+ (+ (+ in_2_1 in_2_0) (+ in_1_1 in_1_0)) (+ in_0_1 in_0_0)) (+ (+ (+ in_2_2 (+ in_2_1 in_2_0)) (+ in_1_2 in_1_1)) (+ (+ in_1_0 in_0_2) (+ in_0_1 in_0_0))) (+ (+ (+ in_2_2 in_2_1) (+ in_1_2 in_1_1)) (+ in_0_2 in_0_1)) (+ (+ in_2_1 in_2_0) (+ in_1_1 in_1_0)) (+ (+ (+ in_2_2 in_2_1) (+ in_2_0 in_1_2)) (+ in_1_1 in_1_0)) (+ (+ in_2_2 in_2_1) (+ in_1_2 in_1_1)))</t>
+          <t>(Vec ( + ( + in_1_1 in_1_0 ) ( + in_0_1 in_0_0 ) ) ( + ( + ( + in_1_2 in_1_1 ) ( + in_1_0 in_0_2 ) ) ( + in_0_1 in_0_0 ) ) ( + ( + in_1_2 in_1_1 ) ( + in_0_2 in_0_1 ) ) ( + ( + ( + in_2_1 in_2_0 ) ( + in_1_1 in_1_0 ) ) ( + in_0_1 in_0_0 ) ) ( + ( + ( + in_2_2 ( + in_2_1 in_2_0 ) ) ( + in_1_2 in_1_1 ) ) ( + ( + in_1_0 in_0_2 ) ( + in_0_1 in_0_0 ) ) ) ( + ( + ( + in_2_2 in_2_1 ) ( + in_1_2 in_1_1 ) ) ( + in_0_2 in_0_1 ) ) ( + ( + in_2_1 in_2_0 ) ( + in_1_1 in_1_0 ) ) ( + ( + ( + in_2_2 in_2_1 ) ( + in_2_0 in_1_2 ) ) ( + in_1_1 in_1_0 ) ) ( + ( + in_2_2 in_2_1 ) ( + in_1_2 in_1_1 ) ) )</t>
         </is>
       </c>
       <c r="E131" t="n">
         <v>10006</v>
       </c>
       <c r="F131" t="n">
-        <v>28578</v>
+        <v>10006</v>
       </c>
       <c r="G131" t="n">
-        <v>-185.61</v>
+        <v>0</v>
       </c>
       <c r="H131" t="n">
         <v>7.19</v>
       </c>
       <c r="I131" t="n">
-        <v>93.44</v>
+        <v>7.19</v>
       </c>
       <c r="J131" t="b">
         <v>0</v>
       </c>
       <c r="K131" t="n">
-        <v>906.5599999999999</v>
+        <v>992.8099999999999</v>
       </c>
       <c r="L131" t="n">
-        <v>75</v>
+        <v>1</v>
       </c>
     </row>
     <row r="132">
@@ -5965,29 +5965,29 @@
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>(Vec (+ (+ in_1_1 in_1_0) (+ in_0_1 in_0_0)) (+ (+ (+ in_1_2 in_1_1) (+ in_1_0 in_0_2)) (+ in_0_1 in_0_0)) (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ in_1_3 in_1_2) (+ in_1_1 in_0_3)) (+ in_0_2 in_0_1)) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) (- 0)) (- 0)) 0) 0) 0) (- 0)) (- 0)) (- 0)) (- (- 0))) (- (- (- 0)))) (- (- (- (- 0))))) (- (- (- (- (- 0)))))) (- (- (- (- (- 0)))))) (- (- (- 0)))) (- (- (- 0)))) (- (- (- 0)))) 0) 0) 0) (+ (+ (+ in_1_4 in_1_3) (+ in_1_2 in_0_4)) (+ in_0_3 in_0_2)) (+ (+ in_1_4 in_1_3) (+ in_0_4 in_0_3)) (+ (+ (+ in_2_1 in_2_0) (+ in_1_1 in_1_0)) (+ in_0_1 in_0_0)) (+ (+ (+ in_2_2 (+ in_2_1 in_2_0)) (+ in_1_2 in_1_1)) (+ (+ in_1_0 in_0_2) (+ in_0_1 in_0_0))) (+ (+ (+ in_2_3 (+ in_2_2 in_2_1)) (+ in_1_3 in_1_2)) (+ (+ in_1_1 in_0_3) (+ in_0_2 in_0_1))) (+ (+ (+ in_2_4 (+ in_2_3 in_2_2)) (+ in_1_4 in_1_3)) (+ (+ in_1_2 in_0_4) (+ in_0_3 in_0_2))) (+ (+ (+ in_2_4 in_2_3) (+ in_1_4 in_1_3)) (+ in_0_4 in_0_3)) (+ (+ (+ in_3_1 in_3_0) (+ in_2_1 in_2_0)) (+ in_1_1 in_1_0)) (+ (+ (+ in_3_2 (+ in_3_1 in_3_0)) (+ in_2_2 in_2_1)) (+ (+ in_2_0 in_1_2) (+ in_1_1 in_1_0))) (+ (+ (+ in_3_3 (+ in_3_2 in_3_1)) (+ in_2_3 in_2_2)) (+ (+ in_2_1 in_1_3) (+ in_1_2 in_1_1))) (+ (+ (+ in_3_4 (+ in_3_3 in_3_2)) (+ in_2_4 in_2_3)) (+ (+ in_2_2 in_1_4) (+ in_1_3 in_1_2))) (+ (+ (+ in_3_4 in_3_3) (+ in_2_4 in_2_3)) (+ in_1_4 in_1_3)) (+ (+ (+ in_4_1 in_4_0) (+ in_3_1 in_3_0)) (+ in_2_1 in_2_0)) (+ (+ (+ in_4_2 (+ in_4_1 in_4_0)) (+ in_3_2 in_3_1)) (+ (+ in_3_0 in_2_2) (+ in_2_1 in_2_0))) (+ (+ (+ in_4_3 (+ in_4_2 in_4_1)) (+ in_3_3 in_3_2)) (+ (+ in_3_1 in_2_3) (+ in_2_2 in_2_1))) (+ (+ (+ in_4_4 (+ in_4_3 in_4_2)) (+ in_3_4 in_3_3)) (+ (+ in_3_2 in_2_4) (+ in_2_3 in_2_2))) (+ (+ (+ in_4_4 in_4_3) (+ in_3_4 in_3_3)) (+ in_2_4 in_2_3)) (+ (+ in_4_1 in_4_0) (+ in_3_1 in_3_0)) (+ (+ (+ in_4_2 in_4_1) (+ in_4_0 in_3_2)) (+ in_3_1 in_3_0)) (+ (+ (+ in_4_3 in_4_2) (+ in_4_1 in_3_3)) (+ in_3_2 in_3_1)) (+ (+ (+ in_4_4 in_4_3) (+ in_4_2 in_3_4)) (+ in_3_3 in_3_2)) (+ (+ in_4_4 in_4_3) (+ in_3_4 in_3_3)))</t>
+          <t>(Vec (* 1 (* 1 (+ (+ in_1_1 in_1_0) (+ in_0_1 in_0_0)))) (* 1 (* 1 (+ (+ (+ in_1_2 in_1_1) (+ in_1_0 in_0_2)) (+ in_0_1 in_0_0)))) (* 1 (* 1 (+ (+ (+ in_1_3 in_1_2) (+ in_1_1 in_0_3)) (+ in_0_2 in_0_1)))) (* 1 (* 1 (* 1 (+ (+ (+ in_1_4 in_1_3) (+ in_1_2 in_0_4)) (+ in_0_3 in_0_2))))) (* 1 (* 1 (* 1 (+ (+ in_1_4 in_1_3) (+ in_0_4 in_0_3))))) (* 1 (* 1 (* 1 (+ (+ (+ in_2_1 in_2_0) (+ in_1_1 in_1_0)) (+ in_0_1 in_0_0))))) (* 1 (* 1 (* 1 (+ (+ (+ in_2_2 (+ in_2_1 in_2_0)) (+ in_1_2 in_1_1)) (+ (+ in_1_0 in_0_2) (+ in_0_1 in_0_0)))))) (* 1 (* 1 (* 1 (+ (+ (+ in_2_3 (+ in_2_2 in_2_1)) (+ in_1_3 in_1_2)) (+ (+ in_1_1 in_0_3) (+ in_0_2 in_0_1)))))) (* 1 (* 1 (* 1 (+ (+ (+ in_2_4 (+ in_2_3 in_2_2)) (+ in_1_4 in_1_3)) (+ (+ in_1_2 in_0_4) (+ in_0_3 in_0_2)))))) (* 1 (* 1 (* 1 (+ (+ (+ in_2_4 in_2_3) (+ in_1_4 in_1_3)) (+ in_0_4 in_0_3))))) (* 1 (* 1 (* 1 (+ (+ (+ in_3_1 in_3_0) (+ in_2_1 in_2_0)) (+ in_1_1 in_1_0))))) (* 1 (* 1 (* 1 (+ (+ (+ in_3_2 (+ in_3_1 in_3_0)) (+ in_2_2 in_2_1)) (+ (+ in_2_0 in_1_2) (+ in_1_1 in_1_0)))))) (* 1 (* 1 (* 1 (+ (+ (+ in_3_3 (+ in_3_2 in_3_1)) (+ in_2_3 in_2_2)) (+ (+ in_2_1 in_1_3) (+ in_1_2 in_1_1)))))) (* 1 (* 1 (* 1 (+ (+ (+ in_3_4 (+ in_3_3 in_3_2)) (+ in_2_4 in_2_3)) (+ (+ in_2_2 in_1_4) (+ in_1_3 in_1_2)))))) (* 1 (* 1 (* 1 (+ (+ (+ in_3_4 in_3_3) (+ in_2_4 in_2_3)) (+ in_1_4 in_1_3))))) (* 1 (* 1 (+ (+ (+ in_4_1 in_4_0) (+ in_3_1 in_3_0)) (+ in_2_1 in_2_0)))) (* 1 (* 1 (+ (+ (+ in_4_2 (+ in_4_1 in_4_0)) (+ in_3_2 in_3_1)) (+ (+ in_3_0 in_2_2) (+ in_2_1 in_2_0))))) (* 1 (* 1 (+ (+ (+ in_4_3 (+ in_4_2 in_4_1)) (+ in_3_3 in_3_2)) (+ (+ in_3_1 in_2_3) (+ in_2_2 in_2_1))))) (* 1 (* 1 (+ (+ (+ in_4_4 (+ in_4_3 in_4_2)) (+ in_3_4 in_3_3)) (+ (+ in_3_2 in_2_4) (+ in_2_3 in_2_2))))) (* 1 (* 1 (+ (+ (+ in_4_4 in_4_3) (+ in_3_4 in_3_3)) (+ in_2_4 in_2_3)))) (* 1 (* 1 (+ (+ in_4_1 in_4_0) (+ in_3_1 in_3_0)))) (* 1 (* 1 (+ (+ (+ in_4_2 in_4_1) (+ in_4_0 in_3_2)) (+ in_3_1 in_3_0)))) (* 1 (* 1 (+ (+ (+ in_4_3 in_4_2) (+ in_4_1 in_3_3)) (+ in_3_2 in_3_1)))) (* 1 (* 1 (+ (+ (+ in_4_4 in_4_3) (+ in_4_2 in_3_4)) (+ in_3_3 in_3_2)))) (* 1 (* 1 (+ (+ in_4_4 in_4_3) (+ in_3_4 in_3_3)))))</t>
         </is>
       </c>
       <c r="E132" t="n">
         <v>36006</v>
       </c>
       <c r="F132" t="n">
-        <v>54546</v>
+        <v>51512</v>
       </c>
       <c r="G132" t="n">
-        <v>-51.49</v>
+        <v>-43.07</v>
       </c>
       <c r="H132" t="n">
         <v>7.19</v>
       </c>
       <c r="I132" t="n">
-        <v>55.11</v>
+        <v>110.93</v>
       </c>
       <c r="J132" t="b">
         <v>0</v>
       </c>
       <c r="K132" t="n">
-        <v>944.89</v>
+        <v>889.0700000000001</v>
       </c>
       <c r="L132" t="n">
         <v>75</v>
@@ -6007,17 +6007,17 @@
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>(VecAdd (Vec v2_0 v2_1 v2_2 v2_3 v2_4 v2_5 v2_6 v2_7) (VecAdd (Vec 2 2 2 2 2 2 2 2) (Vec (* v1_0 5) (* v1_1 5) (* v1_2 5) (* v1_3 5) (* v1_4 5) (* v1_5 5) (* v1_6 5) (* v1_7 5))))</t>
+          <t>(Vec ( + v2_0 ( + 2 ( * v1_0 5 ) ) ) ( + v2_1 ( + 2 ( * v1_1 5 ) ) ) ( + v2_2 ( + 2 ( * v1_2 5 ) ) ) ( + v2_3 ( + 2 ( * v1_3 5 ) ) ) ( + v2_4 ( + 2 ( * v1_4 5 ) ) ) ( + v2_5 ( + 2 ( * v1_5 5 ) ) ) ( + v2_6 ( + 2 ( * v1_6 5 ) ) ) ( + v2_7 ( + 2 ( * v1_7 5 ) ) ) )</t>
         </is>
       </c>
       <c r="E133" t="n">
         <v>6006</v>
       </c>
       <c r="F133" t="n">
-        <v>2008</v>
+        <v>6006</v>
       </c>
       <c r="G133" t="n">
-        <v>66.56999999999999</v>
+        <v>0</v>
       </c>
       <c r="H133" t="n">
         <v>39.37</v>
@@ -6032,7 +6032,7 @@
         <v>960.63</v>
       </c>
       <c r="L133" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="134">
@@ -6049,29 +6049,29 @@
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>(Vec (+ v2_0 (+ 2 (* v1_0 5))) (+ v2_1 (+ 2 (* v1_1 5))) (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ v2_2 (+ 2 (* v1_2 5))) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) (+ v2_3 (+ 2 (* v1_3 5))) (+ v2_4 (+ 2 (* v1_4 5))) (+ v2_5 (+ 2 (* v1_5 5))) (+ v2_6 (+ 2 (* v1_6 5))) (+ v2_7 (+ 2 (* v1_7 5))) (+ v2_8 (+ 2 (* v1_8 5))) (+ v2_9 (+ 2 (* v1_9 5))) (+ v2_10 (+ 2 (* v1_10 5))) (+ v2_11 (+ 2 (* v1_11 5))) (+ v2_12 (+ 2 (* v1_12 5))) (+ v2_13 (+ 2 (* v1_13 5))) (+ v2_14 (+ 2 (* v1_14 5))) (+ v2_15 (+ 2 (* v1_15 5))) (+ v2_16 (+ 2 (* v1_16 5))) (+ v2_17 (+ 2 (* v1_17 5))) (+ v2_18 (+ 2 (* v1_18 5))) (+ v2_19 (+ 2 (* v1_19 5))) (+ v2_20 (+ 2 (* v1_20 5))) (+ v2_21 (+ 2 (* v1_21 5))) (+ v2_22 (+ 2 (* v1_22 5))) (+ v2_23 (+ 2 (* v1_23 5))) (+ v2_24 (+ 2 (* v1_24 5))) (+ v2_25 (+ 2 (* v1_25 5))) (+ v2_26 (+ 2 (* v1_26 5))) (+ v2_27 (+ 2 (* v1_27 5))) (+ v2_28 (+ 2 (* v1_28 5))) (+ v2_29 (+ 2 (* v1_29 5))) (+ v2_30 (+ 2 (* v1_30 5))) (+ v2_31 (+ 2 (* v1_31 5))))</t>
+          <t>(Vec (+ v2_0 (+ 2 (* v1_0 5))) (+ v2_1 (+ 2 (* v1_1 5))) (+ v2_2 (+ 2 (* v1_2 5))) (+ v2_3 (+ 2 (* v1_3 5))) (+ v2_4 (+ 2 (* v1_4 5))) (+ v2_5 (+ 2 (* v1_5 5))) (+ v2_6 (+ 2 (* v1_6 5))) (+ v2_7 (+ 2 (* v1_7 5))) (+ v2_8 (+ 2 (* v1_8 5))) (+ v2_9 (+ 2 (* v1_9 5))) (+ v2_10 (+ 2 (* v1_10 5))) (+ v2_11 (+ 2 (+ 0 (+ 0 (+ 0 (+ 0 (* v1_11 5))))))) (+ v2_12 (+ 2 (+ 0 (+ 0 (+ 0 (+ 0 (* v1_12 5))))))) (+ v2_13 (+ 2 (+ 0 (+ 0 (+ 0 (+ 0 (* v1_13 5))))))) (+ v2_14 (+ 2 (+ 0 (+ 0 (+ 0 (+ 0 (* v1_14 5))))))) (+ v2_15 (+ 2 (+ 0 (+ 0 (+ 0 (+ 0 (* v1_15 5))))))) (+ v2_16 (+ 2 (+ 0 (+ 0 (+ 0 (+ 0 (* v1_16 5))))))) (+ v2_17 (+ 2 (+ 0 (+ 0 (+ 0 (+ 0 (* v1_17 5))))))) (+ v2_18 (+ 2 (+ 0 (+ 0 (+ 0 (+ 0 (* v1_18 5))))))) (+ v2_19 (+ 2 (+ 0 (+ 0 (+ 0 (+ 0 (* v1_19 5))))))) (+ v2_20 (+ 2 (+ 0 (+ 0 (+ 0 (+ 0 (* v1_20 5))))))) (+ v2_21 (+ 2 (+ 0 (+ 0 (+ 0 (+ 0 (* v1_21 5))))))) (+ v2_22 (+ 2 (+ 0 (+ 0 (+ 0 (* v1_22 5)))))) (+ v2_23 (+ 2 (+ 0 (+ 0 (+ 0 (* v1_23 5)))))) (+ v2_24 (+ 2 (+ 0 (+ 0 (+ 0 (* v1_24 5)))))) (+ v2_25 (+ 2 (+ 0 (+ 0 (+ 0 (* v1_25 5)))))) (+ v2_26 (+ 2 (+ 0 (+ 0 (+ 0 (* v1_26 5)))))) (+ v2_27 (+ 2 (+ 0 (+ 0 (+ 0 (* v1_27 5)))))) (+ v2_28 (+ 2 (+ 0 (+ 0 (+ 0 (* v1_28 5)))))) (+ v2_29 (+ 2 (+ 0 (+ 0 (+ 0 (* v1_29 5)))))) (+ v2_30 (+ 2 (+ 0 (+ 0 (+ 0 (* v1_30 5)))))) (+ v2_31 (+ 2 (+ 0 (+ 0 (+ 0 (* v1_31 5)))))))</t>
         </is>
       </c>
       <c r="E134" t="n">
         <v>24006</v>
       </c>
       <c r="F134" t="n">
-        <v>42580</v>
+        <v>42510</v>
       </c>
       <c r="G134" t="n">
-        <v>-77.37</v>
+        <v>-77.08</v>
       </c>
       <c r="H134" t="n">
         <v>39.37</v>
       </c>
       <c r="I134" t="n">
-        <v>128.02</v>
+        <v>44.16</v>
       </c>
       <c r="J134" t="b">
         <v>0</v>
       </c>
       <c r="K134" t="n">
-        <v>871.98</v>
+        <v>955.84</v>
       </c>
       <c r="L134" t="n">
         <v>75</v>
@@ -6091,32 +6091,32 @@
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>(Vec (+ (+ (- (+ v1_0 v2_0) (* (* v1_0 v2_0) 2)) (- (+ v1_1 v2_1) (* 2 (* v1_1 v2_1)))) (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (- (+ v1_2 v2_2) (* 2 (* v1_2 v2_2))) (- (+ v1_3 v2_3) (* 2 (* v1_3 v2_3)))) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0)))</t>
+          <t>(Vec ( + ( + ( - ( + v1_0 v2_0 ) ( * ( * v1_0 v2_0 ) 2 ) ) ( - ( + v1_1 v2_1 ) ( * 2 ( * v1_1 v2_1 ) ) ) ) ( + ( - ( + v1_2 v2_2 ) ( * 2 ( * v1_2 v2_2 ) ) ) ( - ( + v1_3 v2_3 ) ( * 2 ( * v1_3 v2_3 ) ) ) ) ) )</t>
         </is>
       </c>
       <c r="E135" t="n">
         <v>4759</v>
       </c>
       <c r="F135" t="n">
-        <v>23333</v>
+        <v>4759</v>
       </c>
       <c r="G135" t="n">
-        <v>-390.29</v>
+        <v>0</v>
       </c>
       <c r="H135" t="n">
         <v>75.15000000000001</v>
       </c>
       <c r="I135" t="n">
-        <v>163.8</v>
+        <v>75.15000000000001</v>
       </c>
       <c r="J135" t="b">
         <v>0</v>
       </c>
       <c r="K135" t="n">
-        <v>836.2</v>
+        <v>924.85</v>
       </c>
       <c r="L135" t="n">
-        <v>75</v>
+        <v>1</v>
       </c>
     </row>
     <row r="136">
@@ -6133,32 +6133,32 @@
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>(Vec (+ (+ (+ (- (+ v1_0 v2_0) (* (* v1_0 v2_0) 2)) (- (+ v1_1 v2_1) (* 2 (* v1_1 v2_1)))) (+ (- (+ v1_2 v2_2) (* 2 (* v1_2 v2_2))) (- (+ v1_3 v2_3) (* 2 (* v1_3 v2_3))))) (+ (+ (- (+ v1_4 v2_4) (* 2 (* v1_4 v2_4))) (* 1 (* 1 (* 1 (* 1 (- (+ v1_5 v2_5) (* 2 (* v1_5 v2_5)))))))) (* 1 (* 1 (* 1 (+ (- (+ v1_6 v2_6) (* 2 (* v1_6 v2_6))) (- (+ v1_7 v2_7) (* 2 (* v1_7 v2_7))))))))))</t>
+          <t>(Vec ( + ( + ( + ( - ( + v1_0 v2_0 ) ( * ( * v1_0 v2_0 ) 2 ) ) ( - ( + v1_1 v2_1 ) ( * 2 ( * v1_1 v2_1 ) ) ) ) ( + ( - ( + v1_2 v2_2 ) ( * 2 ( * v1_2 v2_2 ) ) ) ( - ( + v1_3 v2_3 ) ( * 2 ( * v1_3 v2_3 ) ) ) ) ) ( + ( + ( - ( + v1_4 v2_4 ) ( * 2 ( * v1_4 v2_4 ) ) ) ( - ( + v1_5 v2_5 ) ( * 2 ( * v1_5 v2_5 ) ) ) ) ( + ( - ( + v1_6 v2_6 ) ( * 2 ( * v1_6 v2_6 ) ) ) ( - ( + v1_7 v2_7 ) ( * 2 ( * v1_7 v2_7 ) ) ) ) ) ) )</t>
         </is>
       </c>
       <c r="E136" t="n">
         <v>9760</v>
       </c>
       <c r="F136" t="n">
-        <v>11518</v>
+        <v>9760</v>
       </c>
       <c r="G136" t="n">
-        <v>-18.01</v>
+        <v>0</v>
       </c>
       <c r="H136" t="n">
         <v>76.34999999999999</v>
       </c>
       <c r="I136" t="n">
-        <v>214.67</v>
+        <v>76.34999999999999</v>
       </c>
       <c r="J136" t="b">
         <v>0</v>
       </c>
       <c r="K136" t="n">
-        <v>785.33</v>
+        <v>923.65</v>
       </c>
       <c r="L136" t="n">
-        <v>14</v>
+        <v>1</v>
       </c>
     </row>
     <row r="137">
@@ -6175,29 +6175,29 @@
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>(Vec (+ (+ (+ (+ (+ (- (+ v1_0 v2_0) (* (* v1_0 v2_0) 2)) (- (+ v1_1 v2_1) (* 2 (* v1_1 v2_1)))) (+ (- (+ v1_2 v2_2) (* 2 (* v1_2 v2_2))) (- (+ v1_3 v2_3) (* 2 (* v1_3 v2_3))))) (+ (+ (- (+ v1_4 v2_4) (* 2 (* v1_4 v2_4))) (- (+ v1_5 v2_5) (* 2 (* v1_5 v2_5)))) (+ (- (+ v1_6 v2_6) (* 2 (* v1_6 v2_6))) (- (+ v1_7 v2_7) (* 2 (* v1_7 v2_7)))))) (+ (+ (+ (- (+ v1_8 v2_8) (* 2 (* v1_8 v2_8))) (- (+ v1_9 v2_9) (* 2 (* v1_9 v2_9)))) (+ (- (+ v1_10 v2_10) (* 2 (* v1_10 v2_10))) (- (+ v1_11 v2_11) (* 2 (* v1_11 v2_11))))) (+ (+ (- (+ v1_12 v2_12) (* 2 (* v1_12 v2_12))) (- (+ v1_13 v2_13) (* 2 (* v1_13 v2_13)))) (+ (- (+ v1_14 v2_14) (* 2 (* v1_14 v2_14))) (- (+ v1_15 v2_15) (* 2 (* v1_15 v2_15))))))) (+ (+ (+ (+ (- (+ v1_16 v2_16) (* 2 (* v1_16 v2_16))) (- (+ v1_17 v2_17) (* 2 (* v1_17 v2_17)))) (+ (- (+ v1_18 v2_18) (* 2 (* v1_18 v2_18))) (- (+ v1_19 v2_19) (* 2 (* v1_19 v2_19))))) (+ (+ (- (+ v1_20 v2_20) (* 2 (* v1_20 v2_20))) (- (+ v1_21 v2_21) (* 2 (* v1_21 v2_21)))) (+ (- (+ v1_22 v2_22) (* 2 (* v1_22 v2_22))) (- (+ v1_23 v2_23) (* 2 (* v1_23 v2_23)))))) (+ (+ (+ (- (+ v1_24 v2_24) (* 2 (* v1_24 v2_24))) (- (+ v1_25 v2_25) (* 2 (* v1_25 v2_25)))) (+ (- (+ v1_26 v2_26) (* 2 (* v1_26 v2_26))) (- (+ v1_27 v2_27) (* 2 (* v1_27 v2_27))))) (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (+ (+ (- (+ v1_28 v2_28) (* 2 (* v1_28 v2_28))) (- (+ v1_29 v2_29) (* 2 (* v1_29 v2_29)))) (+ (- (+ v1_30 v2_30) (* 2 (* v1_30 v2_30))) (- (+ v1_31 v2_31) (* 2 (* v1_31 v2_31))))) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1)))))</t>
+          <t>(Vec (+ (+ (+ (+ (+ (- (+ v1_0 v2_0) (* (+ 0 (+ 0 (* v1_0 v2_0))) 2)) (- (+ v1_1 v2_1) (* 2 (+ 0 (+ 0 (* v1_1 v2_1)))))) (+ (- (+ v1_2 v2_2) (* 2 (+ 0 (+ 0 (* v1_2 v2_2))))) (- (+ v1_3 v2_3) (* 2 (+ 0 (+ 0 (* v1_3 v2_3))))))) (+ (+ (- (+ v1_4 v2_4) (* 2 (+ 0 (+ 0 (* v1_4 v2_4))))) (- (+ v1_5 v2_5) (+ 0 (+ 0 (+ 0 (* 2 (* v1_5 v2_5))))))) (+ (- (+ v1_6 v2_6) (+ 0 (+ 0 (+ 0 (* 2 (* v1_6 v2_6)))))) (- (+ v1_7 v2_7) (+ 0 (+ 0 (+ 0 (* 2 (* v1_7 v2_7))))))))) (+ (+ (+ (- (+ v1_8 v2_8) (+ 0 (+ 0 (+ 0 (* 2 (* v1_8 v2_8)))))) (- (+ v1_9 v2_9) (+ 0 (+ 0 (+ 0 (* 2 (* v1_9 v2_9))))))) (+ (- (+ v1_10 v2_10) (+ 0 (+ 0 (+ 0 (* 2 (* v1_10 v2_10)))))) (- (+ v1_11 v2_11) (+ 0 (+ 0 (+ 0 (* 2 (* v1_11 v2_11)))))))) (+ (+ (- (+ v1_12 v2_12) (+ 0 (+ 0 (+ 0 (* 2 (* v1_12 v2_12)))))) (- (+ v1_13 v2_13) (+ 0 (+ 0 (+ 0 (* 2 (* v1_13 v2_13))))))) (+ (- (+ v1_14 v2_14) (+ 0 (+ 0 (+ 0 (* 2 (* v1_14 v2_14)))))) (- (+ v1_15 v2_15) (+ 0 (+ 0 (* 2 (* v1_15 v2_15))))))))) (+ (+ (+ (+ (- (+ v1_16 v2_16) (+ 0 (+ 0 (* 2 (* v1_16 v2_16))))) (- (+ v1_17 v2_17) (+ 0 (+ 0 (* 2 (* v1_17 v2_17)))))) (+ (- (+ v1_18 v2_18) (+ 0 (+ 0 (* 2 (* v1_18 v2_18))))) (- (+ v1_19 v2_19) (+ 0 (+ 0 (* 2 (* v1_19 v2_19))))))) (+ (+ (- (+ v1_20 v2_20) (+ 0 (+ 0 (* 2 (* v1_20 v2_20))))) (- (+ v1_21 v2_21) (+ 0 (+ 0 (* 2 (* v1_21 v2_21)))))) (+ (- (+ v1_22 v2_22) (+ 0 (+ 0 (* 2 (* v1_22 v2_22))))) (- (+ v1_23 v2_23) (+ 0 (+ 0 (* 2 (* v1_23 v2_23)))))))) (+ (+ (+ (- (+ v1_24 v2_24) (+ 0 (+ 0 (* 2 (* v1_24 v2_24))))) (- (+ v1_25 v2_25) (+ 0 (+ 0 (* 2 (* v1_25 v2_25)))))) (+ (- (+ v1_26 v2_26) (+ 0 (+ 0 (* 2 (* v1_26 v2_26))))) (- (+ v1_27 v2_27) (+ 0 (+ 0 (* 2 (* v1_27 v2_27))))))) (+ (+ (- (+ v1_28 v2_28) (+ 0 (+ 0 (* 2 (* v1_28 v2_28))))) (- (+ v1_29 v2_29) (+ 0 (+ 0 (* 2 (* v1_29 v2_29)))))) (+ (- (+ v1_30 v2_30) (+ 0 (+ 0 (* 2 (* v1_30 v2_30))))) (- (+ v1_31 v2_31) (+ 0 (+ 0 (* 2 (* v1_31 v2_31)))))))))))</t>
         </is>
       </c>
       <c r="E137" t="n">
         <v>39762</v>
       </c>
       <c r="F137" t="n">
-        <v>58410</v>
+        <v>58265</v>
       </c>
       <c r="G137" t="n">
-        <v>-46.9</v>
+        <v>-46.53</v>
       </c>
       <c r="H137" t="n">
         <v>78.75</v>
       </c>
       <c r="I137" t="n">
-        <v>2637.74</v>
+        <v>82.34</v>
       </c>
       <c r="J137" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K137" t="n">
-        <v>-1637.74</v>
+        <v>917.66</v>
       </c>
       <c r="L137" t="n">
         <v>75</v>
@@ -6217,29 +6217,29 @@
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>(Vec (+ c1_0 (+ c2_0 (* c0_0 (+ c3_0 (* c0_0 c4_0))))) (+ c1_1 (+ c2_1 (* c0_1 (+ c3_1 (* c0_1 c4_1))))) (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ c1_2 (+ c2_2 (* c0_2 (+ c3_2 (* c0_2 c4_2))))) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) (+ c1_3 (+ c2_3 (* c0_3 (+ c3_3 (* c0_3 c4_3))))) (+ c1_4 (+ c2_4 (* c0_4 (+ c3_4 (* c0_4 c4_4))))) (+ c1_5 (+ c2_5 (* c0_5 (+ c3_5 (* c0_5 c4_5))))) (+ c1_6 (+ c2_6 (* c0_6 (+ c3_6 (* c0_6 c4_6))))) (+ c1_7 (+ c2_7 (* c0_7 (+ c3_7 (* c0_7 c4_7))))))</t>
+          <t>(Vec (+ c1_0 (+ c2_0 (* c0_0 (+ c3_0 (* c0_0 c4_0))))) (+ c1_1 (+ c2_1 (* c0_1 (+ c3_1 (* c0_1 c4_1))))) (+ c1_2 (+ c2_2 (* c0_2 (+ c3_2 (* c0_2 c4_2))))) (+ c1_3 (+ c2_3 (* c0_3 (+ c3_3 (* c0_3 c4_3))))) (+ c1_4 (+ c2_4 (* c0_4 (+ c3_4 (* c0_4 c4_4))))) (+ c1_5 (+ c2_5 (* c0_5 (+ c3_5 (* c0_5 c4_5))))) (+ c1_6 (+ c2_6 (* c0_6 (+ c3_6 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (* c0_6 c4_6)))))))))))))))))))))))))))))))))))))))))) (+ c1_7 (+ c2_7 (* c0_7 (+ c3_7 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (* c0_7 c4_7)))))))))))))))))))))))))))))))))))))))))))</t>
         </is>
       </c>
       <c r="E138" t="n">
         <v>10009</v>
       </c>
       <c r="F138" t="n">
-        <v>28583</v>
+        <v>28546</v>
       </c>
       <c r="G138" t="n">
-        <v>-185.57</v>
+        <v>-185.2</v>
       </c>
       <c r="H138" t="n">
         <v>75.15000000000001</v>
       </c>
       <c r="I138" t="n">
-        <v>163.8</v>
+        <v>119.48</v>
       </c>
       <c r="J138" t="b">
         <v>0</v>
       </c>
       <c r="K138" t="n">
-        <v>836.2</v>
+        <v>880.52</v>
       </c>
       <c r="L138" t="n">
         <v>75</v>
@@ -6259,29 +6259,29 @@
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>(Vec (+ c1_0 (+ c2_0 (* c0_0 (+ c3_0 (* c0_0 c4_0))))) (+ c1_1 (+ c2_1 (* c0_1 (+ c3_1 (* c0_1 c4_1))))) (+ c1_2 (+ c2_2 (* c0_2 (+ c3_2 (* c0_2 c4_2))))) (+ c1_3 (+ c2_3 (* c0_3 (+ c3_3 (* c0_3 c4_3))))) (+ c1_4 (+ c2_4 (* c0_4 (+ c3_4 (* c0_4 c4_4))))) (+ c1_5 (+ c2_5 (* c0_5 (+ c3_5 (* c0_5 c4_5))))) (+ c1_6 (+ c2_6 (* c0_6 (+ c3_6 (* c0_6 c4_6))))) (+ c1_7 (+ c2_7 (* c0_7 (+ c3_7 (* c0_7 c4_7))))) (+ c1_8 (+ c2_8 (* c0_8 (+ c3_8 (* c0_8 c4_8))))) (+ c1_9 (+ c2_9 (* c0_9 (+ c3_9 (* c0_9 c4_9))))) (+ c1_10 (+ c2_10 (* c0_10 (+ c3_10 (* c0_10 c4_10))))) (+ c1_11 (+ c2_11 (* c0_11 (+ c3_11 (* c0_11 c4_11))))) (+ c1_12 (+ c2_12 (* c0_12 (+ c3_12 (* c0_12 c4_12))))) (+ c1_13 (+ c2_13 (* c0_13 (+ c3_13 (* c0_13 c4_13))))) (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (+ c1_14 (+ c2_14 (* c0_14 (+ c3_14 (* c0_14 c4_14))))) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) (+ c1_15 (+ c2_15 (* c0_15 (+ c3_15 (* c0_15 c4_15))))) (+ c1_16 (+ c2_16 (* c0_16 (+ c3_16 (* c0_16 c4_16))))) (+ c1_17 (+ c2_17 (* c0_17 (+ c3_17 (* c0_17 c4_17))))) (+ c1_18 (+ c2_18 (* c0_18 (+ c3_18 (* c0_18 c4_18))))) (+ c1_19 (+ c2_19 (* c0_19 (+ c3_19 (* c0_19 c4_19))))) (+ c1_20 (+ c2_20 (* c0_20 (+ c3_20 (* c0_20 c4_20))))) (+ c1_21 (+ c2_21 (* c0_21 (+ c3_21 (* c0_21 c4_21))))) (+ c1_22 (+ c2_22 (* c0_22 (+ c3_22 (* c0_22 c4_22))))) (+ c1_23 (+ c2_23 (* c0_23 (+ c3_23 (* c0_23 c4_23))))) (+ c1_24 (+ c2_24 (* c0_24 (+ c3_24 (* c0_24 c4_24))))) (+ c1_25 (+ c2_25 (* c0_25 (+ c3_25 (* c0_25 c4_25))))) (+ c1_26 (+ c2_26 (* c0_26 (+ c3_26 (* c0_26 c4_26))))) (+ c1_27 (+ c2_27 (* c0_27 (+ c3_27 (* c0_27 c4_27))))) (+ c1_28 (+ c2_28 (* c0_28 (+ c3_28 (* c0_28 c4_28))))) (+ c1_29 (+ c2_29 (* c0_29 (+ c3_29 (* c0_29 c4_29))))) (+ c1_30 (+ c2_30 (* c0_30 (+ c3_30 (* c0_30 c4_30))))) (+ c1_31 (+ c2_31 (* c0_31 (+ c3_31 (* c0_31 c4_31))))))</t>
+          <t>(Vec (+ c1_0 (+ c2_0 (* c0_0 (+ c3_0 (+ 0 (* c0_0 c4_0)))))) (+ c1_1 (+ c2_1 (* c0_1 (+ c3_1 (+ 0 (* c0_1 c4_1)))))) (+ c1_2 (+ c2_2 (* c0_2 (+ c3_2 (+ 0 (* c0_2 c4_2)))))) (+ c1_3 (+ c2_3 (* c0_3 (+ c3_3 (+ 0 (* c0_3 c4_3)))))) (+ c1_4 (+ c2_4 (* c0_4 (+ c3_4 (+ 0 (* c0_4 c4_4)))))) (+ c1_5 (+ c2_5 (+ 0 (+ 0 (+ 0 (* c0_5 (+ c3_5 (* c0_5 c4_5)))))))) (+ c1_6 (+ c2_6 (+ 0 (+ 0 (+ 0 (* c0_6 (+ c3_6 (* c0_6 c4_6)))))))) (+ c1_7 (+ c2_7 (+ 0 (+ 0 (+ 0 (* c0_7 (+ c3_7 (* c0_7 c4_7)))))))) (+ c1_8 (+ c2_8 (+ 0 (+ 0 (+ 0 (* c0_8 (+ c3_8 (* c0_8 c4_8)))))))) (+ c1_9 (+ c2_9 (+ 0 (+ 0 (+ 0 (* c0_9 (+ c3_9 (* c0_9 c4_9)))))))) (+ c1_10 (+ c2_10 (+ 0 (+ 0 (+ 0 (* c0_10 (+ c3_10 (* c0_10 c4_10)))))))) (+ c1_11 (+ c2_11 (+ 0 (+ 0 (+ 0 (* c0_11 (+ c3_11 (* c0_11 c4_11)))))))) (+ c1_12 (+ c2_12 (+ 0 (+ 0 (+ 0 (* c0_12 (+ c3_12 (* c0_12 c4_12)))))))) (+ c1_13 (+ c2_13 (+ 0 (+ 0 (+ 0 (* c0_13 (+ c3_13 (* c0_13 c4_13)))))))) (+ c1_14 (+ c2_14 (+ 0 (+ 0 (+ 0 (* c0_14 (+ c3_14 (* c0_14 c4_14)))))))) (+ c1_15 (+ c2_15 (+ 0 (+ 0 (+ 0 (* c0_15 (+ c3_15 (* c0_15 c4_15)))))))) (+ c1_16 (+ c2_16 (+ 0 (+ 0 (+ 0 (* c0_16 (+ c3_16 (* c0_16 c4_16)))))))) (+ c1_17 (+ c2_17 (+ 0 (+ 0 (+ 0 (* c0_17 (+ c3_17 (* c0_17 c4_17)))))))) (+ c1_18 (+ c2_18 (+ 0 (+ 0 (+ 0 (* c0_18 (+ c3_18 (* c0_18 c4_18)))))))) (+ c1_19 (+ c2_19 (+ 0 (+ 0 (+ 0 (* c0_19 (+ c3_19 (* c0_19 c4_19)))))))) (+ c1_20 (+ c2_20 (+ 0 (+ 0 (* c0_20 (+ c3_20 (* c0_20 c4_20))))))) (+ c1_21 (+ c2_21 (+ 0 (+ 0 (* c0_21 (+ c3_21 (* c0_21 c4_21))))))) (+ c1_22 (+ c2_22 (+ 0 (+ 0 (* c0_22 (+ c3_22 (* c0_22 c4_22))))))) (+ c1_23 (+ c2_23 (+ 0 (+ 0 (* c0_23 (+ c3_23 (* c0_23 c4_23))))))) (+ c1_24 (+ c2_24 (+ 0 (+ 0 (* c0_24 (+ c3_24 (* c0_24 c4_24))))))) (+ c1_25 (+ c2_25 (+ 0 (+ 0 (* c0_25 (+ c3_25 (* c0_25 c4_25))))))) (+ c1_26 (+ c2_26 (+ 0 (+ 0 (* c0_26 (+ c3_26 (* c0_26 c4_26))))))) (+ c1_27 (+ c2_27 (+ 0 (+ 0 (* c0_27 (+ c3_27 (* c0_27 c4_27))))))) (+ c1_28 (+ c2_28 (+ 0 (+ 0 (* c0_28 (+ c3_28 (* c0_28 c4_28))))))) (+ c1_29 (+ c2_29 (+ 0 (+ 0 (* c0_29 (+ c3_29 (* c0_29 c4_29))))))) (+ c1_30 (+ c2_30 (+ 0 (+ 0 (* c0_30 (+ c3_30 (* c0_30 c4_30))))))) (+ c1_31 (+ c2_31 (+ 0 (+ 0 (* c0_31 (+ c3_31 (* c0_31 c4_31))))))))</t>
         </is>
       </c>
       <c r="E139" t="n">
         <v>40009</v>
       </c>
       <c r="F139" t="n">
-        <v>58657</v>
+        <v>58512</v>
       </c>
       <c r="G139" t="n">
-        <v>-46.61</v>
+        <v>-46.25</v>
       </c>
       <c r="H139" t="n">
         <v>75.15000000000001</v>
       </c>
       <c r="I139" t="n">
-        <v>2634.14</v>
+        <v>78.75</v>
       </c>
       <c r="J139" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K139" t="n">
-        <v>-1634.14</v>
+        <v>921.25</v>
       </c>
       <c r="L139" t="n">
         <v>75</v>
@@ -6301,32 +6301,32 @@
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>(Vec (+ (+ (* (- c2_0 c1_0) (- c2_0 c1_0)) (* (- c2_1 c1_1) (- c2_1 c1_1))) (+ (* (- c2_2 c1_2) (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (- c2_2 c1_2))))))))) (* (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (- c2_3 c1_3)))))))) (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (- c2_3 c1_3))))))))))))</t>
+          <t>(Vec ( + ( + ( * ( - c2_0 c1_0 ) ( - c2_0 c1_0 ) ) ( * ( - c2_1 c1_1 ) ( - c2_1 c1_1 ) ) ) ( + ( * ( - c2_2 c1_2 ) ( - c2_2 c1_2 ) ) ( * ( - c2_3 c1_3 ) ( - c2_3 c1_3 ) ) ) ) )</t>
         </is>
       </c>
       <c r="E140" t="n">
         <v>3757</v>
       </c>
       <c r="F140" t="n">
-        <v>9021</v>
+        <v>3757</v>
       </c>
       <c r="G140" t="n">
-        <v>-140.11</v>
+        <v>0</v>
       </c>
       <c r="H140" t="n">
         <v>40.57</v>
       </c>
       <c r="I140" t="n">
-        <v>282.64</v>
+        <v>40.57</v>
       </c>
       <c r="J140" t="b">
         <v>0</v>
       </c>
       <c r="K140" t="n">
-        <v>717.36</v>
+        <v>959.4299999999999</v>
       </c>
       <c r="L140" t="n">
-        <v>22</v>
+        <v>1</v>
       </c>
     </row>
     <row r="141">
@@ -6343,29 +6343,29 @@
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>(Vec (+ (+ (+ (* (- c2_0 c1_0) (- c2_0 c1_0)) (* (- c2_1 c1_1) (- c2_1 c1_1))) (+ (* (- c2_2 c1_2) (- c2_2 c1_2)) (* (- c2_3 c1_3) (- c2_3 c1_3)))) (+ (+ (* (- c2_4 c1_4) (- c2_4 c1_4)) (* (- c2_5 c1_5) (- c2_5 c1_5))) (+ (* (- c2_6 c1_6) (- c2_6 c1_6)) (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (- c2_7 c1_7) (- c2_7 c1_7)) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1)))))</t>
+          <t>(Vec (+ (+ (+ (* (- c2_0 c1_0) (- c2_0 c1_0)) (* (- c2_1 c1_1) (- c2_1 c1_1))) (+ (* (- c2_2 c1_2) (- c2_2 c1_2)) (* (- c2_3 c1_3) (- c2_3 c1_3)))) (+ (+ (* (- c2_4 c1_4) (- c2_4 c1_4)) (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (* (- c2_5 c1_5) (- c2_5 c1_5)))))))))))))))))))))))))))) (+ (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (* (- c2_6 c1_6) (- c2_6 c1_6))))))))))))))))))))))))))) (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (* (- c2_7 c1_7) (- c2_7 c1_7))))))))))))))))))))))))))))))</t>
         </is>
       </c>
       <c r="E141" t="n">
         <v>7758</v>
       </c>
       <c r="F141" t="n">
-        <v>26406</v>
+        <v>26283</v>
       </c>
       <c r="G141" t="n">
-        <v>-240.37</v>
+        <v>-238.79</v>
       </c>
       <c r="H141" t="n">
         <v>41.77</v>
       </c>
       <c r="I141" t="n">
-        <v>2600.76</v>
+        <v>71.72</v>
       </c>
       <c r="J141" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K141" t="n">
-        <v>-1600.76</v>
+        <v>928.28</v>
       </c>
       <c r="L141" t="n">
         <v>75</v>
@@ -6385,29 +6385,29 @@
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>(Vec (+ (+ (+ (+ (+ (* (- c2_0 c1_0) (- c2_0 c1_0)) (* (- c2_1 c1_1) (- c2_1 c1_1))) (+ (* (- c2_2 c1_2) (- c2_2 c1_2)) (* (- c2_3 c1_3) (- c2_3 c1_3)))) (+ (+ (* (- c2_4 c1_4) (- c2_4 c1_4)) (* (- c2_5 c1_5) (- c2_5 c1_5))) (+ (* (- c2_6 c1_6) (- c2_6 c1_6)) (* (* 1 (* 1 (- c2_7 c1_7))) (* 1 (* 1 (- c2_7 c1_7))))))) (+ (+ (+ (* (* 1 (* 1 (- c2_8 c1_8))) (* 1 (* 1 (- c2_8 c1_8)))) (* (* 1 (* 1 (- c2_9 c1_9))) (* 1 (* 1 (- c2_9 c1_9))))) (+ (* (* 1 (* 1 (- c2_10 c1_10))) (* 1 (* 1 (- c2_10 c1_10)))) (* (* 1 (* 1 (- c2_11 c1_11))) (* 1 (* 1 (- c2_11 c1_11)))))) (+ (+ (* (* 1 (* 1 (- c2_12 c1_12))) (* 1 (* 1 (- c2_12 c1_12)))) (* (* 1 (* 1 (- c2_13 c1_13))) (* 1 (* 1 (- c2_13 c1_13))))) (+ (* (* 1 (* 1 (- c2_14 c1_14))) (* 1 (* 1 (- c2_14 c1_14)))) (* (* 1 (* 1 (- c2_15 c1_15))) (* 1 (* 1 (- c2_15 c1_15)))))))) (+ (+ (+ (+ (* (* 1 (* 1 (- c2_16 c1_16))) (* 1 (* 1 (- c2_16 c1_16)))) (* (* 1 (* 1 (- c2_17 c1_17))) (* 1 (* 1 (- c2_17 c1_17))))) (+ (* (* 1 (* 1 (- c2_18 c1_18))) (* 1 (* 1 (- c2_18 c1_18)))) (* (* 1 (- c2_19 c1_19)) (* 1 (- c2_19 c1_19))))) (+ (+ (* (* 1 (- c2_20 c1_20)) (* 1 (- c2_20 c1_20))) (* (* 1 (- c2_21 c1_21)) (* 1 (- c2_21 c1_21)))) (+ (* (* 1 (- c2_22 c1_22)) (* 1 (- c2_22 c1_22))) (* (* 1 (- c2_23 c1_23)) (* 1 (- c2_23 c1_23)))))) (+ (+ (+ (* (* 1 (- c2_24 c1_24)) (* 1 (- c2_24 c1_24))) (* (* 1 (- c2_25 c1_25)) (* 1 (- c2_25 c1_25)))) (+ (* (* 1 (- c2_26 c1_26)) (* 1 (- c2_26 c1_26))) (* (* 1 (- c2_27 c1_27)) (* 1 (- c2_27 c1_27))))) (+ (+ (* (* 1 (- c2_28 c1_28)) (* 1 (- c2_28 c1_28))) (* (* 1 (- c2_29 c1_29)) (* 1 (- c2_29 c1_29)))) (+ (* (* 1 (- c2_30 c1_30)) (* 1 (- c2_30 c1_30))) (* (* 1 (- c2_31 c1_31)) (* 1 (- c2_31 c1_31)))))))))</t>
+          <t>(Vec (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (+ (* 1 (+ (+ (+ (+ (* (- c2_0 c1_0) (- c2_0 c1_0)) (* (- c2_1 c1_1) (- c2_1 c1_1))) (+ (* (- c2_2 c1_2) (- c2_2 c1_2)) (* (- c2_3 c1_3) (- c2_3 c1_3)))) (+ (+ (* (- c2_4 c1_4) (- c2_4 c1_4)) (* (- c2_5 c1_5) (- c2_5 c1_5))) (+ (* (- c2_6 c1_6) (- c2_6 c1_6)) (* (- c2_7 c1_7) (- c2_7 c1_7))))) (+ (+ (+ (* (- c2_8 c1_8) (- c2_8 c1_8)) (* (- c2_9 c1_9) (- c2_9 c1_9))) (+ (* (- c2_10 c1_10) (- c2_10 c1_10)) (* (- c2_11 c1_11) (- c2_11 c1_11)))) (+ (+ (* (- c2_12 c1_12) (- c2_12 c1_12)) (* (- c2_13 c1_13) (- c2_13 c1_13))) (+ (* (- c2_14 c1_14) (- c2_14 c1_14)) (* (- c2_15 c1_15) (- c2_15 c1_15))))))) (+ (* 1 (+ (+ (+ (* (- c2_16 c1_16) (- c2_16 c1_16)) (* (- c2_17 c1_17) (- c2_17 c1_17))) (+ (* (- c2_18 c1_18) (- c2_18 c1_18)) (* (- c2_19 c1_19) (- c2_19 c1_19)))) (+ (+ (* (- c2_20 c1_20) (- c2_20 c1_20)) (* (- c2_21 c1_21) (- c2_21 c1_21))) (+ (* (- c2_22 c1_22) (- c2_22 c1_22)) (* (- c2_23 c1_23) (- c2_23 c1_23)))))) (+ (+ (+ (* (- c2_24 c1_24) (- c2_24 c1_24)) (* (- c2_25 c1_25) (- c2_25 c1_25))) (+ (* (- c2_26 c1_26) (- c2_26 c1_26)) (* (- c2_27 c1_27) (- c2_27 c1_27)))) (+ (+ (* (- c2_28 c1_28) (- c2_28 c1_28)) (* (- c2_29 c1_29) (- c2_29 c1_29))) (+ (* (- c2_30 c1_30) (- c2_30 c1_30)) (* (- c2_31 c1_31) (- c2_31 c1_31))))))))))))))))))</t>
         </is>
       </c>
       <c r="E142" t="n">
         <v>31760</v>
       </c>
       <c r="F142" t="n">
-        <v>50264</v>
+        <v>34782</v>
       </c>
       <c r="G142" t="n">
-        <v>-58.26</v>
+        <v>-9.52</v>
       </c>
       <c r="H142" t="n">
         <v>44.16</v>
       </c>
       <c r="I142" t="n">
-        <v>113.33</v>
+        <v>424.56</v>
       </c>
       <c r="J142" t="b">
         <v>0</v>
       </c>
       <c r="K142" t="n">
-        <v>886.67</v>
+        <v>575.4400000000001</v>
       </c>
       <c r="L142" t="n">
         <v>75</v>
@@ -6427,29 +6427,29 @@
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>(Vec (+ (+ (* v1_0 v2_0) (* v1_1 v2_1)) (+ (* v1_2 v2_2) (* v1_3 v2_3))))</t>
+          <t>(Vec (+ (+ (* v1_0 v2_0) (* v1_1 v2_1)) (+ (* v1_2 v2_2) (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (* v1_3 v2_3))))))))))))))))))))))))))))))))))))))))))))))))))))))))))))))))))))))))))))))</t>
         </is>
       </c>
       <c r="E143" t="n">
         <v>1756</v>
       </c>
       <c r="F143" t="n">
-        <v>1756</v>
+        <v>20330</v>
       </c>
       <c r="G143" t="n">
-        <v>0</v>
+        <v>-1057.74</v>
       </c>
       <c r="H143" t="n">
         <v>39.37</v>
       </c>
       <c r="I143" t="n">
-        <v>39.37</v>
+        <v>128.02</v>
       </c>
       <c r="J143" t="b">
         <v>0</v>
       </c>
       <c r="K143" t="n">
-        <v>960.63</v>
+        <v>871.98</v>
       </c>
       <c r="L143" t="n">
         <v>75</v>
@@ -6469,29 +6469,29 @@
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>(Vec (+ (+ (+ (* v1_0 v2_0) (* v1_1 v2_1)) (+ (* v1_2 v2_2) (* v1_3 v2_3))) (+ (+ (* v1_4 v2_4) (* v1_5 v2_5)) (+ (* v1_6 v2_6) (* v1_7 v2_7)))))</t>
+          <t>(Vec (+ (+ (+ (* v1_0 v2_0) (* v1_1 v2_1)) (+ (* v1_2 v2_2) (* v1_3 v2_3))) (+ (+ (* v1_4 v2_4) (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (* v1_5 v2_5)))))))))))))) (+ (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (* v1_6 v2_6)))))))))))))))))))))))))))))))))))))))))))))))))))) (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (* v1_7 v2_7))))))))))))))))</t>
         </is>
       </c>
       <c r="E144" t="n">
         <v>3757</v>
       </c>
       <c r="F144" t="n">
-        <v>3757</v>
+        <v>22308</v>
       </c>
       <c r="G144" t="n">
-        <v>0</v>
+        <v>-493.77</v>
       </c>
       <c r="H144" t="n">
         <v>40.57</v>
       </c>
       <c r="I144" t="n">
-        <v>40.57</v>
+        <v>101.67</v>
       </c>
       <c r="J144" t="b">
         <v>0</v>
       </c>
       <c r="K144" t="n">
-        <v>959.4299999999999</v>
+        <v>898.33</v>
       </c>
       <c r="L144" t="n">
         <v>75</v>
@@ -6511,32 +6511,32 @@
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>(Vec (+ (+ (+ (+ (+ (* v1_0 v2_0) (* v1_1 v2_1)) (+ (* v1_2 v2_2) (* v1_3 v2_3))) (+ (+ (* v1_4 v2_4) (* v1_5 v2_5)) (+ (* v1_6 v2_6) (* v1_7 v2_7)))) (+ (+ (+ (* v1_8 v2_8) (* v1_9 v2_9)) (+ (* v1_10 v2_10) (* v1_11 v2_11))) (+ (+ (* v1_12 v2_12) (* v1_13 v2_13)) (+ (* v1_14 v2_14) (* v1_15 v2_15))))) (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (* v1_16 v2_16) (* v1_17 v2_17)) (+ (* v1_18 v2_18) (* v1_19 v2_19))) (+ (+ (* v1_20 v2_20) (* v1_21 v2_21)) (+ (* v1_22 v2_22) (* v1_23 v2_23)))) (+ (+ (+ (* v1_24 v2_24) (* v1_25 v2_25)) (+ (* v1_26 v2_26) (* v1_27 v2_27))) (+ (+ (* v1_28 v2_28) (* v1_29 v2_29)) (+ (* v1_30 v2_30) (* v1_31 v2_31))))) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0)))</t>
+          <t>(Vec ( + ( + ( + ( + ( + ( * v1_0 v2_0 ) ( * v1_1 v2_1 ) ) ( + ( * v1_2 v2_2 ) ( * v1_3 v2_3 ) ) ) ( + ( + ( * v1_4 v2_4 ) ( * v1_5 v2_5 ) ) ( + ( * v1_6 v2_6 ) ( * v1_7 v2_7 ) ) ) ) ( + ( + ( + ( * v1_8 v2_8 ) ( * v1_9 v2_9 ) ) ( + ( * v1_10 v2_10 ) ( * v1_11 v2_11 ) ) ) ( + ( + ( * v1_12 v2_12 ) ( * v1_13 v2_13 ) ) ( + ( * v1_14 v2_14 ) ( * v1_15 v2_15 ) ) ) ) ) ( + ( + ( + ( + ( * v1_16 v2_16 ) ( * v1_17 v2_17 ) ) ( + ( * v1_18 v2_18 ) ( * v1_19 v2_19 ) ) ) ( + ( + ( * v1_20 v2_20 ) ( * v1_21 v2_21 ) ) ( + ( * v1_22 v2_22 ) ( * v1_23 v2_23 ) ) ) ) ( + ( + ( + ( * v1_24 v2_24 ) ( * v1_25 v2_25 ) ) ( + ( * v1_26 v2_26 ) ( * v1_27 v2_27 ) ) ) ( + ( + ( * v1_28 v2_28 ) ( * v1_29 v2_29 ) ) ( + ( * v1_30 v2_30 ) ( * v1_31 v2_31 ) ) ) ) ) ) )</t>
         </is>
       </c>
       <c r="E145" t="n">
         <v>15759</v>
       </c>
       <c r="F145" t="n">
-        <v>34333</v>
+        <v>15759</v>
       </c>
       <c r="G145" t="n">
-        <v>-117.86</v>
+        <v>0</v>
       </c>
       <c r="H145" t="n">
         <v>42.97</v>
       </c>
       <c r="I145" t="n">
-        <v>131.62</v>
+        <v>42.97</v>
       </c>
       <c r="J145" t="b">
         <v>0</v>
       </c>
       <c r="K145" t="n">
-        <v>868.38</v>
+        <v>957.03</v>
       </c>
       <c r="L145" t="n">
-        <v>75</v>
+        <v>1</v>
       </c>
     </row>
     <row r="146">
@@ -6553,29 +6553,29 @@
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>(Vec (+ in_1_1 (* in_0_1 2)) (+ (+ in_1_2 (- in_1_0)) (+ (* in_0_2 2) (* in_0_0 -2))) (+ (+ in_1_3 (- in_1_1)) (+ (* in_0_3 2) (* in_0_1 -2))) (+ (- in_1_2) (* in_0_2 -2)) (+ in_2_1 (+ in_0_1 (* in_1_1 2))) (+ (+ in_2_2 (- in_2_0)) (+ (+ in_0_2 (- in_0_0)) (+ (* in_1_2 2) (* in_1_0 -2)))) (+ (+ in_2_3 (- in_2_1)) (+ (+ in_0_3 (- in_0_1)) (+ (* in_1_3 2) (* in_1_1 -2)))) (+ (- in_2_2) (+ (- in_0_2) (* in_1_2 -2))) (+ in_3_1 (+ in_1_1 (* in_2_1 2))) (+ (+ in_3_2 (- in_3_0)) (+ (+ in_1_2 (- in_1_0)) (+ (* in_2_2 2) (* in_2_0 -2)))) (+ (+ in_3_3 (- in_3_1)) (+ (+ in_1_3 (- in_1_1)) (+ (* in_2_3 2) (* in_2_1 -2)))) (+ (- in_3_2) (+ (- in_1_2) (* in_2_2 -2))) (+ in_2_1 (* in_3_1 2)) (+ (+ in_2_2 (- in_2_0)) (+ (* in_3_2 2) (* in_3_0 -2))) (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (+ (+ in_2_3 (- in_2_1)) (+ (* in_3_3 2) (* in_3_1 -2))) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) (+ (- in_2_2) (* in_3_2 -2)))</t>
+          <t>(Vec (+ in_1_1 (* in_0_1 2)) (+ (+ in_1_2 (- in_1_0)) (+ (* in_0_2 2) (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (* in_0_0 -2)))))))) (+ (+ in_1_3 (- in_1_1)) (+ (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (* in_0_3 2)))))) (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (* in_0_1 -2)))))))) (+ (- in_1_2) (* in_0_2 -2)) (+ in_2_1 (+ in_0_1 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (* in_1_1 2)))))))) (+ (+ in_2_2 (- in_2_0)) (+ (+ in_0_2 (- in_0_0)) (+ (+ 0 (+ 0 (+ 0 (+ 0 (* in_1_2 2))))) (+ 0 (+ 0 (+ 0 (+ 0 (* in_1_0 -2)))))))) (+ (+ in_2_3 (- in_2_1)) (+ (+ in_0_3 (- in_0_1)) (+ (+ 0 (+ 0 (+ 0 (* in_1_3 2)))) (+ 0 (+ 0 (+ 0 (* in_1_1 -2))))))) (+ (- in_2_2) (+ (- in_0_2) (+ 0 (+ 0 (+ 0 (+ 0 (* in_1_2 -2))))))) (+ in_3_1 (+ in_1_1 (+ 0 (+ 0 (+ 0 (+ 0 (* in_2_1 2))))))) (+ (+ in_3_2 (- in_3_0)) (+ (+ in_1_2 (- in_1_0)) (+ (+ 0 (+ 0 (+ 0 (* in_2_2 2)))) (+ 0 (+ 0 (+ 0 (* in_2_0 -2))))))) (+ (+ in_3_3 (- in_3_1)) (+ (+ in_1_3 (- in_1_1)) (+ (+ 0 (+ 0 (+ 0 (* in_2_3 2)))) (+ 0 (+ 0 (+ 0 (* in_2_1 -2))))))) (+ (- in_3_2) (+ (- in_1_2) (+ 0 (+ 0 (+ 0 (+ 0 (* in_2_2 -2))))))) (+ in_2_1 (* in_3_1 2)) (+ (+ in_2_2 (- in_2_0)) (+ (+ 0 (+ 0 (+ 0 (+ 0 (* in_3_2 2))))) (+ 0 (+ 0 (+ 0 (+ 0 (* in_3_0 -2))))))) (+ (+ in_2_3 (- in_2_1)) (+ (+ 0 (+ 0 (+ 0 (+ 0 (* in_3_3 2))))) (+ 0 (+ 0 (+ 0 (+ 0 (* in_3_1 -2))))))) (+ (- in_2_2) (* in_3_2 -2)))</t>
         </is>
       </c>
       <c r="E146" t="n">
         <v>21507</v>
       </c>
       <c r="F146" t="n">
-        <v>40154</v>
+        <v>40011</v>
       </c>
       <c r="G146" t="n">
-        <v>-86.7</v>
+        <v>-86.04000000000001</v>
       </c>
       <c r="H146" t="n">
         <v>40.57</v>
       </c>
       <c r="I146" t="n">
-        <v>2598.36</v>
+        <v>45.36</v>
       </c>
       <c r="J146" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K146" t="n">
-        <v>-1598.36</v>
+        <v>954.64</v>
       </c>
       <c r="L146" t="n">
         <v>75</v>
@@ -6595,29 +6595,29 @@
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>(Vec (+ (+ (* a_0_0 b_0_0) (* a_0_1 b_1_0)) (* a_0_2 b_2_0)) (+ (+ (* a_0_0 b_0_1) (* a_0_1 b_1_1)) (* a_0_2 b_2_1)) (+ (+ (* a_0_0 b_0_2) (* a_0_1 b_1_2)) (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* a_0_2 b_2_2) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1)) (+ (+ (* a_1_0 b_0_0) (* a_1_1 b_1_0)) (* a_1_2 b_2_0)) (+ (+ (* a_1_0 b_0_1) (* a_1_1 b_1_1)) (* a_1_2 b_2_1)) (+ (+ (* a_1_0 b_0_2) (* a_1_1 b_1_2)) (* a_1_2 b_2_2)) (+ (+ (* a_2_0 b_0_0) (* a_2_1 b_1_0)) (* a_2_2 b_2_0)) (+ (+ (* a_2_0 b_0_1) (* a_2_1 b_1_1)) (* a_2_2 b_2_1)) (+ (+ (* a_2_0 b_0_2) (* a_2_1 b_1_2)) (* a_2_2 b_2_2)))</t>
+          <t>(Vec (+ (+ (+ 0 (+ 0 (+ 0 (+ 0 (* a_0_0 b_0_0))))) (+ 0 (+ 0 (+ 0 (+ 0 (* a_0_1 b_1_0)))))) (* a_0_2 b_2_0)) (+ (+ (+ 0 (+ 0 (+ 0 (+ 0 (* a_0_0 b_0_1))))) (+ 0 (+ 0 (+ 0 (+ 0 (* a_0_1 b_1_1)))))) (* a_0_2 b_2_1)) (+ (+ (+ 0 (+ 0 (+ 0 (* a_0_0 b_0_2)))) (+ 0 (+ 0 (+ 0 (* a_0_1 b_1_2))))) (* a_0_2 b_2_2)) (+ (+ (+ 0 (+ 0 (+ 0 (* a_1_0 b_0_0)))) (+ 0 (+ 0 (+ 0 (* a_1_1 b_1_0))))) (* a_1_2 b_2_0)) (+ (+ (+ 0 (+ 0 (+ 0 (* a_1_0 b_0_1)))) (+ 0 (+ 0 (+ 0 (* a_1_1 b_1_1))))) (* a_1_2 b_2_1)) (+ (+ (+ 0 (+ 0 (+ 0 (* a_1_0 b_0_2)))) (+ 0 (+ 0 (+ 0 (* a_1_1 b_1_2))))) (+ 0 (+ 0 (+ 0 (+ 0 (* a_1_2 b_2_2)))))) (+ (+ (+ 0 (+ 0 (+ 0 (* a_2_0 b_0_0)))) (+ 0 (+ 0 (+ 0 (* a_2_1 b_1_0))))) (+ 0 (+ 0 (+ 0 (+ 0 (* a_2_2 b_2_0)))))) (+ (+ (+ 0 (+ 0 (+ 0 (* a_2_0 b_0_1)))) (+ 0 (+ 0 (+ 0 (* a_2_1 b_1_1))))) (+ 0 (+ 0 (+ 0 (+ 0 (* a_2_2 b_2_1)))))) (+ (+ (+ 0 (+ 0 (+ 0 (* a_2_0 b_0_2)))) (+ 0 (+ 0 (+ 0 (* a_2_1 b_1_2))))) (+ 0 (+ 0 (+ 0 (+ 0 (* a_2_2 b_2_2)))))))</t>
         </is>
       </c>
       <c r="E147" t="n">
         <v>11256</v>
       </c>
       <c r="F147" t="n">
-        <v>29903</v>
+        <v>29760</v>
       </c>
       <c r="G147" t="n">
-        <v>-165.66</v>
+        <v>-164.39</v>
       </c>
       <c r="H147" t="n">
         <v>39.37</v>
       </c>
       <c r="I147" t="n">
-        <v>2597.17</v>
+        <v>44.16</v>
       </c>
       <c r="J147" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K147" t="n">
-        <v>-1597.17</v>
+        <v>955.84</v>
       </c>
       <c r="L147" t="n">
         <v>75</v>
@@ -6637,29 +6637,29 @@
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>(Vec (+ (* (+ (* o3 (- 1 c23)) (* c23 o2)) (- 1 c12)) (* c12 (+ (* o3 (- 1 c13)) (* c13 o1)))))</t>
+          <t>(Vec (+ (* (+ (* o3 (- 1 c23)) (* c23 o2)) (- 1 c12)) (* c12 (+ (* o3 (- 1 c13)) (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (* c13 o1)))))))))))))))))))))))))))))))))))))))))))))))))))))))))))))))))))))))))))))))</t>
         </is>
       </c>
       <c r="E148" t="n">
         <v>3009</v>
       </c>
       <c r="F148" t="n">
-        <v>3009</v>
+        <v>21582</v>
       </c>
       <c r="G148" t="n">
-        <v>0</v>
+        <v>-617.25</v>
       </c>
       <c r="H148" t="n">
         <v>75.15000000000001</v>
       </c>
       <c r="I148" t="n">
-        <v>75.15000000000001</v>
+        <v>162.61</v>
       </c>
       <c r="J148" t="b">
         <v>0</v>
       </c>
       <c r="K148" t="n">
-        <v>924.85</v>
+        <v>837.39</v>
       </c>
       <c r="L148" t="n">
         <v>75</v>
@@ -6679,32 +6679,32 @@
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>(Vec (+ (* (+ (* (+ (* o321 (- 1 c23)) (* c23 o231)) (- 1 c13)) (* c13 o213)) (- 1 c12)) (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (* c12 (+ (* (- 1 c23) (+ (* o312 (- 1 c13)) (* c13 o132))) (* c23 o123))) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0)))</t>
+          <t>(Vec ( + ( * ( + ( * ( + ( * o321 ( - 1 c23 ) ) ( * c23 o231 ) ) ( - 1 c13 ) ) ( * c13 o213 ) ) ( - 1 c12 ) ) ( * c12 ( + ( * ( - 1 c23 ) ( + ( * o312 ( - 1 c13 ) ) ( * c13 o132 ) ) ) ( * c23 o123 ) ) ) ) )</t>
         </is>
       </c>
       <c r="E149" t="n">
         <v>5012</v>
       </c>
       <c r="F149" t="n">
-        <v>23586</v>
+        <v>5012</v>
       </c>
       <c r="G149" t="n">
-        <v>-370.59</v>
+        <v>0</v>
       </c>
       <c r="H149" t="n">
         <v>110.93</v>
       </c>
       <c r="I149" t="n">
-        <v>199.58</v>
+        <v>110.93</v>
       </c>
       <c r="J149" t="b">
         <v>0</v>
       </c>
       <c r="K149" t="n">
-        <v>800.42</v>
+        <v>889.0700000000001</v>
       </c>
       <c r="L149" t="n">
-        <v>75</v>
+        <v>1</v>
       </c>
     </row>
     <row r="150">
@@ -6763,32 +6763,32 @@
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>(Vec (+ (+ (* (+ (* x9604 x9605) (+ x9607 x9608)) (+ (+ x9611 x9612) (+ x9614 x9615))) (* (* (* x9619 x9620) (* x9622 x9623)) (* (+ x9626 x9627) (* x9629 x9630)))) (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (* (+ (+ (* x9634 x9635) (+ x9637 x9638)) (+ (* x9641 x9642) (* x9644 x9645))) (+ (* (+ x9649 x9650) (+ x9652 x9653)) (+ (* x9656 x9657) (* x9659 x9660)))) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0)))</t>
+          <t>(Vec ( + ( + ( * ( + ( * x9604 x9605 ) ( + x9607 x9608 ) ) ( + ( + x9611 x9612 ) ( + x9614 x9615 ) ) ) ( * ( * ( * x9619 x9620 ) ( * x9622 x9623 ) ) ( * ( + x9626 x9627 ) ( * x9629 x9630 ) ) ) ) ( * ( + ( + ( * x9634 x9635 ) ( + x9637 x9638 ) ) ( + ( * x9641 x9642 ) ( * x9644 x9645 ) ) ) ( + ( * ( + x9649 x9650 ) ( + x9652 x9653 ) ) ( + ( * x9656 x9657 ) ( * x9659 x9660 ) ) ) ) ) )</t>
         </is>
       </c>
       <c r="E151" t="n">
         <v>7760</v>
       </c>
       <c r="F151" t="n">
-        <v>26334</v>
+        <v>7760</v>
       </c>
       <c r="G151" t="n">
-        <v>-239.36</v>
+        <v>0</v>
       </c>
       <c r="H151" t="n">
         <v>108.53</v>
       </c>
       <c r="I151" t="n">
-        <v>197.19</v>
+        <v>108.53</v>
       </c>
       <c r="J151" t="b">
         <v>0</v>
       </c>
       <c r="K151" t="n">
-        <v>802.8099999999999</v>
+        <v>891.47</v>
       </c>
       <c r="L151" t="n">
-        <v>75</v>
+        <v>1</v>
       </c>
     </row>
     <row r="152">
@@ -6847,7 +6847,7 @@
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>(Vec (+ (+ in_1_1 in_1_0) (+ in_0_1 in_0_0)) (+ (+ (+ in_1_2 in_1_1) (+ in_1_0 in_0_2)) (+ in_0_1 in_0_0)) (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ in_1_3 in_1_2) (+ in_1_1 in_0_3)) (+ in_0_2 in_0_1)) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) (+ (+ in_1_3 in_1_2) (+ in_0_3 in_0_2)) (+ (+ (+ in_2_1 in_2_0) (+ in_1_1 in_1_0)) (+ in_0_1 in_0_0)) (+ (+ (+ in_2_2 (+ in_2_1 in_2_0)) (+ in_1_2 in_1_1)) (+ (+ in_1_0 in_0_2) (+ in_0_1 in_0_0))) (+ (+ (+ in_2_3 (+ in_2_2 in_2_1)) (+ in_1_3 in_1_2)) (+ (+ in_1_1 in_0_3) (+ in_0_2 in_0_1))) (+ (+ (+ in_2_3 in_2_2) (+ in_1_3 in_1_2)) (+ in_0_3 in_0_2)) (+ (+ in_3_1 in_3_0) (+ (+ in_2_1 in_2_0) (+ in_1_1 in_1_0))) (+ (+ (+ in_3_2 (+ in_3_1 in_3_0)) (+ in_2_2 in_2_1)) (+ (+ in_2_0 in_1_2) (+ in_1_1 in_1_0))) (+ (+ (+ in_3_3 (+ in_3_2 in_3_1)) (+ in_2_3 in_2_2)) (+ (+ in_2_1 in_1_3) (+ in_1_2 in_1_1))) (+ (+ (+ in_3_3 in_3_2) (+ in_2_3 in_2_2)) (+ in_1_3 in_1_2)) (+ (+ in_3_1 in_3_0) (+ in_2_1 in_2_0)) (+ (+ (+ in_3_2 in_3_1) (+ in_3_0 in_2_2)) (+ in_2_1 in_2_0)) (+ (+ (+ in_3_3 in_3_2) (+ in_3_1 in_2_3)) (+ in_2_2 in_2_1)) (+ (+ in_3_3 in_3_2) (+ in_2_3 in_2_2)))</t>
+          <t>(Vec (+ (+ in_1_1 in_1_0) (+ in_0_1 in_0_0)) (+ (+ (+ in_1_2 in_1_1) (+ in_1_0 in_0_2)) (+ in_0_1 in_0_0)) (+ (+ (+ in_1_3 in_1_2) (+ in_1_1 in_0_3)) (+ in_0_2 in_0_1)) (+ (+ in_1_3 in_1_2) (+ in_0_3 in_0_2)) (+ (+ (+ in_2_1 in_2_0) (+ in_1_1 in_1_0)) (+ in_0_1 in_0_0)) (+ (+ (+ in_2_2 (+ in_2_1 in_2_0)) (+ in_1_2 in_1_1)) (+ (+ in_1_0 in_0_2) (+ in_0_1 in_0_0))) (+ (+ (+ in_2_3 (+ in_2_2 in_2_1)) (+ in_1_3 in_1_2)) (+ (+ in_1_1 in_0_3) (+ in_0_2 in_0_1))) (+ (+ (+ in_2_3 in_2_2) (+ in_1_3 in_1_2)) (+ in_0_3 in_0_2)) (+ (+ in_3_1 in_3_0) (+ (+ in_2_1 in_2_0) (+ in_1_1 in_1_0))) (+ (+ (+ in_3_2 (+ in_3_1 in_3_0)) (+ in_2_2 in_2_1)) (+ (+ in_2_0 in_1_2) (+ in_1_1 in_1_0))) (+ (+ (+ in_3_3 (+ in_3_2 in_3_1)) (+ in_2_3 in_2_2)) (+ (+ in_2_1 in_1_3) (+ in_1_2 in_1_1))) (+ (+ (+ in_3_3 in_3_2) (+ in_2_3 in_2_2)) (+ in_1_3 in_1_2)) (+ (+ in_3_1 in_3_0) (+ in_2_1 in_2_0)) (+ (+ (+ in_3_2 in_3_1) (+ in_3_0 in_2_2)) (+ in_2_1 in_2_0)) (+ (+ (+ in_3_3 in_3_2) (+ in_3_1 in_2_3)) (+ in_2_2 in_2_1)) (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (* 1 (+ (+ in_3_3 in_3_2) (+ in_2_3 in_2_2)))))))))))))))))))))))))))))))))))))))))))))))))))))))))))))))))))))))))))))</t>
         </is>
       </c>
       <c r="E153" t="n">
@@ -6863,13 +6863,13 @@
         <v>7.19</v>
       </c>
       <c r="I153" t="n">
-        <v>94.64</v>
+        <v>126.83</v>
       </c>
       <c r="J153" t="b">
         <v>0</v>
       </c>
       <c r="K153" t="n">
-        <v>905.36</v>
+        <v>873.17</v>
       </c>
       <c r="L153" t="n">
         <v>75</v>
@@ -6889,29 +6889,29 @@
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>(Vec (+ v2_0 (+ 2 (* v1_0 5))) (+ v2_1 (+ (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* 2 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) (* v1_1 5))) (+ v2_2 (+ 2 (* v1_2 5))) (+ v2_3 (+ 2 (* v1_3 5))))</t>
+          <t>(Vec (+ v2_0 (+ 2 (* v1_0 5))) (+ v2_1 (+ 2 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (* v1_1 5))))))))))))))))))))))))))))))) (+ v2_2 (+ 2 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (* v1_2 5))))))))))))))))))))))))))))))) (+ v2_3 (+ 2 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (* v1_3 5))))))))))))))))))))))</t>
         </is>
       </c>
       <c r="E154" t="n">
         <v>3006</v>
       </c>
       <c r="F154" t="n">
-        <v>21652</v>
+        <v>21534</v>
       </c>
       <c r="G154" t="n">
-        <v>-620.29</v>
+        <v>-616.37</v>
       </c>
       <c r="H154" t="n">
         <v>39.37</v>
       </c>
       <c r="I154" t="n">
-        <v>2563.78</v>
+        <v>72.92</v>
       </c>
       <c r="J154" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K154" t="n">
-        <v>-1563.78</v>
+        <v>927.08</v>
       </c>
       <c r="L154" t="n">
         <v>75</v>
@@ -6931,29 +6931,29 @@
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>(Vec (+ v2_0 (+ 2 (* v1_0 5))) (+ v2_1 (+ 2 (* v1_1 5))) (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ v2_2 (+ 2 (* v1_2 5))) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) (+ v2_3 (+ 2 (* v1_3 5))) (+ v2_4 (+ 2 (* v1_4 5))) (+ v2_5 (+ 2 (* v1_5 5))) (+ v2_6 (+ 2 (* v1_6 5))) (+ v2_7 (+ 2 (* v1_7 5))) (+ v2_8 (+ 2 (* v1_8 5))) (+ v2_9 (+ 2 (* v1_9 5))) (+ v2_10 (+ 2 (* v1_10 5))) (+ v2_11 (+ 2 (* v1_11 5))) (+ v2_12 (+ 2 (* v1_12 5))) (+ v2_13 (+ 2 (* v1_13 5))) (+ v2_14 (+ 2 (* v1_14 5))) (+ v2_15 (+ 2 (* v1_15 5))))</t>
+          <t>(Vec (+ v2_0 (+ 2 (* v1_0 5))) (+ v2_1 (+ 2 (* v1_1 5))) (+ v2_2 (+ 2 (* v1_2 5))) (+ v2_3 (+ 2 (* v1_3 5))) (+ v2_4 (+ 2 (* v1_4 5))) (+ v2_5 (+ 2 (* v1_5 5))) (+ v2_6 (+ 2 (* v1_6 5))) (+ v2_7 (+ 2 (* v1_7 5))) (+ v2_8 (+ 2 (* v1_8 5))) (+ v2_9 (+ 2 (* v1_9 5))) (+ v2_10 (+ 2 (* v1_10 5))) (+ v2_11 (+ 2 (* v1_11 5))) (+ v2_12 (+ 2 (* v1_12 5))) (+ v2_13 (+ 2 (* v1_13 5))) (+ v2_14 (+ 2 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (* v1_14 5)))))))))))))))))))))))))))))))))))))))) (+ v2_15 (+ 2 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (* v1_15 5)))))))))))))))))))))))))))))))))))))))))</t>
         </is>
       </c>
       <c r="E155" t="n">
         <v>12006</v>
       </c>
       <c r="F155" t="n">
-        <v>30580</v>
+        <v>30543</v>
       </c>
       <c r="G155" t="n">
-        <v>-154.71</v>
+        <v>-154.4</v>
       </c>
       <c r="H155" t="n">
         <v>39.37</v>
       </c>
       <c r="I155" t="n">
-        <v>128.02</v>
+        <v>83.7</v>
       </c>
       <c r="J155" t="b">
         <v>0</v>
       </c>
       <c r="K155" t="n">
-        <v>871.98</v>
+        <v>916.3</v>
       </c>
       <c r="L155" t="n">
         <v>75</v>
@@ -6973,32 +6973,32 @@
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>(Vec (+ (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (+ (- (+ v1_0 v2_0) (* (* v1_0 v2_0) 2)) (- (+ v1_1 v2_1) (* 2 (* v1_1 v2_1)))))))))))))))))))))))))))) (- (+ v1_2 v2_2) (* 2 (* v1_2 v2_2)))))</t>
+          <t>(Vec ( + ( + ( - ( + v1_0 v2_0 ) ( * ( * v1_0 v2_0 ) 2 ) ) ( - ( + v1_1 v2_1 ) ( * 2 ( * v1_1 v2_1 ) ) ) ) ( - ( + v1_2 v2_2 ) ( * 2 ( * v1_2 v2_2 ) ) ) ) )</t>
         </is>
       </c>
       <c r="E156" t="n">
         <v>3509</v>
       </c>
       <c r="F156" t="n">
-        <v>9557</v>
+        <v>3509</v>
       </c>
       <c r="G156" t="n">
-        <v>-172.36</v>
+        <v>0</v>
       </c>
       <c r="H156" t="n">
         <v>75.15000000000001</v>
       </c>
       <c r="I156" t="n">
-        <v>905.09</v>
+        <v>75.15000000000001</v>
       </c>
       <c r="J156" t="b">
         <v>0</v>
       </c>
       <c r="K156" t="n">
-        <v>94.91</v>
+        <v>924.85</v>
       </c>
       <c r="L156" t="n">
-        <v>73</v>
+        <v>1</v>
       </c>
     </row>
     <row r="157">
@@ -7015,29 +7015,29 @@
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>(Vec (+ (+ (- (+ v1_0 v2_0) (* (* v1_0 v2_0) 2)) (- (+ v1_1 v2_1) (* 2 (* v1_1 v2_1)))) (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (- (+ v1_2 v2_2) (* 2 (* v1_2 v2_2))) (- (+ v1_3 v2_3) (* 2 (* v1_3 v2_3)))) (- (+ v1_4 v2_4) (* 2 (* v1_4 v2_4)))) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0)))</t>
+          <t>(Vec (+ (+ (- (+ v1_0 v2_0) (* (* v1_0 v2_0) 2)) (- (+ v1_1 v2_1) (* 2 (* v1_1 v2_1)))) (+ (+ (- (+ v1_2 v2_2) (* 2 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (* v1_2 v2_2)))))))))))))))))))))))))))))))))))))))) (- (+ v1_3 v2_3) (* 2 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (* v1_3 v2_3))))))))))))))))))))))))))))))))))))))))) (- (+ v1_4 v2_4) (* 2 (* v1_4 v2_4))))))</t>
         </is>
       </c>
       <c r="E157" t="n">
         <v>6010</v>
       </c>
       <c r="F157" t="n">
-        <v>24584</v>
+        <v>24547</v>
       </c>
       <c r="G157" t="n">
-        <v>-309.05</v>
+        <v>-308.44</v>
       </c>
       <c r="H157" t="n">
         <v>76.34999999999999</v>
       </c>
       <c r="I157" t="n">
-        <v>165</v>
+        <v>120.68</v>
       </c>
       <c r="J157" t="b">
         <v>0</v>
       </c>
       <c r="K157" t="n">
-        <v>835</v>
+        <v>879.3200000000001</v>
       </c>
       <c r="L157" t="n">
         <v>75</v>
@@ -7057,29 +7057,29 @@
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>(Vec (+ (+ (+ (+ (- (+ v1_0 v2_0) (* (* v1_0 v2_0) 2)) (- (+ v1_1 v2_1) (* 2 (* v1_1 v2_1)))) (+ (- (+ v1_2 v2_2) (* 2 (* v1_2 v2_2))) (- (+ v1_3 v2_3) (* 2 (* v1_3 v2_3))))) (+ (+ (- (+ v1_4 v2_4) (* 2 (* v1_4 v2_4))) (- (+ v1_5 v2_5) (* 2 (* v1_5 v2_5)))) (+ (- (+ v1_6 v2_6) (* 2 (* v1_6 v2_6))) (- (+ v1_7 v2_7) (* 2 (* v1_7 v2_7)))))) (+ (+ (+ (- (+ v1_8 v2_8) (* 2 (* v1_8 v2_8))) (- (+ v1_9 v2_9) (* 2 (* v1_9 v2_9)))) (+ (- (+ v1_10 v2_10) (* 2 (* v1_10 v2_10))) (- (+ v1_11 v2_11) (* 2 (* v1_11 v2_11))))) (+ (+ (- (+ v1_12 v2_12) (* 2 (* v1_12 v2_12))) (- (+ v1_13 v2_13) (* 2 (* v1_13 v2_13)))) (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (+ (* 1 (- (+ v1_14 v2_14) (* 2 (* v1_14 v2_14)))) (* 1 (- (+ v1_15 v2_15) (* 2 (* v1_15 v2_15)))))))))))))))))))))))))))))))))</t>
+          <t>(Vec (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (+ (* 1 (+ (+ (+ (- (+ v1_0 v2_0) (* (* v1_0 v2_0) 2)) (- (+ v1_1 v2_1) (* 2 (* v1_1 v2_1)))) (+ (- (+ v1_2 v2_2) (* 2 (* v1_2 v2_2))) (- (+ v1_3 v2_3) (* 2 (* v1_3 v2_3))))) (+ (+ (- (+ v1_4 v2_4) (* 2 (* v1_4 v2_4))) (- (+ v1_5 v2_5) (* 2 (* v1_5 v2_5)))) (+ (- (+ v1_6 v2_6) (* 2 (* v1_6 v2_6))) (- (+ v1_7 v2_7) (* 2 (* v1_7 v2_7))))))) (+ (* 1 (+ (+ (- (+ v1_8 v2_8) (* 2 (* v1_8 v2_8))) (- (+ v1_9 v2_9) (* 2 (* v1_9 v2_9)))) (+ (- (+ v1_10 v2_10) (* 2 (* v1_10 v2_10))) (- (+ v1_11 v2_11) (* 2 (* v1_11 v2_11)))))) (+ (+ (- (+ v1_12 v2_12) (* 2 (* v1_12 v2_12))) (- (+ v1_13 v2_13) (* 2 (* v1_13 v2_13)))) (+ (- (+ v1_14 v2_14) (* 2 (* v1_14 v2_14))) (- (+ v1_15 v2_15) (* 2 (* v1_15 v2_15))))))))))))))))))</t>
         </is>
       </c>
       <c r="E158" t="n">
         <v>19761</v>
       </c>
       <c r="F158" t="n">
-        <v>26311</v>
+        <v>22783</v>
       </c>
       <c r="G158" t="n">
-        <v>-33.15</v>
+        <v>-15.29</v>
       </c>
       <c r="H158" t="n">
         <v>77.55</v>
       </c>
       <c r="I158" t="n">
-        <v>942.0700000000001</v>
+        <v>457.94</v>
       </c>
       <c r="J158" t="b">
         <v>0</v>
       </c>
       <c r="K158" t="n">
-        <v>57.93</v>
+        <v>542.0599999999999</v>
       </c>
       <c r="L158" t="n">
         <v>75</v>
@@ -7099,29 +7099,29 @@
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>(Vec (+ c1_0 (+ c2_0 (* c0_0 (+ c3_0 (* c0_0 c4_0))))) (+ c1_1 (+ c2_1 (* c0_1 (+ c3_1 (* c0_1 c4_1))))) (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ c1_2 (+ c2_2 (* c0_2 (+ c3_2 (* c0_2 c4_2))))) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) (+ c1_3 (+ c2_3 (* c0_3 (+ c3_3 (* c0_3 c4_3))))))</t>
+          <t>(Vec (+ c1_0 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (+ c2_0 (* c0_0 (+ c3_0 (* c0_0 c4_0))))))))))))))))))) (+ c1_1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (+ c2_1 (* c0_1 (+ c3_1 (* c0_1 c4_1))))))))))))))))))) (+ c1_2 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (+ c2_2 (* c0_2 (+ c3_2 (* c0_2 c4_2))))))))))))))))))) (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (+ c1_3 (+ (+ (* 1 (* 1 (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ c2_3 (* c0_3 (+ c3_3 (* c0_3 c4_3)))) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0))) 0) 0))))))))))))))))))</t>
         </is>
       </c>
       <c r="E159" t="n">
         <v>5009</v>
       </c>
       <c r="F159" t="n">
-        <v>23583</v>
+        <v>23558</v>
       </c>
       <c r="G159" t="n">
-        <v>-370.81</v>
+        <v>-370.31</v>
       </c>
       <c r="H159" t="n">
         <v>75.15000000000001</v>
       </c>
       <c r="I159" t="n">
-        <v>163.8</v>
+        <v>681</v>
       </c>
       <c r="J159" t="b">
         <v>0</v>
       </c>
       <c r="K159" t="n">
-        <v>836.2</v>
+        <v>319</v>
       </c>
       <c r="L159" t="n">
         <v>75</v>
@@ -7141,29 +7141,29 @@
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>(Vec (+ c1_0 (+ c2_0 (* c0_0 (+ c3_0 (* c0_0 c4_0))))) (+ c1_1 (+ c2_1 (* c0_1 (+ c3_1 (* c0_1 c4_1))))) (+ c1_2 (+ c2_2 (* c0_2 (+ c3_2 (* c0_2 c4_2))))) (+ c1_3 (+ c2_3 (* c0_3 (+ c3_3 (* c0_3 c4_3))))) (+ c1_4 (+ c2_4 (* c0_4 (+ c3_4 (* c0_4 c4_4))))) (+ c1_5 (+ c2_5 (* c0_5 (+ c3_5 (* c0_5 c4_5))))) (+ c1_6 (+ c2_6 (* c0_6 (+ c3_6 (* c0_6 c4_6))))) (+ c1_7 (+ c2_7 (* c0_7 (+ c3_7 (* c0_7 c4_7))))) (+ c1_8 (+ c2_8 (* c0_8 (+ c3_8 (* c0_8 c4_8))))) (+ c1_9 (+ c2_9 (* c0_9 (+ c3_9 (* c0_9 c4_9))))) (+ c1_10 (+ c2_10 (* c0_10 (+ c3_10 (* c0_10 c4_10))))) (+ c1_11 (+ c2_11 (* c0_11 (+ c3_11 (* c0_11 c4_11))))) (+ c1_12 (+ c2_12 (* c0_12 (+ c3_12 (* c0_12 c4_12))))) (+ c1_13 (+ c2_13 (* c0_13 (+ c3_13 (* c0_13 c4_13))))) (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (+ c1_14 (+ c2_14 (* c0_14 (+ c3_14 (* c0_14 c4_14))))) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) (+ c1_15 (+ c2_15 (* c0_15 (+ c3_15 (* c0_15 c4_15))))))</t>
+          <t>(Vec (+ c1_0 (+ c2_0 (* c0_0 (+ c3_0 (+ 0 (+ 0 (+ 0 (+ 0 (* c0_0 c4_0))))))))) (+ c1_1 (+ c2_1 (* c0_1 (+ c3_1 (+ 0 (+ 0 (+ 0 (+ 0 (* c0_1 c4_1))))))))) (+ c1_2 (+ c2_2 (* c0_2 (+ c3_2 (+ 0 (+ 0 (+ 0 (+ 0 (* c0_2 c4_2))))))))) (+ c1_3 (+ c2_3 (* c0_3 (+ c3_3 (+ 0 (+ 0 (+ 0 (+ 0 (* c0_3 c4_3))))))))) (+ c1_4 (+ c2_4 (* c0_4 (+ c3_4 (+ 0 (+ 0 (+ 0 (* c0_4 c4_4)))))))) (+ c1_5 (+ c2_5 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (* c0_5 (+ c3_5 (* c0_5 c4_5)))))))))) (+ c1_6 (+ c2_6 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (* c0_6 (+ c3_6 (* c0_6 c4_6)))))))))) (+ c1_7 (+ c2_7 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (* c0_7 (+ c3_7 (* c0_7 c4_7)))))))))) (+ c1_8 (+ c2_8 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (* c0_8 (+ c3_8 (* c0_8 c4_8)))))))))) (+ c1_9 (+ c2_9 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (* c0_9 (+ c3_9 (* c0_9 c4_9)))))))))) (+ c1_10 (+ c2_10 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (* c0_10 (+ c3_10 (* c0_10 c4_10)))))))))) (+ c1_11 (+ c2_11 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (* c0_11 (+ c3_11 (* c0_11 c4_11)))))))))) (+ c1_12 (+ c2_12 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (* c0_12 (+ c3_12 (* c0_12 c4_12)))))))))) (+ c1_13 (+ c2_13 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (* c0_13 (+ c3_13 (* c0_13 c4_13)))))))))) (+ c1_14 (+ c2_14 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (* c0_14 (+ c3_14 (* c0_14 c4_14)))))))))) (+ c1_15 (+ c2_15 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (* c0_15 (+ c3_15 (* c0_15 c4_15)))))))))))</t>
         </is>
       </c>
       <c r="E160" t="n">
         <v>20009</v>
       </c>
       <c r="F160" t="n">
-        <v>38657</v>
+        <v>38514</v>
       </c>
       <c r="G160" t="n">
-        <v>-93.2</v>
+        <v>-92.48</v>
       </c>
       <c r="H160" t="n">
         <v>75.15000000000001</v>
       </c>
       <c r="I160" t="n">
-        <v>2634.14</v>
+        <v>81.14</v>
       </c>
       <c r="J160" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K160" t="n">
-        <v>-1634.14</v>
+        <v>918.86</v>
       </c>
       <c r="L160" t="n">
         <v>75</v>
@@ -7183,29 +7183,29 @@
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>(Vec (+ (+ (* (- c2_0 c1_0) (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (- c2_0 c1_0))))))))))))))))))))))))))) (* (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (- c2_1 c1_1)))))))))))))))))))))))))) (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (- c2_1 c1_1))))))))))))))))))))))))))) (* (- c2_2 c1_2) (- c2_2 c1_2))))</t>
+          <t>(Vec (+ (+ (* (- c2_0 c1_0) (- c2_0 c1_0)) (* (- c2_1 c1_1) (- c2_1 c1_1))) (* (- (+ (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (+ (+ (+ (+ (+ (+ (+ (+ (+ (* 1 (* 1 (* 1 (* 1 (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ c2_2 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0))))) 0) 0) 0) 0) 0) 0) 0) 0) 0))))))))))))))))))))))))))))))))))))))))))))))))) 0) c1_2) (- c2_2 c1_2))))</t>
         </is>
       </c>
       <c r="E161" t="n">
         <v>2757</v>
       </c>
       <c r="F161" t="n">
-        <v>21307</v>
+        <v>21382</v>
       </c>
       <c r="G161" t="n">
-        <v>-672.83</v>
+        <v>-675.55</v>
       </c>
       <c r="H161" t="n">
         <v>40.57</v>
       </c>
       <c r="I161" t="n">
-        <v>905.09</v>
+        <v>1863.94</v>
       </c>
       <c r="J161" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K161" t="n">
-        <v>94.91</v>
+        <v>-863.9400000000001</v>
       </c>
       <c r="L161" t="n">
         <v>75</v>
@@ -7225,29 +7225,29 @@
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>(Vec (+ (+ (* (- c2_0 c1_0) (- c2_0 c1_0)) (* (- c2_1 c1_1) (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (- c2_1 c1_1))))))))))))))) (+ (+ (* (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (- c2_2 c1_2))))))))))) (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (- c2_2 c1_2)))))))))))) (* (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (- c2_3 c1_3))))))))))) (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (- c2_3 c1_3))))))))))))) (* (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (- c2_4 c1_4)))))))))))) (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (- c2_4 c1_4))))))))))))))))</t>
+          <t>(Vec (+ (+ (* (- c2_0 c1_0) (- c2_0 c1_0)) (* (- c2_1 c1_1) (- c2_1 c1_1))) (+ (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (+ (+ (+ (+ (+ (+ (+ (+ (+ (* 1 (* 1 (* 1 (* 1 (+ (+ (+ (+ (+ (+ (+ (+ (+ (* (- c2_2 c1_2) (- c2_2 c1_2)) 0) 0) 0) 0) 0) 0) 0) 0) 0))))) 0) 0) 0) 0) 0) 0) 0) 0) (* (- c2_3 c1_3) (- c2_3 c1_3)))))))))))))))))))))))))))))))))))))))))))))))))))))))) (* (- c2_4 c1_4) (- c2_4 c1_4)))))</t>
         </is>
       </c>
       <c r="E162" t="n">
         <v>4758</v>
       </c>
       <c r="F162" t="n">
-        <v>23281</v>
+        <v>23389</v>
       </c>
       <c r="G162" t="n">
-        <v>-389.3</v>
+        <v>-391.57</v>
       </c>
       <c r="H162" t="n">
         <v>41.77</v>
       </c>
       <c r="I162" t="n">
-        <v>455.54</v>
+        <v>2033.25</v>
       </c>
       <c r="J162" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K162" t="n">
-        <v>544.46</v>
+        <v>-1033.25</v>
       </c>
       <c r="L162" t="n">
         <v>75</v>
@@ -7267,29 +7267,29 @@
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>(Vec (+ (+ (+ (+ (* (- c2_0 c1_0) (- c2_0 c1_0)) (* (- c2_1 c1_1) (- c2_1 c1_1))) (+ (* (- c2_2 c1_2) (- c2_2 c1_2)) (* (- c2_3 c1_3) (- c2_3 c1_3)))) (+ (+ (* (- c2_4 c1_4) (- c2_4 c1_4)) (* (- c2_5 c1_5) (- c2_5 c1_5))) (+ (* (- c2_6 c1_6) (- c2_6 c1_6)) (* (* 1 (* 1 (* 1 (* 1 (* 1 (- c2_7 c1_7)))))) (* 1 (* 1 (* 1 (* 1 (* 1 (- c2_7 c1_7)))))))))) (+ (+ (+ (* (* 1 (* 1 (* 1 (* 1 (- c2_8 c1_8))))) (* 1 (* 1 (* 1 (* 1 (- c2_8 c1_8)))))) (* (* 1 (* 1 (* 1 (* 1 (- c2_9 c1_9))))) (* 1 (* 1 (* 1 (* 1 (- c2_9 c1_9))))))) (+ (* (* 1 (* 1 (* 1 (* 1 (- c2_10 c1_10))))) (* 1 (* 1 (* 1 (* 1 (- c2_10 c1_10)))))) (* (* 1 (* 1 (* 1 (* 1 (- c2_11 c1_11))))) (* 1 (* 1 (* 1 (* 1 (- c2_11 c1_11)))))))) (+ (+ (* (* 1 (* 1 (* 1 (* 1 (- c2_12 c1_12))))) (* 1 (* 1 (* 1 (* 1 (- c2_12 c1_12)))))) (* (* 1 (* 1 (* 1 (* 1 (- c2_13 c1_13))))) (* 1 (* 1 (* 1 (* 1 (- c2_13 c1_13))))))) (+ (* (* 1 (* 1 (* 1 (* 1 (- c2_14 c1_14))))) (* 1 (* 1 (* 1 (* 1 (- c2_14 c1_14)))))) (* (* 1 (* 1 (* 1 (* 1 (- c2_15 c1_15))))) (* 1 (* 1 (* 1 (* 1 (- c2_15 c1_15)))))))))))</t>
+          <t>(Vec (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (+ (* 1 (+ (+ (+ (* (- c2_0 c1_0) (- c2_0 c1_0)) (* (- c2_1 c1_1) (- c2_1 c1_1))) (+ (* (- c2_2 c1_2) (- c2_2 c1_2)) (* (- c2_3 c1_3) (- c2_3 c1_3)))) (+ (+ (* (- c2_4 c1_4) (- c2_4 c1_4)) (* (- c2_5 c1_5) (- c2_5 c1_5))) (+ (* (- c2_6 c1_6) (- c2_6 c1_6)) (* (- c2_7 c1_7) (- c2_7 c1_7)))))) (+ (* 1 (+ (+ (* (- c2_8 c1_8) (- c2_8 c1_8)) (* (- c2_9 c1_9) (- c2_9 c1_9))) (+ (* (- c2_10 c1_10) (- c2_10 c1_10)) (* (- c2_11 c1_11) (- c2_11 c1_11))))) (+ (+ (* (- c2_12 c1_12) (- c2_12 c1_12)) (* (- c2_13 c1_13) (- c2_13 c1_13))) (+ (* (- c2_14 c1_14) (- c2_14 c1_14)) (* (- c2_15 c1_15) (- c2_15 c1_15)))))))))))))))))</t>
         </is>
       </c>
       <c r="E163" t="n">
         <v>15759</v>
       </c>
       <c r="F163" t="n">
-        <v>34269</v>
+        <v>18781</v>
       </c>
       <c r="G163" t="n">
-        <v>-117.46</v>
+        <v>-19.18</v>
       </c>
       <c r="H163" t="n">
         <v>42.97</v>
       </c>
       <c r="I163" t="n">
-        <v>215.87</v>
+        <v>423.36</v>
       </c>
       <c r="J163" t="b">
         <v>0</v>
       </c>
       <c r="K163" t="n">
-        <v>784.13</v>
+        <v>576.64</v>
       </c>
       <c r="L163" t="n">
         <v>75</v>
@@ -7309,29 +7309,29 @@
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>(Vec (+ (+ (* v1_0 v2_0) (* v1_1 v2_1)) (* v1_2 v2_2)))</t>
+          <t>(Vec (+ (+ (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (* v1_0 v2_0)))))))))))))))))))))))))) (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (* v1_1 v2_1)))))))))))))))))))))))))) (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (* v1_2 v2_2))))))))))))))))))))))))))))</t>
         </is>
       </c>
       <c r="E164" t="n">
         <v>1256</v>
       </c>
       <c r="F164" t="n">
-        <v>1256</v>
+        <v>19781</v>
       </c>
       <c r="G164" t="n">
-        <v>0</v>
+        <v>-1474.92</v>
       </c>
       <c r="H164" t="n">
         <v>39.37</v>
       </c>
       <c r="I164" t="n">
-        <v>39.37</v>
+        <v>69.31999999999999</v>
       </c>
       <c r="J164" t="b">
         <v>0</v>
       </c>
       <c r="K164" t="n">
-        <v>960.63</v>
+        <v>930.6799999999999</v>
       </c>
       <c r="L164" t="n">
         <v>75</v>
@@ -7351,29 +7351,29 @@
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>(Vec (+ (+ (* v1_0 v2_0) (* v1_1 v2_1)) (+ (+ (* v1_2 v2_2) (* v1_3 v2_3)) (* v1_4 (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* v2_4 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1)))))</t>
+          <t>(Vec (+ (+ (* v1_0 v2_0) (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (* v1_1 v2_1))))))))))))))))))))))) (+ (+ (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (* v1_2 v2_2))))))))))))))) (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (* v1_3 v2_3))))))))))))))))))))) (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (* v1_4 v2_4))))))))))))))))))))))))</t>
         </is>
       </c>
       <c r="E165" t="n">
         <v>2257</v>
       </c>
       <c r="F165" t="n">
-        <v>20904</v>
+        <v>20777</v>
       </c>
       <c r="G165" t="n">
-        <v>-826.1900000000001</v>
+        <v>-820.5599999999999</v>
       </c>
       <c r="H165" t="n">
         <v>40.57</v>
       </c>
       <c r="I165" t="n">
-        <v>2598.36</v>
+        <v>64.53</v>
       </c>
       <c r="J165" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K165" t="n">
-        <v>-1598.36</v>
+        <v>935.47</v>
       </c>
       <c r="L165" t="n">
         <v>75</v>
@@ -7393,29 +7393,29 @@
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>(Vec (+ (+ (+ (+ (* v1_0 v2_0) (* v1_1 v2_1)) (+ (* v1_2 v2_2) (* v1_3 v2_3))) (+ (+ (* v1_4 v2_4) (* v1_5 v2_5)) (+ (* v1_6 v2_6) (* v1_7 v2_7)))) (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (* v1_8 v2_8) (* v1_9 v2_9)) (+ (* v1_10 v2_10) (* v1_11 v2_11))) (+ (+ (* v1_12 v2_12) (* v1_13 v2_13)) (+ (* v1_14 v2_14) (* v1_15 v2_15)))) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0)))</t>
+          <t>(Vec (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (+ (* 1 (+ (+ (+ (* v1_0 v2_0) (* v1_1 v2_1)) (+ (* v1_2 v2_2) (* v1_3 v2_3))) (+ (+ (* v1_4 v2_4) (* v1_5 v2_5)) (+ (* v1_6 v2_6) (* v1_7 v2_7))))) (+ (+ (+ (+ (+ (+ (+ (+ (* v1_8 v2_8) (* v1_9 v2_9)) 0) 0) 0) 0) 0) (* 1 (+ (* v1_10 v2_10) (* v1_11 v2_11)))) (+ (+ (* v1_12 v2_12) (* v1_13 v2_13)) (+ (* v1_14 v2_14) (* v1_15 v2_15)))))))))))))))</t>
         </is>
       </c>
       <c r="E166" t="n">
         <v>7758</v>
       </c>
       <c r="F166" t="n">
-        <v>26332</v>
+        <v>11782</v>
       </c>
       <c r="G166" t="n">
-        <v>-239.42</v>
+        <v>-51.87</v>
       </c>
       <c r="H166" t="n">
         <v>41.77</v>
       </c>
       <c r="I166" t="n">
-        <v>130.42</v>
+        <v>392.37</v>
       </c>
       <c r="J166" t="b">
         <v>0</v>
       </c>
       <c r="K166" t="n">
-        <v>869.58</v>
+        <v>607.63</v>
       </c>
       <c r="L166" t="n">
         <v>75</v>
@@ -7435,29 +7435,29 @@
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>(Vec (+ in_1_1 (* in_0_1 2)) (+ (+ in_1_2 (- in_1_0)) (+ (* in_0_2 2) (* in_0_0 -2))) (+ (- in_1_1) (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* in_0_1 -2) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1)) (+ in_2_1 (+ in_0_1 (* in_1_1 2))) (+ (+ in_2_2 (- in_2_0)) (+ (+ in_0_2 (- in_0_0)) (+ (* in_1_2 2) (* in_1_0 -2)))) (+ (- in_2_1) (+ (- in_0_1) (* in_1_1 -2))) (+ in_1_1 (* in_2_1 2)) (+ (+ in_1_2 (- in_1_0)) (+ (* in_2_2 2) (* in_2_0 -2))) (+ (- in_1_1) (* in_2_1 -2)))</t>
+          <t>(Vec (+ in_1_1 (* in_0_1 2)) (+ (+ in_1_2 (- in_1_0)) (+ (* in_0_2 2) (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (* in_0_0 -2)))))))))))))) (+ (- in_1_1) (* in_0_1 -2)) (+ in_2_1 (+ in_0_1 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (* in_1_1 2)))))))))))))) (+ (+ in_2_2 (- in_2_0)) (+ (+ in_0_2 (- in_0_0)) (+ (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (* in_1_2 2))))))))))) (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (* in_1_0 -2)))))))))))))) (+ (- in_2_1) (+ (- in_0_1) (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (* in_1_1 -2)))))))))))))) (+ in_1_1 (* in_2_1 2)) (+ (+ in_1_2 (- in_1_0)) (+ (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (* in_2_2 2)))))))))))) (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (* in_2_0 -2))))))))))))) (+ (- in_1_1) (* in_2_1 -2)))</t>
         </is>
       </c>
       <c r="E167" t="n">
         <v>9757</v>
       </c>
       <c r="F167" t="n">
-        <v>28403</v>
+        <v>28267</v>
       </c>
       <c r="G167" t="n">
-        <v>-191.1</v>
+        <v>-189.71</v>
       </c>
       <c r="H167" t="n">
         <v>40.57</v>
       </c>
       <c r="I167" t="n">
-        <v>2597.17</v>
+        <v>52.55</v>
       </c>
       <c r="J167" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K167" t="n">
-        <v>-1597.17</v>
+        <v>947.45</v>
       </c>
       <c r="L167" t="n">
         <v>75</v>
@@ -7477,29 +7477,29 @@
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>(Vec (+ in_1_1 (* in_0_1 2)) (+ (+ in_1_2 (- in_1_0)) (+ (* in_0_2 2) (* in_0_0 -2))) (+ (+ in_1_3 (- in_1_1)) (+ (* in_0_3 2) (* in_0_1 -2))) (+ (+ in_1_4 (- in_1_2)) (+ (* in_0_4 2) (* in_0_2 -2))) (+ (- in_1_3) (* in_0_3 -2)) (+ in_2_1 (+ in_0_1 (* in_1_1 2))) (+ (+ in_2_2 (- in_2_0)) (+ (+ in_0_2 (- in_0_0)) (+ (* in_1_2 2) (* in_1_0 -2)))) (+ (+ in_2_3 (- in_2_1)) (+ (+ in_0_3 (- in_0_1)) (+ (* in_1_3 2) (* in_1_1 -2)))) (+ (+ in_2_4 (- in_2_2)) (+ (+ in_0_4 (- in_0_2)) (+ (* in_1_4 2) (* in_1_2 -2)))) (+ (- in_2_3) (+ (- in_0_3) (* in_1_3 -2))) (+ in_3_1 (+ in_1_1 (* in_2_1 2))) (+ (+ in_3_2 (- in_3_0)) (+ (+ in_1_2 (- in_1_0)) (+ (* in_2_2 2) (* in_2_0 -2)))) (+ (+ in_3_3 (- in_3_1)) (+ (+ in_1_3 (- in_1_1)) (+ (* in_2_3 2) (* in_2_1 -2)))) (+ (+ in_3_4 (- in_3_2)) (+ (+ in_1_4 (- in_1_2)) (+ (* in_2_4 2) (* in_2_2 -2)))) (+ (- in_3_3) (+ (- in_1_3) (* in_2_3 -2))) (+ in_4_1 (+ in_2_1 (* in_3_1 2))) (+ (+ in_4_2 (- in_4_0)) (+ (+ in_2_2 (- in_2_0)) (+ (* in_3_2 2) (* in_3_0 -2)))) (+ (+ in_4_3 (- in_4_1)) (+ (+ in_2_3 (- in_2_1)) (+ (* in_3_3 2) (* in_3_1 -2)))) (+ (+ in_4_4 (- in_4_2)) (+ (+ in_2_4 (- in_2_2)) (+ (* in_3_4 2) (* in_3_2 -2)))) (+ (- in_4_3) (+ (- in_2_3) (* in_3_3 -2))) (+ in_3_1 (* in_4_1 2)) (+ (+ in_3_2 (- in_3_0)) (+ (* in_4_2 2) (* in_4_0 -2))) (+ (+ in_3_3 (- in_3_1)) (+ (* in_4_3 2) (* in_4_1 -2))) (+ (+ in_3_4 (- in_3_2)) (+ (* in_4_4 2) (* in_4_2 -2))) (+ (- in_3_3) (* in_4_3 -2)))</t>
+          <t>(Vec (+ in_1_1 (* in_0_1 2)) (+ (+ in_1_2 (- in_1_0)) (+ (* in_0_2 2) (* in_0_0 -2))) (+ (+ in_1_3 (- in_1_1)) (+ (* in_0_3 2) (* in_0_1 -2))) (+ (+ in_1_4 (- in_1_2)) (+ (* in_0_4 2) (* in_0_2 -2))) (+ (- in_1_3) (* in_0_3 -2)) (+ in_2_1 (+ in_0_1 (* in_1_1 2))) (+ (+ in_2_2 (- in_2_0)) (+ (+ in_0_2 (- in_0_0)) (+ (+ 0 (+ 0 (+ 0 (* in_1_2 2)))) (+ 0 (+ 0 (+ 0 (* in_1_0 -2))))))) (+ (+ in_2_3 (- in_2_1)) (+ (+ in_0_3 (- in_0_1)) (+ (+ 0 (+ 0 (+ 0 (* in_1_3 2)))) (+ 0 (+ 0 (+ 0 (* in_1_1 -2))))))) (+ (+ in_2_4 (- in_2_2)) (+ (+ in_0_4 (- in_0_2)) (+ (+ 0 (+ 0 (+ 0 (* in_1_4 2)))) (+ 0 (+ 0 (+ 0 (* in_1_2 -2))))))) (+ (- in_2_3) (+ (- in_0_3) (* in_1_3 -2))) (+ in_3_1 (+ in_1_1 (* in_2_1 2))) (+ (+ in_3_2 (- in_3_0)) (+ (+ in_1_2 (- in_1_0)) (+ (+ 0 (+ 0 (+ 0 (* in_2_2 2)))) (+ 0 (+ 0 (+ 0 (* in_2_0 -2))))))) (+ (+ in_3_3 (- in_3_1)) (+ (+ in_1_3 (- in_1_1)) (+ (+ 0 (+ 0 (+ 0 (* in_2_3 2)))) (+ 0 (+ 0 (+ 0 (* in_2_1 -2))))))) (+ (+ in_3_4 (- in_3_2)) (+ (+ in_1_4 (- in_1_2)) (+ (+ 0 (+ 0 (+ 0 (* in_2_4 2)))) (+ 0 (+ 0 (+ 0 (* in_2_2 -2))))))) (+ (- in_3_3) (+ (- in_1_3) (* in_2_3 -2))) (+ in_4_1 (+ in_2_1 (+ 0 (+ 0 (+ 0 (+ 0 (* in_3_1 2))))))) (+ (+ in_4_2 (- in_4_0)) (+ (+ in_2_2 (- in_2_0)) (+ (+ 0 (+ 0 (+ 0 (* in_3_2 2)))) (+ 0 (+ 0 (* in_3_0 -2)))))) (+ (+ in_4_3 (- in_4_1)) (+ (+ in_2_3 (- in_2_1)) (+ (+ 0 (+ 0 (* in_3_3 2))) (+ 0 (+ 0 (* in_3_1 -2)))))) (+ (+ in_4_4 (- in_4_2)) (+ (+ in_2_4 (- in_2_2)) (+ (+ 0 (+ 0 (* in_3_4 2))) (+ 0 (+ 0 (* in_3_2 -2)))))) (+ (- in_4_3) (+ (- in_2_3) (+ 0 (+ 0 (+ 0 (* in_3_3 -2)))))) (+ in_3_1 (* in_4_1 2)) (+ (+ in_3_2 (- in_3_0)) (+ (+ 0 (+ 0 (+ 0 (* in_4_2 2)))) (+ 0 (+ 0 (+ 0 (* in_4_0 -2)))))) (+ (+ in_3_3 (- in_3_1)) (+ (+ 0 (+ 0 (+ 0 (* in_4_3 2)))) (+ 0 (+ 0 (+ 0 (* in_4_1 -2)))))) (+ (+ in_3_4 (- in_3_2)) (+ (+ 0 (+ 0 (+ 0 (* in_4_4 2)))) (+ 0 (+ 0 (+ 0 (* in_4_2 -2)))))) (+ (- in_3_3) (* in_4_3 -2)))</t>
         </is>
       </c>
       <c r="E168" t="n">
         <v>37757</v>
       </c>
       <c r="F168" t="n">
-        <v>37757</v>
+        <v>56260</v>
       </c>
       <c r="G168" t="n">
-        <v>0</v>
+        <v>-49.01</v>
       </c>
       <c r="H168" t="n">
         <v>40.57</v>
       </c>
       <c r="I168" t="n">
-        <v>40.57</v>
+        <v>44.16</v>
       </c>
       <c r="J168" t="b">
         <v>0</v>
       </c>
       <c r="K168" t="n">
-        <v>959.4299999999999</v>
+        <v>955.84</v>
       </c>
       <c r="L168" t="n">
         <v>75</v>
@@ -7519,29 +7519,29 @@
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>(Vec (+ (+ (* a_0_0 b_0_0) (* a_0_1 b_1_0)) (+ (* a_0_2 b_2_0) (* a_0_3 b_3_0))) (+ (+ (* a_0_0 b_0_1) (* a_0_1 b_1_1)) (+ (* a_0_2 b_2_1) (* a_0_3 b_3_1))) (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (* a_0_0 b_0_2) (* a_0_1 b_1_2)) (+ (* a_0_2 b_2_2) (* a_0_3 b_3_2))) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) (+ (+ (* a_0_0 b_0_3) (* a_0_1 b_1_3)) (+ (* a_0_2 b_2_3) (* a_0_3 b_3_3))) (+ (+ (* a_1_0 b_0_0) (* a_1_1 b_1_0)) (+ (* a_1_2 b_2_0) (* a_1_3 b_3_0))) (+ (+ (* a_1_0 b_0_1) (* a_1_1 b_1_1)) (+ (* a_1_2 b_2_1) (* a_1_3 b_3_1))) (+ (+ (* a_1_0 b_0_2) (* a_1_1 b_1_2)) (+ (* a_1_2 b_2_2) (* a_1_3 b_3_2))) (+ (+ (* a_1_0 b_0_3) (* a_1_1 b_1_3)) (+ (* a_1_2 b_2_3) (* a_1_3 b_3_3))) (+ (+ (* a_2_0 b_0_0) (* a_2_1 b_1_0)) (+ (* a_2_2 b_2_0) (* a_2_3 b_3_0))) (+ (+ (* a_2_0 b_0_1) (* a_2_1 b_1_1)) (+ (* a_2_2 b_2_1) (* a_2_3 b_3_1))) (+ (+ (* a_2_0 b_0_2) (* a_2_1 b_1_2)) (+ (* a_2_2 b_2_2) (* a_2_3 b_3_2))) (+ (+ (* a_2_0 b_0_3) (* a_2_1 b_1_3)) (+ (* a_2_2 b_2_3) (* a_2_3 b_3_3))) (+ (+ (* a_3_0 b_0_0) (* a_3_1 b_1_0)) (+ (* a_3_2 b_2_0) (* a_3_3 b_3_0))) (+ (+ (* a_3_0 b_0_1) (* a_3_1 b_1_1)) (+ (* a_3_2 b_2_1) (* a_3_3 b_3_1))) (+ (+ (* a_3_0 b_0_2) (* a_3_1 b_1_2)) (+ (* a_3_2 b_2_2) (* a_3_3 b_3_2))) (+ (+ (* a_3_0 b_0_3) (* a_3_1 b_1_3)) (+ (* a_3_2 b_2_3) (* a_3_3 b_3_3))))</t>
+          <t>(Vec (+ (+ (* a_0_0 b_0_0) (* a_0_1 b_1_0)) (+ (* a_0_2 b_2_0) (* a_0_3 b_3_0))) (+ (+ (* a_0_0 b_0_1) (* a_0_1 b_1_1)) (+ (* a_0_2 b_2_1) (* a_0_3 b_3_1))) (+ (+ (* a_0_0 b_0_2) (* a_0_1 b_1_2)) (+ (* a_0_2 b_2_2) (+ 0 (+ 0 (* a_0_3 b_3_2))))) (+ (+ (+ 0 (+ 0 (* a_0_0 b_0_3))) (+ 0 (+ 0 (* a_0_1 b_1_3)))) (+ (+ 0 (+ 0 (* a_0_2 b_2_3))) (+ 0 (+ 0 (* a_0_3 b_3_3))))) (+ (+ (+ 0 (+ 0 (* a_1_0 b_0_0))) (+ 0 (+ 0 (* a_1_1 b_1_0)))) (+ (+ 0 (+ 0 (* a_1_2 b_2_0))) (+ 0 (+ 0 (* a_1_3 b_3_0))))) (+ (+ (+ 0 (+ 0 (* a_1_0 b_0_1))) (+ 0 (+ 0 (* a_1_1 b_1_1)))) (+ (+ 0 (+ 0 (* a_1_2 b_2_1))) (+ 0 (+ 0 (* a_1_3 b_3_1))))) (+ (+ (+ 0 (+ 0 (* a_1_0 b_0_2))) (+ 0 (+ 0 (* a_1_1 b_1_2)))) (+ (+ 0 (+ 0 (* a_1_2 b_2_2))) (+ 0 (+ 0 (* a_1_3 b_3_2))))) (+ (+ (+ 0 (+ 0 (* a_1_0 b_0_3))) (+ 0 (+ 0 (* a_1_1 b_1_3)))) (+ (+ 0 (+ 0 (* a_1_2 b_2_3))) (+ 0 (+ 0 (* a_1_3 b_3_3))))) (+ (+ (+ 0 (* a_2_0 b_0_0)) (+ 0 (* a_2_1 b_1_0))) (+ (+ 0 (* a_2_2 b_2_0)) (+ 0 (* a_2_3 b_3_0)))) (+ (+ (+ 0 (* a_2_0 b_0_1)) (+ 0 (* a_2_1 b_1_1))) (+ (+ 0 (* a_2_2 b_2_1)) (+ 0 (* a_2_3 b_3_1)))) (+ (+ (+ 0 (* a_2_0 b_0_2)) (+ 0 (* a_2_1 b_1_2))) (+ (+ 0 (* a_2_2 b_2_2)) (+ 0 (* a_2_3 b_3_2)))) (+ (+ (+ 0 (* a_2_0 b_0_3)) (+ 0 (* a_2_1 b_1_3))) (+ (+ 0 (* a_2_2 b_2_3)) (+ 0 (* a_2_3 b_3_3)))) (+ (+ (+ 0 (* a_3_0 b_0_0)) (+ 0 (* a_3_1 b_1_0))) (+ (+ 0 (* a_3_2 b_2_0)) (+ 0 (* a_3_3 b_3_0)))) (+ (+ (+ 0 (* a_3_0 b_0_1)) (+ 0 (* a_3_1 b_1_1))) (+ (+ 0 (* a_3_2 b_2_1)) (+ 0 (* a_3_3 b_3_1)))) (+ (+ (+ 0 (* a_3_0 b_0_2)) (+ 0 (* a_3_1 b_1_2))) (+ (+ 0 (* a_3_2 b_2_2)) (+ 0 (* a_3_3 b_3_2)))) (+ (+ (+ 0 (* a_3_0 b_0_3)) (+ 0 (* a_3_1 b_1_3))) (+ (+ 0 (* a_3_2 b_2_3)) (+ 0 (* a_3_3 b_3_3)))))</t>
         </is>
       </c>
       <c r="E169" t="n">
         <v>28006</v>
       </c>
       <c r="F169" t="n">
-        <v>46580</v>
+        <v>46508</v>
       </c>
       <c r="G169" t="n">
-        <v>-66.31999999999999</v>
+        <v>-66.06</v>
       </c>
       <c r="H169" t="n">
         <v>39.37</v>
       </c>
       <c r="I169" t="n">
-        <v>128.02</v>
+        <v>41.77</v>
       </c>
       <c r="J169" t="b">
         <v>0</v>
       </c>
       <c r="K169" t="n">
-        <v>871.98</v>
+        <v>958.23</v>
       </c>
       <c r="L169" t="n">
         <v>75</v>
@@ -7561,29 +7561,29 @@
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>(Vec (+ (* (+ (* (+ (* o4 (- 1 c34)) (* c34 o3)) (- 1 c23)) (* c23 (+ (* o4 (- 1 c24)) (* c24 o2)))) (- 1 c12)) (* c12 (+ (* (+ (* o4 (- 1 c34)) (* c34 o3)) (- 1 c13)) (* c13 (+ (* o4 (- 1 c14)) (* c14 o1)))))))</t>
+          <t>(Vec (+ (* (+ (* (+ (* o4 (- 1 c34)) (* c34 o3)) (- 1 c23)) (* c23 (+ (* o4 (- 1 c24)) (* c24 o2)))) (- 1 c12)) (* c12 (+ (* (+ (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (* o4 (- 1 c34))))))))))))))))))))) (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (* c34 o3))))))))))))))))))))) (- 1 c13)) (* c13 (+ (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (* o4 (- 1 c14)))))))))))))))))))) (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (* c14 o1)))))))))))))))))))))))))</t>
         </is>
       </c>
       <c r="E170" t="n">
         <v>7012</v>
       </c>
       <c r="F170" t="n">
-        <v>7012</v>
+        <v>25531</v>
       </c>
       <c r="G170" t="n">
-        <v>0</v>
+        <v>-264.1</v>
       </c>
       <c r="H170" t="n">
         <v>110.93</v>
       </c>
       <c r="I170" t="n">
-        <v>110.93</v>
+        <v>133.69</v>
       </c>
       <c r="J170" t="b">
         <v>0</v>
       </c>
       <c r="K170" t="n">
-        <v>889.0700000000001</v>
+        <v>866.3099999999999</v>
       </c>
       <c r="L170" t="n">
         <v>75</v>
@@ -7645,29 +7645,29 @@
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>(VecMul (Vec (* (* (+ (* (* x10106 x10108) x10110) x10112) x10115) (* x10117 x10119)) (+ (+ x10121 (* x10125 (+ (+ (* (* x10146 x10147) (* (+ x10149 x10150) x10152)) (* (* (* x10132 x10133) (+ x10135 x10136)) (+ (* x10139 x10140) x10142))) (+ (+ x10154 (* (* x10159 (+ (+ x10162 x10163) x10165)) x10167)) (+ (+ x10170 x10173) (+ x10176 x10178)))))) (+ x10181 x10183))) (&lt;&lt; (Vec (* (* (+ (* (* x10106 x10108) x10110) x10112) x10115) (* x10117 x10119)) (+ (+ x10121 (* x10125 (+ (+ (* (* x10146 x10147) (* (+ x10149 x10150) x10152)) (* (* (* x10132 x10133) (+ x10135 x10136)) (+ (* x10139 x10140) x10142))) (+ (+ x10154 (* (* x10159 (+ (+ x10162 x10163) x10165)) x10167)) (+ (+ x10170 x10173) (+ x10176 x10178)))))) (+ x10181 x10183))) 1))</t>
+          <t>(Vec (* (* (* (+ (* (* x10106 x10108) x10110) x10112) x10115) (* x10117 x10119)) (+ (+ x10121 (* x10125 (+ (+ (* (* (* x10132 x10133) (+ x10135 x10136)) (+ (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (* x10139 x10140)))))))))))))))))))))))))))))))))))))) x10142)) (* (* x10146 x10147) (* (+ x10149 x10150) x10152))) (+ (+ x10154 (* (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (* x10159 (+ (+ x10162 x10163) x10165))))))))))))))))))))))))))))))))))))))) x10167)) (+ (+ x10170 x10173) (+ x10176 x10178)))))) (+ x10181 x10183))))</t>
         </is>
       </c>
       <c r="E172" t="n">
         <v>8018</v>
       </c>
       <c r="F172" t="n">
-        <v>7920</v>
+        <v>26555</v>
       </c>
       <c r="G172" t="n">
-        <v>1.22</v>
+        <v>-231.19</v>
       </c>
       <c r="H172" t="n">
         <v>182.49</v>
       </c>
       <c r="I172" t="n">
-        <v>183.69</v>
+        <v>226.81</v>
       </c>
       <c r="J172" t="b">
         <v>0</v>
       </c>
       <c r="K172" t="n">
-        <v>816.3099999999999</v>
+        <v>773.1900000000001</v>
       </c>
       <c r="L172" t="n">
         <v>75</v>
@@ -7687,29 +7687,29 @@
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>(VecMul (Vec (+ (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* x9604 x9605) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) (* x9607 x9608)) (* (* x9611 x9612) (* x9614 x9615))) (* (* (* x9619 x9620) (* x9622 x9623)) (* (* x9626 x9627) (* x9629 x9630)))) (+ (* (* (* x9634 x9635) (* x9637 x9638)) (* (* x9641 x9642) (* x9644 x9645))) (* (* (* x9649 x9650) (* x9652 x9653)) (* (* x9656 x9657) (* x9659 x9660))))) (&lt;&lt; (Vec (+ (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* x9604 x9605) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) (* x9607 x9608)) (* (* x9611 x9612) (* x9614 x9615))) (* (* (* x9619 x9620) (* x9622 x9623)) (* (* x9626 x9627) (* x9629 x9630)))) (+ (* (* (* x9634 x9635) (* x9637 x9638)) (* (* x9641 x9642) (* x9644 x9645))) (* (* (* x9649 x9650) (* x9652 x9653)) (* (* x9656 x9657) (* x9659 x9660))))) 1))</t>
+          <t>(Vec (* (+ (* (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (* (* x9604 x9605) (* x9607 x9608)))))))))))) (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (* (* x9611 x9612) (* x9614 x9615))))))))))))) (* (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (* (* x9619 x9620) (* x9622 x9623))))))))))) (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (* (* x9626 x9627) (* x9629 x9630))))))))))))) (+ (* (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (* (* x9634 x9635) (* x9637 x9638))))))))))) (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (* (* x9641 x9642) (* x9644 x9645)))))))))))) (* (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (* (* x9649 x9650) (* x9652 x9653))))))))))) (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (* (* x9656 x9657) (* x9659 x9660)))))))))))))))</t>
         </is>
       </c>
       <c r="E173" t="n">
         <v>7761</v>
       </c>
       <c r="F173" t="n">
-        <v>26059</v>
+        <v>26271</v>
       </c>
       <c r="G173" t="n">
-        <v>-235.77</v>
+        <v>-238.5</v>
       </c>
       <c r="H173" t="n">
         <v>141.92</v>
       </c>
       <c r="I173" t="n">
-        <v>2667.53</v>
+        <v>153.9</v>
       </c>
       <c r="J173" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K173" t="n">
-        <v>-1667.53</v>
+        <v>846.1</v>
       </c>
       <c r="L173" t="n">
         <v>75</v>
@@ -7729,17 +7729,17 @@
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>(VecAdd (VecAdd (VecAdd (Vec 0 in_1_2 0 in_2_1 in_2_2 in_2_2 0 in_2_2 0) (Vec in_1_1 in_1_1 in_1_2 in_2_0 (+ in_2_1 in_2_0) in_2_1 in_2_1 in_2_1 in_2_2)) (VecAdd (Vec 0 in_1_0 0 in_1_1 in_1_2 in_1_2 0 in_2_0 0) (Vec in_1_0 in_0_2 in_1_1 in_1_0 in_1_1 in_1_1 in_2_0 in_1_2 in_2_1))) (VecAdd (Vec in_0_1 in_0_1 in_0_2 in_0_1 (+ in_1_0 in_0_2) in_0_2 in_1_1 in_1_1 in_1_2) (Vec in_0_0 in_0_0 in_0_1 in_0_0 (+ in_0_1 in_0_0) in_0_1 in_1_0 in_1_0 in_1_1)))</t>
+          <t>(Vec ( + ( + in_1_1 in_1_0 ) ( + in_0_1 in_0_0 ) ) ( + ( + ( + in_1_2 in_1_1 ) ( + in_1_0 in_0_2 ) ) ( + in_0_1 in_0_0 ) ) ( + ( + in_1_2 in_1_1 ) ( + in_0_2 in_0_1 ) ) ( + ( + ( + in_2_1 in_2_0 ) ( + in_1_1 in_1_0 ) ) ( + in_0_1 in_0_0 ) ) ( + ( + ( + in_2_2 ( + in_2_1 in_2_0 ) ) ( + in_1_2 in_1_1 ) ) ( + ( + in_1_0 in_0_2 ) ( + in_0_1 in_0_0 ) ) ) ( + ( + ( + in_2_2 in_2_1 ) ( + in_1_2 in_1_1 ) ) ( + in_0_2 in_0_1 ) ) ( + ( + in_2_1 in_2_0 ) ( + in_1_1 in_1_0 ) ) ( + ( + ( + in_2_2 in_2_1 ) ( + in_2_0 in_1_2 ) ) ( + in_1_1 in_1_0 ) ) ( + ( + in_2_2 in_2_1 ) ( + in_1_2 in_1_1 ) ) )</t>
         </is>
       </c>
       <c r="E174" t="n">
         <v>10006</v>
       </c>
       <c r="F174" t="n">
-        <v>761</v>
+        <v>10006</v>
       </c>
       <c r="G174" t="n">
-        <v>92.39</v>
+        <v>0</v>
       </c>
       <c r="H174" t="n">
         <v>7.19</v>
@@ -7754,7 +7754,7 @@
         <v>8999992.810000001</v>
       </c>
       <c r="L174" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
     </row>
     <row r="175">
@@ -7771,29 +7771,29 @@
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>(Vec (+ (+ in_1_1 in_1_0) (+ in_0_1 in_0_0)) (+ (+ (+ in_1_2 in_1_1) (+ in_1_0 in_0_2)) (+ in_0_1 in_0_0)) (+ (+ (+ in_1_3 in_1_2) (+ in_1_1 in_0_3)) (+ in_0_2 in_0_1)) (+ (+ (+ in_1_4 in_1_3) (+ in_1_2 in_0_4)) (+ in_0_3 in_0_2)) (+ (+ in_1_4 in_1_3) (+ in_0_4 in_0_3)) (+ (+ (+ in_2_1 in_2_0) (+ in_1_1 in_1_0)) (+ in_0_1 in_0_0)) (+ (+ (+ in_2_2 (+ in_2_1 in_2_0)) (+ in_1_2 in_1_1)) (+ (+ in_1_0 in_0_2) (+ in_0_1 in_0_0))) (+ (+ (+ in_2_3 (+ in_2_2 in_2_1)) (+ in_1_3 in_1_2)) (+ (+ in_1_1 in_0_3) (+ in_0_2 in_0_1))) (+ (+ (+ in_2_4 (+ in_2_3 in_2_2)) (+ in_1_4 in_1_3)) (+ (+ in_1_2 in_0_4) (+ in_0_3 in_0_2))) (+ (+ (+ in_2_4 in_2_3) (+ in_1_4 in_1_3)) (+ in_0_4 in_0_3)) (+ (+ (+ in_3_1 in_3_0) (+ in_2_1 in_2_0)) (+ in_1_1 in_1_0)) (+ (+ (+ in_3_2 (+ in_3_1 in_3_0)) (+ in_2_2 in_2_1)) (+ (+ in_2_0 in_1_2) (+ in_1_1 in_1_0))) (+ (+ (+ in_3_3 (+ in_3_2 in_3_1)) (+ in_2_3 in_2_2)) (+ (+ in_2_1 in_1_3) (+ in_1_2 in_1_1))) (+ (+ (+ in_3_4 (+ in_3_3 in_3_2)) (+ in_2_4 in_2_3)) (+ (+ in_2_2 in_1_4) (+ in_1_3 in_1_2))) (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (+ (+ (+ in_3_4 in_3_3) (+ in_2_4 in_2_3)) (+ in_1_4 in_1_3)) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) (+ (+ (+ in_4_1 in_4_0) (+ in_3_1 in_3_0)) (+ in_2_1 in_2_0)) (+ (+ (+ in_4_2 (+ in_4_1 in_4_0)) (+ in_3_2 in_3_1)) (+ (+ in_3_0 in_2_2) (+ in_2_1 in_2_0))) (+ (+ (+ in_4_3 (+ in_4_2 in_4_1)) (+ in_3_3 in_3_2)) (+ (+ in_3_1 in_2_3) (+ in_2_2 in_2_1))) (+ (+ (+ in_4_4 (+ in_4_3 in_4_2)) (+ in_3_4 in_3_3)) (+ (+ in_3_2 in_2_4) (+ in_2_3 in_2_2))) (+ (+ (+ in_4_4 in_4_3) (+ in_3_4 in_3_3)) (+ in_2_4 in_2_3)) (+ (+ in_4_1 in_4_0) (+ in_3_1 in_3_0)) (+ (+ (+ in_4_2 in_4_1) (+ in_4_0 in_3_2)) (+ in_3_1 in_3_0)) (+ (+ (+ in_4_3 in_4_2) (+ in_4_1 in_3_3)) (+ in_3_2 in_3_1)) (+ (+ (+ in_4_4 in_4_3) (+ in_4_2 in_3_4)) (+ in_3_3 in_3_2)) (+ (+ in_4_4 in_4_3) (+ in_3_4 in_3_3)))</t>
+          <t>(Vec (+ (+ in_1_1 in_1_0) (+ in_0_1 in_0_0)) (+ (+ (+ in_1_2 in_1_1) (+ in_1_0 in_0_2)) (+ in_0_1 in_0_0)) (+ (+ (+ in_1_3 in_1_2) (+ in_1_1 in_0_3)) (+ in_0_2 in_0_1)) (+ (+ (+ in_1_4 in_1_3) (+ in_1_2 in_0_4)) (+ in_0_3 in_0_2)) (+ (+ in_1_4 in_1_3) (+ in_0_4 in_0_3)) (+ (+ (+ in_2_1 in_2_0) (+ in_1_1 in_1_0)) (+ in_0_1 in_0_0)) (+ (+ (+ in_2_2 (+ in_2_1 in_2_0)) (+ in_1_2 in_1_1)) (+ (+ in_1_0 in_0_2) (+ in_0_1 in_0_0))) (+ (+ (+ in_2_3 (+ in_2_2 in_2_1)) (+ in_1_3 in_1_2)) (+ (+ in_1_1 in_0_3) (+ in_0_2 in_0_1))) (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (+ (+ (+ in_2_4 (+ in_2_3 in_2_2)) (+ in_1_4 in_1_3)) (+ (+ in_1_2 in_0_4) (+ in_0_3 in_0_2))) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) (+ (+ (+ in_2_4 in_2_3) (+ in_1_4 in_1_3)) (+ in_0_4 in_0_3)) (+ (+ (+ in_3_1 in_3_0) (+ in_2_1 in_2_0)) (+ in_1_1 in_1_0)) (+ (+ (+ in_3_2 (+ in_3_1 in_3_0)) (+ in_2_2 in_2_1)) (+ (+ in_2_0 in_1_2) (+ in_1_1 in_1_0))) (+ (+ (+ in_3_3 (+ in_3_2 in_3_1)) (+ in_2_3 in_2_2)) (+ (+ in_2_1 in_1_3) (+ in_1_2 in_1_1))) (+ (+ (+ in_3_4 (+ in_3_3 in_3_2)) (+ in_2_4 in_2_3)) (+ (+ in_2_2 in_1_4) (+ in_1_3 in_1_2))) (+ (+ (+ in_3_4 in_3_3) (+ in_2_4 in_2_3)) (+ in_1_4 in_1_3)) (+ (+ (+ in_4_1 in_4_0) (+ in_3_1 in_3_0)) (+ in_2_1 in_2_0)) (+ (+ (+ in_4_2 (+ in_4_1 in_4_0)) (+ in_3_2 in_3_1)) (+ (+ in_3_0 in_2_2) (+ in_2_1 in_2_0))) (+ (+ (+ in_4_3 (+ in_4_2 in_4_1)) (+ in_3_3 in_3_2)) (+ (+ in_3_1 in_2_3) (+ in_2_2 in_2_1))) (+ (+ (+ in_4_4 (+ in_4_3 in_4_2)) (+ in_3_4 in_3_3)) (+ (+ in_3_2 in_2_4) (+ in_2_3 in_2_2))) (+ (+ (+ in_4_4 in_4_3) (+ in_3_4 in_3_3)) (+ in_2_4 in_2_3)) (+ (+ in_4_1 in_4_0) (+ in_3_1 in_3_0)) (+ (+ (+ in_4_2 in_4_1) (+ in_4_0 in_3_2)) (+ in_3_1 in_3_0)) (+ (+ (+ in_4_3 in_4_2) (+ in_4_1 in_3_3)) (+ in_3_2 in_3_1)) (+ (+ (+ in_4_4 in_4_3) (+ in_4_2 in_3_4)) (+ in_3_3 in_3_2)) (+ (+ in_4_4 in_4_3) (+ in_3_4 in_3_3)))</t>
         </is>
       </c>
       <c r="E175" t="n">
         <v>36006</v>
       </c>
       <c r="F175" t="n">
-        <v>54653</v>
+        <v>54580</v>
       </c>
       <c r="G175" t="n">
-        <v>-51.79</v>
+        <v>-51.59</v>
       </c>
       <c r="H175" t="n">
         <v>7.19</v>
       </c>
       <c r="I175" t="n">
-        <v>2564.98</v>
+        <v>95.84</v>
       </c>
       <c r="J175" t="b">
         <v>0</v>
       </c>
       <c r="K175" t="n">
-        <v>8997435.02</v>
+        <v>8999904.16</v>
       </c>
       <c r="L175" t="n">
         <v>75</v>
@@ -7813,29 +7813,29 @@
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>(Vec (+ v2_0 (+ 2 (* v1_0 5))) (+ v2_1 (+ 2 (* v1_1 5))) (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ v2_2 (+ 2 (* v1_2 5))) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) (+ v2_3 (+ 2 (* v1_3 5))) (+ v2_4 (+ 2 (* v1_4 5))) (+ v2_5 (+ 2 (* v1_5 5))) (+ v2_6 (+ 2 (* v1_6 5))) (+ v2_7 (+ 2 (* v1_7 5))))</t>
+          <t>(Vec (+ v2_0 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (+ 2 (* v1_0 5)))))))))) (+ v2_1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ 2 (* v1_1 5)) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0))))))))) (+ v2_2 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (+ 2 (* v1_2 5)))))))))) (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (+ v2_3 (+ 2 (* v1_3 5))))))))))) (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (+ v2_4 (* 1 (+ 2 (* v1_4 5)))))))))))) (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (+ v2_5 (* 1 (+ 2 (* v1_5 5)))))))))))) (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (+ v2_6 (+ 2 (* v1_6 5)))))))))) (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (+ v2_7 (+ 2 (* v1_7 5)))))))))))</t>
         </is>
       </c>
       <c r="E176" t="n">
         <v>6006</v>
       </c>
       <c r="F176" t="n">
-        <v>24580</v>
+        <v>24535</v>
       </c>
       <c r="G176" t="n">
-        <v>-309.26</v>
+        <v>-308.51</v>
       </c>
       <c r="H176" t="n">
         <v>39.37</v>
       </c>
       <c r="I176" t="n">
-        <v>128.02</v>
+        <v>363.78</v>
       </c>
       <c r="J176" t="b">
         <v>0</v>
       </c>
       <c r="K176" t="n">
-        <v>8999871.98</v>
+        <v>8999636.220000001</v>
       </c>
       <c r="L176" t="n">
         <v>75</v>
@@ -7855,29 +7855,29 @@
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>(Vec (+ v2_0 (+ 2 (* v1_0 5))) (+ v2_1 (+ 2 (* v1_1 5))) (+ (+ (+ (+ (+ (+ (+ v2_2 (+ 2 (* v1_2 5))) (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- 0))))))))))))))))))))))) (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- 0)))))))))))))))))))))))) (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- 0)))))))))))))))))))))))) 0) 0) 0) (+ v2_3 (+ 2 (* v1_3 5))) (+ v2_4 (+ 2 (* v1_4 5))) (+ v2_5 (+ 2 (* v1_5 5))) (+ v2_6 (+ 2 (* v1_6 5))) (+ v2_7 (+ 2 (* v1_7 5))) (+ v2_8 (+ 2 (* v1_8 5))) (+ v2_9 (+ 2 (* v1_9 5))) (+ v2_10 (+ 2 (* v1_10 5))) (+ v2_11 (+ 2 (* v1_11 5))) (+ v2_12 (+ 2 (* v1_12 5))) (+ v2_13 (+ 2 (* v1_13 5))) (+ v2_14 (+ 2 (* v1_14 5))) (+ v2_15 (+ 2 (* v1_15 5))) (+ v2_16 (+ 2 (* v1_16 5))) (+ v2_17 (+ 2 (* v1_17 5))) (+ v2_18 (+ 2 (* v1_18 5))) (+ v2_19 (+ 2 (* v1_19 5))) (+ v2_20 (+ 2 (* v1_20 5))) (+ v2_21 (+ 2 (* v1_21 5))) (+ v2_22 (+ 2 (* v1_22 5))) (+ v2_23 (+ 2 (* v1_23 5))) (+ v2_24 (+ 2 (* v1_24 5))) (+ v2_25 (+ 2 (* v1_25 5))) (+ v2_26 (+ 2 (* v1_26 5))) (+ v2_27 (+ 2 (* v1_27 5))) (+ v2_28 (+ 2 (* v1_28 5))) (+ v2_29 (+ 2 (* v1_29 5))) (+ v2_30 (+ 2 (* v1_30 5))) (+ v2_31 (+ 2 (* v1_31 5))))</t>
+          <t>(Vec (+ v2_0 (* 1 (* 1 (+ 2 (* v1_0 5))))) (+ v2_1 (* 1 (* 1 (+ 2 (* v1_1 5))))) (+ v2_2 (* 1 (* 1 (+ 2 (* v1_2 5))))) (* 1 (* 1 (* 1 (+ v2_3 (+ 2 (* v1_3 5)))))) (* 1 (* 1 (* 1 (+ v2_4 (+ 2 (* v1_4 5)))))) (* 1 (* 1 (* 1 (+ v2_5 (+ 2 (* v1_5 5)))))) (* 1 (* 1 (* 1 (+ v2_6 (+ 2 (* v1_6 5)))))) (* 1 (* 1 (* 1 (+ v2_7 (+ 2 (* v1_7 5)))))) (* 1 (* 1 (* 1 (+ v2_8 (+ 2 (* v1_8 5)))))) (* 1 (* 1 (* 1 (+ v2_9 (+ 2 (* v1_9 5)))))) (* 1 (* 1 (* 1 (+ v2_10 (+ 2 (* v1_10 5)))))) (* 1 (* 1 (* 1 (+ v2_11 (+ 2 (* v1_11 5)))))) (* 1 (* 1 (* 1 (+ v2_12 (+ 2 (* v1_12 5)))))) (* 1 (* 1 (+ v2_13 (+ 2 (* v1_13 5))))) (* 1 (* 1 (+ v2_14 (+ 2 (* v1_14 5))))) (* 1 (* 1 (+ v2_15 (+ 2 (* v1_15 5))))) (* 1 (* 1 (+ v2_16 (+ 2 (* v1_16 5))))) (* 1 (* 1 (+ v2_17 (+ 2 (* v1_17 5))))) (* 1 (* 1 (+ v2_18 (+ 2 (* v1_18 5))))) (* 1 (* 1 (+ v2_19 (+ 2 (* v1_19 5))))) (* 1 (* 1 (+ v2_20 (+ 2 (* v1_20 5))))) (* 1 (* 1 (+ v2_21 (+ 2 (* v1_21 5))))) (* 1 (* 1 (+ v2_22 (+ 2 (* v1_22 5))))) (* 1 (* 1 (+ v2_23 (+ 2 (* v1_23 5))))) (* 1 (* 1 (+ v2_24 (+ 2 (* v1_24 5))))) (* 1 (* 1 (+ v2_25 (+ 2 (* v1_25 5))))) (* 1 (* 1 (+ v2_26 (+ 2 (* v1_26 5))))) (* 1 (* 1 (+ v2_27 (+ 2 (* v1_27 5))))) (* 1 (* 1 (+ v2_28 (+ 2 (* v1_28 5))))) (* 1 (* 1 (+ v2_29 (+ 2 (* v1_29 5))))) (* 1 (* 1 (+ v2_30 (+ 2 (* v1_30 5))))) (* 1 (* 1 (+ v2_31 (+ 2 (* v1_31 5))))))</t>
         </is>
       </c>
       <c r="E177" t="n">
         <v>24006</v>
       </c>
       <c r="F177" t="n">
-        <v>42531</v>
+        <v>42512</v>
       </c>
       <c r="G177" t="n">
-        <v>-77.17</v>
+        <v>-77.09</v>
       </c>
       <c r="H177" t="n">
         <v>39.37</v>
       </c>
       <c r="I177" t="n">
-        <v>69.31999999999999</v>
+        <v>143.12</v>
       </c>
       <c r="J177" t="b">
         <v>0</v>
       </c>
       <c r="K177" t="n">
-        <v>8999930.68</v>
+        <v>8999856.880000001</v>
       </c>
       <c r="L177" t="n">
         <v>75</v>
@@ -7897,29 +7897,29 @@
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>(Vec (+ (+ (- (+ v1_0 v2_0) (* (* v1_0 v2_0) 2)) (- (+ v1_1 v2_1) (* 2 (* v1_1 v2_1)))) (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (- (+ v1_2 v2_2) (* 2 (* v1_2 v2_2))) (- (+ v1_3 v2_3) (* 2 (* v1_3 v2_3)))) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0)))</t>
+          <t>(Vec (+ (+ (- (+ v1_0 v2_0) (* (* v1_0 v2_0) 2)) (- (+ v1_1 v2_1) (* 2 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (* v1_1 v2_1)))))))))))))))))))))))))))))))))))))))))))))))))))))))) (+ (- (+ v1_2 v2_2) (* 2 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (* v1_2 v2_2)))))))))))))) (- (+ v1_3 v2_3) (* 2 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (* v1_3 v2_3)))))))))))))))))</t>
         </is>
       </c>
       <c r="E178" t="n">
         <v>4759</v>
       </c>
       <c r="F178" t="n">
-        <v>23333</v>
+        <v>23311</v>
       </c>
       <c r="G178" t="n">
-        <v>-390.29</v>
+        <v>-389.83</v>
       </c>
       <c r="H178" t="n">
         <v>75.15000000000001</v>
       </c>
       <c r="I178" t="n">
-        <v>163.8</v>
+        <v>137.45</v>
       </c>
       <c r="J178" t="b">
         <v>0</v>
       </c>
       <c r="K178" t="n">
-        <v>8999836.199999999</v>
+        <v>8999862.550000001</v>
       </c>
       <c r="L178" t="n">
         <v>75</v>
@@ -7939,29 +7939,29 @@
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>(Vec (+ (+ (+ (- (+ v1_0 v2_0) (* (* v1_0 v2_0) 2)) (- (+ v1_1 v2_1) (* 2 (* v1_1 v2_1)))) (+ (- (+ v1_2 v2_2) (* 2 (* v1_2 v2_2))) (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (- (+ v1_3 v2_3) (* 2 (* v1_3 v2_3))))))))))))))) (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (+ (+ (* 1 (- (+ v1_4 v2_4) (* 2 (* v1_4 v2_4)))) (- (+ v1_5 v2_5) (* 2 (* v1_5 v2_5)))) (+ (- (+ v1_6 v2_6) (* 2 (* v1_6 v2_6))) (- (+ v1_7 v2_7) (* 2 (* v1_7 v2_7))))))))))))))))</t>
+          <t>(Vec (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (+ (+ (* 1 (+ (- (+ v1_0 v2_0) (* (* v1_0 v2_0) 2)) (- (+ v1_1 v2_1) (* 2 (* v1_1 v2_1))))) (* 1 (+ (- (+ v1_2 v2_2) (* 2 (* v1_2 v2_2))) (- (+ v1_3 v2_3) (* 2 (* v1_3 v2_3)))))) (+ (+ (+ (+ (- (+ v1_4 v2_4) (* 2 (* v1_4 v2_4))) 0) 0) (- (+ v1_5 v2_5) (* 2 (* v1_5 v2_5)))) (+ (- (+ v1_6 v2_6) (* 2 (* v1_6 v2_6))) (- (+ v1_7 v2_7) (* 2 (* v1_7 v2_7)))))))))))))))))</t>
         </is>
       </c>
       <c r="E179" t="n">
         <v>9760</v>
       </c>
       <c r="F179" t="n">
-        <v>14780</v>
+        <v>13283</v>
       </c>
       <c r="G179" t="n">
-        <v>-51.43</v>
+        <v>-36.1</v>
       </c>
       <c r="H179" t="n">
         <v>76.34999999999999</v>
       </c>
       <c r="I179" t="n">
-        <v>422.16</v>
+        <v>457.94</v>
       </c>
       <c r="J179" t="b">
         <v>0</v>
       </c>
       <c r="K179" t="n">
-        <v>8999577.84</v>
+        <v>8999542.060000001</v>
       </c>
       <c r="L179" t="n">
         <v>75</v>
@@ -7981,29 +7981,29 @@
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>(Vec (+ (+ (+ (+ (+ (- (+ v1_0 v2_0) (* (* v1_0 v2_0) 2)) (- (+ v1_1 v2_1) (* 2 (* v1_1 v2_1)))) (+ (- (+ v1_2 v2_2) (* 2 (* v1_2 v2_2))) (- (+ v1_3 v2_3) (* 2 (* v1_3 v2_3))))) (+ (+ (- (+ v1_4 v2_4) (* 2 (* v1_4 v2_4))) (- (+ v1_5 v2_5) (* 2 (* v1_5 v2_5)))) (+ (- (+ v1_6 v2_6) (* 2 (* v1_6 v2_6))) (- (+ v1_7 v2_7) (* 2 (* v1_7 v2_7)))))) (+ (+ (+ (- (+ v1_8 v2_8) (* 2 (* v1_8 v2_8))) (- (+ v1_9 v2_9) (* 2 (* v1_9 v2_9)))) (+ (- (+ v1_10 v2_10) (* 2 (* v1_10 v2_10))) (- (+ v1_11 v2_11) (* 2 (* v1_11 v2_11))))) (+ (+ (- (+ v1_12 v2_12) (* 2 (* v1_12 v2_12))) (- (+ v1_13 v2_13) (* 2 (* v1_13 v2_13)))) (+ (- (+ v1_14 v2_14) (* 2 (* v1_14 v2_14))) (- (+ v1_15 v2_15) (* 2 (* v1_15 v2_15))))))) (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (- (+ v1_16 v2_16) (* 2 (* v1_16 v2_16))) (- (+ v1_17 v2_17) (* 2 (* v1_17 v2_17)))) (+ (- (+ v1_18 v2_18) (* 2 (* v1_18 v2_18))) (- (+ v1_19 v2_19) (* 2 (* v1_19 v2_19))))) (+ (+ (- (+ v1_20 v2_20) (* 2 (* v1_20 v2_20))) (- (+ v1_21 v2_21) (* 2 (* v1_21 v2_21)))) (+ (- (+ v1_22 v2_22) (* 2 (* v1_22 v2_22))) (- (+ v1_23 v2_23) (* 2 (* v1_23 v2_23)))))) (+ (+ (+ (- (+ v1_24 v2_24) (* 2 (* v1_24 v2_24))) (- (+ v1_25 v2_25) (* 2 (* v1_25 v2_25)))) (+ (- (+ v1_26 v2_26) (* 2 (* v1_26 v2_26))) (- (+ v1_27 v2_27) (* 2 (* v1_27 v2_27))))) (+ (+ (- (+ v1_28 v2_28) (* 2 (* v1_28 v2_28))) (- (+ v1_29 v2_29) (* 2 (* v1_29 v2_29)))) (+ (- (+ v1_30 v2_30) (* 2 (* v1_30 v2_30))) (- (+ v1_31 v2_31) (* 2 (* v1_31 v2_31))))))) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0)))</t>
+          <t>(Vec (+ (+ (+ (+ (+ (- (+ v1_0 v2_0) (* (+ 0 (+ 0 (* v1_0 v2_0))) 2)) (- (+ v1_1 v2_1) (* 2 (+ 0 (+ 0 (* v1_1 v2_1)))))) (+ (- (+ v1_2 v2_2) (* 2 (+ 0 (+ 0 (* v1_2 v2_2))))) (- (+ v1_3 v2_3) (* 2 (+ 0 (+ 0 (* v1_3 v2_3))))))) (+ (+ (- (+ v1_4 v2_4) (* 2 (+ 0 (+ 0 (* v1_4 v2_4))))) (- (+ v1_5 v2_5) (* 2 (+ 0 (+ 0 (* v1_5 v2_5)))))) (+ (- (+ v1_6 v2_6) (* 2 (+ 0 (+ 0 (* v1_6 v2_6))))) (- (+ v1_7 v2_7) (* 2 (+ 0 (+ 0 (* v1_7 v2_7)))))))) (+ (+ (+ (- (+ v1_8 v2_8) (* 2 (+ 0 (+ 0 (* v1_8 v2_8))))) (- (+ v1_9 v2_9) (* 2 (+ 0 (+ 0 (* v1_9 v2_9)))))) (+ (- (+ v1_10 v2_10) (* 2 (+ 0 (+ 0 (* v1_10 v2_10))))) (- (+ v1_11 v2_11) (+ 0 (+ 0 (+ 0 (* 2 (* v1_11 v2_11)))))))) (+ (+ (- (+ v1_12 v2_12) (+ 0 (+ 0 (+ 0 (* 2 (* v1_12 v2_12)))))) (- (+ v1_13 v2_13) (+ 0 (+ 0 (+ 0 (* 2 (* v1_13 v2_13))))))) (+ (- (+ v1_14 v2_14) (+ 0 (+ 0 (+ 0 (* 2 (* v1_14 v2_14)))))) (- (+ v1_15 v2_15) (+ 0 (+ 0 (+ 0 (* 2 (* v1_15 v2_15)))))))))) (+ (+ (+ (+ (- (+ v1_16 v2_16) (+ 0 (+ 0 (+ 0 (* 2 (* v1_16 v2_16)))))) (- (+ v1_17 v2_17) (+ 0 (+ 0 (+ 0 (* 2 (* v1_17 v2_17))))))) (+ (- (+ v1_18 v2_18) (+ 0 (+ 0 (+ 0 (* 2 (* v1_18 v2_18)))))) (- (+ v1_19 v2_19) (+ 0 (+ 0 (+ 0 (* 2 (* v1_19 v2_19)))))))) (+ (+ (- (+ v1_20 v2_20) (+ 0 (+ 0 (+ 0 (* 2 (* v1_20 v2_20)))))) (- (+ v1_21 v2_21) (+ 0 (+ 0 (* 2 (* v1_21 v2_21)))))) (+ (- (+ v1_22 v2_22) (+ 0 (+ 0 (* 2 (* v1_22 v2_22))))) (- (+ v1_23 v2_23) (+ 0 (+ 0 (* 2 (* v1_23 v2_23)))))))) (+ (+ (+ (- (+ v1_24 v2_24) (+ 0 (+ 0 (* 2 (* v1_24 v2_24))))) (- (+ v1_25 v2_25) (+ 0 (+ 0 (* 2 (* v1_25 v2_25)))))) (+ (- (+ v1_26 v2_26) (+ 0 (+ 0 (* 2 (* v1_26 v2_26))))) (- (+ v1_27 v2_27) (+ 0 (+ 0 (* 2 (* v1_27 v2_27))))))) (+ (+ (- (+ v1_28 v2_28) (+ 0 (+ 0 (* 2 (* v1_28 v2_28))))) (- (+ v1_29 v2_29) (+ 0 (+ 0 (* 2 (* v1_29 v2_29)))))) (+ (- (+ v1_30 v2_30) (+ 0 (+ 0 (* 2 (* v1_30 v2_30))))) (- (+ v1_31 v2_31) (+ 0 (+ 0 (* 2 (* v1_31 v2_31)))))))))))</t>
         </is>
       </c>
       <c r="E180" t="n">
         <v>39762</v>
       </c>
       <c r="F180" t="n">
-        <v>58336</v>
+        <v>58265</v>
       </c>
       <c r="G180" t="n">
-        <v>-46.71</v>
+        <v>-46.53</v>
       </c>
       <c r="H180" t="n">
         <v>78.75</v>
       </c>
       <c r="I180" t="n">
-        <v>167.4</v>
+        <v>82.34</v>
       </c>
       <c r="J180" t="b">
         <v>0</v>
       </c>
       <c r="K180" t="n">
-        <v>8999832.6</v>
+        <v>8999917.66</v>
       </c>
       <c r="L180" t="n">
         <v>75</v>
@@ -8023,29 +8023,29 @@
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>(Vec (+ c1_0 (+ c2_0 (* c0_0 (+ c3_0 (* c0_0 c4_0))))) (+ c1_1 (+ c2_1 (* c0_1 (+ c3_1 (* c0_1 c4_1))))) (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ c1_2 (+ c2_2 (* c0_2 (+ c3_2 (* c0_2 c4_2))))) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) (+ c1_3 (+ c2_3 (* c0_3 (+ c3_3 (* c0_3 c4_3))))) (+ c1_4 (+ c2_4 (* c0_4 (+ c3_4 (* c0_4 c4_4))))) (+ c1_5 (+ c2_5 (* c0_5 (+ c3_5 (* c0_5 c4_5))))) (+ c1_6 (+ c2_6 (* c0_6 (+ c3_6 (* c0_6 c4_6))))) (+ c1_7 (+ c2_7 (* c0_7 (+ c3_7 (* c0_7 c4_7))))))</t>
+          <t>(Vec (+ c1_0 (+ c2_0 (* c0_0 (+ c3_0 (* c0_0 c4_0))))) (+ c1_1 (+ c2_1 (* c0_1 (+ c3_1 (* c0_1 c4_1))))) (+ c1_2 (+ c2_2 (* c0_2 (+ c3_2 (* c0_2 c4_2))))) (+ c1_3 (+ c2_3 (* c0_3 (+ c3_3 (* c0_3 c4_3))))) (+ c1_4 (+ c2_4 (* c0_4 (+ c3_4 (* c0_4 c4_4))))) (+ c1_5 (+ c2_5 (* c0_5 (+ c3_5 (* c0_5 c4_5))))) (+ c1_6 (+ c2_6 (* c0_6 (+ c3_6 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (* c0_6 c4_6)))))))))))))))))))))))))))))))))))))))))) (+ c1_7 (+ c2_7 (* c0_7 (+ c3_7 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (* c0_7 c4_7)))))))))))))))))))))))))))))))))))))))))))</t>
         </is>
       </c>
       <c r="E181" t="n">
         <v>10009</v>
       </c>
       <c r="F181" t="n">
-        <v>28583</v>
+        <v>28546</v>
       </c>
       <c r="G181" t="n">
-        <v>-185.57</v>
+        <v>-185.2</v>
       </c>
       <c r="H181" t="n">
         <v>75.15000000000001</v>
       </c>
       <c r="I181" t="n">
-        <v>163.8</v>
+        <v>119.48</v>
       </c>
       <c r="J181" t="b">
         <v>0</v>
       </c>
       <c r="K181" t="n">
-        <v>8999836.199999999</v>
+        <v>8999880.52</v>
       </c>
       <c r="L181" t="n">
         <v>75</v>
@@ -8065,29 +8065,29 @@
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>(Vec (+ c1_0 (+ c2_0 (* c0_0 (+ c3_0 (* c0_0 c4_0))))) (+ c1_1 (+ c2_1 (* c0_1 (+ c3_1 (* c0_1 c4_1))))) (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ c1_2 (+ c2_2 (* c0_2 (+ c3_2 (* c0_2 c4_2))))) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) (+ c1_3 (+ c2_3 (* c0_3 (+ c3_3 (* c0_3 c4_3))))) (+ c1_4 (+ c2_4 (* c0_4 (+ c3_4 (* c0_4 c4_4))))) (+ c1_5 (+ c2_5 (* c0_5 (+ c3_5 (* c0_5 c4_5))))) (+ c1_6 (+ c2_6 (* c0_6 (+ c3_6 (* c0_6 c4_6))))) (+ c1_7 (+ c2_7 (* c0_7 (+ c3_7 (* c0_7 c4_7))))) (+ c1_8 (+ c2_8 (* c0_8 (+ c3_8 (* c0_8 c4_8))))) (+ c1_9 (+ c2_9 (* c0_9 (+ c3_9 (* c0_9 c4_9))))) (+ c1_10 (+ c2_10 (* c0_10 (+ c3_10 (* c0_10 c4_10))))) (+ c1_11 (+ c2_11 (* c0_11 (+ c3_11 (* c0_11 c4_11))))) (+ c1_12 (+ c2_12 (* c0_12 (+ c3_12 (* c0_12 c4_12))))) (+ c1_13 (+ c2_13 (* c0_13 (+ c3_13 (* c0_13 c4_13))))) (+ c1_14 (+ c2_14 (* c0_14 (+ c3_14 (* c0_14 c4_14))))) (+ c1_15 (+ c2_15 (* c0_15 (+ c3_15 (* c0_15 c4_15))))) (+ c1_16 (+ c2_16 (* c0_16 (+ c3_16 (* c0_16 c4_16))))) (+ c1_17 (+ c2_17 (* c0_17 (+ c3_17 (* c0_17 c4_17))))) (+ c1_18 (+ c2_18 (* c0_18 (+ c3_18 (* c0_18 c4_18))))) (+ c1_19 (+ c2_19 (* c0_19 (+ c3_19 (* c0_19 c4_19))))) (+ c1_20 (+ c2_20 (* c0_20 (+ c3_20 (* c0_20 c4_20))))) (+ c1_21 (+ c2_21 (* c0_21 (+ c3_21 (* c0_21 c4_21))))) (+ c1_22 (+ c2_22 (* c0_22 (+ c3_22 (* c0_22 c4_22))))) (+ c1_23 (+ c2_23 (* c0_23 (+ c3_23 (* c0_23 c4_23))))) (+ c1_24 (+ c2_24 (* c0_24 (+ c3_24 (* c0_24 c4_24))))) (+ c1_25 (+ c2_25 (* c0_25 (+ c3_25 (* c0_25 c4_25))))) (+ c1_26 (+ c2_26 (* c0_26 (+ c3_26 (* c0_26 c4_26))))) (+ c1_27 (+ c2_27 (* c0_27 (+ c3_27 (* c0_27 c4_27))))) (+ c1_28 (+ c2_28 (* c0_28 (+ c3_28 (* c0_28 c4_28))))) (+ c1_29 (+ c2_29 (* c0_29 (+ c3_29 (* c0_29 c4_29))))) (+ c1_30 (+ c2_30 (* c0_30 (+ c3_30 (* c0_30 c4_30))))) (+ c1_31 (+ c2_31 (* c0_31 (+ c3_31 (* c0_31 c4_31))))))</t>
+          <t>(Vec (+ c1_0 (+ c2_0 (* c0_0 (+ c3_0 (+ 0 (* c0_0 c4_0)))))) (+ c1_1 (+ c2_1 (* c0_1 (+ c3_1 (+ 0 (* c0_1 c4_1)))))) (+ c1_2 (+ c2_2 (* c0_2 (+ c3_2 (+ 0 (* c0_2 c4_2)))))) (+ c1_3 (+ c2_3 (* c0_3 (+ c3_3 (+ 0 (* c0_3 c4_3)))))) (+ c1_4 (+ c2_4 (* c0_4 (+ c3_4 (+ 0 (* c0_4 c4_4)))))) (+ c1_5 (+ c2_5 (* c0_5 (+ c3_5 (+ 0 (* c0_5 c4_5)))))) (+ c1_6 (+ c2_6 (* c0_6 (+ c3_6 (+ 0 (* c0_6 c4_6)))))) (+ c1_7 (+ c2_7 (* c0_7 (+ c3_7 (+ 0 (* c0_7 c4_7)))))) (+ c1_8 (+ c2_8 (* c0_8 (+ c3_8 (+ 0 (* c0_8 c4_8)))))) (+ c1_9 (+ c2_9 (* c0_9 (+ c3_9 (+ 0 (* c0_9 c4_9)))))) (+ c1_10 (+ c2_10 (* c0_10 (+ c3_10 (+ 0 (* c0_10 c4_10)))))) (+ c1_11 (+ c2_11 (+ 0 (+ 0 (+ 0 (* c0_11 (+ c3_11 (* c0_11 c4_11)))))))) (+ c1_12 (+ c2_12 (+ 0 (+ 0 (+ 0 (* c0_12 (+ c3_12 (* c0_12 c4_12)))))))) (+ c1_13 (+ c2_13 (+ 0 (+ 0 (+ 0 (* c0_13 (+ c3_13 (* c0_13 c4_13)))))))) (+ c1_14 (+ c2_14 (+ 0 (+ 0 (+ 0 (* c0_14 (+ c3_14 (* c0_14 c4_14)))))))) (+ c1_15 (+ c2_15 (+ 0 (+ 0 (+ 0 (* c0_15 (+ c3_15 (* c0_15 c4_15)))))))) (+ c1_16 (+ c2_16 (+ 0 (+ 0 (+ 0 (* c0_16 (+ c3_16 (* c0_16 c4_16)))))))) (+ c1_17 (+ c2_17 (+ 0 (+ 0 (+ 0 (* c0_17 (+ c3_17 (* c0_17 c4_17)))))))) (+ c1_18 (+ c2_18 (+ 0 (+ 0 (+ 0 (* c0_18 (+ c3_18 (* c0_18 c4_18)))))))) (+ c1_19 (+ c2_19 (+ 0 (+ 0 (+ 0 (* c0_19 (+ c3_19 (* c0_19 c4_19)))))))) (+ c1_20 (+ c2_20 (+ 0 (+ 0 (+ 0 (* c0_20 (+ c3_20 (* c0_20 c4_20)))))))) (+ c1_21 (+ c2_21 (+ 0 (+ 0 (+ 0 (* c0_21 (+ c3_21 (* c0_21 c4_21)))))))) (+ c1_22 (+ c2_22 (+ 0 (+ 0 (+ 0 (* c0_22 (+ c3_22 (* c0_22 c4_22)))))))) (+ c1_23 (+ c2_23 (+ 0 (+ 0 (+ 0 (* c0_23 (+ c3_23 (* c0_23 c4_23)))))))) (+ c1_24 (+ c2_24 (+ 0 (+ 0 (+ 0 (* c0_24 (+ c3_24 (* c0_24 c4_24)))))))) (+ c1_25 (+ c2_25 (+ 0 (+ 0 (+ 0 (* c0_25 (+ c3_25 (* c0_25 c4_25)))))))) (+ c1_26 (+ c2_26 (+ 0 (+ 0 (+ 0 (* c0_26 (+ c3_26 (* c0_26 c4_26)))))))) (+ c1_27 (+ c2_27 (+ 0 (+ 0 (+ 0 (* c0_27 (+ c3_27 (* c0_27 c4_27)))))))) (+ c1_28 (+ c2_28 (+ 0 (+ 0 (+ 0 (* c0_28 (+ c3_28 (* c0_28 c4_28)))))))) (+ c1_29 (+ c2_29 (+ 0 (+ 0 (+ 0 (* c0_29 (+ c3_29 (* c0_29 c4_29)))))))) (+ c1_30 (+ c2_30 (+ 0 (+ 0 (+ 0 (* c0_30 (+ c3_30 (* c0_30 c4_30)))))))) (+ c1_31 (+ c2_31 (+ 0 (+ 0 (+ 0 (* c0_31 (+ c3_31 (* c0_31 c4_31)))))))))</t>
         </is>
       </c>
       <c r="E182" t="n">
         <v>40009</v>
       </c>
       <c r="F182" t="n">
-        <v>58583</v>
+        <v>58512</v>
       </c>
       <c r="G182" t="n">
-        <v>-46.42</v>
+        <v>-46.25</v>
       </c>
       <c r="H182" t="n">
         <v>75.15000000000001</v>
       </c>
       <c r="I182" t="n">
-        <v>163.8</v>
+        <v>78.75</v>
       </c>
       <c r="J182" t="b">
         <v>0</v>
       </c>
       <c r="K182" t="n">
-        <v>8999836.199999999</v>
+        <v>8999921.25</v>
       </c>
       <c r="L182" t="n">
         <v>75</v>
@@ -8107,32 +8107,32 @@
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>(Vec (+ (+ (* (- c2_0 c1_0) (- c2_0 c1_0)) (* (- c2_1 c1_1) (- c2_1 c1_1))) (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (* (- c2_2 c1_2) (- c2_2 c1_2)) (* (- c2_3 c1_3) (- c2_3 c1_3))) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0)))</t>
+          <t>(Vec ( + ( + ( * ( - c2_0 c1_0 ) ( - c2_0 c1_0 ) ) ( * ( - c2_1 c1_1 ) ( - c2_1 c1_1 ) ) ) ( + ( * ( - c2_2 c1_2 ) ( - c2_2 c1_2 ) ) ( * ( - c2_3 c1_3 ) ( - c2_3 c1_3 ) ) ) ) )</t>
         </is>
       </c>
       <c r="E183" t="n">
         <v>3757</v>
       </c>
       <c r="F183" t="n">
-        <v>22331</v>
+        <v>3757</v>
       </c>
       <c r="G183" t="n">
-        <v>-494.38</v>
+        <v>0</v>
       </c>
       <c r="H183" t="n">
         <v>40.57</v>
       </c>
       <c r="I183" t="n">
-        <v>129.22</v>
+        <v>40.57</v>
       </c>
       <c r="J183" t="b">
         <v>0</v>
       </c>
       <c r="K183" t="n">
-        <v>8999870.779999999</v>
+        <v>8999959.43</v>
       </c>
       <c r="L183" t="n">
-        <v>75</v>
+        <v>1</v>
       </c>
     </row>
     <row r="184">
@@ -8149,32 +8149,32 @@
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>(Vec (+ (+ (+ (* (- c2_0 c1_0) (- c2_0 c1_0)) (* (- c2_1 c1_1) (- c2_1 c1_1))) (+ (* (- c2_2 c1_2) (- c2_2 c1_2)) (* (- c2_3 c1_3) (- c2_3 c1_3)))) (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (* (- c2_4 c1_4) (- c2_4 c1_4)) (* (- c2_5 c1_5) (- c2_5 c1_5))) (+ (* (- c2_6 c1_6) (- c2_6 c1_6)) (* (- c2_7 c1_7) (- c2_7 c1_7)))) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0)))</t>
+          <t>(Vec ( + ( + ( + ( * ( - c2_0 c1_0 ) ( - c2_0 c1_0 ) ) ( * ( - c2_1 c1_1 ) ( - c2_1 c1_1 ) ) ) ( + ( * ( - c2_2 c1_2 ) ( - c2_2 c1_2 ) ) ( * ( - c2_3 c1_3 ) ( - c2_3 c1_3 ) ) ) ) ( + ( + ( * ( - c2_4 c1_4 ) ( - c2_4 c1_4 ) ) ( * ( - c2_5 c1_5 ) ( - c2_5 c1_5 ) ) ) ( + ( * ( - c2_6 c1_6 ) ( - c2_6 c1_6 ) ) ( * ( - c2_7 c1_7 ) ( - c2_7 c1_7 ) ) ) ) ) )</t>
         </is>
       </c>
       <c r="E184" t="n">
         <v>7758</v>
       </c>
       <c r="F184" t="n">
-        <v>26332</v>
+        <v>7758</v>
       </c>
       <c r="G184" t="n">
-        <v>-239.42</v>
+        <v>0</v>
       </c>
       <c r="H184" t="n">
         <v>41.77</v>
       </c>
       <c r="I184" t="n">
-        <v>130.42</v>
+        <v>41.77</v>
       </c>
       <c r="J184" t="b">
         <v>0</v>
       </c>
       <c r="K184" t="n">
-        <v>8999869.58</v>
+        <v>8999958.23</v>
       </c>
       <c r="L184" t="n">
-        <v>75</v>
+        <v>1</v>
       </c>
     </row>
     <row r="185">
@@ -8191,29 +8191,29 @@
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>(Vec (+ (+ (+ (+ (+ (* (- c2_0 c1_0) (- c2_0 c1_0)) (* (- c2_1 c1_1) (- c2_1 c1_1))) (+ (* (- c2_2 c1_2) (- c2_2 c1_2)) (* (- c2_3 c1_3) (- c2_3 c1_3)))) (+ (+ (* (- c2_4 c1_4) (- c2_4 c1_4)) (* (- c2_5 c1_5) (- c2_5 c1_5))) (+ (* (- c2_6 c1_6) (- c2_6 c1_6)) (* (- c2_7 c1_7) (- c2_7 c1_7))))) (+ (+ (+ (* (- c2_8 c1_8) (- c2_8 c1_8)) (* (- c2_9 c1_9) (- c2_9 c1_9))) (+ (* (- c2_10 c1_10) (- c2_10 c1_10)) (* (- c2_11 c1_11) (- c2_11 c1_11)))) (+ (+ (* (- c2_12 c1_12) (- c2_12 c1_12)) (* (- c2_13 c1_13) (- c2_13 c1_13))) (+ (* (- c2_14 c1_14) (- c2_14 c1_14)) (* (- c2_15 c1_15) (- c2_15 c1_15)))))) (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (* (- c2_16 c1_16) (- c2_16 c1_16)) (* (- c2_17 c1_17) (- c2_17 c1_17))) (+ (* (- c2_18 c1_18) (- c2_18 c1_18)) (* (- c2_19 c1_19) (- c2_19 c1_19)))) (+ (+ (* (- c2_20 c1_20) (- c2_20 c1_20)) (* (- c2_21 c1_21) (- c2_21 c1_21))) (+ (* (- c2_22 c1_22) (- c2_22 c1_22)) (* (- c2_23 c1_23) (- c2_23 c1_23))))) (+ (+ (+ (* (- c2_24 c1_24) (- c2_24 c1_24)) (* (- c2_25 c1_25) (- c2_25 c1_25))) (+ (* (- c2_26 c1_26) (- c2_26 c1_26)) (* (- c2_27 c1_27) (- c2_27 c1_27)))) (+ (+ (* (- c2_28 c1_28) (- c2_28 c1_28)) (* (- c2_29 c1_29) (- c2_29 c1_29))) (+ (* (- c2_30 c1_30) (- c2_30 c1_30)) (* (- c2_31 c1_31) (- c2_31 c1_31)))))) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0)))</t>
+          <t>(Vec (+ (+ (+ (+ (+ (* (- c2_0 c1_0) (- c2_0 c1_0)) (* (- c2_1 c1_1) (- c2_1 c1_1))) (+ (* (- c2_2 c1_2) (- c2_2 c1_2)) (* (- c2_3 c1_3) (- c2_3 c1_3)))) (+ (+ (* (- c2_4 c1_4) (- c2_4 c1_4)) (* (- c2_5 c1_5) (- c2_5 c1_5))) (+ (* (- c2_6 c1_6) (- c2_6 c1_6)) (* (- c2_7 c1_7) (- c2_7 c1_7))))) (+ (+ (+ (* (- c2_8 c1_8) (- c2_8 c1_8)) (* (- c2_9 c1_9) (- c2_9 c1_9))) (+ (* (- c2_10 c1_10) (- c2_10 c1_10)) (+ 0 (+ 0 (+ 0 (+ 0 (* (- c2_11 c1_11) (- c2_11 c1_11)))))))) (+ (+ (+ 0 (+ 0 (+ 0 (+ 0 (* (- c2_12 c1_12) (- c2_12 c1_12)))))) (+ 0 (+ 0 (+ 0 (+ 0 (* (- c2_13 c1_13) (- c2_13 c1_13))))))) (+ (+ 0 (+ 0 (+ 0 (+ 0 (* (- c2_14 c1_14) (- c2_14 c1_14)))))) (+ 0 (+ 0 (+ 0 (+ 0 (* (- c2_15 c1_15) (- c2_15 c1_15)))))))))) (+ (+ (+ (+ (+ 0 (+ 0 (+ 0 (+ 0 (* (- c2_16 c1_16) (- c2_16 c1_16)))))) (+ 0 (+ 0 (+ 0 (+ 0 (* (- c2_17 c1_17) (- c2_17 c1_17))))))) (+ (+ 0 (+ 0 (+ 0 (+ 0 (* (- c2_18 c1_18) (- c2_18 c1_18)))))) (+ 0 (+ 0 (+ 0 (+ 0 (* (- c2_19 c1_19) (- c2_19 c1_19)))))))) (+ (+ (+ 0 (+ 0 (+ 0 (+ 0 (* (- c2_20 c1_20) (- c2_20 c1_20)))))) (+ 0 (+ 0 (+ 0 (+ 0 (* (- c2_21 c1_21) (- c2_21 c1_21))))))) (+ (+ 0 (+ 0 (+ 0 (* (- c2_22 c1_22) (- c2_22 c1_22))))) (+ 0 (+ 0 (+ 0 (* (- c2_23 c1_23) (- c2_23 c1_23)))))))) (+ (+ (+ (+ 0 (+ 0 (+ 0 (* (- c2_24 c1_24) (- c2_24 c1_24))))) (+ 0 (+ 0 (+ 0 (* (- c2_25 c1_25) (- c2_25 c1_25)))))) (+ (+ 0 (+ 0 (+ 0 (* (- c2_26 c1_26) (- c2_26 c1_26))))) (+ 0 (+ 0 (+ 0 (* (- c2_27 c1_27) (- c2_27 c1_27))))))) (+ (+ (+ 0 (+ 0 (+ 0 (* (- c2_28 c1_28) (- c2_28 c1_28))))) (+ 0 (+ 0 (+ 0 (* (- c2_29 c1_29) (- c2_29 c1_29)))))) (+ (+ 0 (+ 0 (+ 0 (* (- c2_30 c1_30) (- c2_30 c1_30))))) (+ 0 (+ 0 (+ 0 (* (- c2_31 c1_31) (- c2_31 c1_31)))))))))))</t>
         </is>
       </c>
       <c r="E185" t="n">
         <v>31760</v>
       </c>
       <c r="F185" t="n">
-        <v>50334</v>
+        <v>50264</v>
       </c>
       <c r="G185" t="n">
-        <v>-58.48</v>
+        <v>-58.26</v>
       </c>
       <c r="H185" t="n">
         <v>44.16</v>
       </c>
       <c r="I185" t="n">
-        <v>132.82</v>
+        <v>48.96</v>
       </c>
       <c r="J185" t="b">
         <v>0</v>
       </c>
       <c r="K185" t="n">
-        <v>8999867.18</v>
+        <v>8999951.039999999</v>
       </c>
       <c r="L185" t="n">
         <v>75</v>
@@ -8233,32 +8233,32 @@
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t>(Vec (+ (+ (* v1_0 v2_0) (* v1_1 v2_1)) (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (* v1_2 v2_2) (* v1_3 v2_3)) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0)))</t>
+          <t>(Vec ( + ( + ( * v1_0 v2_0 ) ( * v1_1 v2_1 ) ) ( + ( * v1_2 v2_2 ) ( * v1_3 v2_3 ) ) ) )</t>
         </is>
       </c>
       <c r="E186" t="n">
         <v>1756</v>
       </c>
       <c r="F186" t="n">
-        <v>20330</v>
+        <v>1756</v>
       </c>
       <c r="G186" t="n">
-        <v>-1057.74</v>
+        <v>0</v>
       </c>
       <c r="H186" t="n">
         <v>39.37</v>
       </c>
       <c r="I186" t="n">
-        <v>128.02</v>
+        <v>39.37</v>
       </c>
       <c r="J186" t="b">
         <v>0</v>
       </c>
       <c r="K186" t="n">
-        <v>8999871.98</v>
+        <v>8999960.630000001</v>
       </c>
       <c r="L186" t="n">
-        <v>75</v>
+        <v>1</v>
       </c>
     </row>
     <row r="187">
@@ -8275,29 +8275,29 @@
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>(Vec (+ (+ (+ (* v1_0 v2_0) (* v1_1 v2_1)) (+ (* v1_2 v2_2) (* v1_3 v2_3))) (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (* v1_4 v2_4) (* v1_5 v2_5)) (+ (* v1_6 v2_6) (* v1_7 v2_7))) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0)))</t>
+          <t>(Vec (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (+ (+ (* 1 (+ (* v1_0 v2_0) (* v1_1 v2_1))) (+ (* v1_2 v2_2) (* v1_3 v2_3))) (+ (+ (+ (+ (+ (+ (+ (* 1 (* 1 (* 1 (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (* v1_4 v2_4) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0)))) 0) 0) 0) 0) 0) (* v1_5 v2_5)) (+ (* v1_6 v2_6) (* v1_7 v2_7))))))))))))</t>
         </is>
       </c>
       <c r="E187" t="n">
         <v>3757</v>
       </c>
       <c r="F187" t="n">
-        <v>22331</v>
+        <v>11798</v>
       </c>
       <c r="G187" t="n">
-        <v>-494.38</v>
+        <v>-214.03</v>
       </c>
       <c r="H187" t="n">
         <v>40.57</v>
       </c>
       <c r="I187" t="n">
-        <v>129.22</v>
+        <v>411.54</v>
       </c>
       <c r="J187" t="b">
         <v>0</v>
       </c>
       <c r="K187" t="n">
-        <v>8999870.779999999</v>
+        <v>8999588.460000001</v>
       </c>
       <c r="L187" t="n">
         <v>75</v>
@@ -8317,29 +8317,29 @@
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>(Vec (+ (+ (+ (+ (+ (* v1_0 v2_0) (* v1_1 v2_1)) (+ (* v1_2 v2_2) (* v1_3 v2_3))) (+ (+ (* v1_4 v2_4) (* v1_5 v2_5)) (+ (* v1_6 v2_6) (* v1_7 v2_7)))) (+ (+ (+ (* v1_8 v2_8) (* v1_9 v2_9)) (+ (* v1_10 v2_10) (* v1_11 v2_11))) (+ (+ (* v1_12 v2_12) (* v1_13 v2_13)) (+ (* v1_14 v2_14) (* v1_15 v2_15))))) (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (* v1_16 v2_16) (* v1_17 v2_17)) (+ (* v1_18 v2_18) (* v1_19 v2_19))) (+ (+ (* v1_20 v2_20) (* v1_21 v2_21)) (+ (* v1_22 v2_22) (* v1_23 v2_23)))) (+ (+ (+ (* v1_24 v2_24) (* v1_25 v2_25)) (+ (* v1_26 v2_26) (* v1_27 v2_27))) (+ (+ (* v1_28 v2_28) (* v1_29 v2_29)) (+ (* v1_30 v2_30) (* v1_31 v2_31))))) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) (- 0)) (- (- 0))) (- (- (- 0)))) (- (- (- (- 0))))) (- (- (- (- (- 0)))))) (- (- (- (- (- (- 0))))))) (- (- (- (- (- (- (- 0)))))))) 0) 0) 0)))</t>
+          <t>(Vec (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (+ (* 1 (+ (+ (+ (+ (* v1_0 v2_0) (* v1_1 v2_1)) (+ (* v1_2 v2_2) (* v1_3 v2_3))) (+ (+ (* v1_4 v2_4) (* v1_5 v2_5)) (+ (* v1_6 v2_6) (* v1_7 v2_7)))) (+ (+ (+ (* v1_8 v2_8) (* v1_9 v2_9)) (+ (* v1_10 v2_10) (* v1_11 v2_11))) (+ (+ (* v1_12 v2_12) (* v1_13 v2_13)) (+ (* v1_14 v2_14) (* v1_15 v2_15)))))) (+ (* 1 (+ (+ (+ (* v1_16 v2_16) (* v1_17 v2_17)) (+ (* v1_18 v2_18) (* v1_19 v2_19))) (+ (+ (* v1_20 v2_20) (* v1_21 v2_21)) (+ (* v1_22 v2_22) (* v1_23 v2_23))))) (+ (+ (+ (* v1_24 v2_24) (* v1_25 v2_25)) (+ (* v1_26 v2_26) (* v1_27 v2_27))) (+ (+ (* v1_28 v2_28) (* v1_29 v2_29)) (+ (* v1_30 v2_30) (* v1_31 v2_31)))))))))))))))))</t>
         </is>
       </c>
       <c r="E188" t="n">
         <v>15759</v>
       </c>
       <c r="F188" t="n">
-        <v>34305</v>
+        <v>18781</v>
       </c>
       <c r="G188" t="n">
-        <v>-117.69</v>
+        <v>-19.18</v>
       </c>
       <c r="H188" t="n">
         <v>42.97</v>
       </c>
       <c r="I188" t="n">
-        <v>98.06999999999999</v>
+        <v>423.36</v>
       </c>
       <c r="J188" t="b">
         <v>0</v>
       </c>
       <c r="K188" t="n">
-        <v>8999901.93</v>
+        <v>8999576.640000001</v>
       </c>
       <c r="L188" t="n">
         <v>75</v>
@@ -8359,29 +8359,29 @@
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t>(Vec (+ in_1_1 (* in_0_1 2)) (+ (+ in_1_2 (- in_1_0)) (+ (* in_0_2 2) (* in_0_0 -2))) (+ (+ in_1_3 (- in_1_1)) (+ (* in_0_3 2) (* in_0_1 -2))) (+ (- in_1_2) (* in_0_2 -2)) (+ in_2_1 (+ in_0_1 (* in_1_1 2))) (+ (+ in_2_2 (- in_2_0)) (+ (+ in_0_2 (- in_0_0)) (+ (* in_1_2 2) (* in_1_0 -2)))) (+ (+ in_2_3 (- in_2_1)) (+ (+ in_0_3 (- in_0_1)) (+ (* in_1_3 2) (* in_1_1 -2)))) (+ (- in_2_2) (+ (- in_0_2) (* in_1_2 -2))) (+ in_3_1 (+ in_1_1 (* in_2_1 2))) (+ (+ in_3_2 (- in_3_0)) (+ (+ in_1_2 (- in_1_0)) (+ (* in_2_2 2) (* in_2_0 -2)))) (+ (+ in_3_3 (- in_3_1)) (+ (+ in_1_3 (- in_1_1)) (+ (* in_2_3 2) (* in_2_1 -2)))) (+ (- in_3_2) (+ (- in_1_2) (* in_2_2 -2))) (+ in_2_1 (* in_3_1 2)) (+ (+ in_2_2 (- in_2_0)) (+ (* in_3_2 2) (* in_3_0 -2))) (+ (+ in_2_3 (- in_2_1)) (+ (* in_3_3 2) (* in_3_1 -2))) (+ (- in_2_2) (* in_3_2 -2)))</t>
+          <t>(Vec (+ in_1_1 (* in_0_1 2)) (+ (+ in_1_2 (- in_1_0)) (+ (* in_0_2 2) (* in_0_0 -2))) (+ (+ in_1_3 (- in_1_1)) (+ (* in_0_3 2) (* in_0_1 -2))) (+ (- in_1_2) (* in_0_2 -2)) (+ in_2_1 (+ in_0_1 (* in_1_1 2))) (+ (+ in_2_2 (- in_2_0)) (+ (+ in_0_2 (- in_0_0)) (+ (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (* in_1_2 2))))))))) (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (* in_1_0 -2)))))))))))) (+ (+ in_2_3 (- in_2_1)) (+ (+ in_0_3 (- in_0_1)) (+ (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (* in_1_3 2)))))))) (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (* in_1_1 -2))))))))))) (+ (- in_2_2) (+ (- in_0_2) (* in_1_2 -2))) (+ in_3_1 (+ in_1_1 (* in_2_1 2))) (+ (+ in_3_2 (- in_3_0)) (+ (+ in_1_2 (- in_1_0)) (+ (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (* in_2_2 2)))))))) (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (* in_2_0 -2))))))))))) (+ (+ in_3_3 (- in_3_1)) (+ (+ in_1_3 (- in_1_1)) (+ (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (* in_2_3 2)))))))) (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (* in_2_1 -2))))))))))) (+ (- in_3_2) (+ (- in_1_2) (* in_2_2 -2))) (+ in_2_1 (* in_3_1 2)) (+ (+ in_2_2 (- in_2_0)) (+ (* in_3_2 2) (* in_3_0 -2))) (+ (+ in_2_3 (- in_2_1)) (+ (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (* in_3_3 2))))))))) (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (* in_3_1 -2))))))))))) (+ (- in_2_2) (* in_3_2 -2)))</t>
         </is>
       </c>
       <c r="E189" t="n">
         <v>21507</v>
       </c>
       <c r="F189" t="n">
-        <v>21507</v>
+        <v>40015</v>
       </c>
       <c r="G189" t="n">
-        <v>0</v>
+        <v>-86.06</v>
       </c>
       <c r="H189" t="n">
         <v>40.57</v>
       </c>
       <c r="I189" t="n">
-        <v>40.57</v>
+        <v>50.15</v>
       </c>
       <c r="J189" t="b">
         <v>0</v>
       </c>
       <c r="K189" t="n">
-        <v>8999959.43</v>
+        <v>8999949.85</v>
       </c>
       <c r="L189" t="n">
         <v>75</v>
@@ -8401,32 +8401,32 @@
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t>(Vec (+ (+ (* a_0_0 b_0_0) (* a_0_1 b_1_0)) (* a_0_2 b_2_0)) (+ (+ (* a_0_0 b_0_1) (* a_0_1 b_1_1)) (* a_0_2 b_2_1)) (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (* a_0_0 b_0_2) (* a_0_1 b_1_2)) (* a_0_2 b_2_2)) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) (+ (+ (* a_1_0 b_0_0) (* a_1_1 b_1_0)) (* a_1_2 b_2_0)) (+ (+ (* a_1_0 b_0_1) (* a_1_1 b_1_1)) (* a_1_2 b_2_1)) (+ (+ (* a_1_0 b_0_2) (* a_1_1 b_1_2)) (* a_1_2 b_2_2)) (+ (+ (* a_2_0 b_0_0) (* a_2_1 b_1_0)) (* a_2_2 b_2_0)) (+ (+ (* a_2_0 b_0_1) (* a_2_1 b_1_1)) (* a_2_2 b_2_1)) (+ (+ (* a_2_0 b_0_2) (* a_2_1 b_1_2)) (* a_2_2 b_2_2)))</t>
+          <t>(Vec ( + ( + ( * a_0_0 b_0_0 ) ( * a_0_1 b_1_0 ) ) ( * a_0_2 b_2_0 ) ) ( + ( + ( * a_0_0 b_0_1 ) ( * a_0_1 b_1_1 ) ) ( * a_0_2 b_2_1 ) ) ( + ( + ( * a_0_0 b_0_2 ) ( * a_0_1 b_1_2 ) ) ( * a_0_2 b_2_2 ) ) ( + ( + ( * a_1_0 b_0_0 ) ( * a_1_1 b_1_0 ) ) ( * a_1_2 b_2_0 ) ) ( + ( + ( * a_1_0 b_0_1 ) ( * a_1_1 b_1_1 ) ) ( * a_1_2 b_2_1 ) ) ( + ( + ( * a_1_0 b_0_2 ) ( * a_1_1 b_1_2 ) ) ( * a_1_2 b_2_2 ) ) ( + ( + ( * a_2_0 b_0_0 ) ( * a_2_1 b_1_0 ) ) ( * a_2_2 b_2_0 ) ) ( + ( + ( * a_2_0 b_0_1 ) ( * a_2_1 b_1_1 ) ) ( * a_2_2 b_2_1 ) ) ( + ( + ( * a_2_0 b_0_2 ) ( * a_2_1 b_1_2 ) ) ( * a_2_2 b_2_2 ) ) )</t>
         </is>
       </c>
       <c r="E190" t="n">
         <v>11256</v>
       </c>
       <c r="F190" t="n">
-        <v>29830</v>
+        <v>11256</v>
       </c>
       <c r="G190" t="n">
-        <v>-165.01</v>
+        <v>0</v>
       </c>
       <c r="H190" t="n">
         <v>39.37</v>
       </c>
       <c r="I190" t="n">
-        <v>128.02</v>
+        <v>39.37</v>
       </c>
       <c r="J190" t="b">
         <v>0</v>
       </c>
       <c r="K190" t="n">
-        <v>8999871.98</v>
+        <v>8999960.630000001</v>
       </c>
       <c r="L190" t="n">
-        <v>75</v>
+        <v>1</v>
       </c>
     </row>
     <row r="191">
@@ -8443,29 +8443,29 @@
       </c>
       <c r="D191" t="inlineStr">
         <is>
-          <t>(Vec (+ (* (+ (* o3 (- 1 c23)) (* c23 o2)) (- 1 c12)) (* c12 (+ (* o3 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (- 1 c13)))))))))))))))))))))))))))))))))))))))))))))))))))))))))))))))))))))))))))) (* c13 o1)))))</t>
+          <t>(Vec (+ (* (+ (* o3 (- 1 c23)) (* c23 o2)) (- 1 c12)) (* c12 (+ (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (+ (+ (+ (+ (+ (+ (+ (+ (+ (* 1 (* 1 (+ (+ (* 1 (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (* o3 (- 1 c13)) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0)) 0) 0))) 0) 0) 0) 0) 0) 0) 0) 0) 0))))))))))))))))))))))))))))))))))))))))))))))))))) (* c13 o1)))))</t>
         </is>
       </c>
       <c r="E191" t="n">
         <v>3009</v>
       </c>
       <c r="F191" t="n">
-        <v>21657</v>
+        <v>21636</v>
       </c>
       <c r="G191" t="n">
-        <v>-619.74</v>
+        <v>-619.04</v>
       </c>
       <c r="H191" t="n">
         <v>75.15000000000001</v>
       </c>
       <c r="I191" t="n">
-        <v>2634.14</v>
+        <v>1933.1</v>
       </c>
       <c r="J191" t="b">
         <v>0</v>
       </c>
       <c r="K191" t="n">
-        <v>8997365.859999999</v>
+        <v>8998066.9</v>
       </c>
       <c r="L191" t="n">
         <v>75</v>
@@ -8485,29 +8485,29 @@
       </c>
       <c r="D192" t="inlineStr">
         <is>
-          <t>(Vec (+ (* (+ (* (+ (* o321 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (- 1 c23))))))))))))))))))))))))))))))))))))))) (* c23 o231)) (- 1 c13)) (* c13 o213)) (- 1 c12)) (* c12 (+ (* (- 1 c23) (+ (* o312 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (- 1 c13))))))))))))))))))))))))))))))))))))))) (* c13 o132))) (* c23 o123)))))</t>
+          <t>(Vec (+ (* (+ (* (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (+ (* o321 (- 1 c23)) (* c23 o231)))))))))))))))))))))))))))))) (- 1 c13)) (* c13 o213)) (- 1 c12)) (* c12 (+ (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (+ (+ (+ (+ (+ (+ (+ (+ (* 1 (* 1 (+ (+ (+ (+ (+ (+ (+ (* (- 1 c23) (+ (* o312 (- 1 c13)) (* c13 o132))) 0) 0) 0) 0) 0) 0) 0))) 0) 0) 0) 0) 0) 0) 0) 0)))))))))))))))))))))))))))))) (* c23 o123)))))</t>
         </is>
       </c>
       <c r="E192" t="n">
         <v>5012</v>
       </c>
       <c r="F192" t="n">
-        <v>23586</v>
+        <v>23589</v>
       </c>
       <c r="G192" t="n">
-        <v>-370.59</v>
+        <v>-370.65</v>
       </c>
       <c r="H192" t="n">
         <v>110.93</v>
       </c>
       <c r="I192" t="n">
-        <v>1390.43</v>
+        <v>1200.91</v>
       </c>
       <c r="J192" t="b">
         <v>0</v>
       </c>
       <c r="K192" t="n">
-        <v>8998609.57</v>
+        <v>8998799.09</v>
       </c>
       <c r="L192" t="n">
         <v>75</v>
@@ -8527,29 +8527,29 @@
       </c>
       <c r="D193" t="inlineStr">
         <is>
-          <t>(VecMul (Vec (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ x9602 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) x9604) (+ (+ x9608 x9610) (+ x9617 (* x9613 x9615)))) (&lt;&lt; (Vec (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ x9602 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) x9604) (+ (+ x9608 x9610) (+ x9617 (* x9613 x9615)))) 1))</t>
+          <t>(Vec (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (* (+ x9602 x9604) (+ (+ x9608 x9610) (+ (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (* x9613 x9615))))))))))))))))))))))))))))))))))))))))))))))) x9617))))))))))))))))))))))))))))))))</t>
         </is>
       </c>
       <c r="E193" t="n">
         <v>1508</v>
       </c>
       <c r="F193" t="n">
-        <v>19480</v>
+        <v>20082</v>
       </c>
       <c r="G193" t="n">
-        <v>-1191.78</v>
+        <v>-1231.7</v>
       </c>
       <c r="H193" t="n">
         <v>73.95</v>
       </c>
       <c r="I193" t="n">
-        <v>159.01</v>
+        <v>162.61</v>
       </c>
       <c r="J193" t="b">
         <v>0</v>
       </c>
       <c r="K193" t="n">
-        <v>8999840.99</v>
+        <v>8999837.390000001</v>
       </c>
       <c r="L193" t="n">
         <v>75</v>
@@ -8611,29 +8611,29 @@
       </c>
       <c r="D195" t="inlineStr">
         <is>
-          <t>(Vec (+ (* (+ (* (+ (* (+ (* o5 (- 1 c45)) (* c45 o4)) (- 1 c34)) (* c34 (+ (* o5 (- 1 c35)) (* c35 o3)))) (- 1 c23)) (* c23 (+ (* (+ (* o5 (- 1 c45)) (* c45 o4)) (- 1 c24)) (* c24 (+ (* o5 (- 1 c25)) (* c25 o2)))))) (- 1 c12)) (* c12 (+ (* (+ (* (+ (* o5 (- 1 c45)) (* c45 o4)) (- 1 c34)) (* c34 (+ (* o5 (- 1 c35)) (* c35 o3)))) (- 1 c13)) (* c13 (+ (* (+ (* o5 (- 1 c45)) (* c45 o4)) (- 1 c14)) (* c14 (+ (* o5 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (- 1 c15)))))))))))))))))))))))))))))))))))))))))))))))))))))))))))))))))))))))))))) (* c15 o1)))))))))</t>
+          <t>(Vec (+ (* (+ (* (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (+ (* (+ (* o5 (- 1 c45)) (* c45 o4)) (- 1 c34)) (* c34 (+ (* o5 (- 1 c35)) (* c35 o3))))))))))))))))))))))) (- 1 c23)) (* c23 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (+ (* (+ (* o5 (- 1 c45)) (* c45 o4)) (- 1 c24)) (* c24 (+ (* o5 (- 1 c25)) (* c25 o2))))))))))))))))))))))))) (- 1 c12)) (* c12 (+ (* (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (+ (* (+ (* o5 (- 1 c45)) (* c45 o4)) (- 1 c34)) (* c34 (+ (* o5 (- 1 c35)) (* c35 o3)))))))))))))))))))))) (- 1 c13)) (* c13 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (+ (* (+ (* o5 (- 1 c45)) (* c45 o4)) (- 1 c14)) (* c14 (+ (* o5 (- 1 c15)) (* c15 o1)))))))))))))))))))))))))))</t>
         </is>
       </c>
       <c r="E195" t="n">
         <v>15015</v>
       </c>
       <c r="F195" t="n">
-        <v>33663</v>
+        <v>33553</v>
       </c>
       <c r="G195" t="n">
-        <v>-124.2</v>
+        <v>-123.46</v>
       </c>
       <c r="H195" t="n">
         <v>146.71</v>
       </c>
       <c r="I195" t="n">
-        <v>2705.7</v>
+        <v>803.75</v>
       </c>
       <c r="J195" t="b">
         <v>0</v>
       </c>
       <c r="K195" t="n">
-        <v>8997294.300000001</v>
+        <v>8999196.25</v>
       </c>
       <c r="L195" t="n">
         <v>75</v>
@@ -8653,7 +8653,7 @@
       </c>
       <c r="D196" t="inlineStr">
         <is>
-          <t>(Vec (+ (+ in_1_1 in_1_0) (+ in_0_1 in_0_0)) (+ (+ (+ in_1_2 in_1_1) (+ in_1_0 in_0_2)) (+ in_0_1 in_0_0)) (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ in_1_3 in_1_2) (+ in_1_1 in_0_3)) (+ in_0_2 in_0_1)) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) (+ (+ in_1_3 in_1_2) (+ in_0_3 in_0_2)) (+ (+ (+ in_2_1 in_2_0) (+ in_1_1 in_1_0)) (+ in_0_1 in_0_0)) (+ (+ (+ in_2_2 (+ in_2_1 in_2_0)) (+ in_1_2 in_1_1)) (+ (+ in_1_0 in_0_2) (+ in_0_1 in_0_0))) (+ (+ (+ in_2_3 (+ in_2_2 in_2_1)) (+ in_1_3 in_1_2)) (+ (+ in_1_1 in_0_3) (+ in_0_2 in_0_1))) (+ (+ (+ in_2_3 in_2_2) (+ in_1_3 in_1_2)) (+ in_0_3 in_0_2)) (+ (+ in_3_1 in_3_0) (+ (+ in_2_1 in_2_0) (+ in_1_1 in_1_0))) (+ (+ (+ in_3_2 (+ in_3_1 in_3_0)) (+ in_2_2 in_2_1)) (+ (+ in_2_0 in_1_2) (+ in_1_1 in_1_0))) (+ (+ (+ in_3_3 (+ in_3_2 in_3_1)) (+ in_2_3 in_2_2)) (+ (+ in_2_1 in_1_3) (+ in_1_2 in_1_1))) (+ (+ (+ in_3_3 in_3_2) (+ in_2_3 in_2_2)) (+ in_1_3 in_1_2)) (+ (+ in_3_1 in_3_0) (+ in_2_1 in_2_0)) (+ (+ (+ in_3_2 in_3_1) (+ in_3_0 in_2_2)) (+ in_2_1 in_2_0)) (+ (+ (+ in_3_3 in_3_2) (+ in_3_1 in_2_3)) (+ in_2_2 in_2_1)) (+ (+ in_3_3 in_3_2) (+ in_2_3 in_2_2)))</t>
+          <t>(Vec (+ (+ in_1_1 in_1_0) (+ in_0_1 in_0_0)) (+ (+ (+ in_1_2 in_1_1) (+ in_1_0 in_0_2)) (+ in_0_1 in_0_0)) (+ (+ (+ in_1_3 in_1_2) (+ in_1_1 in_0_3)) (+ in_0_2 in_0_1)) (+ (+ in_1_3 in_1_2) (+ in_0_3 in_0_2)) (+ (+ (+ in_2_1 in_2_0) (+ in_1_1 in_1_0)) (+ in_0_1 in_0_0)) (+ (+ (+ in_2_2 (+ in_2_1 in_2_0)) (+ in_1_2 in_1_1)) (+ (+ in_1_0 in_0_2) (+ in_0_1 in_0_0))) (+ (+ (+ in_2_3 (+ in_2_2 in_2_1)) (+ in_1_3 in_1_2)) (+ (+ in_1_1 in_0_3) (+ in_0_2 in_0_1))) (+ (+ (+ in_2_3 in_2_2) (+ in_1_3 in_1_2)) (+ in_0_3 in_0_2)) (+ (+ in_3_1 in_3_0) (+ (+ in_2_1 in_2_0) (+ in_1_1 in_1_0))) (+ (+ (+ in_3_2 (+ in_3_1 in_3_0)) (+ in_2_2 in_2_1)) (+ (+ in_2_0 in_1_2) (+ in_1_1 in_1_0))) (+ (+ (+ in_3_3 (+ in_3_2 in_3_1)) (+ in_2_3 in_2_2)) (+ (+ in_2_1 in_1_3) (+ in_1_2 in_1_1))) (+ (+ (+ in_3_3 in_3_2) (+ in_2_3 in_2_2)) (+ in_1_3 in_1_2)) (+ (+ in_3_1 in_3_0) (+ in_2_1 in_2_0)) (+ (+ (+ in_3_2 in_3_1) (+ in_3_0 in_2_2)) (+ in_2_1 in_2_0)) (+ (+ (+ in_3_3 in_3_2) (+ in_3_1 in_2_3)) (+ in_2_2 in_2_1)) (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (* 1 (+ (+ in_3_3 in_3_2) (+ in_2_3 in_2_2)))))))))))))))))))))))))))))))))))))))))))))))))))))))))))))))))))))))))))))</t>
         </is>
       </c>
       <c r="E196" t="n">
@@ -8669,13 +8669,13 @@
         <v>7.19</v>
       </c>
       <c r="I196" t="n">
-        <v>94.64</v>
+        <v>126.83</v>
       </c>
       <c r="J196" t="b">
         <v>0</v>
       </c>
       <c r="K196" t="n">
-        <v>8999905.359999999</v>
+        <v>8999873.17</v>
       </c>
       <c r="L196" t="n">
         <v>75</v>
@@ -8695,7 +8695,7 @@
       </c>
       <c r="D197" t="inlineStr">
         <is>
-          <t>(Vec (+ v2_0 (+ 2 (* v1_0 5))) (+ v2_1 (+ 2 (* v1_1 5))) (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ v2_2 (+ 2 (* v1_2 5))) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) (+ v2_3 (+ 2 (* v1_3 5))))</t>
+          <t>(Vec (+ v2_0 (+ 2 (* v1_0 5))) (+ v2_1 (+ 2 (* v1_1 5))) (+ v2_2 (+ 2 (* v1_2 5))) (+ v2_3 (+ 2 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (* v1_3 5))))))))))))))))))))))))))))))))))))))))))))))))))))))))))))))))))))))))))))))</t>
         </is>
       </c>
       <c r="E197" t="n">
@@ -8737,17 +8737,17 @@
       </c>
       <c r="D198" t="inlineStr">
         <is>
-          <t>(VecAdd (Vec v2_0 v2_1 v2_2 v2_3 v2_4 v2_5 v2_6 v2_7 v2_8 v2_9 v2_10 v2_11 v2_12 v2_13 v2_14 v2_15) (VecAdd (Vec 2 2 2 2 2 2 2 2 2 2 2 2 2 2 2 2) (Vec (* v1_0 5) (* v1_1 5) (* v1_2 5) (* v1_3 5) (* v1_4 5) (* v1_5 5) (* v1_6 5) (* v1_7 5) (* v1_8 5) (* v1_9 5) (* v1_10 5) (* v1_11 5) (* v1_12 5) (* v1_13 5) (* v1_14 5) (* v1_15 5))))</t>
+          <t>(Vec ( + v2_0 ( + 2 ( * v1_0 5 ) ) ) ( + v2_1 ( + 2 ( * v1_1 5 ) ) ) ( + v2_2 ( + 2 ( * v1_2 5 ) ) ) ( + v2_3 ( + 2 ( * v1_3 5 ) ) ) ( + v2_4 ( + 2 ( * v1_4 5 ) ) ) ( + v2_5 ( + 2 ( * v1_5 5 ) ) ) ( + v2_6 ( + 2 ( * v1_6 5 ) ) ) ( + v2_7 ( + 2 ( * v1_7 5 ) ) ) ( + v2_8 ( + 2 ( * v1_8 5 ) ) ) ( + v2_9 ( + 2 ( * v1_9 5 ) ) ) ( + v2_10 ( + 2 ( * v1_10 5 ) ) ) ( + v2_11 ( + 2 ( * v1_11 5 ) ) ) ( + v2_12 ( + 2 ( * v1_12 5 ) ) ) ( + v2_13 ( + 2 ( * v1_13 5 ) ) ) ( + v2_14 ( + 2 ( * v1_14 5 ) ) ) ( + v2_15 ( + 2 ( * v1_15 5 ) ) ) )</t>
         </is>
       </c>
       <c r="E198" t="n">
         <v>12006</v>
       </c>
       <c r="F198" t="n">
-        <v>4008</v>
+        <v>12006</v>
       </c>
       <c r="G198" t="n">
-        <v>66.62</v>
+        <v>0</v>
       </c>
       <c r="H198" t="n">
         <v>39.37</v>
@@ -8762,7 +8762,7 @@
         <v>8999960.630000001</v>
       </c>
       <c r="L198" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="199">
@@ -8779,32 +8779,32 @@
       </c>
       <c r="D199" t="inlineStr">
         <is>
-          <t>(Vec (+ (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (+ (- (+ v1_0 v2_0) (* (* v1_0 v2_0) 2)) (- (+ v1_1 v2_1) (* 2 (* v1_1 v2_1)))))))))))))))))))))))))))) (- (+ v1_2 v2_2) (* 2 (* v1_2 v2_2)))))</t>
+          <t>(Vec ( + ( + ( - ( + v1_0 v2_0 ) ( * ( * v1_0 v2_0 ) 2 ) ) ( - ( + v1_1 v2_1 ) ( * 2 ( * v1_1 v2_1 ) ) ) ) ( - ( + v1_2 v2_2 ) ( * 2 ( * v1_2 v2_2 ) ) ) ) )</t>
         </is>
       </c>
       <c r="E199" t="n">
         <v>3509</v>
       </c>
       <c r="F199" t="n">
-        <v>9557</v>
+        <v>3509</v>
       </c>
       <c r="G199" t="n">
-        <v>-172.36</v>
+        <v>0</v>
       </c>
       <c r="H199" t="n">
         <v>75.15000000000001</v>
       </c>
       <c r="I199" t="n">
-        <v>905.09</v>
+        <v>75.15000000000001</v>
       </c>
       <c r="J199" t="b">
         <v>0</v>
       </c>
       <c r="K199" t="n">
-        <v>8999094.91</v>
+        <v>8999924.85</v>
       </c>
       <c r="L199" t="n">
-        <v>73</v>
+        <v>1</v>
       </c>
     </row>
     <row r="200">
@@ -8821,32 +8821,32 @@
       </c>
       <c r="D200" t="inlineStr">
         <is>
-          <t>(Vec (+ (+ (- (+ v1_0 v2_0) (* (* v1_0 v2_0) 2)) (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (- (+ v1_1 v2_1) (* 2 (* v1_1 v2_1)))))))))))) (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (+ (+ (- (+ v1_2 v2_2) (* 2 (* v1_2 v2_2))) (- (+ v1_3 v2_3) (* 2 (* v1_3 v2_3)))) (* 1 (- (+ v1_4 v2_4) (* 2 (* v1_4 v2_4)))))))))))))</t>
+          <t>(Vec ( + ( + ( - ( + v1_0 v2_0 ) ( * ( * v1_0 v2_0 ) 2 ) ) ( - ( + v1_1 v2_1 ) ( * 2 ( * v1_1 v2_1 ) ) ) ) ( + ( + ( - ( + v1_2 v2_2 ) ( * 2 ( * v1_2 v2_2 ) ) ) ( - ( + v1_3 v2_3 ) ( * 2 ( * v1_3 v2_3 ) ) ) ) ( - ( + v1_4 v2_4 ) ( * 2 ( * v1_4 v2_4 ) ) ) ) ) )</t>
         </is>
       </c>
       <c r="E200" t="n">
         <v>6010</v>
       </c>
       <c r="F200" t="n">
-        <v>9775</v>
+        <v>6010</v>
       </c>
       <c r="G200" t="n">
-        <v>-62.65</v>
+        <v>0</v>
       </c>
       <c r="H200" t="n">
         <v>76.34999999999999</v>
       </c>
       <c r="I200" t="n">
-        <v>351.8</v>
+        <v>76.34999999999999</v>
       </c>
       <c r="J200" t="b">
         <v>0</v>
       </c>
       <c r="K200" t="n">
-        <v>8999648.199999999</v>
+        <v>8999923.65</v>
       </c>
       <c r="L200" t="n">
-        <v>40</v>
+        <v>1</v>
       </c>
     </row>
     <row r="201">
@@ -8863,29 +8863,29 @@
       </c>
       <c r="D201" t="inlineStr">
         <is>
-          <t>(Vec (+ (+ (+ (+ (- (+ v1_0 v2_0) (* (* v1_0 v2_0) 2)) (- (+ v1_1 v2_1) (* 2 (* v1_1 v2_1)))) (+ (- (+ v1_2 v2_2) (* 2 (* v1_2 v2_2))) (- (+ v1_3 v2_3) (* 2 (* v1_3 v2_3))))) (+ (+ (- (+ v1_4 v2_4) (* 2 (* v1_4 v2_4))) (- (+ v1_5 v2_5) (* 2 (* v1_5 v2_5)))) (+ (- (+ v1_6 v2_6) (* 2 (* v1_6 v2_6))) (- (+ v1_7 v2_7) (* 2 (* v1_7 v2_7)))))) (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (- (+ v1_8 v2_8) (* 2 (* v1_8 v2_8))) (- (+ v1_9 v2_9) (* 2 (* v1_9 v2_9)))) (+ (- (+ v1_10 v2_10) (* 2 (* v1_10 v2_10))) (- (+ v1_11 v2_11) (* 2 (* v1_11 v2_11))))) (+ (+ (- (+ v1_12 v2_12) (* 2 (* v1_12 v2_12))) (- (+ v1_13 v2_13) (* 2 (* v1_13 v2_13)))) (+ (- (+ v1_14 v2_14) (* 2 (* v1_14 v2_14))) (- (+ v1_15 v2_15) (* 2 (* v1_15 v2_15)))))) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0)))</t>
+          <t>(Vec (+ (+ (+ (+ (- (+ v1_0 v2_0) (* (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (* v1_0 v2_0)))))) 2)) (- (+ v1_1 v2_1) (* 2 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (* v1_1 v2_1))))))))) (+ (- (+ v1_2 v2_2) (* 2 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (* v1_2 v2_2)))))))) (- (+ v1_3 v2_3) (* 2 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (* v1_3 v2_3)))))))))) (+ (+ (- (+ v1_4 v2_4) (* 2 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (* v1_4 v2_4)))))))) (- (+ v1_5 v2_5) (* 2 (+ 0 (+ 0 (+ 0 (+ 0 (* v1_5 v2_5)))))))) (+ (- (+ v1_6 v2_6) (* 2 (+ 0 (+ 0 (+ 0 (+ 0 (* v1_6 v2_6))))))) (- (+ v1_7 v2_7) (* 2 (+ 0 (+ 0 (+ 0 (+ 0 (* v1_7 v2_7)))))))))) (+ (+ (+ (- (+ v1_8 v2_8) (* 2 (+ 0 (+ 0 (+ 0 (+ 0 (* v1_8 v2_8))))))) (- (+ v1_9 v2_9) (* 2 (+ 0 (+ 0 (+ 0 (+ 0 (* v1_9 v2_9)))))))) (+ (- (+ v1_10 v2_10) (* 2 (+ 0 (+ 0 (+ 0 (+ 0 (* v1_10 v2_10))))))) (- (+ v1_11 v2_11) (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (* 2 (* v1_11 v2_11)))))))))) (+ (+ (- (+ v1_12 v2_12) (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (* 2 (* v1_12 v2_12)))))))) (- (+ v1_13 v2_13) (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (* 2 (* v1_13 v2_13))))))))) (+ (- (+ v1_14 v2_14) (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (* 2 (* v1_14 v2_14)))))))) (- (+ v1_15 v2_15) (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (* 2 (* v1_15 v2_15)))))))))))))</t>
         </is>
       </c>
       <c r="E201" t="n">
         <v>19761</v>
       </c>
       <c r="F201" t="n">
-        <v>38335</v>
+        <v>38266</v>
       </c>
       <c r="G201" t="n">
-        <v>-93.98999999999999</v>
+        <v>-93.64</v>
       </c>
       <c r="H201" t="n">
         <v>77.55</v>
       </c>
       <c r="I201" t="n">
-        <v>166.2</v>
+        <v>83.54000000000001</v>
       </c>
       <c r="J201" t="b">
         <v>0</v>
       </c>
       <c r="K201" t="n">
-        <v>8999833.800000001</v>
+        <v>8999916.460000001</v>
       </c>
       <c r="L201" t="n">
         <v>75</v>
@@ -8905,29 +8905,29 @@
       </c>
       <c r="D202" t="inlineStr">
         <is>
-          <t>(Vec (+ c1_0 (+ c2_0 (* c0_0 (+ c3_0 (* c0_0 c4_0))))) (+ c1_1 (+ (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* c2_1 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) (* c0_1 (+ c3_1 (* c0_1 c4_1))))) (+ c1_2 (+ c2_2 (* c0_2 (+ c3_2 (* c0_2 c4_2))))) (+ c1_3 (+ c2_3 (* c0_3 (+ c3_3 (* c0_3 c4_3))))))</t>
+          <t>(Vec (+ c1_0 (+ c2_0 (* c0_0 (+ c3_0 (* c0_0 c4_0))))) (+ c1_1 (+ c2_1 (* c0_1 (+ c3_1 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (* c0_1 c4_1)))))))))))))))))))))))))))))) (+ c1_2 (+ c2_2 (* c0_2 (+ c3_2 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (* c0_2 c4_2)))))))))))))))))))))))))))))) (+ c1_3 (+ c2_3 (* c0_3 (+ c3_3 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (* c0_3 c4_3))))))))))))))))))))))))))))))</t>
         </is>
       </c>
       <c r="E202" t="n">
         <v>5009</v>
       </c>
       <c r="F202" t="n">
-        <v>23652</v>
+        <v>23534</v>
       </c>
       <c r="G202" t="n">
-        <v>-372.19</v>
+        <v>-369.83</v>
       </c>
       <c r="H202" t="n">
         <v>75.15000000000001</v>
       </c>
       <c r="I202" t="n">
-        <v>2563.78</v>
+        <v>105.1</v>
       </c>
       <c r="J202" t="b">
         <v>0</v>
       </c>
       <c r="K202" t="n">
-        <v>8997436.220000001</v>
+        <v>8999894.9</v>
       </c>
       <c r="L202" t="n">
         <v>75</v>
@@ -8947,29 +8947,29 @@
       </c>
       <c r="D203" t="inlineStr">
         <is>
-          <t>(Vec (+ c1_0 (+ c2_0 (* c0_0 (+ c3_0 (* c0_0 c4_0))))) (+ c1_1 (+ c2_1 (* c0_1 (+ c3_1 (* c0_1 c4_1))))) (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ c1_2 (+ c2_2 (* c0_2 (+ c3_2 (* c0_2 c4_2))))) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) (+ c1_3 (+ c2_3 (* c0_3 (+ c3_3 (* c0_3 c4_3))))) (+ c1_4 (+ c2_4 (* c0_4 (+ c3_4 (* c0_4 c4_4))))) (+ c1_5 (+ c2_5 (* c0_5 (+ c3_5 (* c0_5 c4_5))))) (+ c1_6 (+ c2_6 (* c0_6 (+ c3_6 (* c0_6 c4_6))))) (+ c1_7 (+ c2_7 (* c0_7 (+ c3_7 (* c0_7 c4_7))))) (+ c1_8 (+ c2_8 (* c0_8 (+ c3_8 (* c0_8 c4_8))))) (+ c1_9 (+ c2_9 (* c0_9 (+ c3_9 (* c0_9 c4_9))))) (+ c1_10 (+ c2_10 (* c0_10 (+ c3_10 (* c0_10 c4_10))))) (+ c1_11 (+ c2_11 (* c0_11 (+ c3_11 (* c0_11 c4_11))))) (+ c1_12 (+ c2_12 (* c0_12 (+ c3_12 (* c0_12 c4_12))))) (+ c1_13 (+ c2_13 (* c0_13 (+ c3_13 (* c0_13 c4_13))))) (+ c1_14 (+ c2_14 (* c0_14 (+ c3_14 (* c0_14 c4_14))))) (+ c1_15 (+ c2_15 (* c0_15 (+ c3_15 (* c0_15 c4_15))))))</t>
+          <t>(Vec (+ c1_0 (+ c2_0 (* c0_0 (+ c3_0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (* c0_0 c4_0)))))))))) (+ c1_1 (+ c2_1 (* c0_1 (+ c3_1 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (* c0_1 c4_1)))))))))) (+ c1_2 (+ c2_2 (* c0_2 (+ c3_2 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (* c0_2 c4_2)))))))))) (+ c1_3 (+ c2_3 (* c0_3 (+ c3_3 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (* c0_3 c4_3)))))))))) (+ c1_4 (+ c2_4 (* c0_4 (+ c3_4 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (* c0_4 c4_4)))))))))) (+ c1_5 (+ c2_5 (* c0_5 (+ c3_5 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (* c0_5 c4_5)))))))))) (+ c1_6 (+ c2_6 (* c0_6 (+ c3_6 (+ 0 (+ 0 (+ 0 (+ 0 (* c0_6 c4_6))))))))) (+ c1_7 (+ c2_7 (* c0_7 (+ c3_7 (+ 0 (+ 0 (+ 0 (+ 0 (* c0_7 c4_7))))))))) (+ c1_8 (+ c2_8 (* c0_8 (+ c3_8 (+ 0 (+ 0 (+ 0 (+ 0 (* c0_8 c4_8))))))))) (+ c1_9 (+ c2_9 (* c0_9 (+ c3_9 (+ 0 (+ 0 (+ 0 (+ 0 (* c0_9 c4_9))))))))) (+ c1_10 (+ c2_10 (* c0_10 (+ c3_10 (+ 0 (+ 0 (+ 0 (+ 0 (* c0_10 c4_10))))))))) (+ c1_11 (+ c2_11 (* c0_11 (+ c3_11 (+ 0 (+ 0 (+ 0 (+ 0 (* c0_11 c4_11))))))))) (+ c1_12 (+ c2_12 (* c0_12 (+ c3_12 (+ 0 (+ 0 (+ 0 (+ 0 (* c0_12 c4_12))))))))) (+ c1_13 (+ c2_13 (* c0_13 (+ c3_13 (+ 0 (+ 0 (+ 0 (+ 0 (* c0_13 c4_13))))))))) (+ c1_14 (+ c2_14 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (* c0_14 (+ c3_14 (* c0_14 c4_14))))))))))) (+ c1_15 (+ c2_15 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (* c0_15 (+ c3_15 (* c0_15 c4_15))))))))))))</t>
         </is>
       </c>
       <c r="E203" t="n">
         <v>20009</v>
       </c>
       <c r="F203" t="n">
-        <v>38583</v>
+        <v>38515</v>
       </c>
       <c r="G203" t="n">
-        <v>-92.83</v>
+        <v>-92.48999999999999</v>
       </c>
       <c r="H203" t="n">
         <v>75.15000000000001</v>
       </c>
       <c r="I203" t="n">
-        <v>163.8</v>
+        <v>82.34</v>
       </c>
       <c r="J203" t="b">
         <v>0</v>
       </c>
       <c r="K203" t="n">
-        <v>8999836.199999999</v>
+        <v>8999917.66</v>
       </c>
       <c r="L203" t="n">
         <v>75</v>
@@ -8989,32 +8989,32 @@
       </c>
       <c r="D204" t="inlineStr">
         <is>
-          <t>(Vec (+ (+ (* (- c2_0 c1_0) (- c2_0 c1_0)) (* (- c2_1 c1_1) (- c2_1 c1_1))) (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (* (- c2_2 c1_2) (- c2_2 c1_2)) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0)))</t>
+          <t>(Vec ( + ( + ( * ( - c2_0 c1_0 ) ( - c2_0 c1_0 ) ) ( * ( - c2_1 c1_1 ) ( - c2_1 c1_1 ) ) ) ( * ( - c2_2 c1_2 ) ( - c2_2 c1_2 ) ) ) )</t>
         </is>
       </c>
       <c r="E204" t="n">
         <v>2757</v>
       </c>
       <c r="F204" t="n">
-        <v>21330</v>
+        <v>2757</v>
       </c>
       <c r="G204" t="n">
-        <v>-673.67</v>
+        <v>0</v>
       </c>
       <c r="H204" t="n">
         <v>40.57</v>
       </c>
       <c r="I204" t="n">
-        <v>128.02</v>
+        <v>40.57</v>
       </c>
       <c r="J204" t="b">
         <v>0</v>
       </c>
       <c r="K204" t="n">
-        <v>8999871.98</v>
+        <v>8999959.43</v>
       </c>
       <c r="L204" t="n">
-        <v>75</v>
+        <v>1</v>
       </c>
     </row>
     <row r="205">
@@ -9031,29 +9031,29 @@
       </c>
       <c r="D205" t="inlineStr">
         <is>
-          <t>(Vec (+ (+ (* (- c2_0 c1_0) (- c2_0 c1_0)) (* (- c2_1 c1_1) (- c2_1 c1_1))) (+ (+ (* (- c2_2 c1_2) (- c2_2 c1_2)) (* (- c2_3 c1_3) (- c2_3 c1_3))) (* (- c2_4 c1_4) (- c2_4 c1_4)))))</t>
+          <t>(Vec (+ (+ (* (- c2_0 c1_0) (- c2_0 c1_0)) (* (- c2_1 c1_1) (- c2_1 c1_1))) (+ (+ (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (* (- c2_2 c1_2) (- c2_2 c1_2))))))))))))))))))))))))))))))))))))))) (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (* (- c2_3 c1_3) (- c2_3 c1_3)))))))))))))))))))))))))))))))))))))))) (* (- c2_4 c1_4) (- c2_4 c1_4)))))</t>
         </is>
       </c>
       <c r="E205" t="n">
         <v>4758</v>
       </c>
       <c r="F205" t="n">
-        <v>4758</v>
+        <v>23295</v>
       </c>
       <c r="G205" t="n">
-        <v>0</v>
+        <v>-389.6</v>
       </c>
       <c r="H205" t="n">
         <v>41.77</v>
       </c>
       <c r="I205" t="n">
-        <v>41.77</v>
+        <v>86.09</v>
       </c>
       <c r="J205" t="b">
         <v>0</v>
       </c>
       <c r="K205" t="n">
-        <v>8999958.23</v>
+        <v>8999913.91</v>
       </c>
       <c r="L205" t="n">
         <v>75</v>
@@ -9115,29 +9115,29 @@
       </c>
       <c r="D207" t="inlineStr">
         <is>
-          <t>(Vec (+ (+ (* v1_0 v2_0) (* v1_1 v2_1)) (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (* v1_2 v2_2) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0)))</t>
+          <t>(Vec (+ (+ (* v1_0 v2_0) (+ (* (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (+ (+ (+ (+ (+ (+ (+ (+ (+ (* 1 (* 1 (* 1 (* 1 (* 1 (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ v1_1 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0)))))) 0) 0) 0) 0) 0) 0) 0) 0) 0)))))))))))))))))))))))))))))))))))))))))))) v2_1) 0)) (* v1_2 v2_2)))</t>
         </is>
       </c>
       <c r="E207" t="n">
         <v>1256</v>
       </c>
       <c r="F207" t="n">
-        <v>19829</v>
+        <v>19878</v>
       </c>
       <c r="G207" t="n">
-        <v>-1478.74</v>
+        <v>-1482.64</v>
       </c>
       <c r="H207" t="n">
         <v>39.37</v>
       </c>
       <c r="I207" t="n">
-        <v>126.83</v>
+        <v>1730.41</v>
       </c>
       <c r="J207" t="b">
         <v>0</v>
       </c>
       <c r="K207" t="n">
-        <v>8999873.17</v>
+        <v>8998269.59</v>
       </c>
       <c r="L207" t="n">
         <v>75</v>
@@ -9199,29 +9199,29 @@
       </c>
       <c r="D209" t="inlineStr">
         <is>
-          <t>(Vec (+ (+ (+ (+ (* v1_0 v2_0) (* v1_1 v2_1)) (+ (* v1_2 v2_2) (* v1_3 v2_3))) (+ (+ (* v1_4 v2_4) (* v1_5 v2_5)) (+ (* v1_6 v2_6) (* v1_7 v2_7)))) (+ (+ (+ (* v1_8 v2_8) (* v1_9 v2_9)) (+ (* v1_10 v2_10) (* v1_11 v2_11))) (+ (+ (* v1_12 v2_12) (* v1_13 v2_13)) (+ (* v1_14 v2_14) (* v1_15 v2_15))))))</t>
+          <t>(Vec (+ (+ (+ (+ (* v1_0 v2_0) (* v1_1 v2_1)) (+ (* v1_2 v2_2) (* v1_3 v2_3))) (+ (+ (* v1_4 v2_4) (* v1_5 v2_5)) (+ (* v1_6 v2_6) (* v1_7 v2_7)))) (+ (+ (+ (* v1_8 v2_8) (* v1_9 v2_9)) (+ (* v1_10 v2_10) (* v1_11 v2_11))) (+ (+ (* v1_12 v2_12) (* v1_13 v2_13)) (+ (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (* v1_14 v2_14)))))))))))))))))))))))))))))))))))))) (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (* v1_15 v2_15)))))))))))))))))))))))))))))))))))))))))))</t>
         </is>
       </c>
       <c r="E209" t="n">
         <v>7758</v>
       </c>
       <c r="F209" t="n">
-        <v>7758</v>
+        <v>26295</v>
       </c>
       <c r="G209" t="n">
-        <v>0</v>
+        <v>-238.94</v>
       </c>
       <c r="H209" t="n">
         <v>41.77</v>
       </c>
       <c r="I209" t="n">
-        <v>41.77</v>
+        <v>86.09</v>
       </c>
       <c r="J209" t="b">
         <v>0</v>
       </c>
       <c r="K209" t="n">
-        <v>8999958.23</v>
+        <v>8999913.91</v>
       </c>
       <c r="L209" t="n">
         <v>75</v>
@@ -9241,29 +9241,29 @@
       </c>
       <c r="D210" t="inlineStr">
         <is>
-          <t>(Vec (+ in_1_1 (* in_0_1 2)) (+ (+ in_1_2 (- in_1_0)) (+ (* in_0_2 2) (* in_0_0 -2))) (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (+ (- in_1_1) (* in_0_1 -2)) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) (+ in_2_1 (+ in_0_1 (* in_1_1 2))) (+ (+ in_2_2 (- in_2_0)) (+ (+ in_0_2 (- in_0_0)) (+ (* in_1_2 2) (* in_1_0 -2)))) (+ (- in_2_1) (+ (- in_0_1) (* in_1_1 -2))) (+ in_1_1 (* in_2_1 2)) (+ (+ in_1_2 (- in_1_0)) (+ (* in_2_2 2) (* in_2_0 -2))) (+ (- in_1_1) (* in_2_1 -2)))</t>
+          <t>(Vec (+ in_1_1 (* in_0_1 2)) (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (+ (* 1 (+ (+ in_1_2 (- in_1_0)) 0)) (* 1 (+ (* in_0_2 2) (* in_0_0 -2))))))))))) (+ (- in_1_1) (* in_0_1 -2)) (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (+ in_2_1 (+ in_0_1 (* in_1_1 2))))))))))) (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (+ (+ in_2_2 (- in_2_0)) (+ (+ in_0_2 (- in_0_0)) (+ (* in_1_2 2) (* in_1_0 -2)))))))))))) (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (+ (- in_2_1) (+ (- in_0_1) (* in_1_1 -2))))))))))) (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (+ in_1_1 (* in_2_1 2)))))))))) (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (+ (+ in_1_2 (- in_1_0)) (+ (* in_2_2 2) (* in_2_0 -2))))))))))) (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (+ (- in_1_1) (* in_2_1 -2)))))))))))</t>
         </is>
       </c>
       <c r="E210" t="n">
         <v>9757</v>
       </c>
       <c r="F210" t="n">
-        <v>28329</v>
+        <v>24273</v>
       </c>
       <c r="G210" t="n">
-        <v>-190.35</v>
+        <v>-148.78</v>
       </c>
       <c r="H210" t="n">
         <v>40.57</v>
       </c>
       <c r="I210" t="n">
-        <v>126.83</v>
+        <v>317.22</v>
       </c>
       <c r="J210" t="b">
         <v>0</v>
       </c>
       <c r="K210" t="n">
-        <v>8999873.17</v>
+        <v>8999682.779999999</v>
       </c>
       <c r="L210" t="n">
         <v>75</v>
@@ -9283,32 +9283,32 @@
       </c>
       <c r="D211" t="inlineStr">
         <is>
-          <t>(Vec (+ in_1_1 (* in_0_1 2)) (+ (+ in_1_2 (+ 0 (+ 0 (+ 0 (- in_1_0))))) (+ (* in_0_2 2) (* in_0_0 -2))) (+ (+ in_1_3 (+ 0 (+ 0 (+ 0 (- in_1_1))))) (+ (* in_0_3 2) (* in_0_1 -2))) (+ (+ in_1_4 (+ 0 (+ 0 (+ 0 (- in_1_2))))) (+ (* in_0_4 2) (* in_0_2 -2))) (+ (- in_1_3) (* in_0_3 -2)) (+ in_2_1 (+ in_0_1 (* in_1_1 2))) (+ (+ in_2_2 (+ 0 (+ 0 (+ 0 (- in_2_0))))) (+ (+ in_0_2 (+ 0 (+ 0 (- in_0_0)))) (+ (* in_1_2 2) (* in_1_0 -2)))) (+ (+ in_2_3 (+ 0 (+ 0 (+ 0 (- in_2_1))))) (+ (+ in_0_3 (+ 0 (+ 0 (- in_0_1)))) (+ (* in_1_3 2) (* in_1_1 -2)))) (+ (+ in_2_4 (+ 0 (+ 0 (+ 0 (- in_2_2))))) (+ (+ in_0_4 (+ 0 (+ 0 (- in_0_2)))) (+ (* in_1_4 2) (* in_1_2 -2)))) (+ (+ 0 (+ 0 (+ 0 (+ 0 (- in_2_3))))) (+ (+ 0 (+ 0 (+ 0 (- in_0_3)))) (* in_1_3 -2))) (+ in_3_1 (+ in_1_1 (* in_2_1 2))) (+ (+ in_3_2 (+ 0 (+ 0 (+ 0 (- in_3_0))))) (+ (+ in_1_2 (+ 0 (+ 0 (- in_1_0)))) (+ (* in_2_2 2) (* in_2_0 -2)))) (+ (+ in_3_3 (+ 0 (+ 0 (+ 0 (- in_3_1))))) (+ (+ in_1_3 (+ 0 (+ 0 (- in_1_1)))) (+ (* in_2_3 2) (* in_2_1 -2)))) (+ (+ in_3_4 (+ 0 (+ 0 (+ 0 (- in_3_2))))) (+ (+ in_1_4 (+ 0 (+ 0 (- in_1_2)))) (+ (* in_2_4 2) (* in_2_2 -2)))) (+ (+ 0 (+ 0 (+ 0 (- in_3_3)))) (+ (+ 0 (+ 0 (- in_1_3))) (* in_2_3 -2))) (+ in_4_1 (+ in_2_1 (* in_3_1 2))) (+ (+ in_4_2 (+ 0 (+ 0 (- in_4_0)))) (+ (+ in_2_2 (+ 0 (- in_2_0))) (+ (* in_3_2 2) (* in_3_0 -2)))) (+ (+ in_4_3 (+ 0 (+ 0 (- in_4_1)))) (+ (+ in_2_3 (+ 0 (- in_2_1))) (+ (* in_3_3 2) (* in_3_1 -2)))) (+ (+ in_4_4 (+ 0 (+ 0 (- in_4_2)))) (+ (+ in_2_4 (+ 0 (- in_2_2))) (+ (* in_3_4 2) (* in_3_2 -2)))) (+ (+ 0 (+ 0 (+ 0 (- in_4_3)))) (+ (+ 0 (+ 0 (- in_2_3))) (* in_3_3 -2))) (+ in_3_1 (* in_4_1 2)) (+ (+ in_3_2 (+ 0 (+ 0 (- in_3_0)))) (+ (* in_4_2 2) (* in_4_0 -2))) (+ (+ in_3_3 (+ 0 (+ 0 (- in_3_1)))) (+ (* in_4_3 2) (* in_4_1 -2))) (+ (+ in_3_4 (+ 0 (+ 0 (- in_3_2)))) (+ (* in_4_4 2) (* in_4_2 -2))) (+ (+ 0 (+ 0 (+ 0 (- in_3_3)))) (* in_4_3 -2)))</t>
+          <t>(Vec ( + in_1_1 ( * in_0_1 2 ) ) ( + ( + in_1_2 ( - in_1_0 ) ) ( + ( * in_0_2 2 ) ( * in_0_0 -2 ) ) ) ( + ( + in_1_3 ( - in_1_1 ) ) ( + ( * in_0_3 2 ) ( * in_0_1 -2 ) ) ) ( + ( + in_1_4 ( - in_1_2 ) ) ( + ( * in_0_4 2 ) ( * in_0_2 -2 ) ) ) ( + ( - in_1_3 ) ( * in_0_3 -2 ) ) ( + in_2_1 ( + in_0_1 ( * in_1_1 2 ) ) ) ( + ( + in_2_2 ( - in_2_0 ) ) ( + ( + in_0_2 ( - in_0_0 ) ) ( + ( * in_1_2 2 ) ( * in_1_0 -2 ) ) ) ) ( + ( + in_2_3 ( - in_2_1 ) ) ( + ( + in_0_3 ( - in_0_1 ) ) ( + ( * in_1_3 2 ) ( * in_1_1 -2 ) ) ) ) ( + ( + in_2_4 ( - in_2_2 ) ) ( + ( + in_0_4 ( - in_0_2 ) ) ( + ( * in_1_4 2 ) ( * in_1_2 -2 ) ) ) ) ( + ( - in_2_3 ) ( + ( - in_0_3 ) ( * in_1_3 -2 ) ) ) ( + in_3_1 ( + in_1_1 ( * in_2_1 2 ) ) ) ( + ( + in_3_2 ( - in_3_0 ) ) ( + ( + in_1_2 ( - in_1_0 ) ) ( + ( * in_2_2 2 ) ( * in_2_0 -2 ) ) ) ) ( + ( + in_3_3 ( - in_3_1 ) ) ( + ( + in_1_3 ( - in_1_1 ) ) ( + ( * in_2_3 2 ) ( * in_2_1 -2 ) ) ) ) ( + ( + in_3_4 ( - in_3_2 ) ) ( + ( + in_1_4 ( - in_1_2 ) ) ( + ( * in_2_4 2 ) ( * in_2_2 -2 ) ) ) ) ( + ( - in_3_3 ) ( + ( - in_1_3 ) ( * in_2_3 -2 ) ) ) ( + in_4_1 ( + in_2_1 ( * in_3_1 2 ) ) ) ( + ( + in_4_2 ( - in_4_0 ) ) ( + ( + in_2_2 ( - in_2_0 ) ) ( + ( * in_3_2 2 ) ( * in_3_0 -2 ) ) ) ) ( + ( + in_4_3 ( - in_4_1 ) ) ( + ( + in_2_3 ( - in_2_1 ) ) ( + ( * in_3_3 2 ) ( * in_3_1 -2 ) ) ) ) ( + ( + in_4_4 ( - in_4_2 ) ) ( + ( + in_2_4 ( - in_2_2 ) ) ( + ( * in_3_4 2 ) ( * in_3_2 -2 ) ) ) ) ( + ( - in_4_3 ) ( + ( - in_2_3 ) ( * in_3_3 -2 ) ) ) ( + in_3_1 ( * in_4_1 2 ) ) ( + ( + in_3_2 ( - in_3_0 ) ) ( + ( * in_4_2 2 ) ( * in_4_0 -2 ) ) ) ( + ( + in_3_3 ( - in_3_1 ) ) ( + ( * in_4_3 2 ) ( * in_4_1 -2 ) ) ) ( + ( + in_3_4 ( - in_3_2 ) ) ( + ( * in_4_4 2 ) ( * in_4_2 -2 ) ) ) ( + ( - in_3_3 ) ( * in_4_3 -2 ) ) )</t>
         </is>
       </c>
       <c r="E211" t="n">
         <v>37757</v>
       </c>
       <c r="F211" t="n">
-        <v>56259</v>
+        <v>37757</v>
       </c>
       <c r="G211" t="n">
-        <v>-49</v>
+        <v>0</v>
       </c>
       <c r="H211" t="n">
         <v>40.57</v>
       </c>
       <c r="I211" t="n">
-        <v>42.97</v>
+        <v>40.57</v>
       </c>
       <c r="J211" t="b">
         <v>0</v>
       </c>
       <c r="K211" t="n">
-        <v>8999957.029999999</v>
+        <v>8999959.43</v>
       </c>
       <c r="L211" t="n">
-        <v>75</v>
+        <v>1</v>
       </c>
     </row>
     <row r="212">
@@ -9325,29 +9325,29 @@
       </c>
       <c r="D212" t="inlineStr">
         <is>
-          <t>(Vec (+ (+ (* a_0_0 b_0_0) (* a_0_1 b_1_0)) (+ (* a_0_2 b_2_0) (* a_0_3 b_3_0))) (+ (+ (* a_0_0 b_0_1) (* a_0_1 b_1_1)) (+ (* a_0_2 b_2_1) (* a_0_3 b_3_1))) (+ (+ (+ (+ (+ (+ (+ (* a_0_0 b_0_2) (* a_0_1 b_1_2)) (+ (* a_0_2 b_2_2) (* a_0_3 b_3_2))) (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- 0))))))))))))))))))))))))))))))))))) (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- 0)))))))))))))))))))))))))))))))))))) 0) 0) 0) (+ (+ (* a_0_0 b_0_3) (* a_0_1 b_1_3)) (+ (* a_0_2 b_2_3) (* a_0_3 b_3_3))) (+ (+ (* a_1_0 b_0_0) (* a_1_1 b_1_0)) (+ (* a_1_2 b_2_0) (* a_1_3 b_3_0))) (+ (+ (* a_1_0 b_0_1) (* a_1_1 b_1_1)) (+ (* a_1_2 b_2_1) (* a_1_3 b_3_1))) (+ (+ (* a_1_0 b_0_2) (* a_1_1 b_1_2)) (+ (* a_1_2 b_2_2) (* a_1_3 b_3_2))) (+ (+ (* a_1_0 b_0_3) (* a_1_1 b_1_3)) (+ (* a_1_2 b_2_3) (* a_1_3 b_3_3))) (+ (+ (* a_2_0 b_0_0) (* a_2_1 b_1_0)) (+ (* a_2_2 b_2_0) (* a_2_3 b_3_0))) (+ (+ (* a_2_0 b_0_1) (* a_2_1 b_1_1)) (+ (* a_2_2 b_2_1) (* a_2_3 b_3_1))) (+ (+ (* a_2_0 b_0_2) (* a_2_1 b_1_2)) (+ (* a_2_2 b_2_2) (* a_2_3 b_3_2))) (+ (+ (* a_2_0 b_0_3) (* a_2_1 b_1_3)) (+ (* a_2_2 b_2_3) (* a_2_3 b_3_3))) (+ (+ (* a_3_0 b_0_0) (* a_3_1 b_1_0)) (+ (* a_3_2 b_2_0) (* a_3_3 b_3_0))) (+ (+ (* a_3_0 b_0_1) (* a_3_1 b_1_1)) (+ (* a_3_2 b_2_1) (* a_3_3 b_3_1))) (+ (+ (* a_3_0 b_0_2) (* a_3_1 b_1_2)) (+ (* a_3_2 b_2_2) (* a_3_3 b_3_2))) (+ (+ (* a_3_0 b_0_3) (* a_3_1 b_1_3)) (+ (* a_3_2 b_2_3) (* a_3_3 b_3_3))))</t>
+          <t>(Vec (* 1 (* 1 (* 1 (+ (+ (* a_0_0 b_0_0) (* a_0_1 b_1_0)) (+ (* a_0_2 b_2_0) (* a_0_3 b_3_0)))))) (* 1 (* 1 (* 1 (+ (+ (* a_0_0 b_0_1) (* a_0_1 b_1_1)) (+ (* a_0_2 b_2_1) (* a_0_3 b_3_1)))))) (* 1 (* 1 (* 1 (+ (+ (* a_0_0 b_0_2) (* a_0_1 b_1_2)) (+ (* a_0_2 b_2_2) (* a_0_3 b_3_2)))))) (* 1 (* 1 (* 1 (* 1 (+ (+ (* a_0_0 b_0_3) (* a_0_1 b_1_3)) (+ (* a_0_2 b_2_3) (* a_0_3 b_3_3))))))) (* 1 (* 1 (* 1 (* 1 (+ (+ (* a_1_0 b_0_0) (* a_1_1 b_1_0)) (+ (* a_1_2 b_2_0) (* a_1_3 b_3_0))))))) (* 1 (* 1 (* 1 (* 1 (+ (+ (* a_1_0 b_0_1) (* a_1_1 b_1_1)) (+ (* a_1_2 b_2_1) (* a_1_3 b_3_1))))))) (* 1 (* 1 (* 1 (* 1 (+ (+ (* a_1_0 b_0_2) (* a_1_1 b_1_2)) (+ (* a_1_2 b_2_2) (* a_1_3 b_3_2))))))) (* 1 (* 1 (* 1 (* 1 (+ (+ (* a_1_0 b_0_3) (* a_1_1 b_1_3)) (+ (* a_1_2 b_2_3) (* a_1_3 b_3_3))))))) (* 1 (* 1 (* 1 (* 1 (+ (+ (* a_2_0 b_0_0) (* a_2_1 b_1_0)) (+ (* a_2_2 b_2_0) (* a_2_3 b_3_0))))))) (* 1 (* 1 (* 1 (* 1 (+ (+ (* a_2_0 b_0_1) (* a_2_1 b_1_1)) (+ (* a_2_2 b_2_1) (* a_2_3 b_3_1))))))) (* 1 (* 1 (* 1 (* 1 (+ (+ (* a_2_0 b_0_2) (* a_2_1 b_1_2)) (+ (* a_2_2 b_2_2) (* a_2_3 b_3_2))))))) (* 1 (* 1 (* 1 (+ (+ (* a_2_0 b_0_3) (* a_2_1 b_1_3)) (+ (* a_2_2 b_2_3) (* a_2_3 b_3_3)))))) (* 1 (* 1 (* 1 (+ (+ (* a_3_0 b_0_0) (* a_3_1 b_1_0)) (+ (* a_3_2 b_2_0) (* a_3_3 b_3_0)))))) (* 1 (* 1 (* 1 (+ (+ (* a_3_0 b_0_1) (* a_3_1 b_1_1)) (+ (* a_3_2 b_2_1) (* a_3_3 b_3_1)))))) (* 1 (* 1 (* 1 (+ (+ (* a_3_0 b_0_2) (* a_3_1 b_1_2)) (+ (* a_3_2 b_2_2) (* a_3_3 b_3_2)))))) (* 1 (* 1 (* 1 (+ (+ (* a_3_0 b_0_3) (* a_3_1 b_1_3)) (+ (* a_3_2 b_2_3) (* a_3_3 b_3_3)))))))</t>
         </is>
       </c>
       <c r="E212" t="n">
         <v>28006</v>
       </c>
       <c r="F212" t="n">
-        <v>46542</v>
+        <v>42014</v>
       </c>
       <c r="G212" t="n">
-        <v>-66.19</v>
+        <v>-50.02</v>
       </c>
       <c r="H212" t="n">
         <v>39.37</v>
       </c>
       <c r="I212" t="n">
-        <v>82.5</v>
+        <v>177.7</v>
       </c>
       <c r="J212" t="b">
         <v>0</v>
       </c>
       <c r="K212" t="n">
-        <v>8999917.5</v>
+        <v>8999822.300000001</v>
       </c>
       <c r="L212" t="n">
         <v>75</v>
@@ -9367,29 +9367,29 @@
       </c>
       <c r="D213" t="inlineStr">
         <is>
-          <t>(Vec (+ (* (+ (* (+ (* o4 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (- 1 c34))))))))))))))))))))) (* c34 o3)) (- 1 c23)) (* c23 (+ (* o4 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (- 1 c24))))))))))))))))))))) (* c24 o2)))) (- 1 c12)) (* c12 (+ (* (+ (* o4 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (- 1 c34)))))))))))))))))))) (* c34 o3)) (- 1 c13)) (* c13 (+ (* o4 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (- 1 c14)))))))))))))))))))) (* c14 o1)))))))</t>
+          <t>(Vec (+ (* (+ (* (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (+ (* o4 (- 1 c34)) (* c34 o3)))))))))))))))))) (- 1 c23)) (* c23 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (+ (* o4 (- 1 c24)) (* c24 o2)))))))))))))))))))) (- 1 c12)) (* c12 (+ (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (+ (+ (+ (+ (+ (+ (+ (* 1 (+ (+ (+ (* (+ (* o4 (- 1 c34)) (* c34 o3)) (- 1 c13)) 0) 0) 0)) 0) 0) 0) 0) 0) 0) 0))))))))))))))))) (* c13 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (+ (* o4 (- 1 c14)) (* c14 o1))))))))))))))))))))))</t>
         </is>
       </c>
       <c r="E213" t="n">
         <v>7012</v>
       </c>
       <c r="F213" t="n">
-        <v>25550</v>
+        <v>25556</v>
       </c>
       <c r="G213" t="n">
-        <v>-264.38</v>
+        <v>-264.46</v>
       </c>
       <c r="H213" t="n">
         <v>110.93</v>
       </c>
       <c r="I213" t="n">
-        <v>767.97</v>
+        <v>710.79</v>
       </c>
       <c r="J213" t="b">
         <v>0</v>
       </c>
       <c r="K213" t="n">
-        <v>8999232.029999999</v>
+        <v>8999289.210000001</v>
       </c>
       <c r="L213" t="n">
         <v>75</v>
@@ -9409,29 +9409,29 @@
       </c>
       <c r="D214" t="inlineStr">
         <is>
-          <t>(Vec (+ (* (+ (* (+ (* o3214 (- 1 c34)) (* c34 (+ (* (+ (* o4321 (- 1 c34)) (* c34 o3421)) (- 1 c24)) (* c24 (+ (* o3241 (- 1 c14)) (* c14 o3214)))))) (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (* (- 1 c23) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1) 1)) (* c23 (+ (* (+ (* o2314 (- 1 c24)) (* c24 (+ (* (- 1 c34) (+ (* o4231 (- 1 c24)) (* c24 o2431))) (* c34 (+ (* o2341 (- 1 c14)) (* c14 o2314)))))) (- 1 c13)) (* c13 (+ (* o2134 (- 1 c24)) (* c24 (+ (* (- 1 c14) (+ (* o4213 (- 1 c24)) (* c24 o2413))) (* c14 (+ (* o2143 (- 1 c34)) (* c34 o2134)))))))))) (- 1 c12)) (* c12 (+ (* (- 1 c13) (+ (* o3124 (- 1 c34)) (* c34 (+ (* (- 1 c14) (+ (* o4312 (- 1 c34)) (* c34 o3412))) (* c14 (+ (* o3142 (- 1 c24)) (* c24 o3124))))))) (* c13 (+ (* (- 1 c23) (+ (* o1324 (- 1 c14)) (* c14 (+ (* (- 1 c34) (+ (* o4132 (- 1 c14)) (* c14 o1432))) (* c34 (+ (* o1342 (- 1 c24)) (* c24 o1324))))))) (* c23 (+ (* o1234 (- 1 c14)) (* c14 (+ (* (- 1 c24) (+ (* o4123 (- 1 c14)) (* c14 o1423))) (* c24 (+ (* o1243 (- 1 c34)) (* c34 o1234)))))))))))))</t>
+          <t>(Vec (+ (* (+ (* (+ (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (* o3214 (- 1 c34))))))))))))) (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (* c34 (+ (* (+ (* o4321 (- 1 c34)) (* c34 o3421)) (- 1 c24)) (* c24 (+ (* o3241 (- 1 c14)) (* c14 o3214))))))))))))))))) (- 1 c23)) (* c23 (+ (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (* (+ (* o2314 (- 1 c24)) (* c24 (+ (* (- 1 c34) (+ (* o4231 (- 1 c24)) (* c24 o2431))) (* c34 (+ (* o2341 (- 1 c14)) (* c14 o2314)))))) (- 1 c13)))))))))))) (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (* c13 (+ (* o2134 (- 1 c24)) (* c24 (+ (* (- 1 c14) (+ (* o4213 (- 1 c24)) (* c24 o2413))) (* c14 (+ (* o2143 (- 1 c34)) (* c34 o2134)))))))))))))))))))) (- 1 c12)) (* c12 (+ (* (- 1 c13) (+ (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (* o3124 (- 1 c34)))))))))))) (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (* c34 (+ (* (- 1 c14) (+ (* o4312 (- 1 c34)) (* c34 o3412))) (* c14 (+ (* o3142 (- 1 c24)) (* c24 o3124))))))))))))))))) (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (* c13 (+ (* (- 1 c23) (+ (* o1324 (- 1 c14)) (* c14 (+ (* (- 1 c34) (+ (* o4132 (- 1 c14)) (* c14 o1432))) (* c34 (+ (* o1342 (- 1 c24)) (* c24 o1324))))))) (* c23 (+ (* o1234 (- 1 c14)) (* c14 (+ (* (- 1 c24) (+ (* o4123 (- 1 c14)) (* c14 o1423))) (* c24 (+ (* o1243 (- 1 c34)) (* c34 o1234)))))))))))))))))))))))))</t>
         </is>
       </c>
       <c r="E214" t="n">
         <v>29021</v>
       </c>
       <c r="F214" t="n">
-        <v>47657</v>
+        <v>47533</v>
       </c>
       <c r="G214" t="n">
-        <v>-64.22</v>
+        <v>-63.79</v>
       </c>
       <c r="H214" t="n">
         <v>218.27</v>
       </c>
       <c r="I214" t="n">
-        <v>2634.14</v>
+        <v>232.64</v>
       </c>
       <c r="J214" t="b">
         <v>0</v>
       </c>
       <c r="K214" t="n">
-        <v>8997365.859999999</v>
+        <v>8999767.359999999</v>
       </c>
       <c r="L214" t="n">
         <v>75</v>
@@ -9451,29 +9451,29 @@
       </c>
       <c r="D215" t="inlineStr">
         <is>
-          <t>(VecMul (Vec (* (* (+ (* (* x10106 x10108) x10110) x10112) x10115) (* x10117 x10119)) (+ (+ x10121 (* x10125 (+ (+ (* (* x10146 x10147) (* (+ x10149 x10150) x10152)) (* (* (* x10132 x10133) (+ x10135 x10136)) (+ (* x10139 x10140) x10142))) (+ (+ x10154 (* (* x10159 (+ (+ x10162 x10163) x10165)) x10167)) (+ (+ x10170 x10173) (+ x10176 x10178)))))) (+ x10181 x10183))) (&lt;&lt; (Vec (* (* (+ (* (* x10106 x10108) x10110) x10112) x10115) (* x10117 x10119)) (+ (+ x10121 (* x10125 (+ (+ (* (* x10146 x10147) (* (+ x10149 x10150) x10152)) (* (* (* x10132 x10133) (+ x10135 x10136)) (+ (* x10139 x10140) x10142))) (+ (+ x10154 (* (* x10159 (+ (+ x10162 x10163) x10165)) x10167)) (+ (+ x10170 x10173) (+ x10176 x10178)))))) (+ x10181 x10183))) 1))</t>
+          <t>(Vec (* (* (* (+ (* (* x10106 x10108) x10110) x10112) x10115) (* x10117 x10119)) (+ (+ x10121 (* x10125 (+ (+ (* (* (* x10132 x10133) (+ x10135 x10136)) (+ (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (* x10139 x10140)))))))))))))))))))))))))))))))))))))) x10142)) (* (* x10146 x10147) (* (+ x10149 x10150) x10152))) (+ (+ x10154 (* (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (+ 0 (* x10159 (+ (+ x10162 x10163) x10165))))))))))))))))))))))))))))))))))))))) x10167)) (+ (+ x10170 x10173) (+ x10176 x10178)))))) (+ x10181 x10183))))</t>
         </is>
       </c>
       <c r="E215" t="n">
         <v>8018</v>
       </c>
       <c r="F215" t="n">
-        <v>7920</v>
+        <v>26555</v>
       </c>
       <c r="G215" t="n">
-        <v>1.22</v>
+        <v>-231.19</v>
       </c>
       <c r="H215" t="n">
         <v>182.49</v>
       </c>
       <c r="I215" t="n">
-        <v>183.69</v>
+        <v>226.81</v>
       </c>
       <c r="J215" t="b">
         <v>0</v>
       </c>
       <c r="K215" t="n">
-        <v>8999816.310000001</v>
+        <v>8999773.189999999</v>
       </c>
       <c r="L215" t="n">
         <v>75</v>
@@ -9585,22 +9585,22 @@
         <v>43</v>
       </c>
       <c r="C2" t="n">
-        <v>-249.29</v>
+        <v>-208.55</v>
       </c>
       <c r="D2" t="n">
-        <v>638.45</v>
+        <v>202.33</v>
       </c>
       <c r="E2" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="F2" t="n">
-        <v>23.3</v>
+        <v>11.6</v>
       </c>
       <c r="G2" t="n">
-        <v>-338.45</v>
+        <v>97.67</v>
       </c>
       <c r="H2" t="n">
-        <v>66.90000000000001</v>
+        <v>44</v>
       </c>
     </row>
     <row r="3">
@@ -9611,22 +9611,22 @@
         <v>43</v>
       </c>
       <c r="C3" t="n">
-        <v>-187.94</v>
+        <v>-222.65</v>
       </c>
       <c r="D3" t="n">
-        <v>727.84</v>
+        <v>202.89</v>
       </c>
       <c r="E3" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="F3" t="n">
-        <v>27.9</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="G3" t="n">
-        <v>-327.84</v>
+        <v>197.11</v>
       </c>
       <c r="H3" t="n">
-        <v>65.5</v>
+        <v>52.6</v>
       </c>
     </row>
     <row r="4">
@@ -9637,22 +9637,22 @@
         <v>43</v>
       </c>
       <c r="C4" t="n">
-        <v>-218.78</v>
+        <v>-213.77</v>
       </c>
       <c r="D4" t="n">
-        <v>732.77</v>
+        <v>163.58</v>
       </c>
       <c r="E4" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="F4" t="n">
-        <v>27.9</v>
+        <v>2.3</v>
       </c>
       <c r="G4" t="n">
-        <v>-232.77</v>
+        <v>336.42</v>
       </c>
       <c r="H4" t="n">
-        <v>67</v>
+        <v>56.1</v>
       </c>
     </row>
     <row r="5">
@@ -9663,22 +9663,22 @@
         <v>43</v>
       </c>
       <c r="C5" t="n">
-        <v>-161.24</v>
+        <v>-213.57</v>
       </c>
       <c r="D5" t="n">
-        <v>770.09</v>
+        <v>222.16</v>
       </c>
       <c r="E5" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="F5" t="n">
-        <v>23.3</v>
+        <v>4.7</v>
       </c>
       <c r="G5" t="n">
-        <v>229.91</v>
+        <v>777.84</v>
       </c>
       <c r="H5" t="n">
-        <v>65.5</v>
+        <v>54.3</v>
       </c>
     </row>
     <row r="6">
@@ -9689,10 +9689,10 @@
         <v>43</v>
       </c>
       <c r="C6" t="n">
-        <v>-237.64</v>
+        <v>-185.93</v>
       </c>
       <c r="D6" t="n">
-        <v>478.59</v>
+        <v>264.67</v>
       </c>
       <c r="E6" t="n">
         <v>0</v>
@@ -9701,10 +9701,10 @@
         <v>0</v>
       </c>
       <c r="G6" t="n">
-        <v>8999521.41</v>
+        <v>8999735.33</v>
       </c>
       <c r="H6" t="n">
-        <v>64</v>
+        <v>50.9</v>
       </c>
     </row>
   </sheetData>
